--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -23,6 +23,7 @@
     <sheet name="INDIAVIX_HIST" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="BFLAFL_HIST" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="RENUKA_HIST" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SOUTHBANK_HIST" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,12 +455,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prev Price</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Today Price</t>
+          <t>Yesterday</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -479,12 +480,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Prev Vol</t>
+          <t>Today Vol</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Today Vol</t>
+          <t>Yesterday Vol</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -519,12 +520,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>From High %</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>52W Low</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>From High %</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -536,121 +537,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BFL Asset Finance</t>
+          <t>Dynamic Cables</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BFLAFL.BO</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>7</v>
+          <t>DYCL.NS</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="G3" t="n">
-        <v>11.35</v>
+        <v>414.9</v>
       </c>
       <c r="H3" t="n">
-        <v>760</v>
+        <v>571380</v>
       </c>
       <c r="I3" t="n">
-        <v>1160</v>
+        <v>680337</v>
       </c>
       <c r="J3" t="n">
         <v>0.24</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="N3" t="n">
-        <v>7.06</v>
+        <v>61.9</v>
       </c>
       <c r="O3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5.29</v>
+        <v>479.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>-57.13</v>
-      </c>
-      <c r="R3" t="n">
-        <v>26.09</v>
+        <v>240.57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dynamic Cables</t>
+          <t>South Indian Bank</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DYCL.NS</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>406</v>
+          <t>SOUTHBANK.NS</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>402.4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.77</v>
+        <v>47.9</v>
       </c>
       <c r="H4" t="n">
-        <v>1441686</v>
+        <v>7738124</v>
       </c>
       <c r="I4" t="n">
-        <v>1153622</v>
+        <v>15756388</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-1.36</v>
+        <v>0.35</v>
       </c>
       <c r="L4" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>336.48</v>
-      </c>
-      <c r="N4" t="n">
-        <v>348.87</v>
+        <v>59.3</v>
       </c>
       <c r="O4" t="n">
-        <v>479.33</v>
-      </c>
-      <c r="P4" t="n">
-        <v>240.57</v>
+        <v>48.49</v>
       </c>
       <c r="Q4" t="n">
-        <v>-16.05</v>
-      </c>
-      <c r="R4" t="n">
-        <v>67.27</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="5">
@@ -664,53 +611,26 @@
           <t>ITC.NS</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>281.3</v>
-      </c>
       <c r="D5" t="n">
-        <v>283.45</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-2.26</v>
+        <v>285.85</v>
       </c>
       <c r="H5" t="n">
-        <v>21143589</v>
+        <v>14843878</v>
       </c>
       <c r="I5" t="n">
-        <v>24954082</v>
+        <v>19312804</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-2.41</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="M5" t="n">
-        <v>324.42</v>
-      </c>
-      <c r="N5" t="n">
-        <v>286.9</v>
+        <v>53.6</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>275.55</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-29.49</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.87</v>
       </c>
     </row>
     <row r="6">
@@ -724,579 +644,460 @@
           <t>NATCOPHARM.NS</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>918.55</v>
-      </c>
       <c r="D6" t="n">
-        <v>921.45</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.96</v>
+        <v>927.1</v>
       </c>
       <c r="H6" t="n">
-        <v>281594</v>
+        <v>151767</v>
       </c>
       <c r="I6" t="n">
-        <v>211503</v>
+        <v>230818</v>
       </c>
       <c r="J6" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.01</v>
+        <v>0.28</v>
       </c>
       <c r="L6" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>937.88</v>
-      </c>
-      <c r="N6" t="n">
-        <v>964.89</v>
+        <v>44.1</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>790.1799999999999</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-23.59</v>
-      </c>
-      <c r="R6" t="n">
-        <v>16.61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Premier Energy</t>
+          <t>Ujjivan SFB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PREMIERENE.NS</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1024.7</v>
+          <t>UJJIVANSFB.NS</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>1019.3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-6.16</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-2.98</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>1035098</v>
+        <v>42462662</v>
       </c>
       <c r="I7" t="n">
-        <v>934272</v>
+        <v>49027357</v>
       </c>
       <c r="J7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.7</v>
+        <v>1.4</v>
       </c>
       <c r="L7" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>938.67</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1051.95</v>
+        <v>74.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1117.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>682.6</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="R7" t="n">
-        <v>49.33</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Renuka Sugar</t>
+          <t>Yatharth Hospital</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RENUKA.NS</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>21.68</v>
+          <t>YATHARTH.NS</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>22.23</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.76</v>
+        <v>843.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2358183</v>
+        <v>118261</v>
       </c>
       <c r="I8" t="n">
-        <v>3308107</v>
+        <v>234669</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.37</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="M8" t="n">
-        <v>25.64</v>
-      </c>
-      <c r="N8" t="n">
-        <v>22.77</v>
+        <v>51.3</v>
       </c>
       <c r="O8" t="n">
-        <v>32.53</v>
-      </c>
-      <c r="P8" t="n">
-        <v>21.49</v>
+        <v>865.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>-31.66</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.44</v>
+        <v>550.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ujjivan SFB</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>UJJIVANSFB.NS</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>68.78</v>
-      </c>
-      <c r="D9" t="n">
-        <v>70.72</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.97</v>
-      </c>
-      <c r="H9" t="n">
-        <v>150100120</v>
-      </c>
-      <c r="I9" t="n">
-        <v>68534652</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="L9" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M9" t="n">
-        <v>56.61</v>
-      </c>
-      <c r="N9" t="n">
-        <v>58.32</v>
-      </c>
-      <c r="O9" t="n">
-        <v>70.72</v>
-      </c>
-      <c r="P9" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>69.70999999999999</v>
+          <t>── Transferred Account ──</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vishwaraj Sugar</t>
+          <t>BFL Asset Finance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VISHWARAJ.NS</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>5.26</v>
+          <t>BFLAFL.BO</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-1.33</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-3.71</v>
+        <v>6.67</v>
       </c>
       <c r="H10" t="n">
-        <v>54660</v>
+        <v>5408</v>
       </c>
       <c r="I10" t="n">
-        <v>138587</v>
+        <v>724</v>
       </c>
       <c r="J10" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2</v>
+        <v>1.09</v>
       </c>
       <c r="L10" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5.51</v>
+        <v>48.4</v>
       </c>
       <c r="O10" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.18</v>
+        <v>15.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>-46.6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>24.16</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yatharth Hospital</t>
+          <t>Premier Energy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YATHARTH.NS</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>841.6</v>
+          <t>PREMIERENE.NS</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>838.8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.21</v>
+        <v>1039.9</v>
       </c>
       <c r="H11" t="n">
-        <v>194085</v>
+        <v>449205</v>
       </c>
       <c r="I11" t="n">
-        <v>148599</v>
+        <v>547770</v>
       </c>
       <c r="J11" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-1.3</v>
+        <v>0.35</v>
       </c>
       <c r="L11" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>745.74</v>
-      </c>
-      <c r="N11" t="n">
-        <v>834.58</v>
+        <v>45.7</v>
       </c>
       <c r="O11" t="n">
-        <v>865.55</v>
-      </c>
-      <c r="P11" t="n">
-        <v>550.8</v>
+        <v>1117.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.09</v>
-      </c>
-      <c r="R11" t="n">
-        <v>52.29</v>
+        <v>682.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Renuka Sugar</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RENUKA.NS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1865205</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2679724</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L12" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>21.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BENCHMARKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Prev Price</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Today Price</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Change %</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Weekly Ret %</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Monthly Ret %</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Z Score</t>
-        </is>
+          <t>Vishwaraj Sugar</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VISHWARAJ.NS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>98219</v>
+      </c>
+      <c r="I13" t="n">
+        <v>78228</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nifty 50</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>^NSEI</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>23869.6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>23767.45</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-2.33</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-2.02</v>
+          <t>BENCHMARKS</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bank Nifty</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>^NSEBANK</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>56592</v>
-      </c>
-      <c r="D16" t="n">
-        <v>56693.5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-1.47</v>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Yesterday</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Weekly Ret %</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Monthly Ret %</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Z Score</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brent Crude (USD)</t>
+          <t>Nifty 50</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BZ=F</t>
+          <t>^NSEI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>100.69</v>
+        <v>23995.95</v>
       </c>
       <c r="D17" t="n">
-        <v>96.78</v>
+        <v>23767.45</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.88</v>
+        <v>0.96</v>
       </c>
       <c r="F17" t="n">
-        <v>9.85</v>
+        <v>-1</v>
       </c>
       <c r="G17" t="n">
-        <v>31.24</v>
+        <v>-0.25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.21</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gold (USD)</t>
+          <t>Bank Nifty</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>^NSEBANK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4046.6</v>
+        <v>57087.2</v>
       </c>
       <c r="D18" t="n">
-        <v>4070.8</v>
+        <v>56693.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F18" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="H18" t="n">
         <v>1.45</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dow Jones</t>
+          <t>Brent Crude (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>^DJI</t>
+          <t>BZ=F</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>51711.65</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>51947.25</v>
+        <v>88.36</v>
       </c>
       <c r="E19" t="n">
-        <v>0.46</v>
+        <v>-5.21</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.38</v>
+        <v>-7.97</v>
       </c>
       <c r="G19" t="n">
-        <v>0.19</v>
+        <v>16.35</v>
       </c>
       <c r="H19" t="n">
-        <v>0.44</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Gold (USD)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GC=F</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4028.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4074.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Dow Jones</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>^DJI</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>52747.32</v>
+      </c>
+      <c r="D21" t="n">
+        <v>52210.08</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>India VIX</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>^INDIAVIX</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C22" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="D22" t="n">
         <v>13.48</v>
       </c>
-      <c r="D20" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="E20" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="F20" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4.78</v>
+      <c r="E22" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="H22" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,6 +1195,29 @@
       </c>
       <c r="G3" t="n">
         <v>-1.47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57087.2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>56693.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>
@@ -1407,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,6 +1315,52 @@
       </c>
       <c r="G3" t="n">
         <v>0.21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>88.36</v>
+      </c>
+      <c r="C4" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-3.14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83.76000000000001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>88.36</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-7.97</v>
+      </c>
+      <c r="F5" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -1504,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,6 +1458,52 @@
       </c>
       <c r="G3" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4074.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4067.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4028.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4074.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -1601,7 +1517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1685,6 +1601,52 @@
       </c>
       <c r="G3" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>52210.08</v>
+      </c>
+      <c r="C4" t="n">
+        <v>51947.25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B5" t="n">
+        <v>52747.32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>52210.08</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -1698,7 +1660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1776,6 +1738,29 @@
       </c>
       <c r="F3" t="n">
         <v>4.78</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="G4" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1789,7 +1774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1930,6 +1915,85 @@
       </c>
       <c r="Q2" t="n">
         <v>26.09</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B3" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="G3" t="n">
+        <v>724</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1160</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="N3" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-57.13</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>26.09</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5408</v>
+      </c>
+      <c r="H4" t="n">
+        <v>724</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K4" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5.29</v>
       </c>
     </row>
   </sheetData>
@@ -1943,6 +2007,239 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Prev Price</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Today Price</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Weekly Ret %</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Monthly Ret %</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Prev Vol</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Today Vol</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>RelVol</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Z Score</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>200 DMA</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>50 DMA</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>52W High</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>52W Low</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>From High %</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>From Low %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B2" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2358183</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3308107</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="K2" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="M2" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O2" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-31.66</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B3" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="C3" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2679724</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3308107</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K3" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="M3" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-32.8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C4" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1865205</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2679724</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="P4" t="n">
+        <v>21.49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1954,12 +2251,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Prev Price</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Today Price</t>
+          <t>Yesterday</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1979,12 +2276,12 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Prev Vol</t>
+          <t>Today Vol</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Today Vol</t>
+          <t>Yesterday Vol</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -2019,12 +2316,12 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>From High %</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>52W Low</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>From High %</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -2035,55 +2332,28 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B2" t="n">
-        <v>21.68</v>
+        <v>46231</v>
       </c>
       <c r="C2" t="n">
-        <v>22.23</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-0.76</v>
+        <v>47.9</v>
       </c>
       <c r="G2" t="n">
-        <v>2358183</v>
+        <v>7738124</v>
       </c>
       <c r="H2" t="n">
-        <v>3308107</v>
+        <v>15756388</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-0.37</v>
+        <v>0.35</v>
       </c>
       <c r="K2" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>25.64</v>
-      </c>
-      <c r="M2" t="n">
-        <v>22.77</v>
+        <v>59.3</v>
       </c>
       <c r="N2" t="n">
-        <v>32.53</v>
-      </c>
-      <c r="O2" t="n">
-        <v>21.49</v>
+        <v>48.49</v>
       </c>
       <c r="P2" t="n">
-        <v>-31.66</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.44</v>
+        <v>28.46</v>
       </c>
     </row>
   </sheetData>
@@ -2097,7 +2367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2291,6 +2561,85 @@
       </c>
       <c r="Q3" t="n">
         <v>67.27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>414.9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>402.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="G4" t="n">
+        <v>680337</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1153622</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>336.55</v>
+      </c>
+      <c r="M4" t="n">
+        <v>351.44</v>
+      </c>
+      <c r="N4" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-13.44</v>
+      </c>
+      <c r="P4" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>72.47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C5" t="n">
+        <v>414.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>571380</v>
+      </c>
+      <c r="H5" t="n">
+        <v>680337</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K5" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="P5" t="n">
+        <v>240.57</v>
       </c>
     </row>
   </sheetData>
@@ -2304,7 +2653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2498,6 +2847,85 @@
       </c>
       <c r="Q3" t="n">
         <v>2.87</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>285.85</v>
+      </c>
+      <c r="C4" t="n">
+        <v>283.45</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19312804</v>
+      </c>
+      <c r="H4" t="n">
+        <v>24954082</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="K4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>323.94</v>
+      </c>
+      <c r="M4" t="n">
+        <v>286.57</v>
+      </c>
+      <c r="N4" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-28.89</v>
+      </c>
+      <c r="P4" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C5" t="n">
+        <v>285.85</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14843878</v>
+      </c>
+      <c r="H5" t="n">
+        <v>19312804</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="P5" t="n">
+        <v>275.55</v>
       </c>
     </row>
   </sheetData>
@@ -2511,7 +2939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2705,6 +3133,85 @@
       </c>
       <c r="Q3" t="n">
         <v>16.61</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>927.1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>921.45</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="G4" t="n">
+        <v>230818</v>
+      </c>
+      <c r="H4" t="n">
+        <v>211503</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K4" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>938.47</v>
+      </c>
+      <c r="M4" t="n">
+        <v>960.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-23.13</v>
+      </c>
+      <c r="P4" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>17.33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C5" t="n">
+        <v>927.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>151767</v>
+      </c>
+      <c r="H5" t="n">
+        <v>230818</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K5" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1206</v>
+      </c>
+      <c r="P5" t="n">
+        <v>790.1799999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2718,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2912,6 +3419,85 @@
       </c>
       <c r="Q3" t="n">
         <v>49.33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1039.9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1019.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="G4" t="n">
+        <v>547770</v>
+      </c>
+      <c r="H4" t="n">
+        <v>934272</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="K4" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>938.78</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1053.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-6.92</v>
+      </c>
+      <c r="P4" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>52.34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1039.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>449205</v>
+      </c>
+      <c r="H5" t="n">
+        <v>547770</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K5" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>682.6</v>
       </c>
     </row>
   </sheetData>
@@ -2925,7 +3511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3119,6 +3705,85 @@
       </c>
       <c r="Q3" t="n">
         <v>69.70999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="C4" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="F4" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="G4" t="n">
+        <v>49027357</v>
+      </c>
+      <c r="H4" t="n">
+        <v>68534652</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K4" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="M4" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="N4" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>71.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C5" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>42462662</v>
+      </c>
+      <c r="H5" t="n">
+        <v>49027357</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="P5" t="n">
+        <v>41.67</v>
       </c>
     </row>
   </sheetData>
@@ -3132,7 +3797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3326,6 +3991,85 @@
       </c>
       <c r="Q3" t="n">
         <v>24.16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>78228</v>
+      </c>
+      <c r="H4" t="n">
+        <v>138587</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-45.99</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="G5" t="n">
+        <v>98219</v>
+      </c>
+      <c r="H5" t="n">
+        <v>78228</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.18</v>
       </c>
     </row>
   </sheetData>
@@ -3339,7 +4083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,6 +4277,85 @@
       </c>
       <c r="Q3" t="n">
         <v>52.29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>843.9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>838.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G4" t="n">
+        <v>234669</v>
+      </c>
+      <c r="H4" t="n">
+        <v>148599</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>746.16</v>
+      </c>
+      <c r="M4" t="n">
+        <v>835.28</v>
+      </c>
+      <c r="N4" t="n">
+        <v>865.55</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>53.21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C5" t="n">
+        <v>843.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>118261</v>
+      </c>
+      <c r="H5" t="n">
+        <v>234669</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K5" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>865.55</v>
+      </c>
+      <c r="P5" t="n">
+        <v>550.8</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +4369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3632,6 +4455,29 @@
         <v>-2.02</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>23995.95</v>
+      </c>
+      <c r="C4" t="n">
+        <v>23767.45</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -545,27 +545,54 @@
           <t>DYCL.NS</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>393.9</v>
+      </c>
       <c r="D3" t="n">
-        <v>414.9</v>
+        <v>394.65</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.26</v>
       </c>
       <c r="H3" t="n">
+        <v>306700</v>
+      </c>
+      <c r="I3" t="n">
         <v>571380</v>
       </c>
-      <c r="I3" t="n">
-        <v>680337</v>
-      </c>
       <c r="J3" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.6</v>
       </c>
       <c r="L3" t="n">
-        <v>61.9</v>
+        <v>53.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>336.49</v>
+      </c>
+      <c r="N3" t="n">
+        <v>355.36</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
+      <c r="P3" t="n">
+        <v>-17.82</v>
+      </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
+      <c r="R3" t="n">
+        <v>63.74</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -578,27 +605,54 @@
           <t>SOUTHBANK.NS</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>46.49</v>
+      </c>
       <c r="D4" t="n">
-        <v>47.9</v>
+        <v>47.13</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.88</v>
       </c>
       <c r="H4" t="n">
+        <v>9015018</v>
+      </c>
+      <c r="I4" t="n">
         <v>7738124</v>
       </c>
-      <c r="I4" t="n">
-        <v>15756388</v>
-      </c>
       <c r="J4" t="n">
-        <v>0.35</v>
+        <v>0.41</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.29</v>
       </c>
       <c r="L4" t="n">
-        <v>59.3</v>
+        <v>52.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="N4" t="n">
+        <v>45.17</v>
       </c>
       <c r="O4" t="n">
         <v>48.49</v>
       </c>
+      <c r="P4" t="n">
+        <v>-4.12</v>
+      </c>
       <c r="Q4" t="n">
         <v>28.46</v>
       </c>
+      <c r="R4" t="n">
+        <v>63.35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -611,27 +665,54 @@
           <t>ITC.NS</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>286.25</v>
+      </c>
       <c r="D5" t="n">
-        <v>285.85</v>
+        <v>284.65</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.24</v>
       </c>
       <c r="H5" t="n">
+        <v>19029524</v>
+      </c>
+      <c r="I5" t="n">
         <v>14843878</v>
       </c>
-      <c r="I5" t="n">
-        <v>19312804</v>
-      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>1.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.73</v>
       </c>
       <c r="L5" t="n">
-        <v>53.6</v>
+        <v>54.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>322.98</v>
+      </c>
+      <c r="N5" t="n">
+        <v>285.96</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
+      <c r="P5" t="n">
+        <v>-28.79</v>
+      </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
+      <c r="R5" t="n">
+        <v>3.88</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -644,27 +725,54 @@
           <t>NATCOPHARM.NS</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>935.95</v>
+      </c>
       <c r="D6" t="n">
-        <v>927.1</v>
+        <v>925.05</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
+        <v>171936</v>
+      </c>
+      <c r="I6" t="n">
         <v>151767</v>
       </c>
-      <c r="I6" t="n">
-        <v>230818</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.98</v>
       </c>
       <c r="L6" t="n">
-        <v>44.1</v>
+        <v>47.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>939.6900000000001</v>
+      </c>
+      <c r="N6" t="n">
+        <v>951.59</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
+      <c r="P6" t="n">
+        <v>-22.39</v>
+      </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
+      <c r="R6" t="n">
+        <v>18.45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -677,27 +785,54 @@
           <t>UJJIVANSFB.NS</t>
         </is>
       </c>
+      <c r="C7" t="n">
+        <v>70.37</v>
+      </c>
       <c r="D7" t="n">
-        <v>71.56999999999999</v>
+        <v>70.12</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19.17</v>
       </c>
       <c r="H7" t="n">
+        <v>12336539</v>
+      </c>
+      <c r="I7" t="n">
         <v>42462662</v>
       </c>
-      <c r="I7" t="n">
-        <v>49027357</v>
-      </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.47</v>
       </c>
       <c r="L7" t="n">
-        <v>74.8</v>
+        <v>69.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="N7" t="n">
+        <v>59.32</v>
       </c>
       <c r="O7" t="n">
         <v>71.56999999999999</v>
       </c>
+      <c r="P7" t="n">
+        <v>-1.68</v>
+      </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
+      <c r="R7" t="n">
+        <v>68.87</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -710,27 +845,54 @@
           <t>YATHARTH.NS</t>
         </is>
       </c>
+      <c r="C8" t="n">
+        <v>832.9</v>
+      </c>
       <c r="D8" t="n">
-        <v>843.9</v>
+        <v>833.95</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-2.99</v>
       </c>
       <c r="H8" t="n">
+        <v>105535</v>
+      </c>
+      <c r="I8" t="n">
         <v>118261</v>
       </c>
-      <c r="I8" t="n">
-        <v>234669</v>
-      </c>
       <c r="J8" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.9</v>
       </c>
       <c r="L8" t="n">
-        <v>51.3</v>
+        <v>47.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>746.21</v>
+      </c>
+      <c r="N8" t="n">
+        <v>835.03</v>
       </c>
       <c r="O8" t="n">
         <v>865.55</v>
       </c>
+      <c r="P8" t="n">
+        <v>-3.77</v>
+      </c>
       <c r="Q8" t="n">
         <v>550.8</v>
       </c>
+      <c r="R8" t="n">
+        <v>51.22</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -750,27 +912,54 @@
           <t>BFLAFL.BO</t>
         </is>
       </c>
+      <c r="C10" t="n">
+        <v>6.16</v>
+      </c>
       <c r="D10" t="n">
-        <v>6.67</v>
+        <v>6.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-10.85</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.32</v>
       </c>
       <c r="H10" t="n">
+        <v>4186</v>
+      </c>
+      <c r="I10" t="n">
         <v>5408</v>
       </c>
-      <c r="I10" t="n">
-        <v>724</v>
-      </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>0.84</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>48.4</v>
+        <v>40.9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6.88</v>
       </c>
       <c r="O10" t="n">
         <v>15.56</v>
       </c>
+      <c r="P10" t="n">
+        <v>-60.41</v>
+      </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
+      <c r="R10" t="n">
+        <v>16.45</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -783,27 +972,54 @@
           <t>PREMIERENE.NS</t>
         </is>
       </c>
+      <c r="C11" t="n">
+        <v>1036.2</v>
+      </c>
       <c r="D11" t="n">
-        <v>1039.9</v>
+        <v>1016.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.41</v>
       </c>
       <c r="H11" t="n">
+        <v>639973</v>
+      </c>
+      <c r="I11" t="n">
         <v>449205</v>
       </c>
-      <c r="I11" t="n">
-        <v>547770</v>
-      </c>
       <c r="J11" t="n">
-        <v>0.35</v>
+        <v>0.52</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.99</v>
       </c>
       <c r="L11" t="n">
-        <v>45.7</v>
+        <v>46</v>
+      </c>
+      <c r="M11" t="n">
+        <v>938.8099999999999</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1054.57</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
+      <c r="P11" t="n">
+        <v>-7.25</v>
+      </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
+      <c r="R11" t="n">
+        <v>51.8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -816,27 +1032,54 @@
           <t>RENUKA.NS</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v>21.81</v>
+      </c>
       <c r="D12" t="n">
-        <v>21.86</v>
+        <v>21.64</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.45</v>
       </c>
       <c r="H12" t="n">
+        <v>2016133</v>
+      </c>
+      <c r="I12" t="n">
         <v>1865205</v>
       </c>
-      <c r="I12" t="n">
-        <v>2679724</v>
-      </c>
       <c r="J12" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.38</v>
       </c>
       <c r="L12" t="n">
-        <v>40.5</v>
+        <v>41</v>
+      </c>
+      <c r="M12" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="N12" t="n">
+        <v>22.65</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
+      <c r="P12" t="n">
+        <v>-32.95</v>
+      </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
+      <c r="R12" t="n">
+        <v>1.49</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -849,27 +1092,54 @@
           <t>VISHWARAJ.NS</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>5.26</v>
+      </c>
       <c r="D13" t="n">
-        <v>5.25</v>
+        <v>5.21</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-3.84</v>
       </c>
       <c r="H13" t="n">
+        <v>100866</v>
+      </c>
+      <c r="I13" t="n">
         <v>98219</v>
       </c>
-      <c r="I13" t="n">
-        <v>78228</v>
-      </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>40.2</v>
+        <v>42.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.51</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
+      <c r="P13" t="n">
+        <v>-45.88</v>
+      </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
+      <c r="R13" t="n">
+        <v>25.84</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -932,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23995.95</v>
+        <v>24250.2</v>
       </c>
       <c r="D17" t="n">
-        <v>23767.45</v>
+        <v>23985.35</v>
       </c>
       <c r="E17" t="n">
-        <v>0.96</v>
+        <v>1.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-1</v>
+        <v>1.06</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.25</v>
+        <v>1.61</v>
       </c>
       <c r="H17" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="18">
@@ -962,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57087.2</v>
+        <v>57205.9</v>
       </c>
       <c r="D18" t="n">
-        <v>56693.5</v>
+        <v>56755.6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.48</v>
+        <v>0.14</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.87</v>
+        <v>-0.59</v>
       </c>
       <c r="H18" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="19">
@@ -992,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>83.76000000000001</v>
+        <v>90.27</v>
       </c>
       <c r="D19" t="n">
-        <v>88.36</v>
+        <v>84.09</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.21</v>
+        <v>7.35</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.97</v>
+        <v>-4.04</v>
       </c>
       <c r="G19" t="n">
-        <v>16.35</v>
+        <v>23.4</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.34</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="20">
@@ -1022,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4028.8</v>
+        <v>4069.1</v>
       </c>
       <c r="D20" t="n">
-        <v>4074.5</v>
+        <v>4036.3</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.12</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.04</v>
+        <v>-1.88</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.22</v>
+        <v>1.16</v>
       </c>
       <c r="H20" t="n">
-        <v>0.39</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="21">
@@ -1052,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>51818.64</v>
+      </c>
+      <c r="D21" t="n">
         <v>52747.32</v>
       </c>
-      <c r="D21" t="n">
-        <v>52210.08</v>
-      </c>
       <c r="E21" t="n">
-        <v>1.03</v>
+        <v>-1.76</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>-0.77</v>
       </c>
       <c r="G21" t="n">
-        <v>1.68</v>
+        <v>-0.7</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="22">
@@ -1082,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12.66</v>
+        <v>12.01</v>
       </c>
       <c r="D22" t="n">
-        <v>13.48</v>
+        <v>12.56</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.08</v>
+        <v>-4.38</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.73</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.45</v>
+        <v>-11.69</v>
       </c>
       <c r="H22" t="n">
         <v/>
@@ -1111,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,6 +1488,52 @@
       </c>
       <c r="G4" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56755.6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>57087.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57205.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>56755.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>
@@ -1231,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1361,6 +1677,29 @@
       </c>
       <c r="G5" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90.27</v>
+      </c>
+      <c r="C6" t="n">
+        <v>84.09</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -1374,7 +1713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,6 +1843,29 @@
       </c>
       <c r="G5" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4069.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4036.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -1517,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1647,6 +2009,29 @@
       </c>
       <c r="G5" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>51818.64</v>
+      </c>
+      <c r="C6" t="n">
+        <v>52747.32</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>
@@ -1660,7 +2045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1759,7 +2144,47 @@
       <c r="F4" t="n">
         <v>-5.45</v>
       </c>
-      <c r="G4" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B5" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-7.71</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-11.69</v>
+      </c>
+      <c r="G6" t="n">
         <v/>
       </c>
     </row>
@@ -1774,7 +2199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1994,6 +2419,59 @@
       </c>
       <c r="P4" t="n">
         <v>5.29</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-10.85</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4186</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5408</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="N5" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-60.41</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16.45</v>
       </c>
     </row>
   </sheetData>
@@ -2007,7 +2485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2227,6 +2705,59 @@
       </c>
       <c r="P4" t="n">
         <v>21.49</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B5" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2016133</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1865205</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K5" t="n">
+        <v>41</v>
+      </c>
+      <c r="L5" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="N5" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-32.95</v>
+      </c>
+      <c r="P5" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>
@@ -2240,7 +2771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,6 +2885,59 @@
       </c>
       <c r="P2" t="n">
         <v>28.46</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B3" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="C3" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9015018</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7738124</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K3" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="M3" t="n">
+        <v>45.17</v>
+      </c>
+      <c r="N3" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="P3" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>63.35</v>
       </c>
     </row>
   </sheetData>
@@ -2367,7 +2951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2640,6 +3224,59 @@
       </c>
       <c r="P5" t="n">
         <v>240.57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>393.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>394.65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>306700</v>
+      </c>
+      <c r="H6" t="n">
+        <v>571380</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>336.49</v>
+      </c>
+      <c r="M6" t="n">
+        <v>355.36</v>
+      </c>
+      <c r="N6" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-17.82</v>
+      </c>
+      <c r="P6" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>63.74</v>
       </c>
     </row>
   </sheetData>
@@ -2653,7 +3290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2926,6 +3563,59 @@
       </c>
       <c r="P5" t="n">
         <v>275.55</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="C6" t="n">
+        <v>284.65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19029524</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14843878</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K6" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>322.98</v>
+      </c>
+      <c r="M6" t="n">
+        <v>285.96</v>
+      </c>
+      <c r="N6" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-28.79</v>
+      </c>
+      <c r="P6" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.88</v>
       </c>
     </row>
   </sheetData>
@@ -2939,7 +3629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3212,6 +3902,59 @@
       </c>
       <c r="P5" t="n">
         <v>790.1799999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>935.95</v>
+      </c>
+      <c r="C6" t="n">
+        <v>925.05</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>171936</v>
+      </c>
+      <c r="H6" t="n">
+        <v>151767</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K6" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>939.6900000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>951.59</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-22.39</v>
+      </c>
+      <c r="P6" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>18.45</v>
       </c>
     </row>
   </sheetData>
@@ -3225,7 +3968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3498,6 +4241,59 @@
       </c>
       <c r="P5" t="n">
         <v>682.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1036.2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1016.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="G6" t="n">
+        <v>639973</v>
+      </c>
+      <c r="H6" t="n">
+        <v>449205</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K6" t="n">
+        <v>46</v>
+      </c>
+      <c r="L6" t="n">
+        <v>938.8099999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1054.57</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>51.8</v>
       </c>
     </row>
   </sheetData>
@@ -3511,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3784,6 +4580,59 @@
       </c>
       <c r="P5" t="n">
         <v>41.67</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>70.37</v>
+      </c>
+      <c r="C6" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12336539</v>
+      </c>
+      <c r="H6" t="n">
+        <v>42462662</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K6" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="M6" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="N6" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="P6" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>68.87</v>
       </c>
     </row>
   </sheetData>
@@ -3797,7 +4646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4070,6 +4919,59 @@
       </c>
       <c r="P5" t="n">
         <v>4.18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-3.84</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100866</v>
+      </c>
+      <c r="H6" t="n">
+        <v>98219</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-45.88</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25.84</v>
       </c>
     </row>
   </sheetData>
@@ -4083,7 +4985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4356,6 +5258,59 @@
       </c>
       <c r="P5" t="n">
         <v>550.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>832.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>833.95</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="G6" t="n">
+        <v>105535</v>
+      </c>
+      <c r="H6" t="n">
+        <v>118261</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>746.21</v>
+      </c>
+      <c r="M6" t="n">
+        <v>835.03</v>
+      </c>
+      <c r="N6" t="n">
+        <v>865.55</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="P6" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>51.22</v>
       </c>
     </row>
   </sheetData>
@@ -4369,7 +5324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4478,6 +5433,52 @@
         <v>1.48</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B5" t="n">
+        <v>23985.35</v>
+      </c>
+      <c r="C5" t="n">
+        <v>23995.95</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>24250.2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23985.35</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>384.65</v>
+      </c>
+      <c r="D3" t="n">
         <v>393.9</v>
       </c>
-      <c r="D3" t="n">
-        <v>394.65</v>
-      </c>
       <c r="E3" t="n">
-        <v>-0.19</v>
+        <v>-2.35</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.27</v>
+        <v>-5.26</v>
       </c>
       <c r="G3" t="n">
-        <v>7.26</v>
+        <v>5.62</v>
       </c>
       <c r="H3" t="n">
-        <v>306700</v>
+        <v>243220</v>
       </c>
       <c r="I3" t="n">
-        <v>571380</v>
+        <v>306914</v>
       </c>
       <c r="J3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6</v>
+        <v>-0.64</v>
       </c>
       <c r="L3" t="n">
-        <v>53.8</v>
+        <v>50.4</v>
       </c>
       <c r="M3" t="n">
-        <v>336.49</v>
+        <v>336.43</v>
       </c>
       <c r="N3" t="n">
-        <v>355.36</v>
+        <v>356.98</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-17.82</v>
+        <v>-19.75</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>63.74</v>
+        <v>59.89</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="D4" t="n">
         <v>46.49</v>
       </c>
-      <c r="D4" t="n">
-        <v>47.13</v>
-      </c>
       <c r="E4" t="n">
-        <v>-1.36</v>
+        <v>0.86</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.15</v>
+        <v>-1.28</v>
       </c>
       <c r="G4" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>9015018</v>
+        <v>5183113</v>
       </c>
       <c r="I4" t="n">
-        <v>7738124</v>
+        <v>9021635</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="K4" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="L4" t="n">
-        <v>52.1</v>
+        <v>53.9</v>
       </c>
       <c r="M4" t="n">
-        <v>40.72</v>
+        <v>40.78</v>
       </c>
       <c r="N4" t="n">
-        <v>45.17</v>
+        <v>45.28</v>
       </c>
       <c r="O4" t="n">
         <v>48.49</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.12</v>
+        <v>-3.3</v>
       </c>
       <c r="Q4" t="n">
         <v>28.46</v>
       </c>
       <c r="R4" t="n">
-        <v>63.35</v>
+        <v>64.76000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>285.05</v>
+      </c>
+      <c r="D5" t="n">
         <v>286.25</v>
       </c>
-      <c r="D5" t="n">
-        <v>284.65</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.42</v>
       </c>
       <c r="F5" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.24</v>
+        <v>-1.81</v>
       </c>
       <c r="H5" t="n">
-        <v>19029524</v>
+        <v>18282297</v>
       </c>
       <c r="I5" t="n">
-        <v>14843878</v>
+        <v>19030590</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="L5" t="n">
-        <v>54.1</v>
+        <v>51.5</v>
       </c>
       <c r="M5" t="n">
-        <v>322.98</v>
+        <v>322.49</v>
       </c>
       <c r="N5" t="n">
-        <v>285.96</v>
+        <v>285.67</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-28.79</v>
+        <v>-29.09</v>
       </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
       <c r="R5" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>929.85</v>
+      </c>
+      <c r="D6" t="n">
         <v>935.95</v>
       </c>
-      <c r="D6" t="n">
-        <v>925.05</v>
-      </c>
       <c r="E6" t="n">
-        <v>1.18</v>
+        <v>-0.65</v>
       </c>
       <c r="F6" t="n">
-        <v>0.18</v>
+        <v>1.23</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="H6" t="n">
-        <v>171936</v>
+        <v>236540</v>
       </c>
       <c r="I6" t="n">
-        <v>151767</v>
+        <v>171943</v>
       </c>
       <c r="J6" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="K6" t="n">
-        <v>0.98</v>
+        <v>-1.62</v>
       </c>
       <c r="L6" t="n">
-        <v>47.3</v>
+        <v>45.5</v>
       </c>
       <c r="M6" t="n">
-        <v>939.6900000000001</v>
+        <v>940.13</v>
       </c>
       <c r="N6" t="n">
-        <v>951.59</v>
+        <v>946.71</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-22.39</v>
+        <v>-22.9</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>18.45</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="D7" t="n">
         <v>70.37</v>
       </c>
-      <c r="D7" t="n">
-        <v>70.12</v>
-      </c>
       <c r="E7" t="n">
-        <v>0.36</v>
+        <v>-0.06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.18</v>
+        <v>2.25</v>
       </c>
       <c r="G7" t="n">
-        <v>19.17</v>
+        <v>14.71</v>
       </c>
       <c r="H7" t="n">
-        <v>12336539</v>
+        <v>11152583</v>
       </c>
       <c r="I7" t="n">
-        <v>42462662</v>
+        <v>12337108</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="K7" t="n">
-        <v>0.47</v>
+        <v>0.1</v>
       </c>
       <c r="L7" t="n">
-        <v>69.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>56.95</v>
+        <v>57.06</v>
       </c>
       <c r="N7" t="n">
-        <v>59.32</v>
+        <v>59.67</v>
       </c>
       <c r="O7" t="n">
         <v>71.56999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.68</v>
+        <v>-1.73</v>
       </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
       <c r="R7" t="n">
-        <v>68.87</v>
+        <v>68.78</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>826.05</v>
+      </c>
+      <c r="D8" t="n">
         <v>832.9</v>
       </c>
-      <c r="D8" t="n">
-        <v>833.95</v>
-      </c>
       <c r="E8" t="n">
-        <v>-0.13</v>
+        <v>-0.82</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.16</v>
+        <v>-1.85</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.99</v>
+        <v>-3.59</v>
       </c>
       <c r="H8" t="n">
+        <v>104795</v>
+      </c>
+      <c r="I8" t="n">
         <v>105535</v>
       </c>
-      <c r="I8" t="n">
-        <v>118261</v>
-      </c>
       <c r="J8" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9</v>
+        <v>-0.64</v>
       </c>
       <c r="L8" t="n">
-        <v>47.4</v>
+        <v>44.9</v>
       </c>
       <c r="M8" t="n">
-        <v>746.21</v>
+        <v>746.29</v>
       </c>
       <c r="N8" t="n">
-        <v>835.03</v>
+        <v>834.36</v>
       </c>
       <c r="O8" t="n">
         <v>865.55</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.77</v>
+        <v>-4.56</v>
       </c>
       <c r="Q8" t="n">
         <v>550.8</v>
       </c>
       <c r="R8" t="n">
-        <v>51.22</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="D10" t="n">
         <v>6.16</v>
       </c>
-      <c r="D10" t="n">
-        <v>6.4</v>
-      </c>
       <c r="E10" t="n">
-        <v>-3.75</v>
+        <v>0.32</v>
       </c>
       <c r="F10" t="n">
-        <v>-10.85</v>
+        <v>-11.71</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.32</v>
+        <v>1.81</v>
       </c>
       <c r="H10" t="n">
+        <v>13321</v>
+      </c>
+      <c r="I10" t="n">
         <v>4186</v>
       </c>
-      <c r="I10" t="n">
-        <v>5408</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.84</v>
+        <v>2.69</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="L10" t="n">
-        <v>40.9</v>
+        <v>41.3</v>
       </c>
       <c r="M10" t="n">
-        <v>9.470000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="N10" t="n">
-        <v>6.88</v>
+        <v>6.83</v>
       </c>
       <c r="O10" t="n">
         <v>15.56</v>
       </c>
       <c r="P10" t="n">
-        <v>-60.41</v>
+        <v>-60.28</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>16.45</v>
+        <v>16.82</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>982.7</v>
+      </c>
+      <c r="D11" t="n">
         <v>1036.2</v>
       </c>
-      <c r="D11" t="n">
-        <v>1016.9</v>
-      </c>
       <c r="E11" t="n">
-        <v>1.9</v>
+        <v>-5.16</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>-4.1</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.41</v>
+        <v>-6.55</v>
       </c>
       <c r="H11" t="n">
-        <v>639973</v>
+        <v>2265116</v>
       </c>
       <c r="I11" t="n">
-        <v>449205</v>
+        <v>640029</v>
       </c>
       <c r="J11" t="n">
-        <v>0.52</v>
+        <v>1.82</v>
       </c>
       <c r="K11" t="n">
-        <v>0.99</v>
+        <v>-2.48</v>
       </c>
       <c r="L11" t="n">
-        <v>46</v>
+        <v>36.1</v>
       </c>
       <c r="M11" t="n">
-        <v>938.8099999999999</v>
+        <v>938.61</v>
       </c>
       <c r="N11" t="n">
-        <v>1054.57</v>
+        <v>1053.92</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.25</v>
+        <v>-12.04</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>51.8</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="D12" t="n">
         <v>21.81</v>
       </c>
-      <c r="D12" t="n">
-        <v>21.64</v>
-      </c>
       <c r="E12" t="n">
-        <v>0.79</v>
+        <v>-0.78</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.95</v>
+        <v>-0.18</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.45</v>
+        <v>-5.91</v>
       </c>
       <c r="H12" t="n">
-        <v>2016133</v>
+        <v>1581211</v>
       </c>
       <c r="I12" t="n">
-        <v>1865205</v>
+        <v>2017639</v>
       </c>
       <c r="J12" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="K12" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>39.2</v>
       </c>
       <c r="M12" t="n">
-        <v>25.51</v>
+        <v>25.46</v>
       </c>
       <c r="N12" t="n">
-        <v>22.65</v>
+        <v>22.61</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-32.95</v>
+        <v>-33.48</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.26</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.21</v>
-      </c>
       <c r="E13" t="n">
-        <v>0.96</v>
+        <v>-1.52</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.19</v>
+        <v>-1.52</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.84</v>
+        <v>-3.72</v>
       </c>
       <c r="H13" t="n">
+        <v>121719</v>
+      </c>
+      <c r="I13" t="n">
         <v>100866</v>
       </c>
-      <c r="I13" t="n">
-        <v>98219</v>
-      </c>
       <c r="J13" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>42.2</v>
+        <v>37.9</v>
       </c>
       <c r="M13" t="n">
-        <v>6.19</v>
+        <v>6.17</v>
       </c>
       <c r="N13" t="n">
-        <v>5.51</v>
+        <v>5.5</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-45.88</v>
+        <v>-46.71</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>25.84</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24317.15</v>
+      </c>
+      <c r="D17" t="n">
         <v>24250.2</v>
       </c>
-      <c r="D17" t="n">
-        <v>23985.35</v>
-      </c>
       <c r="E17" t="n">
-        <v>1.1</v>
+        <v>0.28</v>
       </c>
       <c r="F17" t="n">
-        <v>1.06</v>
+        <v>1.87</v>
       </c>
       <c r="G17" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="H17" t="n">
-        <v>1.67</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57147.5</v>
+      </c>
+      <c r="D18" t="n">
         <v>57205.9</v>
       </c>
-      <c r="D18" t="n">
-        <v>56755.6</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.79</v>
+        <v>-0.1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.14</v>
+        <v>0.98</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.59</v>
+        <v>-1.53</v>
       </c>
       <c r="H18" t="n">
-        <v>1.22</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>90.27</v>
+        <v>89.7</v>
       </c>
       <c r="D19" t="n">
-        <v>84.09</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>7.35</v>
+        <v>-1.15</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.04</v>
+        <v>-10.91</v>
       </c>
       <c r="G19" t="n">
-        <v>23.4</v>
+        <v>23.01</v>
       </c>
       <c r="H19" t="n">
-        <v>0.83</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4069.1</v>
+        <v>4173.6</v>
       </c>
       <c r="D20" t="n">
-        <v>4036.3</v>
+        <v>4034.7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.44</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.88</v>
+        <v>3.14</v>
       </c>
       <c r="G20" t="n">
-        <v>1.16</v>
+        <v>3.75</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.65</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>51818.64</v>
+        <v>52006.44</v>
       </c>
       <c r="D21" t="n">
-        <v>52747.32</v>
+        <v>51594.14</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.76</v>
+        <v>0.8</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.77</v>
+        <v>0.57</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.37</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="D22" t="n">
         <v>12.01</v>
       </c>
-      <c r="D22" t="n">
-        <v>12.56</v>
-      </c>
       <c r="E22" t="n">
-        <v>-4.38</v>
+        <v>1.17</v>
       </c>
       <c r="F22" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-11.69</v>
+        <v>-8.23</v>
       </c>
       <c r="H22" t="n">
         <v/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1534,6 +1534,29 @@
       </c>
       <c r="G6" t="n">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57147.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>57205.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1547,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1700,6 +1723,29 @@
       </c>
       <c r="G6" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>90.73999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-10.91</v>
+      </c>
+      <c r="F7" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.23</v>
       </c>
     </row>
   </sheetData>
@@ -1713,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1866,6 +1912,29 @@
       </c>
       <c r="G6" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4173.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4034.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.87</v>
       </c>
     </row>
   </sheetData>
@@ -1879,7 +1948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2032,6 +2101,29 @@
       </c>
       <c r="G6" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>52006.44</v>
+      </c>
+      <c r="C7" t="n">
+        <v>51594.14</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.64</v>
       </c>
     </row>
   </sheetData>
@@ -2045,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2184,7 +2276,27 @@
       <c r="F6" t="n">
         <v>-11.69</v>
       </c>
-      <c r="G6" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-8.23</v>
+      </c>
+      <c r="G7" t="n">
         <v/>
       </c>
     </row>
@@ -2199,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2472,6 +2584,59 @@
       </c>
       <c r="Q5" t="n">
         <v>16.45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-11.71</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13321</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4186</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="K6" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-60.28</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>16.82</v>
       </c>
     </row>
   </sheetData>
@@ -2485,7 +2650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2758,6 +2923,59 @@
       </c>
       <c r="Q5" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B6" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="C6" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1581211</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2017639</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K6" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="N6" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-33.48</v>
+      </c>
+      <c r="P6" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -2771,7 +2989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2938,6 +3156,59 @@
       </c>
       <c r="Q3" t="n">
         <v>63.35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B4" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="C4" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5183113</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9021635</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="M4" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="N4" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>64.76000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2951,7 +3222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3277,6 +3548,59 @@
       </c>
       <c r="Q6" t="n">
         <v>63.74</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>384.65</v>
+      </c>
+      <c r="C7" t="n">
+        <v>393.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="G7" t="n">
+        <v>243220</v>
+      </c>
+      <c r="H7" t="n">
+        <v>306914</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="K7" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>336.43</v>
+      </c>
+      <c r="M7" t="n">
+        <v>356.98</v>
+      </c>
+      <c r="N7" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-19.75</v>
+      </c>
+      <c r="P7" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>59.89</v>
       </c>
     </row>
   </sheetData>
@@ -3290,7 +3614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3616,6 +3940,59 @@
       </c>
       <c r="Q6" t="n">
         <v>3.88</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>285.05</v>
+      </c>
+      <c r="C7" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18282297</v>
+      </c>
+      <c r="H7" t="n">
+        <v>19030590</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K7" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>322.49</v>
+      </c>
+      <c r="M7" t="n">
+        <v>285.67</v>
+      </c>
+      <c r="N7" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-29.09</v>
+      </c>
+      <c r="P7" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.45</v>
       </c>
     </row>
   </sheetData>
@@ -3629,7 +4006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3955,6 +4332,59 @@
       </c>
       <c r="Q6" t="n">
         <v>18.45</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>929.85</v>
+      </c>
+      <c r="C7" t="n">
+        <v>935.95</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G7" t="n">
+        <v>236540</v>
+      </c>
+      <c r="H7" t="n">
+        <v>171943</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="K7" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>940.13</v>
+      </c>
+      <c r="M7" t="n">
+        <v>946.71</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-22.9</v>
+      </c>
+      <c r="P7" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>17.68</v>
       </c>
     </row>
   </sheetData>
@@ -3968,7 +4398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4294,6 +4724,59 @@
       </c>
       <c r="Q6" t="n">
         <v>51.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>982.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1036.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-6.55</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2265116</v>
+      </c>
+      <c r="H7" t="n">
+        <v>640029</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="K7" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>938.61</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1053.92</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-12.04</v>
+      </c>
+      <c r="P7" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>43.96</v>
       </c>
     </row>
   </sheetData>
@@ -4307,7 +4790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4633,6 +5116,59 @@
       </c>
       <c r="Q6" t="n">
         <v>68.87</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="C7" t="n">
+        <v>70.37</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11152583</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12337108</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="L7" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="M7" t="n">
+        <v>59.67</v>
+      </c>
+      <c r="N7" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="P7" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>68.78</v>
       </c>
     </row>
   </sheetData>
@@ -4646,7 +5182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4972,6 +5508,59 @@
       </c>
       <c r="Q6" t="n">
         <v>25.84</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-3.72</v>
+      </c>
+      <c r="G7" t="n">
+        <v>121719</v>
+      </c>
+      <c r="H7" t="n">
+        <v>100866</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-46.71</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23.92</v>
       </c>
     </row>
   </sheetData>
@@ -4985,7 +5574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5311,6 +5900,59 @@
       </c>
       <c r="Q6" t="n">
         <v>51.22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>826.05</v>
+      </c>
+      <c r="C7" t="n">
+        <v>832.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-3.59</v>
+      </c>
+      <c r="G7" t="n">
+        <v>104795</v>
+      </c>
+      <c r="H7" t="n">
+        <v>105535</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="K7" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>746.29</v>
+      </c>
+      <c r="M7" t="n">
+        <v>834.36</v>
+      </c>
+      <c r="N7" t="n">
+        <v>865.55</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="P7" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>49.97</v>
       </c>
     </row>
   </sheetData>
@@ -5324,7 +5966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5479,6 +6121,29 @@
         <v>1.67</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>24317.15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>24250.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>395.2</v>
+      </c>
+      <c r="D3" t="n">
         <v>384.65</v>
       </c>
-      <c r="D3" t="n">
-        <v>393.9</v>
-      </c>
       <c r="E3" t="n">
-        <v>-2.35</v>
+        <v>2.74</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.26</v>
+        <v>-1.79</v>
       </c>
       <c r="G3" t="n">
-        <v>5.62</v>
+        <v>8.51</v>
       </c>
       <c r="H3" t="n">
-        <v>243220</v>
+        <v>406765</v>
       </c>
       <c r="I3" t="n">
-        <v>306914</v>
+        <v>243245</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.64</v>
+        <v>-0.18</v>
       </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>53.9</v>
       </c>
       <c r="M3" t="n">
-        <v>336.43</v>
+        <v>336.45</v>
       </c>
       <c r="N3" t="n">
-        <v>356.98</v>
+        <v>358.89</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-19.75</v>
+        <v>-17.55</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>59.89</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D4" t="n">
         <v>46.89</v>
       </c>
-      <c r="D4" t="n">
-        <v>46.49</v>
-      </c>
       <c r="E4" t="n">
-        <v>0.86</v>
+        <v>-0.41</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.28</v>
+        <v>0.39</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="H4" t="n">
-        <v>5183113</v>
+        <v>7680830</v>
       </c>
       <c r="I4" t="n">
-        <v>9021635</v>
+        <v>5193772</v>
       </c>
       <c r="J4" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="L4" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="M4" t="n">
-        <v>40.78</v>
+        <v>40.85</v>
       </c>
       <c r="N4" t="n">
-        <v>45.28</v>
+        <v>45.4</v>
       </c>
       <c r="O4" t="n">
         <v>48.49</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.3</v>
+        <v>-3.69</v>
       </c>
       <c r="Q4" t="n">
         <v>28.46</v>
       </c>
       <c r="R4" t="n">
-        <v>64.76000000000001</v>
+        <v>64.09</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>281</v>
+      </c>
+      <c r="D5" t="n">
         <v>285.05</v>
       </c>
-      <c r="D5" t="n">
-        <v>286.25</v>
-      </c>
       <c r="E5" t="n">
-        <v>-0.42</v>
+        <v>-1.42</v>
       </c>
       <c r="F5" t="n">
-        <v>1.33</v>
+        <v>-0.86</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.81</v>
+        <v>-3.07</v>
       </c>
       <c r="H5" t="n">
-        <v>18282297</v>
+        <v>16821515</v>
       </c>
       <c r="I5" t="n">
-        <v>19030590</v>
+        <v>18283697</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.12</v>
+        <v>0.38</v>
       </c>
       <c r="L5" t="n">
-        <v>51.5</v>
+        <v>43.7</v>
       </c>
       <c r="M5" t="n">
-        <v>322.49</v>
+        <v>321.99</v>
       </c>
       <c r="N5" t="n">
-        <v>285.67</v>
+        <v>285.41</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-29.09</v>
+        <v>-30.1</v>
       </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
       <c r="R5" t="n">
-        <v>3.45</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>917</v>
+      </c>
+      <c r="D6" t="n">
         <v>929.85</v>
       </c>
-      <c r="D6" t="n">
-        <v>935.95</v>
-      </c>
       <c r="E6" t="n">
-        <v>-0.65</v>
+        <v>-1.38</v>
       </c>
       <c r="F6" t="n">
-        <v>1.23</v>
+        <v>-0.48</v>
       </c>
       <c r="G6" t="n">
-        <v>0.39</v>
+        <v>-1.87</v>
       </c>
       <c r="H6" t="n">
-        <v>236540</v>
+        <v>325800</v>
       </c>
       <c r="I6" t="n">
-        <v>171943</v>
+        <v>236650</v>
       </c>
       <c r="J6" t="n">
-        <v>0.47</v>
+        <v>0.66</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.62</v>
+        <v>1.18</v>
       </c>
       <c r="L6" t="n">
-        <v>45.5</v>
+        <v>41.7</v>
       </c>
       <c r="M6" t="n">
-        <v>940.13</v>
+        <v>940.53</v>
       </c>
       <c r="N6" t="n">
-        <v>946.71</v>
+        <v>941.65</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-22.9</v>
+        <v>-23.96</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>17.68</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="D7" t="n">
         <v>70.33</v>
       </c>
-      <c r="D7" t="n">
-        <v>70.37</v>
-      </c>
       <c r="E7" t="n">
-        <v>-0.06</v>
+        <v>2.02</v>
       </c>
       <c r="F7" t="n">
-        <v>2.25</v>
+        <v>1.46</v>
       </c>
       <c r="G7" t="n">
-        <v>14.71</v>
+        <v>16.86</v>
       </c>
       <c r="H7" t="n">
-        <v>11152583</v>
+        <v>18146002</v>
       </c>
       <c r="I7" t="n">
-        <v>12337108</v>
+        <v>11155624</v>
       </c>
       <c r="J7" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1</v>
+        <v>-0.38</v>
       </c>
       <c r="L7" t="n">
-        <v>69.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="M7" t="n">
-        <v>57.06</v>
+        <v>57.17</v>
       </c>
       <c r="N7" t="n">
-        <v>59.67</v>
+        <v>60.05</v>
       </c>
       <c r="O7" t="n">
-        <v>71.56999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.73</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
       <c r="R7" t="n">
-        <v>68.78</v>
+        <v>72.19</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>818.45</v>
+      </c>
+      <c r="D8" t="n">
         <v>826.05</v>
       </c>
-      <c r="D8" t="n">
-        <v>832.9</v>
-      </c>
       <c r="E8" t="n">
-        <v>-0.82</v>
+        <v>-0.92</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.85</v>
+        <v>-2.43</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.59</v>
+        <v>-5.12</v>
       </c>
       <c r="H8" t="n">
-        <v>104795</v>
+        <v>157471</v>
       </c>
       <c r="I8" t="n">
-        <v>105535</v>
+        <v>104810</v>
       </c>
       <c r="J8" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.64</v>
+        <v>0.18</v>
       </c>
       <c r="L8" t="n">
-        <v>44.9</v>
+        <v>42.2</v>
       </c>
       <c r="M8" t="n">
-        <v>746.29</v>
+        <v>746.33</v>
       </c>
       <c r="N8" t="n">
-        <v>834.36</v>
+        <v>833.49</v>
       </c>
       <c r="O8" t="n">
         <v>865.55</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.56</v>
+        <v>-5.44</v>
       </c>
       <c r="Q8" t="n">
         <v>550.8</v>
       </c>
       <c r="R8" t="n">
-        <v>49.97</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="D10" t="n">
         <v>6.18</v>
       </c>
-      <c r="D10" t="n">
-        <v>6.16</v>
-      </c>
       <c r="E10" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="F10" t="n">
-        <v>-11.71</v>
+        <v>-6.75</v>
       </c>
       <c r="G10" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="H10" t="n">
+        <v>8552</v>
+      </c>
+      <c r="I10" t="n">
         <v>13321</v>
       </c>
-      <c r="I10" t="n">
-        <v>4186</v>
-      </c>
       <c r="J10" t="n">
-        <v>2.69</v>
+        <v>1.58</v>
       </c>
       <c r="K10" t="n">
-        <v>5.94</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>41.3</v>
+        <v>42.1</v>
       </c>
       <c r="M10" t="n">
-        <v>9.44</v>
+        <v>9.41</v>
       </c>
       <c r="N10" t="n">
-        <v>6.83</v>
+        <v>6.79</v>
       </c>
       <c r="O10" t="n">
         <v>15.56</v>
       </c>
       <c r="P10" t="n">
-        <v>-60.28</v>
+        <v>-60.03</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>16.82</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1022.2</v>
+      </c>
+      <c r="D11" t="n">
         <v>982.7</v>
       </c>
-      <c r="D11" t="n">
-        <v>1036.2</v>
-      </c>
       <c r="E11" t="n">
-        <v>-5.16</v>
+        <v>4.02</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.1</v>
+        <v>0.28</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.55</v>
+        <v>-2.66</v>
       </c>
       <c r="H11" t="n">
-        <v>2265116</v>
+        <v>1706689</v>
       </c>
       <c r="I11" t="n">
-        <v>640029</v>
+        <v>2265269</v>
       </c>
       <c r="J11" t="n">
-        <v>1.82</v>
+        <v>1.29</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.48</v>
+        <v>1.14</v>
       </c>
       <c r="L11" t="n">
-        <v>36.1</v>
+        <v>45.4</v>
       </c>
       <c r="M11" t="n">
-        <v>938.61</v>
+        <v>938.5700000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>1053.92</v>
+        <v>1054.69</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-12.04</v>
+        <v>-8.5</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>43.96</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="D12" t="n">
         <v>21.64</v>
       </c>
-      <c r="D12" t="n">
-        <v>21.81</v>
-      </c>
       <c r="E12" t="n">
-        <v>-0.78</v>
+        <v>1.06</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.18</v>
+        <v>-1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.91</v>
+        <v>-5.57</v>
       </c>
       <c r="H12" t="n">
-        <v>1581211</v>
+        <v>1969615</v>
       </c>
       <c r="I12" t="n">
-        <v>2017639</v>
+        <v>1585685</v>
       </c>
       <c r="J12" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="K12" t="n">
-        <v>0.54</v>
+        <v>-0.14</v>
       </c>
       <c r="L12" t="n">
-        <v>39.2</v>
+        <v>42.9</v>
       </c>
       <c r="M12" t="n">
-        <v>25.46</v>
+        <v>25.42</v>
       </c>
       <c r="N12" t="n">
-        <v>22.61</v>
+        <v>22.57</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-33.48</v>
+        <v>-32.77</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="13">
@@ -1093,37 +1093,37 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.18</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.26</v>
-      </c>
       <c r="E13" t="n">
-        <v>-1.52</v>
+        <v>-1.16</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.52</v>
+        <v>-1.35</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.72</v>
+        <v>-4.3</v>
       </c>
       <c r="H13" t="n">
+        <v>329288</v>
+      </c>
+      <c r="I13" t="n">
         <v>121719</v>
       </c>
-      <c r="I13" t="n">
-        <v>100866</v>
-      </c>
       <c r="J13" t="n">
-        <v>0.8</v>
+        <v>2.16</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-1.81</v>
       </c>
       <c r="L13" t="n">
-        <v>37.9</v>
+        <v>35</v>
       </c>
       <c r="M13" t="n">
-        <v>6.17</v>
+        <v>6.16</v>
       </c>
       <c r="N13" t="n">
         <v>5.5</v>
@@ -1132,13 +1132,13 @@
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-46.71</v>
+        <v>-47.33</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>23.92</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24383.6</v>
+      </c>
+      <c r="D17" t="n">
         <v>24317.15</v>
       </c>
-      <c r="D17" t="n">
-        <v>24250.2</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="F17" t="n">
-        <v>1.87</v>
+        <v>2.59</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3</v>
+        <v>0.86</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.01</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57264.85</v>
+      </c>
+      <c r="D18" t="n">
         <v>57147.5</v>
       </c>
-      <c r="D18" t="n">
-        <v>57205.9</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.1</v>
+        <v>0.21</v>
       </c>
       <c r="F18" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.53</v>
+        <v>-1.32</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>89.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>90.73999999999999</v>
+        <v>89.03</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.15</v>
+        <v>0.98</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.91</v>
+        <v>-7.11</v>
       </c>
       <c r="G19" t="n">
-        <v>23.01</v>
+        <v>25.61</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.23</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4173.6</v>
+        <v>4101.2</v>
       </c>
       <c r="D20" t="n">
-        <v>4034.7</v>
+        <v>4100.1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.44</v>
+        <v>0.03</v>
       </c>
       <c r="F20" t="n">
-        <v>3.14</v>
+        <v>0.83</v>
       </c>
       <c r="G20" t="n">
-        <v>3.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>3.87</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52006.44</v>
+        <v>52407.88</v>
       </c>
       <c r="D21" t="n">
-        <v>51594.14</v>
+        <v>52208.06</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8</v>
+        <v>0.38</v>
       </c>
       <c r="F21" t="n">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="H21" t="n">
-        <v>2.64</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12.15</v>
+        <v>11.76</v>
       </c>
       <c r="D22" t="n">
-        <v>12.01</v>
+        <v>12.16</v>
       </c>
       <c r="E22" t="n">
-        <v>1.17</v>
+        <v>-3.29</v>
       </c>
       <c r="F22" t="n">
-        <v>-9.869999999999999</v>
+        <v>-16.18</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.23</v>
+        <v>-4.31</v>
       </c>
       <c r="H22" t="n">
         <v/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,29 @@
       </c>
       <c r="G7" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57264.85</v>
+      </c>
+      <c r="C8" t="n">
+        <v>57147.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1746,6 +1769,29 @@
       </c>
       <c r="G7" t="n">
         <v>-0.23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>89.03</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-7.11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -1759,7 +1805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1935,6 +1981,29 @@
       </c>
       <c r="G7" t="n">
         <v>3.87</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4101.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4100.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.54</v>
       </c>
     </row>
   </sheetData>
@@ -1948,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2124,6 +2193,29 @@
       </c>
       <c r="G7" t="n">
         <v>2.64</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>52407.88</v>
+      </c>
+      <c r="C8" t="n">
+        <v>52208.06</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -2137,7 +2229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2296,7 +2388,27 @@
       <c r="F7" t="n">
         <v>-8.23</v>
       </c>
-      <c r="G7" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-16.18</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="G8" t="n">
         <v/>
       </c>
     </row>
@@ -2311,7 +2423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2637,6 +2749,59 @@
       </c>
       <c r="Q6" t="n">
         <v>16.82</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8552</v>
+      </c>
+      <c r="H7" t="n">
+        <v>13321</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="N7" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-60.03</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>17.58</v>
       </c>
     </row>
   </sheetData>
@@ -2650,7 +2815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2976,6 +3141,59 @@
       </c>
       <c r="Q6" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B7" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="C7" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1969615</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1585685</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="K7" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="M7" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="N7" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-32.77</v>
+      </c>
+      <c r="P7" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.77</v>
       </c>
     </row>
   </sheetData>
@@ -2989,7 +3207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3209,6 +3427,59 @@
       </c>
       <c r="Q4" t="n">
         <v>64.76000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B5" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7680830</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5193772</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K5" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="M5" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="P5" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>64.09</v>
       </c>
     </row>
   </sheetData>
@@ -3222,7 +3493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3601,6 +3872,59 @@
       </c>
       <c r="Q7" t="n">
         <v>59.89</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>395.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>384.65</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="G8" t="n">
+        <v>406765</v>
+      </c>
+      <c r="H8" t="n">
+        <v>243245</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="K8" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>336.45</v>
+      </c>
+      <c r="M8" t="n">
+        <v>358.89</v>
+      </c>
+      <c r="N8" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-17.55</v>
+      </c>
+      <c r="P8" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>64.28</v>
       </c>
     </row>
   </sheetData>
@@ -3614,7 +3938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3993,6 +4317,59 @@
       </c>
       <c r="Q7" t="n">
         <v>3.45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>281</v>
+      </c>
+      <c r="C8" t="n">
+        <v>285.05</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16821515</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18283697</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K8" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>321.99</v>
+      </c>
+      <c r="M8" t="n">
+        <v>285.41</v>
+      </c>
+      <c r="N8" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-30.1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.98</v>
       </c>
     </row>
   </sheetData>
@@ -4006,7 +4383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4385,6 +4762,59 @@
       </c>
       <c r="Q7" t="n">
         <v>17.68</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>917</v>
+      </c>
+      <c r="C8" t="n">
+        <v>929.85</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="G8" t="n">
+        <v>325800</v>
+      </c>
+      <c r="H8" t="n">
+        <v>236650</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="K8" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>940.53</v>
+      </c>
+      <c r="M8" t="n">
+        <v>941.65</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-23.96</v>
+      </c>
+      <c r="P8" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>16.05</v>
       </c>
     </row>
   </sheetData>
@@ -4398,7 +4828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4777,6 +5207,59 @@
       </c>
       <c r="Q7" t="n">
         <v>43.96</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1022.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>982.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1706689</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2265269</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="K8" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>938.5700000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1054.69</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>49.75</v>
       </c>
     </row>
   </sheetData>
@@ -4790,7 +5273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5169,6 +5652,59 @@
       </c>
       <c r="Q7" t="n">
         <v>68.78</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="C8" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18146002</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11155624</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="K8" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="M8" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>72.19</v>
       </c>
     </row>
   </sheetData>
@@ -5182,7 +5718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5561,6 +6097,59 @@
       </c>
       <c r="Q7" t="n">
         <v>23.92</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>329288</v>
+      </c>
+      <c r="H8" t="n">
+        <v>121719</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="K8" t="n">
+        <v>35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-47.33</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>22.49</v>
       </c>
     </row>
   </sheetData>
@@ -5574,7 +6163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5953,6 +6542,59 @@
       </c>
       <c r="Q7" t="n">
         <v>49.97</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>818.45</v>
+      </c>
+      <c r="C8" t="n">
+        <v>826.05</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-5.12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>157471</v>
+      </c>
+      <c r="H8" t="n">
+        <v>104810</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K8" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>746.33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>833.49</v>
+      </c>
+      <c r="N8" t="n">
+        <v>865.55</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="P8" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>48.59</v>
       </c>
     </row>
   </sheetData>
@@ -5966,7 +6608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6144,6 +6786,29 @@
         <v>-0.01</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>24383.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>24317.15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>395.2</v>
+        <v>402.45</v>
       </c>
       <c r="D3" t="n">
         <v>384.65</v>
       </c>
       <c r="E3" t="n">
-        <v>2.74</v>
+        <v>4.63</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.79</v>
+        <v>0.01</v>
       </c>
       <c r="G3" t="n">
-        <v>8.51</v>
+        <v>10.5</v>
       </c>
       <c r="H3" t="n">
-        <v>406765</v>
+        <v>345781</v>
       </c>
       <c r="I3" t="n">
         <v>243245</v>
       </c>
       <c r="J3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.18</v>
+        <v>3.66</v>
       </c>
       <c r="L3" t="n">
-        <v>53.9</v>
+        <v>56.1</v>
       </c>
       <c r="M3" t="n">
-        <v>336.45</v>
+        <v>336.49</v>
       </c>
       <c r="N3" t="n">
-        <v>358.89</v>
+        <v>359.03</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-17.55</v>
+        <v>-16.04</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>64.28</v>
+        <v>67.29000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="D4" t="n">
         <v>46.7</v>
       </c>
-      <c r="D4" t="n">
-        <v>46.89</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.41</v>
+        <v>0.79</v>
       </c>
       <c r="F4" t="n">
-        <v>0.39</v>
+        <v>-1.73</v>
       </c>
       <c r="G4" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="H4" t="n">
-        <v>7680830</v>
+        <v>8218426</v>
       </c>
       <c r="I4" t="n">
-        <v>5193772</v>
+        <v>7682155</v>
       </c>
       <c r="J4" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="K4" t="n">
-        <v>0.51</v>
+        <v>1.49</v>
       </c>
       <c r="L4" t="n">
-        <v>52.9</v>
+        <v>54.6</v>
       </c>
       <c r="M4" t="n">
-        <v>40.85</v>
+        <v>40.92</v>
       </c>
       <c r="N4" t="n">
-        <v>45.4</v>
+        <v>45.52</v>
       </c>
       <c r="O4" t="n">
         <v>48.49</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.69</v>
+        <v>-2.93</v>
       </c>
       <c r="Q4" t="n">
         <v>28.46</v>
       </c>
       <c r="R4" t="n">
-        <v>64.09</v>
+        <v>65.39</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>287</v>
+      </c>
+      <c r="D5" t="n">
         <v>281</v>
       </c>
-      <c r="D5" t="n">
-        <v>285.05</v>
-      </c>
       <c r="E5" t="n">
-        <v>-1.42</v>
+        <v>2.14</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.86</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.07</v>
+        <v>-1.02</v>
       </c>
       <c r="H5" t="n">
-        <v>16821515</v>
+        <v>45362245</v>
       </c>
       <c r="I5" t="n">
-        <v>18283697</v>
+        <v>16833813</v>
       </c>
       <c r="J5" t="n">
-        <v>1.08</v>
+        <v>2.82</v>
       </c>
       <c r="K5" t="n">
-        <v>0.38</v>
+        <v>2.74</v>
       </c>
       <c r="L5" t="n">
-        <v>43.7</v>
+        <v>54.7</v>
       </c>
       <c r="M5" t="n">
-        <v>321.99</v>
+        <v>321.53</v>
       </c>
       <c r="N5" t="n">
-        <v>285.41</v>
+        <v>285.23</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-30.1</v>
+        <v>-28.61</v>
       </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.98</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>929.1</v>
+      </c>
+      <c r="D6" t="n">
         <v>917</v>
       </c>
-      <c r="D6" t="n">
-        <v>929.85</v>
-      </c>
       <c r="E6" t="n">
-        <v>-1.38</v>
+        <v>1.32</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.48</v>
+        <v>0.22</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.87</v>
+        <v>-0.25</v>
       </c>
       <c r="H6" t="n">
-        <v>325800</v>
+        <v>289045</v>
       </c>
       <c r="I6" t="n">
-        <v>236650</v>
+        <v>329649</v>
       </c>
       <c r="J6" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="K6" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="L6" t="n">
-        <v>41.7</v>
+        <v>46.2</v>
       </c>
       <c r="M6" t="n">
-        <v>940.53</v>
+        <v>941.14</v>
       </c>
       <c r="N6" t="n">
-        <v>941.65</v>
+        <v>936.77</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-23.96</v>
+        <v>-22.96</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>16.05</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="D7" t="n">
         <v>71.75</v>
       </c>
-      <c r="D7" t="n">
-        <v>70.33</v>
-      </c>
       <c r="E7" t="n">
-        <v>2.02</v>
+        <v>-0.85</v>
       </c>
       <c r="F7" t="n">
-        <v>1.46</v>
+        <v>-0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>16.86</v>
+        <v>19.36</v>
       </c>
       <c r="H7" t="n">
-        <v>18146002</v>
+        <v>13429290</v>
       </c>
       <c r="I7" t="n">
-        <v>11155624</v>
+        <v>18147741</v>
       </c>
       <c r="J7" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.38</v>
+        <v>1.41</v>
       </c>
       <c r="L7" t="n">
-        <v>71.8</v>
+        <v>69</v>
       </c>
       <c r="M7" t="n">
-        <v>57.17</v>
+        <v>57.29</v>
       </c>
       <c r="N7" t="n">
-        <v>60.05</v>
+        <v>60.38</v>
       </c>
       <c r="O7" t="n">
         <v>71.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
       <c r="R7" t="n">
-        <v>72.19</v>
+        <v>70.72</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>833.95</v>
+      </c>
+      <c r="D8" t="n">
         <v>818.45</v>
       </c>
-      <c r="D8" t="n">
-        <v>826.05</v>
-      </c>
       <c r="E8" t="n">
-        <v>-0.92</v>
+        <v>1.89</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.43</v>
+        <v>-1.18</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.12</v>
+        <v>-3.65</v>
       </c>
       <c r="H8" t="n">
-        <v>157471</v>
+        <v>199696</v>
       </c>
       <c r="I8" t="n">
-        <v>104810</v>
+        <v>157508</v>
       </c>
       <c r="J8" t="n">
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="K8" t="n">
-        <v>0.18</v>
+        <v>1.26</v>
       </c>
       <c r="L8" t="n">
-        <v>42.2</v>
+        <v>48.9</v>
       </c>
       <c r="M8" t="n">
-        <v>746.33</v>
+        <v>746.4299999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>833.49</v>
+        <v>833.75</v>
       </c>
       <c r="O8" t="n">
         <v>865.55</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.44</v>
+        <v>-3.65</v>
       </c>
       <c r="Q8" t="n">
         <v>550.8</v>
       </c>
       <c r="R8" t="n">
-        <v>48.59</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="9">
@@ -913,34 +913,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.22</v>
+        <v>6.35</v>
       </c>
       <c r="D10" t="n">
         <v>6.18</v>
       </c>
       <c r="E10" t="n">
-        <v>0.65</v>
+        <v>2.75</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.75</v>
+        <v>-4.8</v>
       </c>
       <c r="G10" t="n">
-        <v>1.97</v>
+        <v>4.1</v>
       </c>
       <c r="H10" t="n">
-        <v>8552</v>
+        <v>1407</v>
       </c>
       <c r="I10" t="n">
         <v>13321</v>
       </c>
       <c r="J10" t="n">
-        <v>1.58</v>
+        <v>0.26</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="L10" t="n">
-        <v>42.1</v>
+        <v>44.7</v>
       </c>
       <c r="M10" t="n">
         <v>9.41</v>
@@ -949,16 +949,16 @@
         <v>6.79</v>
       </c>
       <c r="O10" t="n">
-        <v>15.56</v>
+        <v>14.69</v>
       </c>
       <c r="P10" t="n">
-        <v>-60.03</v>
+        <v>-56.77</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>17.58</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1022.2</v>
+        <v>1020.7</v>
       </c>
       <c r="D11" t="n">
         <v>982.7</v>
       </c>
       <c r="E11" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="F11" t="n">
-        <v>0.28</v>
+        <v>0.14</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.66</v>
+        <v>-2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1706689</v>
+        <v>614627</v>
       </c>
       <c r="I11" t="n">
         <v>2265269</v>
       </c>
       <c r="J11" t="n">
-        <v>1.29</v>
+        <v>0.47</v>
       </c>
       <c r="K11" t="n">
-        <v>1.14</v>
+        <v>5.37</v>
       </c>
       <c r="L11" t="n">
-        <v>45.4</v>
+        <v>45.1</v>
       </c>
       <c r="M11" t="n">
-        <v>938.5700000000001</v>
+        <v>938.5599999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>1054.69</v>
+        <v>1054.66</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-8.5</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>49.75</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="D12" t="n">
         <v>21.87</v>
       </c>
-      <c r="D12" t="n">
-        <v>21.64</v>
-      </c>
       <c r="E12" t="n">
-        <v>1.06</v>
+        <v>2.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.62</v>
+        <v>2.15</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.57</v>
+        <v>-2.87</v>
       </c>
       <c r="H12" t="n">
-        <v>1969615</v>
+        <v>8134611</v>
       </c>
       <c r="I12" t="n">
-        <v>1585685</v>
+        <v>1970045</v>
       </c>
       <c r="J12" t="n">
-        <v>0.65</v>
+        <v>2.74</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.14</v>
+        <v>-1.37</v>
       </c>
       <c r="L12" t="n">
-        <v>42.9</v>
+        <v>49.6</v>
       </c>
       <c r="M12" t="n">
-        <v>25.42</v>
+        <v>25.38</v>
       </c>
       <c r="N12" t="n">
-        <v>22.57</v>
+        <v>22.54</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-32.77</v>
+        <v>-31.36</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>1.77</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="13">
@@ -1093,34 +1093,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.12</v>
+        <v>5.24</v>
       </c>
       <c r="D13" t="n">
         <v>5.18</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.16</v>
+        <v>1.16</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.35</v>
+        <v>0.96</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.3</v>
+        <v>-2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>329288</v>
+        <v>416008</v>
       </c>
       <c r="I13" t="n">
         <v>121719</v>
       </c>
       <c r="J13" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.81</v>
+        <v>-0.2</v>
       </c>
       <c r="L13" t="n">
-        <v>35</v>
+        <v>42.6</v>
       </c>
       <c r="M13" t="n">
         <v>6.16</v>
@@ -1132,13 +1132,13 @@
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-47.33</v>
+        <v>-46.09</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>22.49</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24774.3</v>
+      </c>
+      <c r="D17" t="n">
         <v>24383.6</v>
       </c>
-      <c r="D17" t="n">
-        <v>24317.15</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.27</v>
+        <v>1.6</v>
       </c>
       <c r="F17" t="n">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="G17" t="n">
-        <v>0.86</v>
+        <v>2.07</v>
       </c>
       <c r="H17" t="n">
-        <v>0.36</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>58247.95</v>
+      </c>
+      <c r="D18" t="n">
         <v>57264.85</v>
       </c>
-      <c r="D18" t="n">
-        <v>57147.5</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.21</v>
+        <v>1.72</v>
       </c>
       <c r="F18" t="n">
-        <v>1.01</v>
+        <v>2.03</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.32</v>
+        <v>0.53</v>
       </c>
       <c r="H18" t="n">
-        <v>0.25</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>89.90000000000001</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>89.03</v>
+        <v>90.12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.98</v>
+        <v>-7.06</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.11</v>
+        <v>-5.21</v>
       </c>
       <c r="G19" t="n">
-        <v>25.61</v>
+        <v>16.66</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4101.2</v>
+        <v>4090.3</v>
       </c>
       <c r="D20" t="n">
-        <v>4100.1</v>
+        <v>4049.1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03</v>
+        <v>1.02</v>
       </c>
       <c r="F20" t="n">
-        <v>0.83</v>
+        <v>0.39</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.54</v>
       </c>
       <c r="H20" t="n">
-        <v>2.54</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52407.88</v>
+        <v>52996.27</v>
       </c>
       <c r="D21" t="n">
-        <v>52208.06</v>
+        <v>52485.03</v>
       </c>
       <c r="E21" t="n">
-        <v>0.38</v>
+        <v>0.97</v>
       </c>
       <c r="F21" t="n">
-        <v>0.89</v>
+        <v>1.51</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H21" t="n">
-        <v>0.12</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.76</v>
       </c>
-      <c r="D22" t="n">
-        <v>12.16</v>
-      </c>
       <c r="E22" t="n">
-        <v>-3.29</v>
+        <v>1.45</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.18</v>
+        <v>-5.77</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.31</v>
+        <v>1.1</v>
       </c>
       <c r="H22" t="n">
         <v/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,6 +1580,29 @@
       </c>
       <c r="G8" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58247.95</v>
+      </c>
+      <c r="C9" t="n">
+        <v>57264.85</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -1593,7 +1616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1792,6 +1815,29 @@
       </c>
       <c r="G8" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83.76000000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>90.12</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-7.06</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1805,7 +1851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,6 +2050,29 @@
       </c>
       <c r="G8" t="n">
         <v>2.54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4090.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4049.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.46</v>
       </c>
     </row>
   </sheetData>
@@ -2017,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2216,6 +2285,29 @@
       </c>
       <c r="G8" t="n">
         <v>0.12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>52996.27</v>
+      </c>
+      <c r="C9" t="n">
+        <v>52485.03</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>
@@ -2229,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2408,7 +2500,27 @@
       <c r="F8" t="n">
         <v>-4.31</v>
       </c>
-      <c r="G8" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-5.77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G9" t="n">
         <v/>
       </c>
     </row>
@@ -2423,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2802,6 +2914,59 @@
       </c>
       <c r="Q7" t="n">
         <v>17.58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1407</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13321</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="K8" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-56.77</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>20.04</v>
       </c>
     </row>
   </sheetData>
@@ -2815,7 +2980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3194,6 +3359,59 @@
       </c>
       <c r="Q7" t="n">
         <v>1.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B8" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="C8" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8134611</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1970045</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="K8" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="M8" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="N8" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-31.36</v>
+      </c>
+      <c r="P8" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.91</v>
       </c>
     </row>
   </sheetData>
@@ -3207,7 +3425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3480,6 +3698,59 @@
       </c>
       <c r="Q5" t="n">
         <v>64.09</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B6" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="C6" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8218426</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7682155</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="K6" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="M6" t="n">
+        <v>45.52</v>
+      </c>
+      <c r="N6" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="P6" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>65.39</v>
       </c>
     </row>
   </sheetData>
@@ -3493,7 +3764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3925,6 +4196,59 @@
       </c>
       <c r="Q8" t="n">
         <v>64.28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>402.45</v>
+      </c>
+      <c r="C9" t="n">
+        <v>384.65</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>345781</v>
+      </c>
+      <c r="H9" t="n">
+        <v>243245</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="K9" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>336.49</v>
+      </c>
+      <c r="M9" t="n">
+        <v>359.03</v>
+      </c>
+      <c r="N9" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-16.04</v>
+      </c>
+      <c r="P9" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>67.29000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3938,7 +4262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4370,6 +4694,59 @@
       </c>
       <c r="Q8" t="n">
         <v>1.98</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>287</v>
+      </c>
+      <c r="C9" t="n">
+        <v>281</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="G9" t="n">
+        <v>45362245</v>
+      </c>
+      <c r="H9" t="n">
+        <v>16833813</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K9" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>321.53</v>
+      </c>
+      <c r="M9" t="n">
+        <v>285.23</v>
+      </c>
+      <c r="N9" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-28.61</v>
+      </c>
+      <c r="P9" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.16</v>
       </c>
     </row>
   </sheetData>
@@ -4383,7 +4760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4815,6 +5192,59 @@
       </c>
       <c r="Q8" t="n">
         <v>16.05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>929.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>917</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G9" t="n">
+        <v>289045</v>
+      </c>
+      <c r="H9" t="n">
+        <v>329649</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>941.14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>936.77</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-22.96</v>
+      </c>
+      <c r="P9" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>17.58</v>
       </c>
     </row>
   </sheetData>
@@ -4828,7 +5258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5260,6 +5690,59 @@
       </c>
       <c r="Q8" t="n">
         <v>49.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1020.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>982.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>614627</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2265269</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="K9" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>938.5599999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1054.66</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="P9" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>49.53</v>
       </c>
     </row>
   </sheetData>
@@ -5273,7 +5756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5705,6 +6188,59 @@
       </c>
       <c r="Q8" t="n">
         <v>72.19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="C9" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13429290</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18147741</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="K9" t="n">
+        <v>69</v>
+      </c>
+      <c r="L9" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="M9" t="n">
+        <v>60.38</v>
+      </c>
+      <c r="N9" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="P9" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>70.72</v>
       </c>
     </row>
   </sheetData>
@@ -5718,7 +6254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6150,6 +6686,59 @@
       </c>
       <c r="Q8" t="n">
         <v>22.49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="G9" t="n">
+        <v>416008</v>
+      </c>
+      <c r="H9" t="n">
+        <v>121719</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-46.09</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>25.36</v>
       </c>
     </row>
   </sheetData>
@@ -6163,7 +6752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6595,6 +7184,59 @@
       </c>
       <c r="Q8" t="n">
         <v>48.59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>833.95</v>
+      </c>
+      <c r="C9" t="n">
+        <v>818.45</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="G9" t="n">
+        <v>199696</v>
+      </c>
+      <c r="H9" t="n">
+        <v>157508</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K9" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>746.4299999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>833.75</v>
+      </c>
+      <c r="N9" t="n">
+        <v>865.55</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="P9" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>51.41</v>
       </c>
     </row>
   </sheetData>
@@ -6608,7 +7250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6809,6 +7451,29 @@
         <v>0.36</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>24774.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>24383.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>398.3</v>
+      </c>
+      <c r="D3" t="n">
         <v>402.45</v>
       </c>
-      <c r="D3" t="n">
-        <v>384.65</v>
-      </c>
       <c r="E3" t="n">
-        <v>4.63</v>
+        <v>-1.03</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01</v>
+        <v>-4</v>
       </c>
       <c r="G3" t="n">
-        <v>10.5</v>
+        <v>9.91</v>
       </c>
       <c r="H3" t="n">
-        <v>345781</v>
+        <v>303617</v>
       </c>
       <c r="I3" t="n">
-        <v>243245</v>
+        <v>345799</v>
       </c>
       <c r="J3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="K3" t="n">
-        <v>3.66</v>
+        <v>-0.3</v>
       </c>
       <c r="L3" t="n">
-        <v>56.1</v>
+        <v>54.5</v>
       </c>
       <c r="M3" t="n">
         <v>336.49</v>
       </c>
       <c r="N3" t="n">
-        <v>359.03</v>
+        <v>360.55</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-16.04</v>
+        <v>-16.9</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>67.29000000000001</v>
+        <v>65.56999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="D4" t="n">
         <v>47.07</v>
       </c>
-      <c r="D4" t="n">
-        <v>46.7</v>
-      </c>
       <c r="E4" t="n">
-        <v>0.79</v>
+        <v>-0.45</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.73</v>
+        <v>-0.57</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>8218426</v>
+        <v>4902939</v>
       </c>
       <c r="I4" t="n">
-        <v>7682155</v>
+        <v>8220206</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="K4" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>54.6</v>
+        <v>53.4</v>
       </c>
       <c r="M4" t="n">
-        <v>40.92</v>
+        <v>40.99</v>
       </c>
       <c r="N4" t="n">
-        <v>45.52</v>
+        <v>45.65</v>
       </c>
       <c r="O4" t="n">
         <v>48.49</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.93</v>
+        <v>-3.36</v>
       </c>
       <c r="Q4" t="n">
         <v>28.46</v>
       </c>
       <c r="R4" t="n">
-        <v>65.39</v>
+        <v>64.65000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>289</v>
+      </c>
+      <c r="D5" t="n">
         <v>287</v>
       </c>
-      <c r="D5" t="n">
-        <v>281</v>
-      </c>
       <c r="E5" t="n">
-        <v>2.14</v>
+        <v>0.7</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>1.53</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.02</v>
+        <v>0.26</v>
       </c>
       <c r="H5" t="n">
-        <v>45362245</v>
+        <v>12685347</v>
       </c>
       <c r="I5" t="n">
-        <v>16833813</v>
+        <v>45392755</v>
       </c>
       <c r="J5" t="n">
-        <v>2.82</v>
+        <v>0.75</v>
       </c>
       <c r="K5" t="n">
-        <v>2.74</v>
+        <v>-0.64</v>
       </c>
       <c r="L5" t="n">
-        <v>54.7</v>
+        <v>57.6</v>
       </c>
       <c r="M5" t="n">
-        <v>321.53</v>
+        <v>321.07</v>
       </c>
       <c r="N5" t="n">
-        <v>285.23</v>
+        <v>285.14</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-28.61</v>
+        <v>-28.11</v>
       </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
       <c r="R5" t="n">
-        <v>4.16</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>917</v>
+      </c>
+      <c r="D6" t="n">
         <v>929.1</v>
       </c>
-      <c r="D6" t="n">
-        <v>917</v>
-      </c>
       <c r="E6" t="n">
-        <v>1.32</v>
+        <v>-1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.22</v>
+        <v>-0.87</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.25</v>
+        <v>-1.61</v>
       </c>
       <c r="H6" t="n">
-        <v>289045</v>
+        <v>315242</v>
       </c>
       <c r="I6" t="n">
-        <v>329649</v>
+        <v>289116</v>
       </c>
       <c r="J6" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="K6" t="n">
-        <v>1.02</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>46.2</v>
+        <v>42.7</v>
       </c>
       <c r="M6" t="n">
-        <v>941.14</v>
+        <v>941.64</v>
       </c>
       <c r="N6" t="n">
-        <v>936.77</v>
+        <v>931.39</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-22.96</v>
+        <v>-23.96</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>17.58</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="D7" t="n">
         <v>71.14</v>
       </c>
-      <c r="D7" t="n">
-        <v>71.75</v>
-      </c>
       <c r="E7" t="n">
-        <v>-0.85</v>
+        <v>-1.11</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6</v>
+        <v>0.33</v>
       </c>
       <c r="G7" t="n">
-        <v>19.36</v>
+        <v>17.68</v>
       </c>
       <c r="H7" t="n">
-        <v>13429290</v>
+        <v>22529878</v>
       </c>
       <c r="I7" t="n">
-        <v>18147741</v>
+        <v>13435710</v>
       </c>
       <c r="J7" t="n">
-        <v>0.46</v>
+        <v>0.77</v>
       </c>
       <c r="K7" t="n">
-        <v>1.41</v>
+        <v>-0.23</v>
       </c>
       <c r="L7" t="n">
-        <v>69</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>57.29</v>
+        <v>57.4</v>
       </c>
       <c r="N7" t="n">
-        <v>60.38</v>
+        <v>60.68</v>
       </c>
       <c r="O7" t="n">
         <v>71.75</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.85</v>
+        <v>-1.95</v>
       </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
       <c r="R7" t="n">
-        <v>70.72</v>
+        <v>68.83</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>845.5</v>
+      </c>
+      <c r="D8" t="n">
         <v>833.95</v>
       </c>
-      <c r="D8" t="n">
-        <v>818.45</v>
-      </c>
       <c r="E8" t="n">
-        <v>1.89</v>
+        <v>1.38</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.18</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.65</v>
+        <v>0.35</v>
       </c>
       <c r="H8" t="n">
-        <v>199696</v>
+        <v>221654</v>
       </c>
       <c r="I8" t="n">
-        <v>157508</v>
+        <v>199791</v>
       </c>
       <c r="J8" t="n">
-        <v>0.92</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>48.9</v>
+        <v>53.2</v>
       </c>
       <c r="M8" t="n">
-        <v>746.4299999999999</v>
+        <v>746.59</v>
       </c>
       <c r="N8" t="n">
-        <v>833.75</v>
+        <v>834.34</v>
       </c>
       <c r="O8" t="n">
         <v>865.55</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.65</v>
+        <v>-2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>550.8</v>
       </c>
       <c r="R8" t="n">
-        <v>51.41</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="D10" t="n">
         <v>6.35</v>
       </c>
-      <c r="D10" t="n">
-        <v>6.18</v>
-      </c>
       <c r="E10" t="n">
-        <v>2.75</v>
+        <v>7.56</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.8</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>4.1</v>
+        <v>12.15</v>
       </c>
       <c r="H10" t="n">
+        <v>16647</v>
+      </c>
+      <c r="I10" t="n">
         <v>1407</v>
       </c>
-      <c r="I10" t="n">
-        <v>13321</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.26</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.19</v>
+        <v>3.32</v>
       </c>
       <c r="L10" t="n">
-        <v>44.7</v>
+        <v>53.1</v>
       </c>
       <c r="M10" t="n">
-        <v>9.41</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>6.79</v>
+        <v>6.76</v>
       </c>
       <c r="O10" t="n">
         <v>14.69</v>
       </c>
       <c r="P10" t="n">
-        <v>-56.77</v>
+        <v>-53.51</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>20.04</v>
+        <v>29.11</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1036.3</v>
+      </c>
+      <c r="D11" t="n">
         <v>1020.7</v>
       </c>
-      <c r="D11" t="n">
-        <v>982.7</v>
-      </c>
       <c r="E11" t="n">
-        <v>3.87</v>
+        <v>1.53</v>
       </c>
       <c r="F11" t="n">
-        <v>0.14</v>
+        <v>-0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>614627</v>
+        <v>1063626</v>
       </c>
       <c r="I11" t="n">
-        <v>2265269</v>
+        <v>617990</v>
       </c>
       <c r="J11" t="n">
-        <v>0.47</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>5.37</v>
+        <v>0.19</v>
       </c>
       <c r="L11" t="n">
-        <v>45.1</v>
+        <v>48.4</v>
       </c>
       <c r="M11" t="n">
-        <v>938.5599999999999</v>
+        <v>938.46</v>
       </c>
       <c r="N11" t="n">
-        <v>1054.66</v>
+        <v>1055.69</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-8.640000000000001</v>
+        <v>-7.24</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>49.53</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="D12" t="n">
         <v>22.33</v>
       </c>
-      <c r="D12" t="n">
-        <v>21.87</v>
-      </c>
       <c r="E12" t="n">
-        <v>2.1</v>
+        <v>0.36</v>
       </c>
       <c r="F12" t="n">
-        <v>2.15</v>
+        <v>3.56</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.87</v>
+        <v>-2.9</v>
       </c>
       <c r="H12" t="n">
-        <v>8134611</v>
+        <v>9969439</v>
       </c>
       <c r="I12" t="n">
-        <v>1970045</v>
+        <v>8155897</v>
       </c>
       <c r="J12" t="n">
-        <v>2.74</v>
+        <v>3.26</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.37</v>
+        <v>-0.39</v>
       </c>
       <c r="L12" t="n">
-        <v>49.6</v>
+        <v>50.6</v>
       </c>
       <c r="M12" t="n">
-        <v>25.38</v>
+        <v>25.35</v>
       </c>
       <c r="N12" t="n">
-        <v>22.54</v>
+        <v>22.52</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-31.36</v>
+        <v>-31.11</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>3.91</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="13">
@@ -1093,37 +1093,37 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.24</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.18</v>
-      </c>
       <c r="E13" t="n">
-        <v>1.16</v>
+        <v>4.39</v>
       </c>
       <c r="F13" t="n">
-        <v>0.96</v>
+        <v>4.19</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.06</v>
+        <v>1.86</v>
       </c>
       <c r="H13" t="n">
+        <v>323780</v>
+      </c>
+      <c r="I13" t="n">
         <v>416008</v>
       </c>
-      <c r="I13" t="n">
-        <v>121719</v>
-      </c>
       <c r="J13" t="n">
-        <v>2.73</v>
+        <v>1.97</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2</v>
+        <v>1.89</v>
       </c>
       <c r="L13" t="n">
-        <v>42.6</v>
+        <v>56.3</v>
       </c>
       <c r="M13" t="n">
-        <v>6.16</v>
+        <v>6.14</v>
       </c>
       <c r="N13" t="n">
         <v>5.5</v>
@@ -1132,13 +1132,13 @@
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-46.09</v>
+        <v>-43.72</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>25.36</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24614.9</v>
+      </c>
+      <c r="D17" t="n">
         <v>24774.3</v>
       </c>
-      <c r="D17" t="n">
-        <v>24383.6</v>
-      </c>
       <c r="E17" t="n">
-        <v>1.6</v>
+        <v>-0.64</v>
       </c>
       <c r="F17" t="n">
-        <v>3.24</v>
+        <v>2.62</v>
       </c>
       <c r="G17" t="n">
-        <v>2.07</v>
+        <v>0.76</v>
       </c>
       <c r="H17" t="n">
-        <v>1.64</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57907.2</v>
+      </c>
+      <c r="D18" t="n">
         <v>58247.95</v>
       </c>
-      <c r="D18" t="n">
-        <v>57264.85</v>
-      </c>
       <c r="E18" t="n">
-        <v>1.72</v>
+        <v>-0.58</v>
       </c>
       <c r="F18" t="n">
         <v>2.03</v>
       </c>
       <c r="G18" t="n">
-        <v>0.53</v>
+        <v>-0.66</v>
       </c>
       <c r="H18" t="n">
-        <v>0.98</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>83.76000000000001</v>
+        <v>79.66</v>
       </c>
       <c r="D19" t="n">
-        <v>90.12</v>
+        <v>83.77</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.06</v>
+        <v>-4.91</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.21</v>
+        <v>-5.27</v>
       </c>
       <c r="G19" t="n">
-        <v>16.66</v>
+        <v>10.65</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4090.3</v>
+        <v>4150.4</v>
       </c>
       <c r="D20" t="n">
-        <v>4049.1</v>
+        <v>4033.7</v>
       </c>
       <c r="E20" t="n">
-        <v>1.02</v>
+        <v>2.89</v>
       </c>
       <c r="F20" t="n">
-        <v>0.39</v>
+        <v>2.83</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.54</v>
+        <v>-0.11</v>
       </c>
       <c r="H20" t="n">
-        <v>3.46</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52996.27</v>
+        <v>54173.91</v>
       </c>
       <c r="D21" t="n">
-        <v>52485.03</v>
+        <v>53178.41</v>
       </c>
       <c r="E21" t="n">
-        <v>0.97</v>
+        <v>1.87</v>
       </c>
       <c r="F21" t="n">
-        <v>1.51</v>
+        <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>0.18</v>
+        <v>2.11</v>
       </c>
       <c r="H21" t="n">
-        <v>1.19</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.93</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.76</v>
-      </c>
       <c r="E22" t="n">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.77</v>
+        <v>-2.95</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1</v>
+        <v>3.13</v>
       </c>
       <c r="H22" t="n">
         <v/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1603,6 +1603,29 @@
       </c>
       <c r="G9" t="n">
         <v>0.98</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57907.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>58247.95</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -1616,7 +1639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,6 +1861,29 @@
       </c>
       <c r="G9" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79.66</v>
+      </c>
+      <c r="C10" t="n">
+        <v>83.77</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-4.91</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1851,7 +1897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2073,6 +2119,29 @@
       </c>
       <c r="G9" t="n">
         <v>3.46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4150.4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4033.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.53</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2308,6 +2377,29 @@
       </c>
       <c r="G9" t="n">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>54173.91</v>
+      </c>
+      <c r="C10" t="n">
+        <v>53178.41</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>
@@ -2321,7 +2413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2520,7 +2612,27 @@
       <c r="F9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G9" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="C10" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="G10" t="n">
         <v/>
       </c>
     </row>
@@ -2535,7 +2647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2967,6 +3079,59 @@
       </c>
       <c r="Q8" t="n">
         <v>20.04</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B9" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16647</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1407</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="K9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-53.51</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>29.11</v>
       </c>
     </row>
   </sheetData>
@@ -2980,7 +3145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3412,6 +3577,59 @@
       </c>
       <c r="Q8" t="n">
         <v>3.91</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B9" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="C9" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9969439</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8155897</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="K9" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="M9" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="N9" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-31.11</v>
+      </c>
+      <c r="P9" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.28</v>
       </c>
     </row>
   </sheetData>
@@ -3425,7 +3643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3751,6 +3969,59 @@
       </c>
       <c r="Q6" t="n">
         <v>65.39</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B7" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="C7" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4902939</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8220206</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="M7" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="N7" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="P7" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>64.65000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3764,7 +4035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4249,6 +4520,59 @@
       </c>
       <c r="Q9" t="n">
         <v>67.29000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>398.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>402.45</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="G10" t="n">
+        <v>303617</v>
+      </c>
+      <c r="H10" t="n">
+        <v>345799</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>336.49</v>
+      </c>
+      <c r="M10" t="n">
+        <v>360.55</v>
+      </c>
+      <c r="N10" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>65.56999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4262,7 +4586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4747,6 +5071,59 @@
       </c>
       <c r="Q9" t="n">
         <v>4.16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>289</v>
+      </c>
+      <c r="C10" t="n">
+        <v>287</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12685347</v>
+      </c>
+      <c r="H10" t="n">
+        <v>45392755</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="K10" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>321.07</v>
+      </c>
+      <c r="M10" t="n">
+        <v>285.14</v>
+      </c>
+      <c r="N10" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-28.11</v>
+      </c>
+      <c r="P10" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.88</v>
       </c>
     </row>
   </sheetData>
@@ -4760,7 +5137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5245,6 +5622,59 @@
       </c>
       <c r="Q9" t="n">
         <v>17.58</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>917</v>
+      </c>
+      <c r="C10" t="n">
+        <v>929.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G10" t="n">
+        <v>315242</v>
+      </c>
+      <c r="H10" t="n">
+        <v>289116</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K10" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>941.64</v>
+      </c>
+      <c r="M10" t="n">
+        <v>931.39</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-23.96</v>
+      </c>
+      <c r="P10" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>16.05</v>
       </c>
     </row>
   </sheetData>
@@ -5258,7 +5688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5743,6 +6173,59 @@
       </c>
       <c r="Q9" t="n">
         <v>49.53</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1036.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1020.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1063626</v>
+      </c>
+      <c r="H10" t="n">
+        <v>617990</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K10" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>938.46</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1055.69</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="P10" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>51.82</v>
       </c>
     </row>
   </sheetData>
@@ -5756,7 +6239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6241,6 +6724,59 @@
       </c>
       <c r="Q9" t="n">
         <v>70.72</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="C10" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F10" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22529878</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13435710</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="K10" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="N10" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="P10" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>68.83</v>
       </c>
     </row>
   </sheetData>
@@ -6254,7 +6790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6739,6 +7275,59 @@
       </c>
       <c r="Q9" t="n">
         <v>25.36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G10" t="n">
+        <v>323780</v>
+      </c>
+      <c r="H10" t="n">
+        <v>416008</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K10" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-43.72</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>30.86</v>
       </c>
     </row>
   </sheetData>
@@ -6752,7 +7341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7237,6 +7826,59 @@
       </c>
       <c r="Q9" t="n">
         <v>51.41</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>845.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>833.95</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G10" t="n">
+        <v>221654</v>
+      </c>
+      <c r="H10" t="n">
+        <v>199791</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>746.59</v>
+      </c>
+      <c r="M10" t="n">
+        <v>834.34</v>
+      </c>
+      <c r="N10" t="n">
+        <v>865.55</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="P10" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>53.5</v>
       </c>
     </row>
   </sheetData>
@@ -7250,7 +7892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7474,6 +8116,29 @@
         <v>1.64</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>24614.9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>24774.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>405.6</v>
+      </c>
+      <c r="D3" t="n">
         <v>398.3</v>
       </c>
-      <c r="D3" t="n">
-        <v>402.45</v>
-      </c>
       <c r="E3" t="n">
-        <v>-1.03</v>
+        <v>1.83</v>
       </c>
       <c r="F3" t="n">
-        <v>-4</v>
+        <v>2.97</v>
       </c>
       <c r="G3" t="n">
-        <v>9.91</v>
+        <v>14.61</v>
       </c>
       <c r="H3" t="n">
-        <v>303617</v>
+        <v>433335</v>
       </c>
       <c r="I3" t="n">
-        <v>345799</v>
+        <v>303618</v>
       </c>
       <c r="J3" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3</v>
+        <v>2.04</v>
       </c>
       <c r="L3" t="n">
-        <v>54.5</v>
+        <v>57</v>
       </c>
       <c r="M3" t="n">
-        <v>336.49</v>
+        <v>336.48</v>
       </c>
       <c r="N3" t="n">
-        <v>360.55</v>
+        <v>363.58</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-16.9</v>
+        <v>-15.38</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>65.56999999999999</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="D4" t="n">
         <v>46.86</v>
       </c>
-      <c r="D4" t="n">
-        <v>47.07</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.45</v>
+        <v>0.13</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.57</v>
+        <v>0.92</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>-1.57</v>
       </c>
       <c r="H4" t="n">
-        <v>4902939</v>
+        <v>4468783</v>
       </c>
       <c r="I4" t="n">
-        <v>8220206</v>
+        <v>4904547</v>
       </c>
       <c r="J4" t="n">
         <v>0.24</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L4" t="n">
-        <v>53.4</v>
+        <v>53.7</v>
       </c>
       <c r="M4" t="n">
-        <v>40.99</v>
+        <v>41.06</v>
       </c>
       <c r="N4" t="n">
-        <v>45.65</v>
+        <v>45.76</v>
       </c>
       <c r="O4" t="n">
         <v>48.49</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.36</v>
+        <v>-3.24</v>
       </c>
       <c r="Q4" t="n">
         <v>28.46</v>
       </c>
       <c r="R4" t="n">
-        <v>64.65000000000001</v>
+        <v>64.86</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>286.95</v>
+      </c>
+      <c r="D5" t="n">
         <v>289</v>
       </c>
-      <c r="D5" t="n">
-        <v>287</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="F5" t="n">
-        <v>1.53</v>
+        <v>0.24</v>
       </c>
       <c r="G5" t="n">
-        <v>0.26</v>
+        <v>-0.62</v>
       </c>
       <c r="H5" t="n">
-        <v>12685347</v>
+        <v>11762170</v>
       </c>
       <c r="I5" t="n">
-        <v>45392755</v>
+        <v>12689243</v>
       </c>
       <c r="J5" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.64</v>
+        <v>-0.49</v>
       </c>
       <c r="L5" t="n">
-        <v>57.6</v>
+        <v>53.7</v>
       </c>
       <c r="M5" t="n">
-        <v>321.07</v>
+        <v>320.58</v>
       </c>
       <c r="N5" t="n">
-        <v>285.14</v>
+        <v>285.04</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-28.11</v>
+        <v>-28.62</v>
       </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
       <c r="R5" t="n">
-        <v>4.88</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>917.55</v>
+      </c>
+      <c r="D6" t="n">
         <v>917</v>
       </c>
-      <c r="D6" t="n">
-        <v>929.1</v>
-      </c>
       <c r="E6" t="n">
-        <v>-1.3</v>
+        <v>0.06</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.87</v>
+        <v>-1.97</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.61</v>
+        <v>-6.77</v>
       </c>
       <c r="H6" t="n">
-        <v>315242</v>
+        <v>240009</v>
       </c>
       <c r="I6" t="n">
-        <v>289116</v>
+        <v>315967</v>
       </c>
       <c r="J6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>1.77</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="M6" t="n">
-        <v>941.64</v>
+        <v>942.13</v>
       </c>
       <c r="N6" t="n">
-        <v>931.39</v>
+        <v>926.23</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-23.96</v>
+        <v>-23.92</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>16.05</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>69.59</v>
+      </c>
+      <c r="D7" t="n">
         <v>70.34999999999999</v>
       </c>
-      <c r="D7" t="n">
-        <v>71.14</v>
-      </c>
       <c r="E7" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="F7" t="n">
         <v>-1.11</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.33</v>
-      </c>
       <c r="G7" t="n">
-        <v>17.68</v>
+        <v>12.93</v>
       </c>
       <c r="H7" t="n">
-        <v>22529878</v>
+        <v>11302518</v>
       </c>
       <c r="I7" t="n">
-        <v>13435710</v>
+        <v>22530135</v>
       </c>
       <c r="J7" t="n">
-        <v>0.77</v>
+        <v>0.38</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.23</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>65.40000000000001</v>
+        <v>62</v>
       </c>
       <c r="M7" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="N7" t="n">
-        <v>60.68</v>
+        <v>60.98</v>
       </c>
       <c r="O7" t="n">
         <v>71.75</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.95</v>
+        <v>-3.01</v>
       </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
       <c r="R7" t="n">
-        <v>68.83</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>858.35</v>
+      </c>
+      <c r="D8" t="n">
         <v>845.5</v>
       </c>
-      <c r="D8" t="n">
-        <v>833.95</v>
-      </c>
       <c r="E8" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="F8" t="n">
-        <v>1.38</v>
+        <v>3.06</v>
       </c>
       <c r="G8" t="n">
-        <v>0.35</v>
+        <v>3.79</v>
       </c>
       <c r="H8" t="n">
-        <v>221654</v>
+        <v>216163</v>
       </c>
       <c r="I8" t="n">
-        <v>199791</v>
+        <v>221744</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="L8" t="n">
-        <v>53.2</v>
+        <v>57.5</v>
       </c>
       <c r="M8" t="n">
-        <v>746.59</v>
+        <v>746.8099999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>834.34</v>
+        <v>835.24</v>
       </c>
       <c r="O8" t="n">
         <v>865.55</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.32</v>
+        <v>-0.83</v>
       </c>
       <c r="Q8" t="n">
         <v>550.8</v>
       </c>
       <c r="R8" t="n">
-        <v>53.5</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="D10" t="n">
         <v>6.83</v>
       </c>
-      <c r="D10" t="n">
-        <v>6.35</v>
-      </c>
       <c r="E10" t="n">
-        <v>7.56</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>21.92</v>
       </c>
       <c r="G10" t="n">
-        <v>12.15</v>
+        <v>33.63</v>
       </c>
       <c r="H10" t="n">
+        <v>25749</v>
+      </c>
+      <c r="I10" t="n">
         <v>16647</v>
       </c>
-      <c r="I10" t="n">
-        <v>1407</v>
-      </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>4.47</v>
       </c>
       <c r="K10" t="n">
-        <v>3.32</v>
+        <v>2.99</v>
       </c>
       <c r="L10" t="n">
-        <v>53.1</v>
+        <v>62.8</v>
       </c>
       <c r="M10" t="n">
-        <v>9.380000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="N10" t="n">
-        <v>6.76</v>
+        <v>6.7</v>
       </c>
       <c r="O10" t="n">
         <v>14.69</v>
       </c>
       <c r="P10" t="n">
-        <v>-53.51</v>
+        <v>-48.88</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>29.11</v>
+        <v>41.97</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1044</v>
+      </c>
+      <c r="D11" t="n">
         <v>1036.3</v>
       </c>
-      <c r="D11" t="n">
-        <v>1020.7</v>
-      </c>
       <c r="E11" t="n">
-        <v>1.53</v>
+        <v>0.74</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.35</v>
+        <v>0.75</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="H11" t="n">
-        <v>1063626</v>
+        <v>454084</v>
       </c>
       <c r="I11" t="n">
-        <v>617990</v>
+        <v>1063672</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="K11" t="n">
-        <v>0.19</v>
+        <v>0.63</v>
       </c>
       <c r="L11" t="n">
-        <v>48.4</v>
+        <v>50.2</v>
       </c>
       <c r="M11" t="n">
-        <v>938.46</v>
+        <v>938.16</v>
       </c>
       <c r="N11" t="n">
-        <v>1055.69</v>
+        <v>1055.76</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.24</v>
+        <v>-6.55</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>51.82</v>
+        <v>52.94</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="D12" t="n">
         <v>22.41</v>
       </c>
-      <c r="D12" t="n">
-        <v>22.33</v>
-      </c>
       <c r="E12" t="n">
-        <v>0.36</v>
+        <v>-0.36</v>
       </c>
       <c r="F12" t="n">
-        <v>3.56</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9</v>
+        <v>-4.2</v>
       </c>
       <c r="H12" t="n">
-        <v>9969439</v>
+        <v>7148464</v>
       </c>
       <c r="I12" t="n">
-        <v>8155897</v>
+        <v>9970752</v>
       </c>
       <c r="J12" t="n">
-        <v>3.26</v>
+        <v>2.12</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.39</v>
+        <v>3.47</v>
       </c>
       <c r="L12" t="n">
-        <v>50.6</v>
+        <v>49.5</v>
       </c>
       <c r="M12" t="n">
-        <v>25.35</v>
+        <v>25.31</v>
       </c>
       <c r="N12" t="n">
-        <v>22.52</v>
+        <v>22.5</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-31.11</v>
+        <v>-31.36</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>4.28</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="13">
@@ -1096,37 +1096,37 @@
         <v>5.47</v>
       </c>
       <c r="D13" t="n">
-        <v>5.24</v>
+        <v>5.47</v>
       </c>
       <c r="E13" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4.19</v>
+        <v>3.99</v>
       </c>
       <c r="G13" t="n">
-        <v>1.86</v>
+        <v>-0.91</v>
       </c>
       <c r="H13" t="n">
-        <v>323780</v>
+        <v>156734</v>
       </c>
       <c r="I13" t="n">
-        <v>416008</v>
+        <v>323900</v>
       </c>
       <c r="J13" t="n">
-        <v>1.97</v>
+        <v>0.89</v>
       </c>
       <c r="K13" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="L13" t="n">
-        <v>56.3</v>
+        <v>56.7</v>
       </c>
       <c r="M13" t="n">
-        <v>6.14</v>
+        <v>6.11</v>
       </c>
       <c r="N13" t="n">
-        <v>5.5</v>
+        <v>5.48</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24624.65</v>
+      </c>
+      <c r="D17" t="n">
         <v>24614.9</v>
       </c>
-      <c r="D17" t="n">
-        <v>24774.3</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.64</v>
+        <v>0.04</v>
       </c>
       <c r="F17" t="n">
-        <v>2.62</v>
+        <v>1.54</v>
       </c>
       <c r="G17" t="n">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.57</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57739.95</v>
+      </c>
+      <c r="D18" t="n">
         <v>57907.2</v>
       </c>
-      <c r="D18" t="n">
-        <v>58247.95</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.58</v>
+        <v>-0.29</v>
       </c>
       <c r="F18" t="n">
-        <v>2.03</v>
+        <v>0.93</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.66</v>
+        <v>-0.79</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.55</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>79.66</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>83.77</v>
+        <v>79.36</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.91</v>
+        <v>0.37</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.27</v>
+        <v>-12.22</v>
       </c>
       <c r="G19" t="n">
-        <v>10.65</v>
+        <v>7.4</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4150.4</v>
+        <v>4293</v>
       </c>
       <c r="D20" t="n">
-        <v>4033.7</v>
+        <v>4095.4</v>
       </c>
       <c r="E20" t="n">
-        <v>2.89</v>
+        <v>4.82</v>
       </c>
       <c r="F20" t="n">
-        <v>2.83</v>
+        <v>6.4</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.11</v>
+        <v>3.56</v>
       </c>
       <c r="H20" t="n">
-        <v>3.53</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>54173.91</v>
+        <v>54544.79</v>
       </c>
       <c r="D21" t="n">
-        <v>53178.41</v>
+        <v>54085.88</v>
       </c>
       <c r="E21" t="n">
-        <v>1.87</v>
+        <v>0.85</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7</v>
+        <v>5.72</v>
       </c>
       <c r="G21" t="n">
-        <v>2.11</v>
+        <v>3.06</v>
       </c>
       <c r="H21" t="n">
-        <v>1.93</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="D22" t="n">
         <v>12.19</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.93</v>
-      </c>
       <c r="E22" t="n">
-        <v>2.18</v>
+        <v>-1.07</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.95</v>
+        <v>0.42</v>
       </c>
       <c r="G22" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="H22" t="n">
-        <v/>
+        <v>3.52</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1626,6 +1623,29 @@
       </c>
       <c r="G10" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57739.95</v>
+      </c>
+      <c r="C11" t="n">
+        <v>57907.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>
@@ -1639,7 +1659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1884,6 +1904,29 @@
       </c>
       <c r="G10" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79.65000000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>79.36</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-12.22</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1897,7 +1940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2142,6 +2185,29 @@
       </c>
       <c r="G10" t="n">
         <v>3.53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4293</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4095.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.78</v>
       </c>
     </row>
   </sheetData>
@@ -2155,7 +2221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2400,6 +2466,29 @@
       </c>
       <c r="G10" t="n">
         <v>1.93</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>54544.79</v>
+      </c>
+      <c r="C11" t="n">
+        <v>54085.88</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2413,7 +2502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2632,8 +2721,25 @@
       <c r="F10" t="n">
         <v>3.13</v>
       </c>
-      <c r="G10" t="n">
-        <v/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="C11" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.52</v>
       </c>
     </row>
   </sheetData>
@@ -2647,7 +2753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3132,6 +3238,59 @@
       </c>
       <c r="Q9" t="n">
         <v>29.11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="F10" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="G10" t="n">
+        <v>25749</v>
+      </c>
+      <c r="H10" t="n">
+        <v>16647</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K10" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-48.88</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>41.97</v>
       </c>
     </row>
   </sheetData>
@@ -3145,7 +3304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3630,6 +3789,59 @@
       </c>
       <c r="Q9" t="n">
         <v>4.28</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B10" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7148464</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9970752</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="K10" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="M10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-31.36</v>
+      </c>
+      <c r="P10" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.91</v>
       </c>
     </row>
   </sheetData>
@@ -3643,7 +3855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3988,7 +4200,7 @@
         <v>-0.57</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>4902939</v>
@@ -4022,6 +4234,59 @@
       </c>
       <c r="Q7" t="n">
         <v>64.65000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B8" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="C8" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4468783</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4904547</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="M8" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="N8" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="P8" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>64.86</v>
       </c>
     </row>
   </sheetData>
@@ -4035,7 +4300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4573,6 +4838,59 @@
       </c>
       <c r="Q10" t="n">
         <v>65.56999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>405.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>398.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>433335</v>
+      </c>
+      <c r="H11" t="n">
+        <v>303618</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K11" t="n">
+        <v>57</v>
+      </c>
+      <c r="L11" t="n">
+        <v>336.48</v>
+      </c>
+      <c r="M11" t="n">
+        <v>363.58</v>
+      </c>
+      <c r="N11" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-15.38</v>
+      </c>
+      <c r="P11" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>68.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4586,7 +4904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5124,6 +5442,59 @@
       </c>
       <c r="Q10" t="n">
         <v>4.88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>286.95</v>
+      </c>
+      <c r="C11" t="n">
+        <v>289</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11762170</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12689243</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="K11" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>320.58</v>
+      </c>
+      <c r="M11" t="n">
+        <v>285.04</v>
+      </c>
+      <c r="N11" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-28.62</v>
+      </c>
+      <c r="P11" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.14</v>
       </c>
     </row>
   </sheetData>
@@ -5137,7 +5508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5675,6 +6046,59 @@
       </c>
       <c r="Q10" t="n">
         <v>16.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>917.55</v>
+      </c>
+      <c r="C11" t="n">
+        <v>917</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-6.77</v>
+      </c>
+      <c r="G11" t="n">
+        <v>240009</v>
+      </c>
+      <c r="H11" t="n">
+        <v>315967</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>942.13</v>
+      </c>
+      <c r="M11" t="n">
+        <v>926.23</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-23.92</v>
+      </c>
+      <c r="P11" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>16.12</v>
       </c>
     </row>
   </sheetData>
@@ -5688,7 +6112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6226,6 +6650,59 @@
       </c>
       <c r="Q10" t="n">
         <v>51.82</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1044</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1036.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>454084</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1063672</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K11" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>938.16</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1055.76</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-6.55</v>
+      </c>
+      <c r="P11" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>52.94</v>
       </c>
     </row>
   </sheetData>
@@ -6239,7 +6716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6777,6 +7254,59 @@
       </c>
       <c r="Q10" t="n">
         <v>68.83</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>69.59</v>
+      </c>
+      <c r="C11" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11302518</v>
+      </c>
+      <c r="H11" t="n">
+        <v>22530135</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="K11" t="n">
+        <v>62</v>
+      </c>
+      <c r="L11" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>60.98</v>
+      </c>
+      <c r="N11" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="P11" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -6790,7 +7320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7327,6 +7857,59 @@
         <v>4.18</v>
       </c>
       <c r="Q10" t="n">
+        <v>30.86</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="G11" t="n">
+        <v>156734</v>
+      </c>
+      <c r="H11" t="n">
+        <v>323900</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-43.72</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q11" t="n">
         <v>30.86</v>
       </c>
     </row>
@@ -7341,7 +7924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7879,6 +8462,59 @@
       </c>
       <c r="Q10" t="n">
         <v>53.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>858.35</v>
+      </c>
+      <c r="C11" t="n">
+        <v>845.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="G11" t="n">
+        <v>216163</v>
+      </c>
+      <c r="H11" t="n">
+        <v>221744</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K11" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>746.8099999999999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>835.24</v>
+      </c>
+      <c r="N11" t="n">
+        <v>865.55</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="P11" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>55.84</v>
       </c>
     </row>
   </sheetData>
@@ -7892,7 +8528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8139,6 +8775,29 @@
         <v>-0.57</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>24624.65</v>
+      </c>
+      <c r="C11" t="n">
+        <v>24614.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>405.6</v>
+        <v>401.9</v>
       </c>
       <c r="D3" t="n">
-        <v>398.3</v>
+        <v>405</v>
       </c>
       <c r="E3" t="n">
-        <v>1.83</v>
+        <v>-0.77</v>
       </c>
       <c r="F3" t="n">
-        <v>2.97</v>
+        <v>4.48</v>
       </c>
       <c r="G3" t="n">
-        <v>14.61</v>
+        <v>14.68</v>
       </c>
       <c r="H3" t="n">
-        <v>433335</v>
+        <v>152336</v>
       </c>
       <c r="I3" t="n">
-        <v>303618</v>
+        <v>231635</v>
       </c>
       <c r="J3" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="K3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>57</v>
+        <v>55.2</v>
       </c>
       <c r="M3" t="n">
-        <v>336.48</v>
+        <v>336.57</v>
       </c>
       <c r="N3" t="n">
-        <v>363.58</v>
+        <v>365.3</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-15.38</v>
+        <v>-16.15</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>68.59999999999999</v>
+        <v>67.06</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>46.92</v>
+        <v>47.17</v>
       </c>
       <c r="D4" t="n">
-        <v>46.86</v>
+        <v>47.43</v>
       </c>
       <c r="E4" t="n">
-        <v>0.13</v>
+        <v>-0.55</v>
       </c>
       <c r="F4" t="n">
-        <v>0.92</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.57</v>
+        <v>6.67</v>
       </c>
       <c r="H4" t="n">
-        <v>4468783</v>
+        <v>3894243</v>
       </c>
       <c r="I4" t="n">
-        <v>4904547</v>
+        <v>10025026</v>
       </c>
       <c r="J4" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6</v>
+        <v>0.39</v>
       </c>
       <c r="L4" t="n">
-        <v>53.7</v>
+        <v>54.7</v>
       </c>
       <c r="M4" t="n">
-        <v>41.06</v>
+        <v>41.18</v>
       </c>
       <c r="N4" t="n">
-        <v>45.76</v>
+        <v>46</v>
       </c>
       <c r="O4" t="n">
         <v>48.49</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.24</v>
+        <v>-2.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>28.46</v>
+        <v>28.59</v>
       </c>
       <c r="R4" t="n">
-        <v>64.86</v>
+        <v>64.98999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>286.95</v>
+        <v>286.1</v>
       </c>
       <c r="D5" t="n">
-        <v>289</v>
+        <v>285.9</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.71</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.24</v>
+        <v>1.81</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.62</v>
+        <v>1.44</v>
       </c>
       <c r="H5" t="n">
-        <v>11762170</v>
+        <v>6124188</v>
       </c>
       <c r="I5" t="n">
-        <v>12689243</v>
+        <v>12447629</v>
       </c>
       <c r="J5" t="n">
-        <v>0.71</v>
+        <v>0.38</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.49</v>
+        <v>-0.6</v>
       </c>
       <c r="L5" t="n">
-        <v>53.7</v>
+        <v>52.2</v>
       </c>
       <c r="M5" t="n">
-        <v>320.58</v>
+        <v>319.5</v>
       </c>
       <c r="N5" t="n">
-        <v>285.04</v>
+        <v>284.9</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-28.62</v>
+        <v>-28.83</v>
       </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
       <c r="R5" t="n">
-        <v>4.14</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>917.55</v>
+        <v>916.65</v>
       </c>
       <c r="D6" t="n">
-        <v>917</v>
+        <v>912.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06</v>
+        <v>0.45</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.97</v>
+        <v>-0.04</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.77</v>
+        <v>-4.67</v>
       </c>
       <c r="H6" t="n">
-        <v>240009</v>
+        <v>168435</v>
       </c>
       <c r="I6" t="n">
-        <v>315967</v>
+        <v>209740</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="K6" t="n">
-        <v>1.77</v>
+        <v>0.38</v>
       </c>
       <c r="L6" t="n">
-        <v>42.9</v>
+        <v>43.2</v>
       </c>
       <c r="M6" t="n">
-        <v>942.13</v>
+        <v>943.01</v>
       </c>
       <c r="N6" t="n">
-        <v>926.23</v>
+        <v>918.98</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-23.92</v>
+        <v>-23.99</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>16.12</v>
+        <v>16.01</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>69.59</v>
+        <v>70.11</v>
       </c>
       <c r="D7" t="n">
-        <v>70.34999999999999</v>
+        <v>72.05</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.08</v>
+        <v>-2.69</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.11</v>
+        <v>-2.29</v>
       </c>
       <c r="G7" t="n">
-        <v>12.93</v>
+        <v>12.03</v>
       </c>
       <c r="H7" t="n">
-        <v>11302518</v>
+        <v>8652553</v>
       </c>
       <c r="I7" t="n">
-        <v>22530135</v>
+        <v>16057454</v>
       </c>
       <c r="J7" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="L7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M7" t="n">
-        <v>57.5</v>
+        <v>57.71</v>
       </c>
       <c r="N7" t="n">
-        <v>60.98</v>
+        <v>61.65</v>
       </c>
       <c r="O7" t="n">
-        <v>71.75</v>
+        <v>72.05</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.01</v>
+        <v>-2.69</v>
       </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
       <c r="R7" t="n">
-        <v>67</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>858.35</v>
+        <v>870.5</v>
       </c>
       <c r="D8" t="n">
-        <v>845.5</v>
+        <v>871.45</v>
       </c>
       <c r="E8" t="n">
-        <v>1.52</v>
+        <v>-0.11</v>
       </c>
       <c r="F8" t="n">
-        <v>3.06</v>
+        <v>6.36</v>
       </c>
       <c r="G8" t="n">
-        <v>3.79</v>
+        <v>6.04</v>
       </c>
       <c r="H8" t="n">
-        <v>216163</v>
+        <v>161734</v>
       </c>
       <c r="I8" t="n">
-        <v>221744</v>
+        <v>342884</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K8" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="L8" t="n">
-        <v>57.5</v>
+        <v>60.9</v>
       </c>
       <c r="M8" t="n">
-        <v>746.8099999999999</v>
+        <v>747.35</v>
       </c>
       <c r="N8" t="n">
-        <v>835.24</v>
+        <v>837.88</v>
       </c>
       <c r="O8" t="n">
-        <v>865.55</v>
+        <v>871.45</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.83</v>
+        <v>-0.11</v>
       </c>
       <c r="Q8" t="n">
         <v>550.8</v>
       </c>
       <c r="R8" t="n">
-        <v>55.84</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.51</v>
+        <v>7.55</v>
       </c>
       <c r="D10" t="n">
-        <v>6.83</v>
+        <v>7.9</v>
       </c>
       <c r="E10" t="n">
-        <v>9.960000000000001</v>
+        <v>-4.43</v>
       </c>
       <c r="F10" t="n">
-        <v>21.92</v>
+        <v>22.17</v>
       </c>
       <c r="G10" t="n">
-        <v>33.63</v>
+        <v>30.17</v>
       </c>
       <c r="H10" t="n">
-        <v>25749</v>
+        <v>956</v>
       </c>
       <c r="I10" t="n">
-        <v>16647</v>
+        <v>8431</v>
       </c>
       <c r="J10" t="n">
-        <v>4.47</v>
+        <v>0.17</v>
       </c>
       <c r="K10" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>62.8</v>
+        <v>59.8</v>
       </c>
       <c r="M10" t="n">
-        <v>9.32</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>6.7</v>
+        <v>6.72</v>
       </c>
       <c r="O10" t="n">
         <v>14.69</v>
       </c>
       <c r="P10" t="n">
-        <v>-48.88</v>
+        <v>-48.6</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>41.97</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1044</v>
+        <v>1047.2</v>
       </c>
       <c r="D11" t="n">
-        <v>1036.3</v>
+        <v>1041.7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
       <c r="F11" t="n">
-        <v>0.75</v>
+        <v>6.56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9</v>
+        <v>0.32</v>
       </c>
       <c r="H11" t="n">
-        <v>454084</v>
+        <v>2579319</v>
       </c>
       <c r="I11" t="n">
-        <v>1063672</v>
+        <v>589524</v>
       </c>
       <c r="J11" t="n">
-        <v>0.35</v>
+        <v>2.21</v>
       </c>
       <c r="K11" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="L11" t="n">
-        <v>50.2</v>
+        <v>50.7</v>
       </c>
       <c r="M11" t="n">
-        <v>938.16</v>
+        <v>938.17</v>
       </c>
       <c r="N11" t="n">
-        <v>1055.76</v>
+        <v>1056.17</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.55</v>
+        <v>-6.27</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>52.94</v>
+        <v>53.41</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.33</v>
+        <v>22.17</v>
       </c>
       <c r="D12" t="n">
-        <v>22.41</v>
+        <v>22.12</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.36</v>
+        <v>0.23</v>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>1.37</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2</v>
+        <v>-1.95</v>
       </c>
       <c r="H12" t="n">
-        <v>7148464</v>
+        <v>2663854</v>
       </c>
       <c r="I12" t="n">
-        <v>9970752</v>
+        <v>5113131</v>
       </c>
       <c r="J12" t="n">
-        <v>2.12</v>
+        <v>0.72</v>
       </c>
       <c r="K12" t="n">
-        <v>3.47</v>
+        <v>1.13</v>
       </c>
       <c r="L12" t="n">
-        <v>49.5</v>
+        <v>47.3</v>
       </c>
       <c r="M12" t="n">
-        <v>25.31</v>
+        <v>25.24</v>
       </c>
       <c r="N12" t="n">
-        <v>22.5</v>
+        <v>22.46</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-31.36</v>
+        <v>-31.85</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>3.91</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="13">
@@ -1093,37 +1093,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.47</v>
+        <v>5.32</v>
       </c>
       <c r="D13" t="n">
-        <v>5.47</v>
+        <v>5.3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="F13" t="n">
-        <v>3.99</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.91</v>
+        <v>-2.92</v>
       </c>
       <c r="H13" t="n">
-        <v>156734</v>
+        <v>93525</v>
       </c>
       <c r="I13" t="n">
-        <v>323900</v>
+        <v>234713</v>
       </c>
       <c r="J13" t="n">
-        <v>0.89</v>
+        <v>0.54</v>
       </c>
       <c r="K13" t="n">
-        <v>2.09</v>
+        <v>-0.39</v>
       </c>
       <c r="L13" t="n">
-        <v>56.7</v>
+        <v>47.9</v>
       </c>
       <c r="M13" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="N13" t="n">
         <v>5.48</v>
@@ -1132,13 +1132,13 @@
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-43.72</v>
+        <v>-45.27</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>30.86</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24624.65</v>
+        <v>24570.65</v>
       </c>
       <c r="D17" t="n">
-        <v>24614.9</v>
+        <v>24636</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04</v>
+        <v>-0.27</v>
       </c>
       <c r="F17" t="n">
-        <v>1.54</v>
+        <v>0.77</v>
       </c>
       <c r="G17" t="n">
-        <v>0.93</v>
+        <v>2.54</v>
       </c>
       <c r="H17" t="n">
-        <v>0.44</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57739.95</v>
+        <v>57746.45</v>
       </c>
       <c r="D18" t="n">
-        <v>57907.2</v>
+        <v>58063.65</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.29</v>
+        <v>-0.55</v>
       </c>
       <c r="F18" t="n">
-        <v>0.93</v>
+        <v>0.84</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.79</v>
+        <v>0.86</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.31</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>79.65000000000001</v>
+        <v>82.87</v>
       </c>
       <c r="D19" t="n">
-        <v>79.36</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="F19" t="n">
-        <v>-12.22</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>7.4</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.25</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4293</v>
+        <v>4397</v>
       </c>
       <c r="D20" t="n">
-        <v>4095.4</v>
+        <v>4242</v>
       </c>
       <c r="E20" t="n">
-        <v>4.82</v>
+        <v>3.65</v>
       </c>
       <c r="F20" t="n">
-        <v>6.4</v>
+        <v>8.59</v>
       </c>
       <c r="G20" t="n">
-        <v>3.56</v>
+        <v>6.45</v>
       </c>
       <c r="H20" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>54544.79</v>
+        <v>53987.31</v>
       </c>
       <c r="D21" t="n">
-        <v>54085.88</v>
+        <v>53885.1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.85</v>
+        <v>0.19</v>
       </c>
       <c r="F21" t="n">
-        <v>5.72</v>
+        <v>2.86</v>
       </c>
       <c r="G21" t="n">
-        <v>3.06</v>
+        <v>2.86</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12.06</v>
+        <v>12.16</v>
       </c>
       <c r="D22" t="n">
-        <v>12.19</v>
+        <v>12.16</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.07</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.42</v>
+        <v>3.4</v>
       </c>
       <c r="G22" t="n">
-        <v>3.52</v>
+        <v>-8.98</v>
+      </c>
+      <c r="H22" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,6 +1649,52 @@
       </c>
       <c r="G11" t="n">
         <v>-0.31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58063.65</v>
+      </c>
+      <c r="C12" t="n">
+        <v>57739.95</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57746.45</v>
+      </c>
+      <c r="C13" t="n">
+        <v>58063.65</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -1659,7 +1708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1927,6 +1976,52 @@
       </c>
       <c r="G11" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>82.87</v>
+      </c>
+      <c r="C13" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -1940,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2208,6 +2303,52 @@
       </c>
       <c r="G11" t="n">
         <v>1.78</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4242</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4245.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4397</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4242</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
@@ -2221,7 +2362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2489,6 +2630,52 @@
       </c>
       <c r="G11" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>53885.1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>54349.12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>53987.31</v>
+      </c>
+      <c r="C13" t="n">
+        <v>53885.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>
@@ -2502,7 +2689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2740,6 +2927,49 @@
       </c>
       <c r="F11" t="n">
         <v>3.52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-17.17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-8.98</v>
+      </c>
+      <c r="G13" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2753,7 +2983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3291,6 +3521,112 @@
       </c>
       <c r="Q10" t="n">
         <v>41.97</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E11" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="F11" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8431</v>
+      </c>
+      <c r="H11" t="n">
+        <v>25749</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="N11" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-46.22</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>49.34</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B12" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="E12" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="G12" t="n">
+        <v>956</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8431</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="N12" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-48.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>42.72</v>
       </c>
     </row>
   </sheetData>
@@ -3304,7 +3640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3842,6 +4178,112 @@
       </c>
       <c r="Q10" t="n">
         <v>3.91</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B11" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="C11" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5113131</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7156235</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="K11" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="M11" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="N11" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-32</v>
+      </c>
+      <c r="P11" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B12" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="C12" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2663854</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5113131</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="K12" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="M12" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="N12" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-31.85</v>
+      </c>
+      <c r="P12" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.16</v>
       </c>
     </row>
   </sheetData>
@@ -3855,7 +4297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4287,6 +4729,112 @@
       </c>
       <c r="Q8" t="n">
         <v>64.86</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B9" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="C9" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10025026</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4470613</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K9" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>45.89</v>
+      </c>
+      <c r="N9" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="P9" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>65.90000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B10" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="C10" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3894243</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10025026</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K10" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="M10" t="n">
+        <v>46</v>
+      </c>
+      <c r="N10" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="P10" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>64.98999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4300,7 +4848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4891,6 +5439,112 @@
       </c>
       <c r="Q11" t="n">
         <v>68.59999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>405</v>
+      </c>
+      <c r="C12" t="n">
+        <v>405.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="G12" t="n">
+        <v>231635</v>
+      </c>
+      <c r="H12" t="n">
+        <v>433844</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K12" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>336.53</v>
+      </c>
+      <c r="M12" t="n">
+        <v>363.77</v>
+      </c>
+      <c r="N12" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-15.51</v>
+      </c>
+      <c r="P12" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>68.34999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>401.9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>405</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="G13" t="n">
+        <v>152336</v>
+      </c>
+      <c r="H13" t="n">
+        <v>231635</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>336.57</v>
+      </c>
+      <c r="M13" t="n">
+        <v>365.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-16.15</v>
+      </c>
+      <c r="P13" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>67.06</v>
       </c>
     </row>
   </sheetData>
@@ -4904,7 +5558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5495,6 +6149,112 @@
       </c>
       <c r="Q11" t="n">
         <v>4.14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>286.95</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12447629</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11771241</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="K12" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>320.04</v>
+      </c>
+      <c r="M12" t="n">
+        <v>284.92</v>
+      </c>
+      <c r="N12" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-28.88</v>
+      </c>
+      <c r="P12" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6124188</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12447629</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>284.9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-28.83</v>
+      </c>
+      <c r="P13" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.83</v>
       </c>
     </row>
   </sheetData>
@@ -5508,7 +6268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6099,6 +6859,112 @@
       </c>
       <c r="Q11" t="n">
         <v>16.12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>912.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>917.55</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="G12" t="n">
+        <v>209740</v>
+      </c>
+      <c r="H12" t="n">
+        <v>240030</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K12" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>942.58</v>
+      </c>
+      <c r="M12" t="n">
+        <v>920.96</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-24.34</v>
+      </c>
+      <c r="P12" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>15.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>916.65</v>
+      </c>
+      <c r="C13" t="n">
+        <v>912.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-4.67</v>
+      </c>
+      <c r="G13" t="n">
+        <v>168435</v>
+      </c>
+      <c r="H13" t="n">
+        <v>209740</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K13" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>943.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>918.98</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-23.99</v>
+      </c>
+      <c r="P13" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>16.01</v>
       </c>
     </row>
   </sheetData>
@@ -6112,7 +6978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6703,6 +7569,112 @@
       </c>
       <c r="Q11" t="n">
         <v>52.94</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1041.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1044</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G12" t="n">
+        <v>589524</v>
+      </c>
+      <c r="H12" t="n">
+        <v>454099</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>938.26</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1056.15</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-6.76</v>
+      </c>
+      <c r="P12" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>52.61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1047.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1041.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2579319</v>
+      </c>
+      <c r="H13" t="n">
+        <v>589524</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K13" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>938.17</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1056.17</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="P13" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>53.41</v>
       </c>
     </row>
   </sheetData>
@@ -6716,7 +7688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7307,6 +8279,112 @@
       </c>
       <c r="Q11" t="n">
         <v>67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="C12" t="n">
+        <v>69.59</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F12" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16057454</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11303955</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K12" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="M12" t="n">
+        <v>61.33</v>
+      </c>
+      <c r="N12" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>72.91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>70.11</v>
+      </c>
+      <c r="C13" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8652553</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16057454</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="K13" t="n">
+        <v>60</v>
+      </c>
+      <c r="L13" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="M13" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="N13" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="P13" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>68.25</v>
       </c>
     </row>
   </sheetData>
@@ -7320,7 +8398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7911,6 +8989,112 @@
       </c>
       <c r="Q11" t="n">
         <v>30.86</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-3.11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="G12" t="n">
+        <v>234713</v>
+      </c>
+      <c r="H12" t="n">
+        <v>156734</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K12" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-45.47</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>26.79</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="G13" t="n">
+        <v>93525</v>
+      </c>
+      <c r="H13" t="n">
+        <v>234713</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="K13" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="N13" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-45.27</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>27.27</v>
       </c>
     </row>
   </sheetData>
@@ -7924,7 +9108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8515,6 +9699,112 @@
       </c>
       <c r="Q11" t="n">
         <v>55.84</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>871.45</v>
+      </c>
+      <c r="C12" t="n">
+        <v>858.35</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="G12" t="n">
+        <v>342884</v>
+      </c>
+      <c r="H12" t="n">
+        <v>216163</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="K12" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>747.11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>836.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>871.45</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>58.22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>871.45</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>161734</v>
+      </c>
+      <c r="H13" t="n">
+        <v>342884</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K13" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>747.35</v>
+      </c>
+      <c r="M13" t="n">
+        <v>837.88</v>
+      </c>
+      <c r="N13" t="n">
+        <v>871.45</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="P13" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>58.04</v>
       </c>
     </row>
   </sheetData>
@@ -8528,7 +9818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8798,6 +10088,52 @@
         <v>0.44</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>24636</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24624.65</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>24570.65</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24636</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>422.85</v>
+      </c>
+      <c r="D3" t="n">
         <v>401.9</v>
       </c>
-      <c r="D3" t="n">
-        <v>405</v>
-      </c>
       <c r="E3" t="n">
-        <v>-0.77</v>
+        <v>5.21</v>
       </c>
       <c r="F3" t="n">
-        <v>4.48</v>
+        <v>5.07</v>
       </c>
       <c r="G3" t="n">
-        <v>14.68</v>
+        <v>17.38</v>
       </c>
       <c r="H3" t="n">
-        <v>152336</v>
+        <v>1226108</v>
       </c>
       <c r="I3" t="n">
-        <v>231635</v>
+        <v>152556</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06</v>
+        <v>0.51</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="L3" t="n">
-        <v>55.2</v>
+        <v>61.9</v>
       </c>
       <c r="M3" t="n">
-        <v>336.57</v>
+        <v>336.7</v>
       </c>
       <c r="N3" t="n">
-        <v>365.3</v>
+        <v>367.41</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-16.15</v>
+        <v>-11.78</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>67.06</v>
+        <v>75.77</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46</v>
+      </c>
+      <c r="D4" t="n">
         <v>47.17</v>
       </c>
-      <c r="D4" t="n">
-        <v>47.43</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.55</v>
+        <v>-2.48</v>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>-2.27</v>
       </c>
       <c r="G4" t="n">
-        <v>6.67</v>
+        <v>0.41</v>
       </c>
       <c r="H4" t="n">
-        <v>3894243</v>
+        <v>10925959</v>
       </c>
       <c r="I4" t="n">
-        <v>10025026</v>
+        <v>3899463</v>
       </c>
       <c r="J4" t="n">
-        <v>0.26</v>
+        <v>0.79</v>
       </c>
       <c r="K4" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>54.7</v>
+        <v>47.4</v>
       </c>
       <c r="M4" t="n">
-        <v>41.18</v>
+        <v>41.22</v>
       </c>
       <c r="N4" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="O4" t="n">
         <v>48.49</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.72</v>
+        <v>-5.14</v>
       </c>
       <c r="Q4" t="n">
         <v>28.59</v>
       </c>
       <c r="R4" t="n">
-        <v>64.98999999999999</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>282.65</v>
+      </c>
+      <c r="D5" t="n">
         <v>286.1</v>
       </c>
-      <c r="D5" t="n">
-        <v>285.9</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.21</v>
       </c>
       <c r="F5" t="n">
-        <v>1.81</v>
+        <v>-1.52</v>
       </c>
       <c r="G5" t="n">
-        <v>1.44</v>
+        <v>0.32</v>
       </c>
       <c r="H5" t="n">
-        <v>6124188</v>
+        <v>9325475</v>
       </c>
       <c r="I5" t="n">
-        <v>12447629</v>
+        <v>6128841</v>
       </c>
       <c r="J5" t="n">
-        <v>0.38</v>
+        <v>0.59</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.2</v>
+        <v>45.9</v>
       </c>
       <c r="M5" t="n">
-        <v>319.5</v>
+        <v>318.95</v>
       </c>
       <c r="N5" t="n">
-        <v>284.9</v>
+        <v>284.96</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-28.83</v>
+        <v>-29.69</v>
       </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
       <c r="R5" t="n">
-        <v>3.83</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>910.5</v>
+      </c>
+      <c r="D6" t="n">
         <v>916.65</v>
       </c>
-      <c r="D6" t="n">
-        <v>912.5</v>
-      </c>
       <c r="E6" t="n">
-        <v>0.45</v>
+        <v>-0.67</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.04</v>
+        <v>-2</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.67</v>
+        <v>-7.48</v>
       </c>
       <c r="H6" t="n">
-        <v>168435</v>
+        <v>198817</v>
       </c>
       <c r="I6" t="n">
-        <v>209740</v>
+        <v>168655</v>
       </c>
       <c r="J6" t="n">
-        <v>0.49</v>
+        <v>0.63</v>
       </c>
       <c r="K6" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="L6" t="n">
-        <v>43.2</v>
+        <v>41.2</v>
       </c>
       <c r="M6" t="n">
-        <v>943.01</v>
+        <v>943.36</v>
       </c>
       <c r="N6" t="n">
-        <v>918.98</v>
+        <v>918.52</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-23.99</v>
+        <v>-24.5</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>16.01</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>69.76000000000001</v>
+      </c>
+      <c r="D7" t="n">
         <v>70.11</v>
       </c>
-      <c r="D7" t="n">
-        <v>72.05</v>
-      </c>
       <c r="E7" t="n">
-        <v>-2.69</v>
+        <v>-0.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.29</v>
+        <v>-1.94</v>
       </c>
       <c r="G7" t="n">
-        <v>12.03</v>
+        <v>6.88</v>
       </c>
       <c r="H7" t="n">
-        <v>8652553</v>
+        <v>6796352</v>
       </c>
       <c r="I7" t="n">
-        <v>16057454</v>
+        <v>8655583</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.08</v>
+        <v>0.72</v>
       </c>
       <c r="L7" t="n">
-        <v>60</v>
+        <v>58.7</v>
       </c>
       <c r="M7" t="n">
-        <v>57.71</v>
+        <v>57.81</v>
       </c>
       <c r="N7" t="n">
-        <v>61.65</v>
+        <v>61.96</v>
       </c>
       <c r="O7" t="n">
         <v>72.05</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.69</v>
+        <v>-3.18</v>
       </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
       <c r="R7" t="n">
-        <v>68.25</v>
+        <v>67.41</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>898.75</v>
+      </c>
+      <c r="D8" t="n">
         <v>870.5</v>
       </c>
-      <c r="D8" t="n">
-        <v>871.45</v>
-      </c>
       <c r="E8" t="n">
-        <v>-0.11</v>
+        <v>3.25</v>
       </c>
       <c r="F8" t="n">
-        <v>6.36</v>
+        <v>7.77</v>
       </c>
       <c r="G8" t="n">
-        <v>6.04</v>
+        <v>8.32</v>
       </c>
       <c r="H8" t="n">
-        <v>161734</v>
+        <v>1064015</v>
       </c>
       <c r="I8" t="n">
-        <v>342884</v>
+        <v>161744</v>
       </c>
       <c r="J8" t="n">
-        <v>0.75</v>
+        <v>4.93</v>
       </c>
       <c r="K8" t="n">
-        <v>0.13</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>60.9</v>
+        <v>68.2</v>
       </c>
       <c r="M8" t="n">
-        <v>747.35</v>
+        <v>747.7</v>
       </c>
       <c r="N8" t="n">
-        <v>837.88</v>
+        <v>840</v>
       </c>
       <c r="O8" t="n">
-        <v>871.45</v>
+        <v>898.75</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>550.8</v>
       </c>
       <c r="R8" t="n">
-        <v>58.04</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="D10" t="n">
         <v>7.55</v>
       </c>
-      <c r="D10" t="n">
-        <v>7.9</v>
-      </c>
       <c r="E10" t="n">
-        <v>-4.43</v>
+        <v>4.9</v>
       </c>
       <c r="F10" t="n">
-        <v>22.17</v>
+        <v>24.72</v>
       </c>
       <c r="G10" t="n">
-        <v>30.17</v>
+        <v>24.14</v>
       </c>
       <c r="H10" t="n">
+        <v>9166</v>
+      </c>
+      <c r="I10" t="n">
         <v>956</v>
       </c>
-      <c r="I10" t="n">
-        <v>8431</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.17</v>
+        <v>1.74</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="L10" t="n">
-        <v>59.8</v>
+        <v>63.6</v>
       </c>
       <c r="M10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>6.72</v>
+        <v>6.71</v>
       </c>
       <c r="O10" t="n">
         <v>14.69</v>
       </c>
       <c r="P10" t="n">
-        <v>-48.6</v>
+        <v>-46.09</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>42.72</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1044.1</v>
+      </c>
+      <c r="D11" t="n">
         <v>1047.2</v>
       </c>
-      <c r="D11" t="n">
-        <v>1041.7</v>
-      </c>
       <c r="E11" t="n">
-        <v>0.53</v>
+        <v>-0.3</v>
       </c>
       <c r="F11" t="n">
-        <v>6.56</v>
+        <v>2.29</v>
       </c>
       <c r="G11" t="n">
-        <v>0.32</v>
+        <v>-4.14</v>
       </c>
       <c r="H11" t="n">
-        <v>2579319</v>
+        <v>1171702</v>
       </c>
       <c r="I11" t="n">
-        <v>589524</v>
+        <v>2579738</v>
       </c>
       <c r="J11" t="n">
-        <v>2.21</v>
+        <v>0.98</v>
       </c>
       <c r="K11" t="n">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="L11" t="n">
-        <v>50.7</v>
+        <v>49.9</v>
       </c>
       <c r="M11" t="n">
-        <v>938.17</v>
+        <v>938.14</v>
       </c>
       <c r="N11" t="n">
-        <v>1056.17</v>
+        <v>1055.83</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.27</v>
+        <v>-6.54</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>53.41</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="12">
@@ -1033,37 +1033,37 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="D12" t="n">
         <v>22.17</v>
       </c>
-      <c r="D12" t="n">
-        <v>22.12</v>
-      </c>
       <c r="E12" t="n">
-        <v>0.23</v>
+        <v>1.22</v>
       </c>
       <c r="F12" t="n">
-        <v>1.37</v>
+        <v>0.49</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.95</v>
+        <v>-1.28</v>
       </c>
       <c r="H12" t="n">
-        <v>2663854</v>
+        <v>5020464</v>
       </c>
       <c r="I12" t="n">
-        <v>5113131</v>
+        <v>2663872</v>
       </c>
       <c r="J12" t="n">
-        <v>0.72</v>
+        <v>1.35</v>
       </c>
       <c r="K12" t="n">
-        <v>1.13</v>
+        <v>0.27</v>
       </c>
       <c r="L12" t="n">
-        <v>47.3</v>
+        <v>51.6</v>
       </c>
       <c r="M12" t="n">
-        <v>25.24</v>
+        <v>25.2</v>
       </c>
       <c r="N12" t="n">
         <v>22.46</v>
@@ -1072,13 +1072,13 @@
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-31.85</v>
+        <v>-31.02</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>3.16</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.32</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.3</v>
-      </c>
       <c r="E13" t="n">
-        <v>0.38</v>
+        <v>1.5</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.92</v>
+        <v>-0.55</v>
       </c>
       <c r="H13" t="n">
+        <v>286508</v>
+      </c>
+      <c r="I13" t="n">
         <v>93525</v>
       </c>
-      <c r="I13" t="n">
-        <v>234713</v>
-      </c>
       <c r="J13" t="n">
-        <v>0.54</v>
+        <v>1.76</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.39</v>
+        <v>-1.55</v>
       </c>
       <c r="L13" t="n">
-        <v>47.9</v>
+        <v>52.2</v>
       </c>
       <c r="M13" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="N13" t="n">
-        <v>5.48</v>
+        <v>5.47</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-45.27</v>
+        <v>-44.44</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>27.27</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24583.8</v>
+      </c>
+      <c r="D17" t="n">
         <v>24570.65</v>
       </c>
-      <c r="D17" t="n">
-        <v>24636</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.27</v>
+        <v>0.05</v>
       </c>
       <c r="F17" t="n">
-        <v>0.77</v>
+        <v>-0.77</v>
       </c>
       <c r="G17" t="n">
-        <v>2.54</v>
+        <v>1.56</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57686.95</v>
+      </c>
+      <c r="D18" t="n">
         <v>57746.45</v>
       </c>
-      <c r="D18" t="n">
-        <v>58063.65</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.55</v>
+        <v>-0.1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.84</v>
+        <v>-0.96</v>
       </c>
       <c r="G18" t="n">
-        <v>0.86</v>
+        <v>-0.62</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.58</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>82.87</v>
+        <v>85.8</v>
       </c>
       <c r="D19" t="n">
-        <v>82.48999999999999</v>
+        <v>83.55</v>
       </c>
       <c r="E19" t="n">
-        <v>0.46</v>
+        <v>2.69</v>
       </c>
       <c r="F19" t="n">
-        <v>-8.039999999999999</v>
+        <v>2.42</v>
       </c>
       <c r="G19" t="n">
-        <v>8.609999999999999</v>
+        <v>12.88</v>
       </c>
       <c r="H19" t="n">
-        <v>0.49</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4397</v>
+        <v>4401.4</v>
       </c>
       <c r="D20" t="n">
-        <v>4242</v>
+        <v>4340.7</v>
       </c>
       <c r="E20" t="n">
-        <v>3.65</v>
+        <v>1.4</v>
       </c>
       <c r="F20" t="n">
-        <v>8.59</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>6.45</v>
+        <v>7.24</v>
       </c>
       <c r="H20" t="n">
         <v>2.2</v>
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53987.31</v>
+        <v>53969.28</v>
       </c>
       <c r="D21" t="n">
-        <v>53885.1</v>
+        <v>54036.93</v>
       </c>
       <c r="E21" t="n">
-        <v>0.19</v>
+        <v>-0.13</v>
       </c>
       <c r="F21" t="n">
-        <v>2.86</v>
+        <v>1.49</v>
       </c>
       <c r="G21" t="n">
-        <v>2.86</v>
+        <v>2.53</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.14</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12.16</v>
+        <v>12.24</v>
       </c>
       <c r="D22" t="n">
         <v>12.16</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="F22" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.98</v>
+        <v>-0.08</v>
       </c>
       <c r="H22" t="n">
         <v/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1695,6 +1695,29 @@
       </c>
       <c r="G13" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57686.95</v>
+      </c>
+      <c r="C14" t="n">
+        <v>57746.45</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -1708,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2022,6 +2045,29 @@
       </c>
       <c r="G13" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -2035,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2348,6 +2394,29 @@
         <v>6.45</v>
       </c>
       <c r="G13" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4401.4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4340.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="G14" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -2362,7 +2431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2676,6 +2745,29 @@
       </c>
       <c r="G13" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>53969.28</v>
+      </c>
+      <c r="C14" t="n">
+        <v>54036.93</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -2689,7 +2781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2968,7 +3060,27 @@
       <c r="F13" t="n">
         <v>-8.98</v>
       </c>
-      <c r="G13" t="n">
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="C14" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G14" t="n">
         <v/>
       </c>
     </row>
@@ -2983,7 +3095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3627,6 +3739,59 @@
       </c>
       <c r="Q12" t="n">
         <v>42.72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="F13" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9166</v>
+      </c>
+      <c r="H13" t="n">
+        <v>956</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K13" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="N13" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-46.09</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>49.72</v>
       </c>
     </row>
   </sheetData>
@@ -3640,7 +3805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4284,6 +4449,59 @@
       </c>
       <c r="Q12" t="n">
         <v>3.16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B13" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="C13" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5020464</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2663872</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K13" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="N13" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-31.02</v>
+      </c>
+      <c r="P13" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.42</v>
       </c>
     </row>
   </sheetData>
@@ -4297,7 +4515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4835,6 +5053,59 @@
       </c>
       <c r="Q10" t="n">
         <v>64.98999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C11" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10925959</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3899463</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="M11" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="P11" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>60.9</v>
       </c>
     </row>
   </sheetData>
@@ -4848,7 +5119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5545,6 +5816,59 @@
       </c>
       <c r="Q13" t="n">
         <v>67.06</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>422.85</v>
+      </c>
+      <c r="C14" t="n">
+        <v>401.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1226108</v>
+      </c>
+      <c r="H14" t="n">
+        <v>152556</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="K14" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>367.41</v>
+      </c>
+      <c r="N14" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-11.78</v>
+      </c>
+      <c r="P14" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>75.77</v>
       </c>
     </row>
   </sheetData>
@@ -5558,7 +5882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6255,6 +6579,59 @@
       </c>
       <c r="Q13" t="n">
         <v>3.83</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>282.65</v>
+      </c>
+      <c r="C14" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9325475</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6128841</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>318.95</v>
+      </c>
+      <c r="M14" t="n">
+        <v>284.96</v>
+      </c>
+      <c r="N14" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-29.69</v>
+      </c>
+      <c r="P14" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.58</v>
       </c>
     </row>
   </sheetData>
@@ -6268,7 +6645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6965,6 +7342,59 @@
       </c>
       <c r="Q13" t="n">
         <v>16.01</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>910.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>916.65</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="G14" t="n">
+        <v>198817</v>
+      </c>
+      <c r="H14" t="n">
+        <v>168655</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K14" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>943.36</v>
+      </c>
+      <c r="M14" t="n">
+        <v>918.52</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>15.23</v>
       </c>
     </row>
   </sheetData>
@@ -6978,7 +7408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7675,6 +8105,59 @@
       </c>
       <c r="Q13" t="n">
         <v>53.41</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1044.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1047.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1171702</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2579738</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K14" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>938.14</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1055.83</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-6.54</v>
+      </c>
+      <c r="P14" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>52.96</v>
       </c>
     </row>
   </sheetData>
@@ -7688,7 +8171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8385,6 +8868,59 @@
       </c>
       <c r="Q13" t="n">
         <v>68.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>69.76000000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>70.11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6796352</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8655583</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K14" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="M14" t="n">
+        <v>61.96</v>
+      </c>
+      <c r="N14" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="P14" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>67.41</v>
       </c>
     </row>
   </sheetData>
@@ -8398,7 +8934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9095,6 +9631,59 @@
       </c>
       <c r="Q13" t="n">
         <v>27.27</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="G14" t="n">
+        <v>286508</v>
+      </c>
+      <c r="H14" t="n">
+        <v>93525</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-44.44</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>29.19</v>
       </c>
     </row>
   </sheetData>
@@ -9108,7 +9697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9805,6 +10394,59 @@
       </c>
       <c r="Q13" t="n">
         <v>58.04</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>898.75</v>
+      </c>
+      <c r="C14" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1064015</v>
+      </c>
+      <c r="H14" t="n">
+        <v>161744</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>747.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>840</v>
+      </c>
+      <c r="N14" t="n">
+        <v>898.75</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>63.17</v>
       </c>
     </row>
   </sheetData>
@@ -9818,7 +10460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10134,6 +10776,29 @@
         <v>-0.8100000000000001</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>24583.8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24570.65</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>441.2</v>
+      </c>
+      <c r="D3" t="n">
         <v>422.85</v>
       </c>
-      <c r="D3" t="n">
-        <v>401.9</v>
-      </c>
       <c r="E3" t="n">
-        <v>5.21</v>
+        <v>4.34</v>
       </c>
       <c r="F3" t="n">
-        <v>5.07</v>
+        <v>10.77</v>
       </c>
       <c r="G3" t="n">
-        <v>17.38</v>
+        <v>19.36</v>
       </c>
       <c r="H3" t="n">
-        <v>1226108</v>
+        <v>860068</v>
       </c>
       <c r="I3" t="n">
-        <v>152556</v>
+        <v>1226625</v>
       </c>
       <c r="J3" t="n">
-        <v>0.51</v>
+        <v>0.35</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.28</v>
+        <v>0.59</v>
       </c>
       <c r="L3" t="n">
-        <v>61.9</v>
+        <v>67.2</v>
       </c>
       <c r="M3" t="n">
-        <v>336.7</v>
+        <v>336.75</v>
       </c>
       <c r="N3" t="n">
-        <v>367.41</v>
+        <v>371.4</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-11.78</v>
+        <v>-7.95</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>75.77</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="D4" t="n">
         <v>46</v>
       </c>
-      <c r="D4" t="n">
-        <v>47.17</v>
-      </c>
       <c r="E4" t="n">
-        <v>-2.48</v>
+        <v>-0.41</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.27</v>
+        <v>-2.24</v>
       </c>
       <c r="G4" t="n">
-        <v>0.41</v>
+        <v>-0.15</v>
       </c>
       <c r="H4" t="n">
-        <v>10925959</v>
+        <v>6727333</v>
       </c>
       <c r="I4" t="n">
-        <v>3899463</v>
+        <v>10928785</v>
       </c>
       <c r="J4" t="n">
-        <v>0.79</v>
+        <v>0.49</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>47.4</v>
+        <v>46.4</v>
       </c>
       <c r="M4" t="n">
-        <v>41.22</v>
+        <v>41.26</v>
       </c>
       <c r="N4" t="n">
-        <v>46.1</v>
+        <v>46.18</v>
       </c>
       <c r="O4" t="n">
         <v>48.49</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.14</v>
+        <v>-5.53</v>
       </c>
       <c r="Q4" t="n">
         <v>28.59</v>
       </c>
       <c r="R4" t="n">
-        <v>60.9</v>
+        <v>60.23</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>279</v>
+      </c>
+      <c r="D5" t="n">
         <v>282.65</v>
       </c>
-      <c r="D5" t="n">
-        <v>286.1</v>
-      </c>
       <c r="E5" t="n">
-        <v>-1.21</v>
+        <v>-1.29</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.52</v>
+        <v>-3.46</v>
       </c>
       <c r="G5" t="n">
-        <v>0.32</v>
+        <v>-0.23</v>
       </c>
       <c r="H5" t="n">
-        <v>9325475</v>
+        <v>13041002</v>
       </c>
       <c r="I5" t="n">
-        <v>6128841</v>
+        <v>9347929</v>
       </c>
       <c r="J5" t="n">
-        <v>0.59</v>
+        <v>0.83</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="L5" t="n">
-        <v>45.9</v>
+        <v>40.4</v>
       </c>
       <c r="M5" t="n">
-        <v>318.95</v>
+        <v>318.36</v>
       </c>
       <c r="N5" t="n">
-        <v>284.96</v>
+        <v>284.88</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-29.69</v>
+        <v>-30.6</v>
       </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
       <c r="R5" t="n">
-        <v>2.58</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>907</v>
+      </c>
+      <c r="D6" t="n">
         <v>910.5</v>
       </c>
-      <c r="D6" t="n">
-        <v>916.65</v>
-      </c>
       <c r="E6" t="n">
-        <v>-0.67</v>
+        <v>-0.38</v>
       </c>
       <c r="F6" t="n">
-        <v>-2</v>
+        <v>-1.09</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.48</v>
+        <v>-7.44</v>
       </c>
       <c r="H6" t="n">
-        <v>198817</v>
+        <v>406107</v>
       </c>
       <c r="I6" t="n">
-        <v>168655</v>
+        <v>199069</v>
       </c>
       <c r="J6" t="n">
-        <v>0.63</v>
+        <v>1.36</v>
       </c>
       <c r="K6" t="n">
-        <v>0.26</v>
+        <v>-0.01</v>
       </c>
       <c r="L6" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>943.36</v>
+        <v>943.74</v>
       </c>
       <c r="N6" t="n">
-        <v>918.52</v>
+        <v>917.88</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-24.5</v>
+        <v>-24.79</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>15.23</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="D7" t="n">
         <v>69.76000000000001</v>
       </c>
-      <c r="D7" t="n">
-        <v>70.11</v>
-      </c>
       <c r="E7" t="n">
-        <v>-0.5</v>
+        <v>0.54</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.94</v>
+        <v>-0.3</v>
       </c>
       <c r="G7" t="n">
-        <v>6.88</v>
+        <v>4.89</v>
       </c>
       <c r="H7" t="n">
-        <v>6796352</v>
+        <v>9887807</v>
       </c>
       <c r="I7" t="n">
-        <v>8655583</v>
+        <v>6802649</v>
       </c>
       <c r="J7" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="K7" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="L7" t="n">
-        <v>58.7</v>
+        <v>59.8</v>
       </c>
       <c r="M7" t="n">
-        <v>57.81</v>
+        <v>57.9</v>
       </c>
       <c r="N7" t="n">
-        <v>61.96</v>
+        <v>62.3</v>
       </c>
       <c r="O7" t="n">
         <v>72.05</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.18</v>
+        <v>-2.65</v>
       </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
       <c r="R7" t="n">
-        <v>67.41</v>
+        <v>68.31999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>865.7</v>
+      </c>
+      <c r="D8" t="n">
         <v>898.75</v>
       </c>
-      <c r="D8" t="n">
-        <v>870.5</v>
-      </c>
       <c r="E8" t="n">
-        <v>3.25</v>
+        <v>-3.68</v>
       </c>
       <c r="F8" t="n">
-        <v>7.77</v>
+        <v>2.39</v>
       </c>
       <c r="G8" t="n">
-        <v>8.32</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1064015</v>
+        <v>1063646</v>
       </c>
       <c r="I8" t="n">
-        <v>161744</v>
+        <v>1064212</v>
       </c>
       <c r="J8" t="n">
-        <v>4.93</v>
+        <v>4.17</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2.98</v>
       </c>
       <c r="L8" t="n">
-        <v>68.2</v>
+        <v>55.3</v>
       </c>
       <c r="M8" t="n">
-        <v>747.7</v>
+        <v>748</v>
       </c>
       <c r="N8" t="n">
-        <v>840</v>
+        <v>841.0599999999999</v>
       </c>
       <c r="O8" t="n">
         <v>898.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-3.68</v>
       </c>
       <c r="Q8" t="n">
         <v>550.8</v>
       </c>
       <c r="R8" t="n">
-        <v>63.17</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D10" t="n">
         <v>7.92</v>
       </c>
-      <c r="D10" t="n">
-        <v>7.55</v>
-      </c>
       <c r="E10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F10" t="n">
-        <v>24.72</v>
+        <v>21.52</v>
       </c>
       <c r="G10" t="n">
-        <v>24.14</v>
+        <v>10.23</v>
       </c>
       <c r="H10" t="n">
+        <v>41816</v>
+      </c>
+      <c r="I10" t="n">
         <v>9166</v>
       </c>
-      <c r="I10" t="n">
-        <v>956</v>
-      </c>
       <c r="J10" t="n">
-        <v>1.74</v>
+        <v>7.71</v>
       </c>
       <c r="K10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="L10" t="n">
-        <v>63.6</v>
+        <v>67.8</v>
       </c>
       <c r="M10" t="n">
-        <v>9.279999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="N10" t="n">
-        <v>6.71</v>
+        <v>6.68</v>
       </c>
       <c r="O10" t="n">
         <v>14.69</v>
       </c>
       <c r="P10" t="n">
-        <v>-46.09</v>
+        <v>-43.5</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>49.72</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D11" t="n">
         <v>1044.1</v>
       </c>
-      <c r="D11" t="n">
-        <v>1047.2</v>
-      </c>
       <c r="E11" t="n">
-        <v>-0.3</v>
+        <v>0.57</v>
       </c>
       <c r="F11" t="n">
-        <v>2.29</v>
+        <v>1.32</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.14</v>
+        <v>-5.36</v>
       </c>
       <c r="H11" t="n">
-        <v>1171702</v>
+        <v>469971</v>
       </c>
       <c r="I11" t="n">
-        <v>2579738</v>
+        <v>1171794</v>
       </c>
       <c r="J11" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>49.9</v>
+        <v>51.7</v>
       </c>
       <c r="M11" t="n">
-        <v>938.14</v>
+        <v>937.89</v>
       </c>
       <c r="N11" t="n">
-        <v>1055.83</v>
+        <v>1054.74</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.54</v>
+        <v>-6.02</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>52.96</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="12">
@@ -1033,37 +1033,37 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="D12" t="n">
         <v>22.44</v>
       </c>
-      <c r="D12" t="n">
-        <v>22.17</v>
-      </c>
       <c r="E12" t="n">
-        <v>1.22</v>
+        <v>-1.11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.49</v>
+        <v>-0.98</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.28</v>
+        <v>-3.81</v>
       </c>
       <c r="H12" t="n">
-        <v>5020464</v>
+        <v>2348869</v>
       </c>
       <c r="I12" t="n">
-        <v>2663872</v>
+        <v>5024865</v>
       </c>
       <c r="J12" t="n">
-        <v>1.35</v>
+        <v>0.63</v>
       </c>
       <c r="K12" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>51.6</v>
+        <v>47.8</v>
       </c>
       <c r="M12" t="n">
-        <v>25.2</v>
+        <v>25.16</v>
       </c>
       <c r="N12" t="n">
         <v>22.46</v>
@@ -1072,13 +1072,13 @@
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-31.02</v>
+        <v>-31.79</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>4.42</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.4</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.32</v>
-      </c>
       <c r="E13" t="n">
-        <v>1.5</v>
+        <v>-0.19</v>
       </c>
       <c r="F13" t="n">
-        <v>3.05</v>
+        <v>-1.46</v>
       </c>
       <c r="G13" t="n">
         <v>-0.55</v>
       </c>
       <c r="H13" t="n">
-        <v>286508</v>
+        <v>106100</v>
       </c>
       <c r="I13" t="n">
-        <v>93525</v>
+        <v>286509</v>
       </c>
       <c r="J13" t="n">
-        <v>1.76</v>
+        <v>0.63</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.55</v>
+        <v>0.83</v>
       </c>
       <c r="L13" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="M13" t="n">
-        <v>6.09</v>
+        <v>6.06</v>
       </c>
       <c r="N13" t="n">
-        <v>5.47</v>
+        <v>5.45</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-44.44</v>
+        <v>-44.55</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>29.19</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24471.7</v>
+      </c>
+      <c r="D17" t="n">
         <v>24583.8</v>
       </c>
-      <c r="D17" t="n">
-        <v>24570.65</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.05</v>
+        <v>-0.46</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.77</v>
+        <v>-0.58</v>
       </c>
       <c r="G17" t="n">
-        <v>1.56</v>
+        <v>1.08</v>
       </c>
       <c r="H17" t="n">
-        <v>0.09</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57446.25</v>
+      </c>
+      <c r="D18" t="n">
         <v>57686.95</v>
       </c>
-      <c r="D18" t="n">
-        <v>57746.45</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.1</v>
+        <v>-0.42</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.96</v>
+        <v>-0.8</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.62</v>
+        <v>-1.18</v>
       </c>
       <c r="H18" t="n">
-        <v>0.22</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>85.8</v>
+        <v>87.62</v>
       </c>
       <c r="D19" t="n">
-        <v>83.55</v>
+        <v>87.72</v>
       </c>
       <c r="E19" t="n">
-        <v>2.69</v>
+        <v>-0.11</v>
       </c>
       <c r="F19" t="n">
-        <v>2.42</v>
+        <v>10.41</v>
       </c>
       <c r="G19" t="n">
-        <v>12.88</v>
+        <v>5.19</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4401.4</v>
+        <v>4442.2</v>
       </c>
       <c r="D20" t="n">
-        <v>4340.7</v>
+        <v>4361.8</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="F20" t="n">
-        <v>9.119999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>7.24</v>
+        <v>11.14</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53969.28</v>
+        <v>54016.06</v>
       </c>
       <c r="D21" t="n">
-        <v>54036.93</v>
+        <v>53975.98</v>
       </c>
       <c r="E21" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F21" t="n">
         <v>-0.13</v>
       </c>
-      <c r="F21" t="n">
-        <v>1.49</v>
-      </c>
       <c r="G21" t="n">
-        <v>2.53</v>
+        <v>2.89</v>
       </c>
       <c r="H21" t="n">
-        <v>0.14</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12.24</v>
+        <v>11.85</v>
       </c>
       <c r="D22" t="n">
-        <v>12.16</v>
+        <v>12.25</v>
       </c>
       <c r="E22" t="n">
-        <v>0.66</v>
+        <v>-3.27</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>-2.79</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.08</v>
+        <v>-10.77</v>
       </c>
       <c r="H22" t="n">
         <v/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1718,6 +1718,29 @@
       </c>
       <c r="G14" t="n">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57446.25</v>
+      </c>
+      <c r="C15" t="n">
+        <v>57686.95</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -1731,7 +1754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2068,6 +2091,29 @@
       </c>
       <c r="G14" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="C15" t="n">
+        <v>87.72</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -2081,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2418,6 +2464,29 @@
       </c>
       <c r="G14" t="n">
         <v>2.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4442.2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4361.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.22</v>
       </c>
     </row>
   </sheetData>
@@ -2431,7 +2500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2768,6 +2837,29 @@
       </c>
       <c r="G14" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>54016.06</v>
+      </c>
+      <c r="C15" t="n">
+        <v>53975.98</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -2781,7 +2873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3080,7 +3172,27 @@
       <c r="F14" t="n">
         <v>-0.08</v>
       </c>
-      <c r="G14" t="n">
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="C15" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-10.77</v>
+      </c>
+      <c r="G15" t="n">
         <v/>
       </c>
     </row>
@@ -3095,7 +3207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3792,6 +3904,59 @@
       </c>
       <c r="Q13" t="n">
         <v>49.72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="G14" t="n">
+        <v>41816</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9166</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K14" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-43.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>56.9</v>
       </c>
     </row>
   </sheetData>
@@ -3805,7 +3970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4502,6 +4667,59 @@
       </c>
       <c r="Q13" t="n">
         <v>4.42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B14" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="C14" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2348869</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5024865</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="M14" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="N14" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-31.79</v>
+      </c>
+      <c r="P14" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.26</v>
       </c>
     </row>
   </sheetData>
@@ -4515,7 +4733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5106,6 +5324,59 @@
       </c>
       <c r="Q11" t="n">
         <v>60.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B12" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="C12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6727333</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10928785</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="M12" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="N12" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="P12" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>60.23</v>
       </c>
     </row>
   </sheetData>
@@ -5119,7 +5390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5869,6 +6140,59 @@
       </c>
       <c r="Q14" t="n">
         <v>75.77</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>441.2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>422.85</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="F15" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="G15" t="n">
+        <v>860068</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1226625</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K15" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>336.75</v>
+      </c>
+      <c r="M15" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-7.95</v>
+      </c>
+      <c r="P15" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>83.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5882,7 +6206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6632,6 +6956,59 @@
       </c>
       <c r="Q14" t="n">
         <v>2.58</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>279</v>
+      </c>
+      <c r="C15" t="n">
+        <v>282.65</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="G15" t="n">
+        <v>13041002</v>
+      </c>
+      <c r="H15" t="n">
+        <v>9347929</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="K15" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>318.36</v>
+      </c>
+      <c r="M15" t="n">
+        <v>284.88</v>
+      </c>
+      <c r="N15" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-30.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -6645,7 +7022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7395,6 +7772,59 @@
       </c>
       <c r="Q14" t="n">
         <v>15.23</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>907</v>
+      </c>
+      <c r="C15" t="n">
+        <v>910.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="G15" t="n">
+        <v>406107</v>
+      </c>
+      <c r="H15" t="n">
+        <v>199069</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="K15" t="n">
+        <v>40</v>
+      </c>
+      <c r="L15" t="n">
+        <v>943.74</v>
+      </c>
+      <c r="M15" t="n">
+        <v>917.88</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-24.79</v>
+      </c>
+      <c r="P15" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>14.78</v>
       </c>
     </row>
   </sheetData>
@@ -7408,7 +7838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8158,6 +8588,59 @@
       </c>
       <c r="Q14" t="n">
         <v>52.96</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1044.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="G15" t="n">
+        <v>469971</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1171794</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>937.89</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1054.74</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-6.02</v>
+      </c>
+      <c r="P15" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>53.82</v>
       </c>
     </row>
   </sheetData>
@@ -8171,7 +8654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8921,6 +9404,59 @@
       </c>
       <c r="Q14" t="n">
         <v>67.41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="C15" t="n">
+        <v>69.76000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9887807</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6802649</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K15" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="P15" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>68.31999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8934,7 +9470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9684,6 +10220,59 @@
       </c>
       <c r="Q14" t="n">
         <v>29.19</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="G15" t="n">
+        <v>106100</v>
+      </c>
+      <c r="H15" t="n">
+        <v>286509</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K15" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-44.55</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>28.95</v>
       </c>
     </row>
   </sheetData>
@@ -9697,7 +10286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10447,6 +11036,59 @@
       </c>
       <c r="Q14" t="n">
         <v>63.17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>865.7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>898.75</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-3.68</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1063646</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1064212</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K15" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>748</v>
+      </c>
+      <c r="M15" t="n">
+        <v>841.0599999999999</v>
+      </c>
+      <c r="N15" t="n">
+        <v>898.75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-3.68</v>
+      </c>
+      <c r="P15" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>57.17</v>
       </c>
     </row>
   </sheetData>
@@ -10460,7 +11102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10799,6 +11441,29 @@
         <v>0.09</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>24471.7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>24583.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>454</v>
+      </c>
+      <c r="D3" t="n">
         <v>441.2</v>
       </c>
-      <c r="D3" t="n">
-        <v>422.85</v>
-      </c>
       <c r="E3" t="n">
-        <v>4.34</v>
+        <v>2.9</v>
       </c>
       <c r="F3" t="n">
-        <v>10.77</v>
+        <v>11.93</v>
       </c>
       <c r="G3" t="n">
-        <v>19.36</v>
+        <v>16.16</v>
       </c>
       <c r="H3" t="n">
-        <v>860068</v>
+        <v>1716384</v>
       </c>
       <c r="I3" t="n">
-        <v>1226625</v>
+        <v>860070</v>
       </c>
       <c r="J3" t="n">
-        <v>0.35</v>
+        <v>0.84</v>
       </c>
       <c r="K3" t="n">
-        <v>0.59</v>
+        <v>1.34</v>
       </c>
       <c r="L3" t="n">
-        <v>67.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>336.75</v>
+        <v>336.76</v>
       </c>
       <c r="N3" t="n">
-        <v>371.4</v>
+        <v>373.91</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.95</v>
+        <v>-5.28</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>83.40000000000001</v>
+        <v>88.72</v>
       </c>
     </row>
     <row r="4">
@@ -606,25 +606,25 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="D4" t="n">
         <v>45.81</v>
       </c>
-      <c r="D4" t="n">
-        <v>46</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.41</v>
+        <v>0.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.24</v>
+        <v>-1.49</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.15</v>
+        <v>1.96</v>
       </c>
       <c r="H4" t="n">
-        <v>6727333</v>
+        <v>6627719</v>
       </c>
       <c r="I4" t="n">
-        <v>10928785</v>
+        <v>6729091</v>
       </c>
       <c r="J4" t="n">
         <v>0.49</v>
@@ -633,25 +633,25 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>46.4</v>
+        <v>49</v>
       </c>
       <c r="M4" t="n">
-        <v>41.26</v>
+        <v>41.3</v>
       </c>
       <c r="N4" t="n">
-        <v>46.18</v>
+        <v>46.23</v>
       </c>
       <c r="O4" t="n">
         <v>48.49</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.53</v>
+        <v>-4.68</v>
       </c>
       <c r="Q4" t="n">
         <v>28.59</v>
       </c>
       <c r="R4" t="n">
-        <v>60.23</v>
+        <v>61.66</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>276.15</v>
+      </c>
+      <c r="D5" t="n">
         <v>279</v>
       </c>
-      <c r="D5" t="n">
-        <v>282.65</v>
-      </c>
       <c r="E5" t="n">
-        <v>-1.29</v>
+        <v>-1.02</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.46</v>
+        <v>-3.76</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.23</v>
+        <v>0.22</v>
       </c>
       <c r="H5" t="n">
-        <v>13041002</v>
+        <v>12620332</v>
       </c>
       <c r="I5" t="n">
-        <v>9347929</v>
+        <v>13053722</v>
       </c>
       <c r="J5" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40.4</v>
+        <v>36.7</v>
       </c>
       <c r="M5" t="n">
-        <v>318.36</v>
+        <v>317.75</v>
       </c>
       <c r="N5" t="n">
-        <v>284.88</v>
+        <v>284.86</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-30.6</v>
+        <v>-31.3</v>
       </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>915.3</v>
+      </c>
+      <c r="D6" t="n">
         <v>907</v>
       </c>
-      <c r="D6" t="n">
-        <v>910.5</v>
-      </c>
       <c r="E6" t="n">
-        <v>-0.38</v>
+        <v>0.92</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.09</v>
+        <v>-0.25</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.44</v>
+        <v>-5.86</v>
       </c>
       <c r="H6" t="n">
-        <v>406107</v>
+        <v>270044</v>
       </c>
       <c r="I6" t="n">
-        <v>199069</v>
+        <v>406109</v>
       </c>
       <c r="J6" t="n">
-        <v>1.36</v>
+        <v>0.89</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01</v>
+        <v>0.26</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M6" t="n">
-        <v>943.74</v>
+        <v>944.21</v>
       </c>
       <c r="N6" t="n">
-        <v>917.88</v>
+        <v>917.49</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-24.79</v>
+        <v>-24.1</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>14.78</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>72.38</v>
+      </c>
+      <c r="D7" t="n">
         <v>70.14</v>
       </c>
-      <c r="D7" t="n">
-        <v>69.76000000000001</v>
-      </c>
       <c r="E7" t="n">
-        <v>0.54</v>
+        <v>3.19</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3</v>
+        <v>4.01</v>
       </c>
       <c r="G7" t="n">
-        <v>4.89</v>
+        <v>11.11</v>
       </c>
       <c r="H7" t="n">
-        <v>9887807</v>
+        <v>18055935</v>
       </c>
       <c r="I7" t="n">
-        <v>6802649</v>
+        <v>9888564</v>
       </c>
       <c r="J7" t="n">
-        <v>0.38</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.78</v>
+        <v>0.31</v>
       </c>
       <c r="L7" t="n">
-        <v>59.8</v>
+        <v>65.2</v>
       </c>
       <c r="M7" t="n">
-        <v>57.9</v>
+        <v>58</v>
       </c>
       <c r="N7" t="n">
-        <v>62.3</v>
+        <v>62.68</v>
       </c>
       <c r="O7" t="n">
-        <v>72.05</v>
+        <v>72.38</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.65</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
       <c r="R7" t="n">
-        <v>68.31999999999999</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>868.85</v>
+      </c>
+      <c r="D8" t="n">
         <v>865.7</v>
       </c>
-      <c r="D8" t="n">
-        <v>898.75</v>
-      </c>
       <c r="E8" t="n">
-        <v>-3.68</v>
+        <v>0.36</v>
       </c>
       <c r="F8" t="n">
-        <v>2.39</v>
+        <v>1.22</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>4.78</v>
       </c>
       <c r="H8" t="n">
-        <v>1063646</v>
+        <v>431371</v>
       </c>
       <c r="I8" t="n">
-        <v>1064212</v>
+        <v>1063773</v>
       </c>
       <c r="J8" t="n">
-        <v>4.17</v>
+        <v>1.66</v>
       </c>
       <c r="K8" t="n">
-        <v>2.98</v>
+        <v>-0.74</v>
       </c>
       <c r="L8" t="n">
-        <v>55.3</v>
+        <v>56.1</v>
       </c>
       <c r="M8" t="n">
-        <v>748</v>
+        <v>748.35</v>
       </c>
       <c r="N8" t="n">
-        <v>841.0599999999999</v>
+        <v>842.22</v>
       </c>
       <c r="O8" t="n">
         <v>898.75</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.68</v>
+        <v>-3.33</v>
       </c>
       <c r="Q8" t="n">
         <v>550.8</v>
       </c>
       <c r="R8" t="n">
-        <v>57.17</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="D10" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="D10" t="n">
-        <v>7.92</v>
-      </c>
       <c r="E10" t="n">
-        <v>4.8</v>
+        <v>-4.58</v>
       </c>
       <c r="F10" t="n">
-        <v>21.52</v>
+        <v>5.46</v>
       </c>
       <c r="G10" t="n">
-        <v>10.23</v>
+        <v>13.14</v>
       </c>
       <c r="H10" t="n">
+        <v>20309</v>
+      </c>
+      <c r="I10" t="n">
         <v>41816</v>
       </c>
-      <c r="I10" t="n">
-        <v>9166</v>
-      </c>
       <c r="J10" t="n">
-        <v>7.71</v>
+        <v>2.75</v>
       </c>
       <c r="K10" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="L10" t="n">
-        <v>67.8</v>
+        <v>61.4</v>
       </c>
       <c r="M10" t="n">
-        <v>9.23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>6.68</v>
       </c>
       <c r="O10" t="n">
-        <v>14.69</v>
+        <v>14.21</v>
       </c>
       <c r="P10" t="n">
-        <v>-43.5</v>
+        <v>-44.26</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>56.9</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1026.1</v>
+      </c>
+      <c r="D11" t="n">
         <v>1050</v>
       </c>
-      <c r="D11" t="n">
-        <v>1044.1</v>
-      </c>
       <c r="E11" t="n">
-        <v>0.57</v>
+        <v>-2.28</v>
       </c>
       <c r="F11" t="n">
-        <v>1.32</v>
+        <v>-1.71</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.36</v>
+        <v>-6.79</v>
       </c>
       <c r="H11" t="n">
-        <v>469971</v>
+        <v>593498</v>
       </c>
       <c r="I11" t="n">
-        <v>1171794</v>
+        <v>470027</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="L11" t="n">
-        <v>51.7</v>
+        <v>45.7</v>
       </c>
       <c r="M11" t="n">
-        <v>937.89</v>
+        <v>937.67</v>
       </c>
       <c r="N11" t="n">
-        <v>1054.74</v>
+        <v>1053.48</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.02</v>
+        <v>-8.15</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>53.82</v>
+        <v>50.32</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="D12" t="n">
         <v>22.19</v>
       </c>
-      <c r="D12" t="n">
-        <v>22.44</v>
-      </c>
       <c r="E12" t="n">
-        <v>-1.11</v>
+        <v>-0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.98</v>
+        <v>-1.52</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.81</v>
+        <v>-3.21</v>
       </c>
       <c r="H12" t="n">
-        <v>2348869</v>
+        <v>2749816</v>
       </c>
       <c r="I12" t="n">
-        <v>5024865</v>
+        <v>2348989</v>
       </c>
       <c r="J12" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="L12" t="n">
-        <v>47.8</v>
+        <v>44.9</v>
       </c>
       <c r="M12" t="n">
-        <v>25.16</v>
+        <v>25.12</v>
       </c>
       <c r="N12" t="n">
-        <v>22.46</v>
+        <v>22.47</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-31.79</v>
+        <v>-32.4</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>3.26</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.39</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.4</v>
-      </c>
       <c r="E13" t="n">
-        <v>-0.19</v>
+        <v>-1.3</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.46</v>
+        <v>-2.74</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.55</v>
+        <v>-1.48</v>
       </c>
       <c r="H13" t="n">
-        <v>106100</v>
+        <v>176374</v>
       </c>
       <c r="I13" t="n">
-        <v>286509</v>
+        <v>112092</v>
       </c>
       <c r="J13" t="n">
-        <v>0.63</v>
+        <v>1.04</v>
       </c>
       <c r="K13" t="n">
-        <v>0.83</v>
+        <v>-0.85</v>
       </c>
       <c r="L13" t="n">
-        <v>52.1</v>
+        <v>48.3</v>
       </c>
       <c r="M13" t="n">
-        <v>6.06</v>
+        <v>6.05</v>
       </c>
       <c r="N13" t="n">
-        <v>5.45</v>
+        <v>5.44</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-44.55</v>
+        <v>-45.27</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>28.95</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24435.95</v>
+      </c>
+      <c r="D17" t="n">
         <v>24471.7</v>
       </c>
-      <c r="D17" t="n">
-        <v>24583.8</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.46</v>
+        <v>-0.15</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.58</v>
+        <v>-0.77</v>
       </c>
       <c r="G17" t="n">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57885.85</v>
+      </c>
+      <c r="D18" t="n">
         <v>57446.25</v>
       </c>
-      <c r="D18" t="n">
-        <v>57686.95</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.42</v>
+        <v>0.77</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8</v>
+        <v>0.25</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.18</v>
+        <v>0.74</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.29</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>87.62</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>87.72</v>
+        <v>88.91</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.11</v>
+        <v>-0.38</v>
       </c>
       <c r="F19" t="n">
-        <v>10.41</v>
+        <v>11.48</v>
       </c>
       <c r="G19" t="n">
-        <v>5.19</v>
+        <v>4.53</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4442.2</v>
+        <v>4496.6</v>
       </c>
       <c r="D20" t="n">
-        <v>4361.8</v>
+        <v>4383</v>
       </c>
       <c r="E20" t="n">
-        <v>1.84</v>
+        <v>2.59</v>
       </c>
       <c r="F20" t="n">
-        <v>8.470000000000001</v>
+        <v>5.91</v>
       </c>
       <c r="G20" t="n">
-        <v>11.14</v>
+        <v>10.72</v>
       </c>
       <c r="H20" t="n">
-        <v>3.22</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>54016.06</v>
+        <v>53795.51</v>
       </c>
       <c r="D21" t="n">
-        <v>53975.98</v>
+        <v>53791.85</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.13</v>
+        <v>-1.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11.85</v>
+        <v>11.69</v>
       </c>
       <c r="D22" t="n">
-        <v>12.25</v>
+        <v>11.86</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.27</v>
+        <v>-1.43</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.79</v>
+        <v>-3.07</v>
       </c>
       <c r="G22" t="n">
-        <v>-10.77</v>
+        <v>-14.98</v>
       </c>
       <c r="H22" t="n">
         <v/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1741,29 @@
       </c>
       <c r="G15" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57885.85</v>
+      </c>
+      <c r="C16" t="n">
+        <v>57446.25</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +1777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2114,6 +2137,29 @@
       </c>
       <c r="G15" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>88.56999999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>88.91</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +2173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2487,6 +2533,29 @@
       </c>
       <c r="G15" t="n">
         <v>3.22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4496.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4383</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.69</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2860,6 +2929,29 @@
       </c>
       <c r="G15" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>53795.51</v>
+      </c>
+      <c r="C16" t="n">
+        <v>53791.85</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -2873,7 +2965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3192,7 +3284,27 @@
       <c r="F15" t="n">
         <v>-10.77</v>
       </c>
-      <c r="G15" t="n">
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="C16" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-14.98</v>
+      </c>
+      <c r="G16" t="n">
         <v/>
       </c>
     </row>
@@ -3207,7 +3319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3957,6 +4069,59 @@
       </c>
       <c r="Q14" t="n">
         <v>56.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>20309</v>
+      </c>
+      <c r="H15" t="n">
+        <v>41816</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K15" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="N15" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-44.26</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>49.72</v>
       </c>
     </row>
   </sheetData>
@@ -3970,7 +4135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4720,6 +4885,59 @@
       </c>
       <c r="Q14" t="n">
         <v>3.26</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B15" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="C15" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2749816</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2348989</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K15" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="M15" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="N15" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-32.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>
@@ -4733,7 +4951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5377,6 +5595,59 @@
       </c>
       <c r="Q12" t="n">
         <v>60.23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B13" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="C13" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6627719</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6729091</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>49</v>
+      </c>
+      <c r="L13" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>46.23</v>
+      </c>
+      <c r="N13" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="P13" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>61.66</v>
       </c>
     </row>
   </sheetData>
@@ -5390,7 +5661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6193,6 +6464,59 @@
       </c>
       <c r="Q15" t="n">
         <v>83.40000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>454</v>
+      </c>
+      <c r="C16" t="n">
+        <v>441.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="F16" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1716384</v>
+      </c>
+      <c r="H16" t="n">
+        <v>860070</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="K16" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="L16" t="n">
+        <v>336.76</v>
+      </c>
+      <c r="M16" t="n">
+        <v>373.91</v>
+      </c>
+      <c r="N16" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="P16" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>88.72</v>
       </c>
     </row>
   </sheetData>
@@ -6206,7 +6530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7009,6 +7333,59 @@
       </c>
       <c r="Q15" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>276.15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>279</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12620332</v>
+      </c>
+      <c r="H16" t="n">
+        <v>13053722</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>317.75</v>
+      </c>
+      <c r="M16" t="n">
+        <v>284.86</v>
+      </c>
+      <c r="N16" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-31.3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -7022,7 +7399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7825,6 +8202,59 @@
       </c>
       <c r="Q15" t="n">
         <v>14.78</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>915.3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>907</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="G16" t="n">
+        <v>270044</v>
+      </c>
+      <c r="H16" t="n">
+        <v>406109</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K16" t="n">
+        <v>44</v>
+      </c>
+      <c r="L16" t="n">
+        <v>944.21</v>
+      </c>
+      <c r="M16" t="n">
+        <v>917.49</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-24.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>15.83</v>
       </c>
     </row>
   </sheetData>
@@ -7838,7 +8268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8641,6 +9071,59 @@
       </c>
       <c r="Q15" t="n">
         <v>53.82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1026.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="G16" t="n">
+        <v>593498</v>
+      </c>
+      <c r="H16" t="n">
+        <v>470027</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K16" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>937.67</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1053.48</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>50.32</v>
       </c>
     </row>
   </sheetData>
@@ -8654,7 +9137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9457,6 +9940,59 @@
       </c>
       <c r="Q15" t="n">
         <v>68.31999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>72.38</v>
+      </c>
+      <c r="C16" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>18055935</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9888564</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K16" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>58</v>
+      </c>
+      <c r="M16" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="N16" t="n">
+        <v>72.38</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>73.7</v>
       </c>
     </row>
   </sheetData>
@@ -9470,7 +10006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10273,6 +10809,59 @@
       </c>
       <c r="Q15" t="n">
         <v>28.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="G16" t="n">
+        <v>176374</v>
+      </c>
+      <c r="H16" t="n">
+        <v>112092</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="K16" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-45.27</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>27.27</v>
       </c>
     </row>
   </sheetData>
@@ -10286,7 +10875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11089,6 +11678,59 @@
       </c>
       <c r="Q15" t="n">
         <v>57.17</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>868.85</v>
+      </c>
+      <c r="C16" t="n">
+        <v>865.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="G16" t="n">
+        <v>431371</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1063773</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="K16" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>748.35</v>
+      </c>
+      <c r="M16" t="n">
+        <v>842.22</v>
+      </c>
+      <c r="N16" t="n">
+        <v>898.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="P16" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>57.74</v>
       </c>
     </row>
   </sheetData>
@@ -11102,7 +11744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11464,6 +12106,29 @@
         <v>-0.08</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>24435.95</v>
+      </c>
+      <c r="C16" t="n">
+        <v>24471.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DYCL_HIST" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ITC_HIST" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="NATCOPHARM_HIST" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="PREMIERENE_HIST" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="UJJIVANSFB_HIST" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="VISHWARAJ_HIST" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="YATHARTH_HIST" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="NSEI_HIST" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="NSEBANK_HIST" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="BZF_HIST" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="GCF_HIST" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="DJI_HIST" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="INDIAVIX_HIST" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="BFLAFL_HIST" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="RENUKA_HIST" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="SOUTHBANK_HIST" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DYCL_HIST" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ITC_HIST" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NATCOPHARM_HIST" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PREMIERENE_HIST" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UJJIVANSFB_HIST" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VISHWARAJ_HIST" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YATHARTH_HIST" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSEI_HIST" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSEBANK_HIST" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BZF_HIST" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GCF_HIST" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DJI_HIST" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INDIAVIX_HIST" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BFLAFL_HIST" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RENUKA_HIST" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOUTHBANK_HIST" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>455.35</v>
+      </c>
+      <c r="D3" t="n">
         <v>454</v>
       </c>
-      <c r="D3" t="n">
-        <v>441.2</v>
-      </c>
       <c r="E3" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>11.93</v>
+        <v>12.43</v>
       </c>
       <c r="G3" t="n">
-        <v>16.16</v>
+        <v>17.54</v>
       </c>
       <c r="H3" t="n">
-        <v>1716384</v>
+        <v>675974</v>
       </c>
       <c r="I3" t="n">
-        <v>860070</v>
+        <v>1716733</v>
       </c>
       <c r="J3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.84</v>
       </c>
-      <c r="K3" t="n">
-        <v>1.34</v>
-      </c>
       <c r="L3" t="n">
-        <v>70.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>336.76</v>
+        <v>336.8</v>
       </c>
       <c r="N3" t="n">
-        <v>373.91</v>
+        <v>376.54</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-5.28</v>
+        <v>-5</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>88.72</v>
+        <v>89.28</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>46.22</v>
+        <v>45.66</v>
       </c>
       <c r="D4" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7197060</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6627720</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L4" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="N4" t="n">
         <v>45.81</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6627719</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6729091</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>49</v>
-      </c>
-      <c r="M4" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>46.23</v>
-      </c>
       <c r="O4" t="n">
-        <v>48.49</v>
+        <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.68</v>
+        <v>-4.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>28.59</v>
+        <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>61.66</v>
+        <v>61.29</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>278.5</v>
+      </c>
+      <c r="D5" t="n">
         <v>276.15</v>
       </c>
-      <c r="D5" t="n">
-        <v>279</v>
-      </c>
       <c r="E5" t="n">
-        <v>-1.02</v>
+        <v>0.85</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.76</v>
+        <v>-2.59</v>
       </c>
       <c r="G5" t="n">
-        <v>0.22</v>
+        <v>0.67</v>
       </c>
       <c r="H5" t="n">
-        <v>12620332</v>
+        <v>11196589</v>
       </c>
       <c r="I5" t="n">
-        <v>13053722</v>
+        <v>12630816</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="L5" t="n">
-        <v>36.7</v>
+        <v>41.5</v>
       </c>
       <c r="M5" t="n">
-        <v>317.75</v>
+        <v>317.14</v>
       </c>
       <c r="N5" t="n">
-        <v>284.86</v>
+        <v>284.83</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-31.3</v>
+        <v>-30.72</v>
       </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
       <c r="R5" t="n">
-        <v>0.22</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>951.7</v>
+      </c>
+      <c r="D6" t="n">
         <v>915.3</v>
       </c>
-      <c r="D6" t="n">
-        <v>907</v>
-      </c>
       <c r="E6" t="n">
-        <v>0.92</v>
+        <v>3.98</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.25</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.86</v>
+        <v>-2.88</v>
       </c>
       <c r="H6" t="n">
-        <v>270044</v>
+        <v>1199695</v>
       </c>
       <c r="I6" t="n">
-        <v>406109</v>
+        <v>270111</v>
       </c>
       <c r="J6" t="n">
-        <v>0.89</v>
+        <v>4.56</v>
       </c>
       <c r="K6" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
+        <v>56.8</v>
       </c>
       <c r="M6" t="n">
-        <v>944.21</v>
+        <v>943.65</v>
       </c>
       <c r="N6" t="n">
-        <v>917.49</v>
+        <v>917.52</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-24.1</v>
+        <v>-21.09</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>15.83</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="D7" t="n">
         <v>72.38</v>
       </c>
-      <c r="D7" t="n">
-        <v>70.14</v>
-      </c>
       <c r="E7" t="n">
-        <v>3.19</v>
+        <v>-1.64</v>
       </c>
       <c r="F7" t="n">
-        <v>4.01</v>
+        <v>-1.19</v>
       </c>
       <c r="G7" t="n">
-        <v>11.11</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>18055935</v>
+        <v>7789848</v>
       </c>
       <c r="I7" t="n">
-        <v>9888564</v>
+        <v>18062565</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="L7" t="n">
-        <v>65.2</v>
+        <v>60.6</v>
       </c>
       <c r="M7" t="n">
-        <v>58</v>
+        <v>58.03</v>
       </c>
       <c r="N7" t="n">
-        <v>62.68</v>
+        <v>62.79</v>
       </c>
       <c r="O7" t="n">
         <v>72.38</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.64</v>
       </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
       <c r="R7" t="n">
-        <v>73.7</v>
+        <v>70.84</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>845.1</v>
+      </c>
+      <c r="D8" t="n">
         <v>868.85</v>
       </c>
-      <c r="D8" t="n">
-        <v>865.7</v>
-      </c>
       <c r="E8" t="n">
-        <v>0.36</v>
+        <v>-2.73</v>
       </c>
       <c r="F8" t="n">
-        <v>1.22</v>
+        <v>-3.02</v>
       </c>
       <c r="G8" t="n">
-        <v>4.78</v>
+        <v>1.92</v>
       </c>
       <c r="H8" t="n">
-        <v>431371</v>
+        <v>443733</v>
       </c>
       <c r="I8" t="n">
-        <v>1063773</v>
+        <v>431376</v>
       </c>
       <c r="J8" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.74</v>
+        <v>-0.17</v>
       </c>
       <c r="L8" t="n">
-        <v>56.1</v>
+        <v>48.7</v>
       </c>
       <c r="M8" t="n">
-        <v>748.35</v>
+        <v>748.33</v>
       </c>
       <c r="N8" t="n">
-        <v>842.22</v>
+        <v>842.15</v>
       </c>
       <c r="O8" t="n">
         <v>898.75</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.33</v>
+        <v>-5.97</v>
       </c>
       <c r="Q8" t="n">
         <v>550.8</v>
       </c>
       <c r="R8" t="n">
-        <v>57.74</v>
+        <v>53.43</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D10" t="n">
         <v>7.92</v>
       </c>
-      <c r="D10" t="n">
-        <v>8.300000000000001</v>
-      </c>
       <c r="E10" t="n">
-        <v>-4.58</v>
+        <v>3.54</v>
       </c>
       <c r="F10" t="n">
-        <v>5.46</v>
+        <v>3.8</v>
       </c>
       <c r="G10" t="n">
-        <v>13.14</v>
+        <v>17.65</v>
       </c>
       <c r="H10" t="n">
+        <v>1005</v>
+      </c>
+      <c r="I10" t="n">
         <v>20309</v>
       </c>
-      <c r="I10" t="n">
-        <v>41816</v>
-      </c>
       <c r="J10" t="n">
-        <v>2.75</v>
+        <v>0.12</v>
       </c>
       <c r="K10" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="L10" t="n">
-        <v>61.4</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="N10" t="n">
-        <v>6.68</v>
+        <v>6.69</v>
       </c>
       <c r="O10" t="n">
         <v>14.21</v>
       </c>
       <c r="P10" t="n">
-        <v>-44.26</v>
+        <v>-42.29</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>49.72</v>
+        <v>55.01</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1035.8</v>
+      </c>
+      <c r="D11" t="n">
         <v>1026.1</v>
       </c>
-      <c r="D11" t="n">
-        <v>1050</v>
-      </c>
       <c r="E11" t="n">
-        <v>-2.28</v>
+        <v>0.95</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.71</v>
+        <v>-0.57</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.79</v>
+        <v>-5.91</v>
       </c>
       <c r="H11" t="n">
-        <v>593498</v>
+        <v>294645</v>
       </c>
       <c r="I11" t="n">
-        <v>470027</v>
+        <v>595125</v>
       </c>
       <c r="J11" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.12</v>
+        <v>0.59</v>
       </c>
       <c r="L11" t="n">
-        <v>45.7</v>
+        <v>48.2</v>
       </c>
       <c r="M11" t="n">
-        <v>937.67</v>
+        <v>937.74</v>
       </c>
       <c r="N11" t="n">
-        <v>1053.48</v>
+        <v>1053.75</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-8.15</v>
+        <v>-7.29</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>50.32</v>
+        <v>51.74</v>
       </c>
     </row>
     <row r="12">
@@ -1033,34 +1033,34 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="D12" t="n">
         <v>21.99</v>
       </c>
-      <c r="D12" t="n">
-        <v>22.19</v>
-      </c>
       <c r="E12" t="n">
-        <v>-0.9</v>
+        <v>0.59</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.52</v>
+        <v>-0</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.21</v>
+        <v>-2.64</v>
       </c>
       <c r="H12" t="n">
-        <v>2749816</v>
+        <v>5473387</v>
       </c>
       <c r="I12" t="n">
-        <v>2348989</v>
+        <v>2750061</v>
       </c>
       <c r="J12" t="n">
-        <v>0.75</v>
+        <v>1.48</v>
       </c>
       <c r="K12" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>44.9</v>
+        <v>46.9</v>
       </c>
       <c r="M12" t="n">
         <v>25.12</v>
@@ -1072,13 +1072,13 @@
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-32.4</v>
+        <v>-32</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>2.33</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.32</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.39</v>
-      </c>
       <c r="E13" t="n">
-        <v>-1.3</v>
+        <v>2.44</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.74</v>
+        <v>2.83</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.48</v>
+        <v>0.55</v>
       </c>
       <c r="H13" t="n">
-        <v>176374</v>
+        <v>578713</v>
       </c>
       <c r="I13" t="n">
-        <v>112092</v>
+        <v>177684</v>
       </c>
       <c r="J13" t="n">
-        <v>1.04</v>
+        <v>3.67</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.85</v>
+        <v>0.76</v>
       </c>
       <c r="L13" t="n">
-        <v>48.3</v>
+        <v>54.3</v>
       </c>
       <c r="M13" t="n">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="N13" t="n">
-        <v>5.44</v>
+        <v>5.46</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-45.27</v>
+        <v>-43.93</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>27.27</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24395.85</v>
+      </c>
+      <c r="D17" t="n">
         <v>24435.95</v>
       </c>
-      <c r="D17" t="n">
-        <v>24471.7</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.77</v>
+        <v>-0.97</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6</v>
+        <v>0.78</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57635.25</v>
+      </c>
+      <c r="D18" t="n">
         <v>57885.85</v>
       </c>
-      <c r="D18" t="n">
-        <v>57446.25</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.77</v>
+        <v>-0.43</v>
       </c>
       <c r="F18" t="n">
-        <v>0.25</v>
+        <v>-0.74</v>
       </c>
       <c r="G18" t="n">
-        <v>0.74</v>
+        <v>-0.71</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>88.56999999999999</v>
+        <v>86.42</v>
       </c>
       <c r="D19" t="n">
-        <v>88.91</v>
+        <v>88.98</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.38</v>
+        <v>-2.88</v>
       </c>
       <c r="F19" t="n">
-        <v>11.48</v>
+        <v>4.76</v>
       </c>
       <c r="G19" t="n">
-        <v>4.53</v>
+        <v>1.73</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4496.6</v>
+        <v>4428.5</v>
       </c>
       <c r="D20" t="n">
-        <v>4383</v>
+        <v>4408.9</v>
       </c>
       <c r="E20" t="n">
-        <v>2.59</v>
+        <v>0.44</v>
       </c>
       <c r="F20" t="n">
-        <v>5.91</v>
+        <v>4.4</v>
       </c>
       <c r="G20" t="n">
-        <v>10.72</v>
+        <v>9.51</v>
       </c>
       <c r="H20" t="n">
-        <v>1.69</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53795.51</v>
+        <v>53964.83</v>
       </c>
       <c r="D21" t="n">
-        <v>53791.85</v>
+        <v>53770.27</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01</v>
+        <v>0.36</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.02</v>
+        <v>0.15</v>
       </c>
       <c r="G21" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="H21" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.69</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.86</v>
-      </c>
       <c r="E22" t="n">
-        <v>-1.43</v>
+        <v>-2.31</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.07</v>
+        <v>-6.09</v>
       </c>
       <c r="G22" t="n">
-        <v>-14.98</v>
+        <v>-6.78</v>
       </c>
       <c r="H22" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1764,6 +1764,29 @@
       </c>
       <c r="G16" t="n">
         <v>-0.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57635.25</v>
+      </c>
+      <c r="C17" t="n">
+        <v>57885.85</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.22</v>
       </c>
     </row>
   </sheetData>
@@ -1777,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2160,6 +2183,29 @@
       </c>
       <c r="G16" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="C17" t="n">
+        <v>88.98</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -2173,7 +2219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2556,6 +2602,29 @@
       </c>
       <c r="G16" t="n">
         <v>1.69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4428.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4408.9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>
@@ -2569,7 +2638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2952,6 +3021,29 @@
       </c>
       <c r="G16" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>53964.83</v>
+      </c>
+      <c r="C17" t="n">
+        <v>53770.27</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
@@ -2965,7 +3057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3304,8 +3396,28 @@
       <c r="F16" t="n">
         <v>-14.98</v>
       </c>
-      <c r="G16" t="n">
-        <v/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="C17" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-6.09</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-6.78</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3319,7 +3431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4122,6 +4234,59 @@
       </c>
       <c r="Q15" t="n">
         <v>49.72</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>20309</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K16" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="N16" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-42.29</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>55.01</v>
       </c>
     </row>
   </sheetData>
@@ -4135,7 +4300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4938,6 +5103,59 @@
       </c>
       <c r="Q15" t="n">
         <v>2.33</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B16" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="C16" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5473387</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2750061</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="M16" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="N16" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-32</v>
+      </c>
+      <c r="P16" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.93</v>
       </c>
     </row>
   </sheetData>
@@ -4951,7 +5169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5648,6 +5866,59 @@
       </c>
       <c r="Q13" t="n">
         <v>61.66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B14" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="C14" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7197060</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6627720</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K14" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="M14" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="N14" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-4.91</v>
+      </c>
+      <c r="P14" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>61.29</v>
       </c>
     </row>
   </sheetData>
@@ -5661,7 +5932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6517,6 +6788,59 @@
       </c>
       <c r="Q16" t="n">
         <v>88.72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>455.35</v>
+      </c>
+      <c r="C17" t="n">
+        <v>454</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="F17" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="G17" t="n">
+        <v>675974</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1716733</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K17" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>336.8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="N17" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>89.28</v>
       </c>
     </row>
   </sheetData>
@@ -6530,7 +6854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7386,6 +7710,59 @@
       </c>
       <c r="Q16" t="n">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>278.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>276.15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11196589</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12630816</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>317.14</v>
+      </c>
+      <c r="M17" t="n">
+        <v>284.83</v>
+      </c>
+      <c r="N17" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-30.72</v>
+      </c>
+      <c r="P17" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.07</v>
       </c>
     </row>
   </sheetData>
@@ -7399,7 +7776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8255,6 +8632,59 @@
       </c>
       <c r="Q16" t="n">
         <v>15.83</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>951.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>915.3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1199695</v>
+      </c>
+      <c r="H17" t="n">
+        <v>270111</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K17" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>943.65</v>
+      </c>
+      <c r="M17" t="n">
+        <v>917.52</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-21.09</v>
+      </c>
+      <c r="P17" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>20.44</v>
       </c>
     </row>
   </sheetData>
@@ -8268,7 +8698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9124,6 +9554,59 @@
       </c>
       <c r="Q16" t="n">
         <v>50.32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1035.8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1026.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="G17" t="n">
+        <v>294645</v>
+      </c>
+      <c r="H17" t="n">
+        <v>595125</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K17" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>937.74</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1053.75</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="P17" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>51.74</v>
       </c>
     </row>
   </sheetData>
@@ -9137,7 +9620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9993,6 +10476,59 @@
       </c>
       <c r="Q16" t="n">
         <v>73.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="C17" t="n">
+        <v>72.38</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7789848</v>
+      </c>
+      <c r="H17" t="n">
+        <v>18062565</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K17" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>58.03</v>
+      </c>
+      <c r="M17" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="N17" t="n">
+        <v>72.38</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="P17" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>70.84</v>
       </c>
     </row>
   </sheetData>
@@ -10006,7 +10542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10862,6 +11398,59 @@
       </c>
       <c r="Q16" t="n">
         <v>27.27</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G17" t="n">
+        <v>578713</v>
+      </c>
+      <c r="H17" t="n">
+        <v>177684</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K17" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="N17" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-43.93</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>30.38</v>
       </c>
     </row>
   </sheetData>
@@ -10875,7 +11464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11731,6 +12320,59 @@
       </c>
       <c r="Q16" t="n">
         <v>57.74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>845.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>868.85</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G17" t="n">
+        <v>443733</v>
+      </c>
+      <c r="H17" t="n">
+        <v>431376</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="K17" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>748.33</v>
+      </c>
+      <c r="M17" t="n">
+        <v>842.15</v>
+      </c>
+      <c r="N17" t="n">
+        <v>898.75</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="P17" t="n">
+        <v>550.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>53.43</v>
       </c>
     </row>
   </sheetData>
@@ -11744,7 +12386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12129,6 +12771,29 @@
         <v>0.01</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>24395.85</v>
+      </c>
+      <c r="C17" t="n">
+        <v>24435.95</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>450.2</v>
+      </c>
+      <c r="D3" t="n">
         <v>455.35</v>
       </c>
-      <c r="D3" t="n">
-        <v>454</v>
-      </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>-1.13</v>
       </c>
       <c r="F3" t="n">
-        <v>12.43</v>
+        <v>12.02</v>
       </c>
       <c r="G3" t="n">
-        <v>17.54</v>
+        <v>16.21</v>
       </c>
       <c r="H3" t="n">
-        <v>675974</v>
+        <v>614375</v>
       </c>
       <c r="I3" t="n">
-        <v>1716733</v>
+        <v>676050</v>
       </c>
       <c r="J3" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="K3" t="n">
-        <v>0.84</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>70.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>336.8</v>
+        <v>337.07</v>
       </c>
       <c r="N3" t="n">
-        <v>376.54</v>
+        <v>377.64</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-5</v>
+        <v>-6.08</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>89.28</v>
+        <v>87.14</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="D4" t="n">
         <v>45.66</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3365712</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7199181</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="N4" t="n">
         <v>45.77</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-2.79</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7197060</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6627720</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="L4" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>40.94</v>
-      </c>
-      <c r="N4" t="n">
-        <v>45.81</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.91</v>
+        <v>-4.75</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>61.29</v>
+        <v>61.57</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>278.2</v>
+      </c>
+      <c r="D5" t="n">
         <v>278.5</v>
       </c>
-      <c r="D5" t="n">
-        <v>276.15</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.85</v>
+        <v>-0.11</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.59</v>
+        <v>-2.76</v>
       </c>
       <c r="G5" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>11196589</v>
+        <v>7336182</v>
       </c>
       <c r="I5" t="n">
-        <v>12630816</v>
+        <v>11335590</v>
       </c>
       <c r="J5" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="L5" t="n">
-        <v>41.5</v>
+        <v>41.1</v>
       </c>
       <c r="M5" t="n">
-        <v>317.14</v>
+        <v>317.13</v>
       </c>
       <c r="N5" t="n">
-        <v>284.83</v>
+        <v>284.77</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-30.72</v>
+        <v>-30.79</v>
       </c>
       <c r="Q5" t="n">
         <v>275.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.07</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>903.15</v>
+      </c>
+      <c r="D6" t="n">
         <v>951.7</v>
       </c>
-      <c r="D6" t="n">
-        <v>915.3</v>
-      </c>
       <c r="E6" t="n">
-        <v>3.98</v>
+        <v>-5.1</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3</v>
+        <v>-1.47</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.88</v>
+        <v>-7.11</v>
       </c>
       <c r="H6" t="n">
-        <v>1199695</v>
+        <v>2493926</v>
       </c>
       <c r="I6" t="n">
-        <v>270111</v>
+        <v>1200054</v>
       </c>
       <c r="J6" t="n">
-        <v>4.56</v>
+        <v>8.09</v>
       </c>
       <c r="K6" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>56.8</v>
+        <v>42.9</v>
       </c>
       <c r="M6" t="n">
-        <v>943.65</v>
+        <v>944.0599999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>917.52</v>
+        <v>916.89</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-21.09</v>
+        <v>-25.11</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>20.44</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="D7" t="n">
         <v>71.19</v>
       </c>
-      <c r="D7" t="n">
-        <v>72.38</v>
-      </c>
       <c r="E7" t="n">
-        <v>-1.64</v>
+        <v>1.8</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.19</v>
+        <v>3.37</v>
       </c>
       <c r="G7" t="n">
-        <v>9.289999999999999</v>
+        <v>10.62</v>
       </c>
       <c r="H7" t="n">
-        <v>7789848</v>
+        <v>16653713</v>
       </c>
       <c r="I7" t="n">
-        <v>18062565</v>
+        <v>7792102</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="K7" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="L7" t="n">
-        <v>60.6</v>
+        <v>63.6</v>
       </c>
       <c r="M7" t="n">
-        <v>58.03</v>
+        <v>58.12</v>
       </c>
       <c r="N7" t="n">
-        <v>62.79</v>
+        <v>63.17</v>
       </c>
       <c r="O7" t="n">
-        <v>72.38</v>
+        <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.64</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>41.67</v>
       </c>
       <c r="R7" t="n">
-        <v>70.84</v>
+        <v>73.91</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>845.1</v>
+        <v>844.7</v>
       </c>
       <c r="D8" t="n">
-        <v>868.85</v>
+        <v>844.6</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.73</v>
+        <v>0.01</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.02</v>
+        <v>-2.91</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92</v>
+        <v>-1.64</v>
       </c>
       <c r="H8" t="n">
-        <v>443733</v>
+        <v>286054</v>
       </c>
       <c r="I8" t="n">
-        <v>431376</v>
+        <v>444022</v>
       </c>
       <c r="J8" t="n">
-        <v>1.61</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.17</v>
+        <v>0.13</v>
       </c>
       <c r="L8" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="M8" t="n">
-        <v>748.33</v>
+        <v>748.4</v>
       </c>
       <c r="N8" t="n">
-        <v>842.15</v>
+        <v>843.2</v>
       </c>
       <c r="O8" t="n">
-        <v>898.75</v>
+        <v>898.22</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.97</v>
+        <v>-5.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>550.8</v>
+        <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>53.43</v>
+        <v>53.45</v>
       </c>
     </row>
     <row r="9">
@@ -916,43 +916,43 @@
         <v>8.199999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>7.92</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>17.65</v>
       </c>
       <c r="H10" t="n">
+        <v>2541</v>
+      </c>
+      <c r="I10" t="n">
         <v>1005</v>
       </c>
-      <c r="I10" t="n">
-        <v>20309</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="K10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>9.18</v>
+        <v>9.16</v>
       </c>
       <c r="N10" t="n">
-        <v>6.69</v>
+        <v>6.72</v>
       </c>
       <c r="O10" t="n">
-        <v>14.21</v>
+        <v>14.13</v>
       </c>
       <c r="P10" t="n">
-        <v>-42.29</v>
+        <v>-41.97</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1017.3</v>
+      </c>
+      <c r="D11" t="n">
         <v>1035.8</v>
       </c>
-      <c r="D11" t="n">
-        <v>1026.1</v>
-      </c>
       <c r="E11" t="n">
-        <v>0.95</v>
+        <v>-1.79</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.57</v>
+        <v>-2.86</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.91</v>
+        <v>-6.73</v>
       </c>
       <c r="H11" t="n">
-        <v>294645</v>
+        <v>535592</v>
       </c>
       <c r="I11" t="n">
-        <v>595125</v>
+        <v>294930</v>
       </c>
       <c r="J11" t="n">
-        <v>0.28</v>
+        <v>0.52</v>
       </c>
       <c r="K11" t="n">
-        <v>0.59</v>
+        <v>0.02</v>
       </c>
       <c r="L11" t="n">
-        <v>48.2</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>937.74</v>
+        <v>937.33</v>
       </c>
       <c r="N11" t="n">
-        <v>1053.75</v>
+        <v>1052.54</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.29</v>
+        <v>-8.94</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>51.74</v>
+        <v>49.03</v>
       </c>
     </row>
     <row r="12">
@@ -1033,37 +1033,37 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="D12" t="n">
         <v>22.12</v>
       </c>
-      <c r="D12" t="n">
-        <v>21.99</v>
-      </c>
       <c r="E12" t="n">
-        <v>0.59</v>
+        <v>-0.77</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>-0.99</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.64</v>
+        <v>-2.66</v>
       </c>
       <c r="H12" t="n">
-        <v>5473387</v>
+        <v>3606951</v>
       </c>
       <c r="I12" t="n">
-        <v>2750061</v>
+        <v>5479087</v>
       </c>
       <c r="J12" t="n">
-        <v>1.48</v>
+        <v>0.93</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L12" t="n">
-        <v>46.9</v>
+        <v>44.4</v>
       </c>
       <c r="M12" t="n">
-        <v>25.12</v>
+        <v>25.09</v>
       </c>
       <c r="N12" t="n">
         <v>22.47</v>
@@ -1072,13 +1072,13 @@
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-32</v>
+        <v>-32.52</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>2.93</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.45</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.32</v>
-      </c>
       <c r="E13" t="n">
-        <v>2.44</v>
+        <v>-2.94</v>
       </c>
       <c r="F13" t="n">
-        <v>2.83</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.55</v>
+        <v>-2.04</v>
       </c>
       <c r="H13" t="n">
+        <v>250320</v>
+      </c>
+      <c r="I13" t="n">
         <v>578713</v>
       </c>
-      <c r="I13" t="n">
-        <v>177684</v>
-      </c>
       <c r="J13" t="n">
-        <v>3.67</v>
+        <v>1.37</v>
       </c>
       <c r="K13" t="n">
-        <v>0.76</v>
+        <v>-1.92</v>
       </c>
       <c r="L13" t="n">
-        <v>54.3</v>
+        <v>46.2</v>
       </c>
       <c r="M13" t="n">
-        <v>6.06</v>
+        <v>6.05</v>
       </c>
       <c r="N13" t="n">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-43.93</v>
+        <v>-45.58</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>30.38</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24366</v>
+      </c>
+      <c r="D17" t="n">
         <v>24395.85</v>
       </c>
-      <c r="D17" t="n">
-        <v>24435.95</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.16</v>
+        <v>-0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.97</v>
+        <v>-0.83</v>
       </c>
       <c r="G17" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.03</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57491.1</v>
+      </c>
+      <c r="D18" t="n">
         <v>57635.25</v>
       </c>
-      <c r="D18" t="n">
-        <v>57885.85</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.43</v>
+        <v>-0.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.74</v>
+        <v>-0.44</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.71</v>
+        <v>-1.1</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.22</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>86.42</v>
+        <v>87.38</v>
       </c>
       <c r="D19" t="n">
-        <v>88.98</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.88</v>
+        <v>0.36</v>
       </c>
       <c r="F19" t="n">
-        <v>4.76</v>
+        <v>4.58</v>
       </c>
       <c r="G19" t="n">
-        <v>1.73</v>
+        <v>3.74</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.29</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4428.5</v>
+        <v>4446.7</v>
       </c>
       <c r="D20" t="n">
-        <v>4408.9</v>
+        <v>4363.6</v>
       </c>
       <c r="E20" t="n">
-        <v>0.44</v>
+        <v>1.9</v>
       </c>
       <c r="F20" t="n">
-        <v>4.4</v>
+        <v>2.44</v>
       </c>
       <c r="G20" t="n">
-        <v>9.51</v>
+        <v>11.57</v>
       </c>
       <c r="H20" t="n">
-        <v>2.16</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53964.83</v>
+        <v>53804.83</v>
       </c>
       <c r="D21" t="n">
-        <v>53770.27</v>
+        <v>53839.99</v>
       </c>
       <c r="E21" t="n">
-        <v>0.36</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.15</v>
+        <v>-0.43</v>
       </c>
       <c r="G21" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="H21" t="n">
-        <v>0.24</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.42</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.69</v>
-      </c>
       <c r="E22" t="n">
-        <v>-2.31</v>
+        <v>-0.96</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.09</v>
+        <v>-6.99</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.78</v>
+        <v>-12.19</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1787,6 +1787,29 @@
       </c>
       <c r="G17" t="n">
         <v>-0.22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57491.1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>57635.25</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -1800,7 +1823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2206,6 +2229,29 @@
       </c>
       <c r="G17" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="C18" t="n">
+        <v>87.06999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>
@@ -2219,7 +2265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2625,6 +2671,29 @@
       </c>
       <c r="G17" t="n">
         <v>2.16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4446.7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4363.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>
@@ -2638,7 +2707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3044,6 +3113,29 @@
       </c>
       <c r="G17" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>53804.83</v>
+      </c>
+      <c r="C18" t="n">
+        <v>53839.99</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -3057,7 +3149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3418,6 +3510,29 @@
       </c>
       <c r="G17" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="C18" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-12.19</v>
+      </c>
+      <c r="G18" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3431,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4286,6 +4401,59 @@
         <v>5.29</v>
       </c>
       <c r="Q16" t="n">
+        <v>55.01</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2541</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1005</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-41.97</v>
+      </c>
+      <c r="P17" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q17" t="n">
         <v>55.01</v>
       </c>
     </row>
@@ -4300,7 +4468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5119,7 +5287,7 @@
         <v>0.59</v>
       </c>
       <c r="E16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>-2.64</v>
@@ -5156,6 +5324,59 @@
       </c>
       <c r="Q16" t="n">
         <v>2.93</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B17" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="C17" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3606951</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5479087</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="M17" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="N17" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-32.52</v>
+      </c>
+      <c r="P17" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.14</v>
       </c>
     </row>
   </sheetData>
@@ -5169,7 +5390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5919,6 +6140,59 @@
       </c>
       <c r="Q14" t="n">
         <v>61.29</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B15" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="C15" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3365712</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7199181</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="M15" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="N15" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="P15" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>61.57</v>
       </c>
     </row>
   </sheetData>
@@ -5932,7 +6206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6841,6 +7115,59 @@
       </c>
       <c r="Q17" t="n">
         <v>89.28</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>450.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>455.35</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="E18" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="F18" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="G18" t="n">
+        <v>614375</v>
+      </c>
+      <c r="H18" t="n">
+        <v>676050</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="K18" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="L18" t="n">
+        <v>337.07</v>
+      </c>
+      <c r="M18" t="n">
+        <v>377.64</v>
+      </c>
+      <c r="N18" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="P18" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>87.14</v>
       </c>
     </row>
   </sheetData>
@@ -6854,7 +7181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7763,6 +8090,59 @@
       </c>
       <c r="Q17" t="n">
         <v>1.07</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>278.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>278.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7336182</v>
+      </c>
+      <c r="H18" t="n">
+        <v>11335590</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>317.13</v>
+      </c>
+      <c r="M18" t="n">
+        <v>284.77</v>
+      </c>
+      <c r="N18" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-30.79</v>
+      </c>
+      <c r="P18" t="n">
+        <v>275.55</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -7776,7 +8156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8685,6 +9065,59 @@
       </c>
       <c r="Q17" t="n">
         <v>20.44</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>903.15</v>
+      </c>
+      <c r="C18" t="n">
+        <v>951.7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-7.11</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2493926</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1200054</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>944.0599999999999</v>
+      </c>
+      <c r="M18" t="n">
+        <v>916.89</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-25.11</v>
+      </c>
+      <c r="P18" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>14.3</v>
       </c>
     </row>
   </sheetData>
@@ -8698,7 +9131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9607,6 +10040,59 @@
       </c>
       <c r="Q17" t="n">
         <v>51.74</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1017.3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1035.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-6.73</v>
+      </c>
+      <c r="G18" t="n">
+        <v>535592</v>
+      </c>
+      <c r="H18" t="n">
+        <v>294930</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K18" t="n">
+        <v>44</v>
+      </c>
+      <c r="L18" t="n">
+        <v>937.33</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1052.54</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-8.94</v>
+      </c>
+      <c r="P18" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>49.03</v>
       </c>
     </row>
   </sheetData>
@@ -9620,7 +10106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10529,6 +11015,59 @@
       </c>
       <c r="Q17" t="n">
         <v>70.84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="C18" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="G18" t="n">
+        <v>16653713</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7792102</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K18" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="M18" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="N18" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>73.91</v>
       </c>
     </row>
   </sheetData>
@@ -10542,7 +11081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11451,6 +11990,59 @@
       </c>
       <c r="Q17" t="n">
         <v>30.38</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="G18" t="n">
+        <v>250320</v>
+      </c>
+      <c r="H18" t="n">
+        <v>578713</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="K18" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-45.58</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>26.56</v>
       </c>
     </row>
   </sheetData>
@@ -11464,7 +12056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12373,6 +12965,59 @@
       </c>
       <c r="Q17" t="n">
         <v>53.43</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>844.7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>844.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="G18" t="n">
+        <v>286054</v>
+      </c>
+      <c r="H18" t="n">
+        <v>444022</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K18" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>748.4</v>
+      </c>
+      <c r="M18" t="n">
+        <v>843.2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>898.22</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="P18" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>53.45</v>
       </c>
     </row>
   </sheetData>
@@ -12386,7 +13031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12794,6 +13439,29 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>24366</v>
+      </c>
+      <c r="C18" t="n">
+        <v>24395.85</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>465.35</v>
+      </c>
+      <c r="D3" t="n">
         <v>450.2</v>
       </c>
-      <c r="D3" t="n">
-        <v>455.35</v>
-      </c>
       <c r="E3" t="n">
-        <v>-1.13</v>
+        <v>3.37</v>
       </c>
       <c r="F3" t="n">
-        <v>12.02</v>
+        <v>10.05</v>
       </c>
       <c r="G3" t="n">
-        <v>16.21</v>
+        <v>20.4</v>
       </c>
       <c r="H3" t="n">
-        <v>614375</v>
+        <v>712810</v>
       </c>
       <c r="I3" t="n">
-        <v>676050</v>
+        <v>614949</v>
       </c>
       <c r="J3" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="L3" t="n">
-        <v>67.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="M3" t="n">
-        <v>337.07</v>
+        <v>337.24</v>
       </c>
       <c r="N3" t="n">
-        <v>377.64</v>
+        <v>382.12</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-6.08</v>
+        <v>-2.92</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>87.14</v>
+        <v>93.44</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45.74</v>
+        <v>45.22</v>
       </c>
       <c r="D4" t="n">
         <v>45.66</v>
       </c>
       <c r="E4" t="n">
-        <v>0.18</v>
+        <v>-0.96</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.08</v>
+        <v>-3.19</v>
       </c>
       <c r="G4" t="n">
-        <v>1.47</v>
+        <v>0.32</v>
       </c>
       <c r="H4" t="n">
-        <v>3365712</v>
+        <v>5695277</v>
       </c>
       <c r="I4" t="n">
         <v>7199181</v>
       </c>
       <c r="J4" t="n">
-        <v>0.27</v>
+        <v>0.45</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.15</v>
+        <v>1.74</v>
       </c>
       <c r="L4" t="n">
-        <v>49.3</v>
+        <v>45.9</v>
       </c>
       <c r="M4" t="n">
-        <v>40.93</v>
+        <v>40.92</v>
       </c>
       <c r="N4" t="n">
-        <v>45.77</v>
+        <v>45.76</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.75</v>
+        <v>-5.83</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>61.57</v>
+        <v>59.73</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>273.05</v>
+      </c>
+      <c r="D5" t="n">
         <v>278.2</v>
       </c>
-      <c r="D5" t="n">
-        <v>278.5</v>
-      </c>
       <c r="E5" t="n">
-        <v>-0.11</v>
+        <v>-1.85</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.76</v>
+        <v>-3.4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5600000000000001</v>
+        <v>-2.26</v>
       </c>
       <c r="H5" t="n">
-        <v>7336182</v>
+        <v>12767180</v>
       </c>
       <c r="I5" t="n">
-        <v>11335590</v>
+        <v>7338537</v>
       </c>
       <c r="J5" t="n">
-        <v>0.47</v>
+        <v>0.82</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>41.1</v>
+        <v>34.6</v>
       </c>
       <c r="M5" t="n">
-        <v>317.13</v>
+        <v>316.5</v>
       </c>
       <c r="N5" t="n">
-        <v>284.77</v>
+        <v>284.62</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-30.79</v>
+        <v>-32.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>275.55</v>
+        <v>273.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>889.8</v>
+      </c>
+      <c r="D6" t="n">
         <v>903.15</v>
       </c>
-      <c r="D6" t="n">
-        <v>951.7</v>
-      </c>
       <c r="E6" t="n">
-        <v>-5.1</v>
+        <v>-1.48</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.47</v>
+        <v>-2.27</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.11</v>
+        <v>-5.84</v>
       </c>
       <c r="H6" t="n">
-        <v>2493926</v>
+        <v>844381</v>
       </c>
       <c r="I6" t="n">
-        <v>1200054</v>
+        <v>2494304</v>
       </c>
       <c r="J6" t="n">
-        <v>8.09</v>
+        <v>1.85</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-1.91</v>
       </c>
       <c r="L6" t="n">
-        <v>42.9</v>
+        <v>39.7</v>
       </c>
       <c r="M6" t="n">
-        <v>944.0599999999999</v>
+        <v>945.58</v>
       </c>
       <c r="N6" t="n">
-        <v>916.89</v>
+        <v>918.78</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-25.11</v>
+        <v>-26.22</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>14.3</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>72.20999999999999</v>
+      </c>
+      <c r="D7" t="n">
         <v>72.47</v>
       </c>
-      <c r="D7" t="n">
-        <v>71.19</v>
-      </c>
       <c r="E7" t="n">
-        <v>1.8</v>
+        <v>-0.36</v>
       </c>
       <c r="F7" t="n">
-        <v>3.37</v>
+        <v>3.51</v>
       </c>
       <c r="G7" t="n">
-        <v>10.62</v>
+        <v>10.04</v>
       </c>
       <c r="H7" t="n">
-        <v>16653713</v>
+        <v>9089543</v>
       </c>
       <c r="I7" t="n">
-        <v>7792102</v>
+        <v>16653738</v>
       </c>
       <c r="J7" t="n">
-        <v>0.64</v>
+        <v>0.35</v>
       </c>
       <c r="K7" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="L7" t="n">
-        <v>63.6</v>
+        <v>62.6</v>
       </c>
       <c r="M7" t="n">
-        <v>58.12</v>
+        <v>58.22</v>
       </c>
       <c r="N7" t="n">
-        <v>63.17</v>
+        <v>63.55</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.67</v>
+        <v>42.43</v>
       </c>
       <c r="R7" t="n">
-        <v>73.91</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>842.85</v>
+      </c>
+      <c r="D8" t="n">
         <v>844.7</v>
       </c>
-      <c r="D8" t="n">
-        <v>844.6</v>
-      </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>-0.22</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.91</v>
+        <v>-6.16</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.64</v>
+        <v>-1.86</v>
       </c>
       <c r="H8" t="n">
-        <v>286054</v>
+        <v>191336</v>
       </c>
       <c r="I8" t="n">
-        <v>444022</v>
+        <v>286086</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="K8" t="n">
-        <v>0.13</v>
+        <v>1.28</v>
       </c>
       <c r="L8" t="n">
-        <v>48.6</v>
+        <v>48.2</v>
       </c>
       <c r="M8" t="n">
-        <v>748.4</v>
+        <v>748.37</v>
       </c>
       <c r="N8" t="n">
-        <v>843.2</v>
+        <v>843.09</v>
       </c>
       <c r="O8" t="n">
         <v>898.22</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.96</v>
+        <v>-6.16</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>53.45</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="D10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-3.66</v>
       </c>
       <c r="F10" t="n">
-        <v>8.609999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="G10" t="n">
-        <v>17.65</v>
+        <v>13.34</v>
       </c>
       <c r="H10" t="n">
+        <v>1589</v>
+      </c>
+      <c r="I10" t="n">
         <v>2541</v>
       </c>
-      <c r="I10" t="n">
-        <v>1005</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>64.09999999999999</v>
+        <v>58.5</v>
       </c>
       <c r="M10" t="n">
-        <v>9.16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>6.72</v>
+        <v>6.75</v>
       </c>
       <c r="O10" t="n">
         <v>14.13</v>
       </c>
       <c r="P10" t="n">
-        <v>-41.97</v>
+        <v>-44.09</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>55.01</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1015.5</v>
+      </c>
+      <c r="D11" t="n">
         <v>1017.3</v>
       </c>
-      <c r="D11" t="n">
-        <v>1035.8</v>
-      </c>
       <c r="E11" t="n">
-        <v>-1.79</v>
+        <v>-0.18</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.86</v>
+        <v>-2.74</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.73</v>
+        <v>-7.73</v>
       </c>
       <c r="H11" t="n">
-        <v>535592</v>
+        <v>430621</v>
       </c>
       <c r="I11" t="n">
-        <v>294930</v>
+        <v>535800</v>
       </c>
       <c r="J11" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02</v>
+        <v>0.29</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="M11" t="n">
-        <v>937.33</v>
+        <v>936.96</v>
       </c>
       <c r="N11" t="n">
-        <v>1052.54</v>
+        <v>1051.25</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-8.94</v>
+        <v>-9.1</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>49.03</v>
+        <v>48.77</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" t="n">
         <v>21.95</v>
       </c>
-      <c r="D12" t="n">
-        <v>22.12</v>
-      </c>
       <c r="E12" t="n">
-        <v>-0.77</v>
+        <v>4.78</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.99</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.66</v>
+        <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>3606951</v>
+        <v>12856046</v>
       </c>
       <c r="I12" t="n">
-        <v>5479087</v>
+        <v>3607964</v>
       </c>
       <c r="J12" t="n">
-        <v>0.93</v>
+        <v>3.27</v>
       </c>
       <c r="K12" t="n">
-        <v>0.25</v>
+        <v>0.84</v>
       </c>
       <c r="L12" t="n">
-        <v>44.4</v>
+        <v>58.9</v>
       </c>
       <c r="M12" t="n">
-        <v>25.09</v>
+        <v>25.05</v>
       </c>
       <c r="N12" t="n">
-        <v>22.47</v>
+        <v>22.48</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-32.52</v>
+        <v>-29.3</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>2.14</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.29</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.45</v>
-      </c>
       <c r="E13" t="n">
-        <v>-2.94</v>
+        <v>1.51</v>
       </c>
       <c r="F13" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.04</v>
+        <v>1.7</v>
       </c>
       <c r="H13" t="n">
+        <v>196031</v>
+      </c>
+      <c r="I13" t="n">
         <v>250320</v>
       </c>
-      <c r="I13" t="n">
-        <v>578713</v>
-      </c>
       <c r="J13" t="n">
-        <v>1.37</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.92</v>
+        <v>0.16</v>
       </c>
       <c r="L13" t="n">
-        <v>46.2</v>
+        <v>50.8</v>
       </c>
       <c r="M13" t="n">
-        <v>6.05</v>
+        <v>6.01</v>
       </c>
       <c r="N13" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-45.58</v>
+        <v>-44.75</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>26.56</v>
+        <v>28.47</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24287.65</v>
+      </c>
+      <c r="D17" t="n">
         <v>24366</v>
       </c>
-      <c r="D17" t="n">
-        <v>24395.85</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.12</v>
+        <v>-0.32</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.83</v>
+        <v>-1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.64</v>
+        <v>0.98</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.25</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57497.8</v>
+      </c>
+      <c r="D18" t="n">
         <v>57491.1</v>
       </c>
-      <c r="D18" t="n">
-        <v>57635.25</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.25</v>
+        <v>0.01</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.44</v>
+        <v>-0.33</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1</v>
+        <v>0.06</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.12</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>87.38</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>87.06999999999999</v>
+        <v>88.52</v>
       </c>
       <c r="E19" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="n">
-        <v>4.58</v>
+        <v>1.41</v>
       </c>
       <c r="G19" t="n">
-        <v>3.74</v>
+        <v>0.98</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.11</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4446.7</v>
+        <v>4460.5</v>
       </c>
       <c r="D20" t="n">
-        <v>4363.6</v>
+        <v>4380.4</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="F20" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="G20" t="n">
-        <v>11.57</v>
+        <v>11.16</v>
       </c>
       <c r="H20" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="21">
@@ -1322,19 +1322,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53804.83</v>
+        <v>53732.41</v>
       </c>
       <c r="D21" t="n">
         <v>53839.99</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.43</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="H21" t="n">
         <v>0.01</v>
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.31</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.42</v>
-      </c>
       <c r="E22" t="n">
-        <v>-0.96</v>
+        <v>0.09</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.99</v>
+        <v>-7.59</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.19</v>
+        <v>-17.67</v>
       </c>
       <c r="H22" t="n">
-        <v/>
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1810,6 +1810,29 @@
       </c>
       <c r="G18" t="n">
         <v>-0.12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57497.8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>57491.1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -1823,7 +1846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2252,6 +2275,29 @@
       </c>
       <c r="G18" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>88.95999999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>88.52</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -2265,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2694,6 +2740,29 @@
       </c>
       <c r="G18" t="n">
         <v>1.65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4460.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4380.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.03</v>
       </c>
     </row>
   </sheetData>
@@ -3149,7 +3218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3531,8 +3600,28 @@
       <c r="F18" t="n">
         <v>-12.19</v>
       </c>
-      <c r="G18" t="n">
-        <v/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="C19" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-7.59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-17.67</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4455,6 +4544,59 @@
       </c>
       <c r="Q17" t="n">
         <v>55.01</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F18" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1589</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2541</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="N18" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-44.09</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>49.34</v>
       </c>
     </row>
   </sheetData>
@@ -4468,7 +4610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5377,6 +5519,59 @@
       </c>
       <c r="Q17" t="n">
         <v>2.14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B18" t="n">
+        <v>23</v>
+      </c>
+      <c r="C18" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12856046</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3607964</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K18" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="N18" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-29.3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7.03</v>
       </c>
     </row>
   </sheetData>
@@ -5390,7 +5585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6193,6 +6388,59 @@
       </c>
       <c r="Q15" t="n">
         <v>61.57</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B16" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="C16" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5695277</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7199181</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K16" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="M16" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="N16" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-5.83</v>
+      </c>
+      <c r="P16" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>59.73</v>
       </c>
     </row>
   </sheetData>
@@ -6206,7 +6454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7168,6 +7416,59 @@
       </c>
       <c r="Q18" t="n">
         <v>87.14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>465.35</v>
+      </c>
+      <c r="C19" t="n">
+        <v>450.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="F19" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>712810</v>
+      </c>
+      <c r="H19" t="n">
+        <v>614949</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K19" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>337.24</v>
+      </c>
+      <c r="M19" t="n">
+        <v>382.12</v>
+      </c>
+      <c r="N19" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="P19" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>93.44</v>
       </c>
     </row>
   </sheetData>
@@ -7181,7 +7482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8143,6 +8444,59 @@
       </c>
       <c r="Q18" t="n">
         <v>0.96</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>273.05</v>
+      </c>
+      <c r="C19" t="n">
+        <v>278.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12767180</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7338537</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>284.62</v>
+      </c>
+      <c r="N19" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-32.08</v>
+      </c>
+      <c r="P19" t="n">
+        <v>273.05</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8156,7 +8510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9118,6 +9472,59 @@
       </c>
       <c r="Q18" t="n">
         <v>14.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>889.8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>903.15</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-5.84</v>
+      </c>
+      <c r="G19" t="n">
+        <v>844381</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2494304</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="K19" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>945.58</v>
+      </c>
+      <c r="M19" t="n">
+        <v>918.78</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-26.22</v>
+      </c>
+      <c r="P19" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>12.61</v>
       </c>
     </row>
   </sheetData>
@@ -9131,7 +9538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10093,6 +10500,59 @@
       </c>
       <c r="Q18" t="n">
         <v>49.03</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1015.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1017.3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-7.73</v>
+      </c>
+      <c r="G19" t="n">
+        <v>430621</v>
+      </c>
+      <c r="H19" t="n">
+        <v>535800</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K19" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>936.96</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1051.25</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>48.77</v>
       </c>
     </row>
   </sheetData>
@@ -10106,7 +10566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11068,6 +11528,59 @@
       </c>
       <c r="Q18" t="n">
         <v>73.91</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>72.20999999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9089543</v>
+      </c>
+      <c r="H19" t="n">
+        <v>16653738</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="M19" t="n">
+        <v>63.55</v>
+      </c>
+      <c r="N19" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="P19" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>70.19</v>
       </c>
     </row>
   </sheetData>
@@ -11081,7 +11594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12043,6 +12556,59 @@
       </c>
       <c r="Q18" t="n">
         <v>26.56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>196031</v>
+      </c>
+      <c r="H19" t="n">
+        <v>250320</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K19" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-44.75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>28.47</v>
       </c>
     </row>
   </sheetData>
@@ -12056,7 +12622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13018,6 +13584,59 @@
       </c>
       <c r="Q18" t="n">
         <v>53.45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>842.85</v>
+      </c>
+      <c r="C19" t="n">
+        <v>844.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="G19" t="n">
+        <v>191336</v>
+      </c>
+      <c r="H19" t="n">
+        <v>286086</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K19" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>748.37</v>
+      </c>
+      <c r="M19" t="n">
+        <v>843.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>898.22</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="P19" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>53.11</v>
       </c>
     </row>
   </sheetData>
@@ -13031,7 +13650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13462,6 +14081,29 @@
         <v>-0.25</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>24287.65</v>
+      </c>
+      <c r="C19" t="n">
+        <v>24366</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>452.9</v>
+      </c>
+      <c r="D3" t="n">
         <v>465.35</v>
       </c>
-      <c r="D3" t="n">
-        <v>450.2</v>
-      </c>
       <c r="E3" t="n">
-        <v>3.37</v>
+        <v>-2.68</v>
       </c>
       <c r="F3" t="n">
-        <v>10.05</v>
+        <v>2.65</v>
       </c>
       <c r="G3" t="n">
-        <v>20.4</v>
+        <v>17.18</v>
       </c>
       <c r="H3" t="n">
-        <v>712810</v>
+        <v>396701</v>
       </c>
       <c r="I3" t="n">
-        <v>614949</v>
+        <v>713278</v>
       </c>
       <c r="J3" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="K3" t="n">
-        <v>1.04</v>
+        <v>-0.27</v>
       </c>
       <c r="L3" t="n">
-        <v>71.2</v>
+        <v>64.5</v>
       </c>
       <c r="M3" t="n">
-        <v>337.24</v>
+        <v>337.53</v>
       </c>
       <c r="N3" t="n">
-        <v>382.12</v>
+        <v>383.28</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.92</v>
+        <v>-5.51</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>93.44</v>
+        <v>88.26000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="D4" t="n">
         <v>45.22</v>
       </c>
-      <c r="D4" t="n">
-        <v>45.66</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.96</v>
+        <v>-0.29</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.19</v>
+        <v>-1.01</v>
       </c>
       <c r="G4" t="n">
         <v>0.32</v>
       </c>
       <c r="H4" t="n">
-        <v>5695277</v>
+        <v>5224300</v>
       </c>
       <c r="I4" t="n">
-        <v>7199181</v>
+        <v>5696877</v>
       </c>
       <c r="J4" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="K4" t="n">
-        <v>1.74</v>
+        <v>-0.05</v>
       </c>
       <c r="L4" t="n">
-        <v>45.9</v>
+        <v>45</v>
       </c>
       <c r="M4" t="n">
-        <v>40.92</v>
+        <v>40.96</v>
       </c>
       <c r="N4" t="n">
-        <v>45.76</v>
+        <v>45.79</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.83</v>
+        <v>-6.1</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>59.73</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="5">
@@ -666,49 +666,49 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>270</v>
+      </c>
+      <c r="D5" t="n">
         <v>273.05</v>
       </c>
-      <c r="D5" t="n">
-        <v>278.2</v>
-      </c>
       <c r="E5" t="n">
-        <v>-1.85</v>
+        <v>-1.12</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.4</v>
+        <v>-3.23</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.26</v>
+        <v>-3.81</v>
       </c>
       <c r="H5" t="n">
-        <v>12767180</v>
+        <v>14222864</v>
       </c>
       <c r="I5" t="n">
-        <v>7338537</v>
+        <v>12795275</v>
       </c>
       <c r="J5" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>34.6</v>
+        <v>31.5</v>
       </c>
       <c r="M5" t="n">
-        <v>316.5</v>
+        <v>315.84</v>
       </c>
       <c r="N5" t="n">
-        <v>284.62</v>
+        <v>284.43</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-32.08</v>
+        <v>-32.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>273.05</v>
+        <v>270</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>898.35</v>
+      </c>
+      <c r="D6" t="n">
         <v>889.8</v>
       </c>
-      <c r="D6" t="n">
-        <v>903.15</v>
-      </c>
       <c r="E6" t="n">
-        <v>-1.48</v>
+        <v>0.96</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.27</v>
+        <v>-1.33</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.84</v>
+        <v>-7.36</v>
       </c>
       <c r="H6" t="n">
-        <v>844381</v>
+        <v>280967</v>
       </c>
       <c r="I6" t="n">
-        <v>2494304</v>
+        <v>844481</v>
       </c>
       <c r="J6" t="n">
-        <v>1.85</v>
+        <v>0.83</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.91</v>
+        <v>0.06</v>
       </c>
       <c r="L6" t="n">
-        <v>39.7</v>
+        <v>42.7</v>
       </c>
       <c r="M6" t="n">
-        <v>945.58</v>
+        <v>944.37</v>
       </c>
       <c r="N6" t="n">
-        <v>918.78</v>
+        <v>916.22</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-26.22</v>
+        <v>-25.51</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>12.61</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="D7" t="n">
         <v>72.20999999999999</v>
       </c>
-      <c r="D7" t="n">
-        <v>72.47</v>
-      </c>
       <c r="E7" t="n">
-        <v>-0.36</v>
+        <v>0.17</v>
       </c>
       <c r="F7" t="n">
-        <v>3.51</v>
+        <v>3.12</v>
       </c>
       <c r="G7" t="n">
-        <v>10.04</v>
+        <v>11.48</v>
       </c>
       <c r="H7" t="n">
-        <v>9089543</v>
+        <v>11366563</v>
       </c>
       <c r="I7" t="n">
-        <v>16653738</v>
+        <v>9089704</v>
       </c>
       <c r="J7" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2</v>
+        <v>-0.28</v>
       </c>
       <c r="L7" t="n">
-        <v>62.6</v>
+        <v>62.9</v>
       </c>
       <c r="M7" t="n">
-        <v>58.22</v>
+        <v>58.32</v>
       </c>
       <c r="N7" t="n">
-        <v>63.55</v>
+        <v>63.95</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.36</v>
+        <v>-0.19</v>
       </c>
       <c r="Q7" t="n">
         <v>42.43</v>
       </c>
       <c r="R7" t="n">
-        <v>70.19</v>
+        <v>70.47</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>854</v>
+      </c>
+      <c r="D8" t="n">
         <v>842.85</v>
       </c>
-      <c r="D8" t="n">
-        <v>844.7</v>
-      </c>
       <c r="E8" t="n">
-        <v>-0.22</v>
+        <v>1.32</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.16</v>
+        <v>-1.29</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.86</v>
+        <v>1.24</v>
       </c>
       <c r="H8" t="n">
-        <v>191336</v>
+        <v>218146</v>
       </c>
       <c r="I8" t="n">
-        <v>286086</v>
+        <v>191341</v>
       </c>
       <c r="J8" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="K8" t="n">
-        <v>1.28</v>
+        <v>-1.01</v>
       </c>
       <c r="L8" t="n">
-        <v>48.2</v>
+        <v>51.8</v>
       </c>
       <c r="M8" t="n">
-        <v>748.37</v>
+        <v>748.67</v>
       </c>
       <c r="N8" t="n">
-        <v>843.09</v>
+        <v>843.84</v>
       </c>
       <c r="O8" t="n">
         <v>898.22</v>
       </c>
       <c r="P8" t="n">
-        <v>-6.16</v>
+        <v>-4.92</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>53.11</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="D10" t="n">
         <v>7.9</v>
       </c>
-      <c r="D10" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="E10" t="n">
-        <v>-3.66</v>
+        <v>0.89</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.25</v>
+        <v>-3.98</v>
       </c>
       <c r="G10" t="n">
-        <v>13.34</v>
+        <v>14.35</v>
       </c>
       <c r="H10" t="n">
+        <v>2283</v>
+      </c>
+      <c r="I10" t="n">
         <v>1589</v>
       </c>
-      <c r="I10" t="n">
-        <v>2541</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="L10" t="n">
-        <v>58.5</v>
+        <v>59.3</v>
       </c>
       <c r="M10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="N10" t="n">
-        <v>6.75</v>
+        <v>6.77</v>
       </c>
       <c r="O10" t="n">
         <v>14.13</v>
       </c>
       <c r="P10" t="n">
-        <v>-44.09</v>
+        <v>-43.6</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>49.34</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1014.7</v>
+      </c>
+      <c r="D11" t="n">
         <v>1015.5</v>
       </c>
-      <c r="D11" t="n">
-        <v>1017.3</v>
-      </c>
       <c r="E11" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.74</v>
+        <v>-3.36</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.73</v>
+        <v>-6.58</v>
       </c>
       <c r="H11" t="n">
-        <v>430621</v>
+        <v>538817</v>
       </c>
       <c r="I11" t="n">
-        <v>535800</v>
+        <v>430713</v>
       </c>
       <c r="J11" t="n">
-        <v>0.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="L11" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="M11" t="n">
-        <v>936.96</v>
+        <v>936.54</v>
       </c>
       <c r="N11" t="n">
-        <v>1051.25</v>
+        <v>1049.73</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-9.1</v>
+        <v>-9.17</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>48.77</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D12" t="n">
         <v>23</v>
       </c>
-      <c r="D12" t="n">
-        <v>21.95</v>
-      </c>
       <c r="E12" t="n">
-        <v>4.78</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.04</v>
+        <v>4.16</v>
       </c>
       <c r="H12" t="n">
-        <v>12856046</v>
+        <v>13988980</v>
       </c>
       <c r="I12" t="n">
-        <v>3607964</v>
+        <v>12864772</v>
       </c>
       <c r="J12" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="K12" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>58.9</v>
+        <v>61.9</v>
       </c>
       <c r="M12" t="n">
-        <v>25.05</v>
+        <v>25.02</v>
       </c>
       <c r="N12" t="n">
-        <v>22.48</v>
+        <v>22.5</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-29.3</v>
+        <v>-28.37</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>7.03</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.37</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.29</v>
-      </c>
       <c r="E13" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="H13" t="n">
-        <v>196031</v>
+        <v>595969</v>
       </c>
       <c r="I13" t="n">
-        <v>250320</v>
+        <v>196403</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>50.8</v>
+        <v>53.9</v>
       </c>
       <c r="M13" t="n">
-        <v>6.01</v>
+        <v>6.02</v>
       </c>
       <c r="N13" t="n">
-        <v>5.42</v>
+        <v>5.44</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-44.75</v>
+        <v>-43.93</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>28.47</v>
+        <v>30.38</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24287.65</v>
+        <v>24154.9</v>
       </c>
       <c r="D17" t="n">
         <v>24366</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.32</v>
+        <v>-0.87</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2</v>
+        <v>-1.74</v>
       </c>
       <c r="G17" t="n">
-        <v>0.98</v>
+        <v>0.43</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.17</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57497.8</v>
+        <v>57262.4</v>
       </c>
       <c r="D18" t="n">
         <v>57491.1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01</v>
+        <v>-0.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.33</v>
+        <v>-0.74</v>
       </c>
       <c r="G18" t="n">
-        <v>0.06</v>
+        <v>-0.35</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.19</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>88.95999999999999</v>
+        <v>90.88</v>
       </c>
       <c r="D19" t="n">
-        <v>88.52</v>
+        <v>90.87</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="F19" t="n">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="G19" t="n">
-        <v>0.98</v>
+        <v>1.86</v>
       </c>
       <c r="H19" t="n">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4460.5</v>
+        <v>4445.3</v>
       </c>
       <c r="D20" t="n">
-        <v>4380.4</v>
+        <v>4417.8</v>
       </c>
       <c r="E20" t="n">
-        <v>1.83</v>
+        <v>0.62</v>
       </c>
       <c r="F20" t="n">
-        <v>2.26</v>
+        <v>1.42</v>
       </c>
       <c r="G20" t="n">
-        <v>11.16</v>
+        <v>10.85</v>
       </c>
       <c r="H20" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="21">
@@ -1321,23 +1321,8 @@
           <t>^DJI</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>53732.41</v>
-      </c>
-      <c r="D21" t="n">
-        <v>53839.99</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1337,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11.32</v>
+        <v>11.39</v>
       </c>
       <c r="D22" t="n">
         <v>11.31</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09</v>
+        <v>0.71</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.59</v>
+        <v>-7.02</v>
       </c>
       <c r="G22" t="n">
-        <v>-17.67</v>
+        <v>-17.16</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.05</v>
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1833,6 +1818,29 @@
       </c>
       <c r="G19" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57262.4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>57491.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.44</v>
       </c>
     </row>
   </sheetData>
@@ -1846,7 +1854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2298,6 +2306,29 @@
       </c>
       <c r="G19" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90.88</v>
+      </c>
+      <c r="C20" t="n">
+        <v>90.87</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -2311,7 +2342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2763,6 +2794,29 @@
       </c>
       <c r="G19" t="n">
         <v>2.03</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4445.3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4417.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.91</v>
       </c>
     </row>
   </sheetData>
@@ -2776,7 +2830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3205,6 +3259,14 @@
       </c>
       <c r="G18" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C19" t="n">
+        <v>53732.41</v>
       </c>
     </row>
   </sheetData>
@@ -3218,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3622,6 +3684,29 @@
       </c>
       <c r="G19" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="C20" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-17.16</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -3635,7 +3720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4597,6 +4682,59 @@
       </c>
       <c r="Q18" t="n">
         <v>49.34</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2283</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1589</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K19" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="M19" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="N19" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-43.6</v>
+      </c>
+      <c r="P19" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>50.66</v>
       </c>
     </row>
   </sheetData>
@@ -4610,7 +4748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5572,6 +5710,59 @@
       </c>
       <c r="Q18" t="n">
         <v>7.03</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B19" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>23</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13988980</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12864772</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="M19" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-28.37</v>
+      </c>
+      <c r="P19" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>8.42</v>
       </c>
     </row>
   </sheetData>
@@ -5585,7 +5776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6441,6 +6632,59 @@
       </c>
       <c r="Q16" t="n">
         <v>59.73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B17" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="C17" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5224300</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5696877</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K17" t="n">
+        <v>45</v>
+      </c>
+      <c r="L17" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="M17" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="N17" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>59.27</v>
       </c>
     </row>
   </sheetData>
@@ -6454,7 +6698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7469,6 +7713,59 @@
       </c>
       <c r="Q19" t="n">
         <v>93.44</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>452.9</v>
+      </c>
+      <c r="C20" t="n">
+        <v>465.35</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="G20" t="n">
+        <v>396701</v>
+      </c>
+      <c r="H20" t="n">
+        <v>713278</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="K20" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>337.53</v>
+      </c>
+      <c r="M20" t="n">
+        <v>383.28</v>
+      </c>
+      <c r="N20" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-5.51</v>
+      </c>
+      <c r="P20" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>88.26000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7482,7 +7779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8496,6 +8793,59 @@
         <v>273.05</v>
       </c>
       <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>270</v>
+      </c>
+      <c r="C20" t="n">
+        <v>273.05</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14222864</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12795275</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>315.84</v>
+      </c>
+      <c r="M20" t="n">
+        <v>284.43</v>
+      </c>
+      <c r="N20" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-32.83</v>
+      </c>
+      <c r="P20" t="n">
+        <v>270</v>
+      </c>
+      <c r="Q20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8510,7 +8860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9525,6 +9875,59 @@
       </c>
       <c r="Q19" t="n">
         <v>12.61</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>898.35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>889.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-7.36</v>
+      </c>
+      <c r="G20" t="n">
+        <v>280967</v>
+      </c>
+      <c r="H20" t="n">
+        <v>844481</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K20" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>944.37</v>
+      </c>
+      <c r="M20" t="n">
+        <v>916.22</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-25.51</v>
+      </c>
+      <c r="P20" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>13.69</v>
       </c>
     </row>
   </sheetData>
@@ -9538,7 +9941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10553,6 +10956,59 @@
       </c>
       <c r="Q19" t="n">
         <v>48.77</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1014.7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1015.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-6.58</v>
+      </c>
+      <c r="G20" t="n">
+        <v>538817</v>
+      </c>
+      <c r="H20" t="n">
+        <v>430713</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K20" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>936.54</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1049.73</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-9.17</v>
+      </c>
+      <c r="P20" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>48.65</v>
       </c>
     </row>
   </sheetData>
@@ -10566,7 +11022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11581,6 +12037,59 @@
       </c>
       <c r="Q19" t="n">
         <v>70.19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="C20" t="n">
+        <v>72.20999999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11366563</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9089704</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="K20" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="M20" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="N20" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>70.47</v>
       </c>
     </row>
   </sheetData>
@@ -11594,7 +12103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12609,6 +13118,59 @@
       </c>
       <c r="Q19" t="n">
         <v>28.47</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G20" t="n">
+        <v>595969</v>
+      </c>
+      <c r="H20" t="n">
+        <v>196403</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="N20" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-43.93</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>30.38</v>
       </c>
     </row>
   </sheetData>
@@ -12622,7 +13184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13637,6 +14199,59 @@
       </c>
       <c r="Q19" t="n">
         <v>53.11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>854</v>
+      </c>
+      <c r="C20" t="n">
+        <v>842.85</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G20" t="n">
+        <v>218146</v>
+      </c>
+      <c r="H20" t="n">
+        <v>191341</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="K20" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>748.67</v>
+      </c>
+      <c r="M20" t="n">
+        <v>843.84</v>
+      </c>
+      <c r="N20" t="n">
+        <v>898.22</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="P20" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>55.14</v>
       </c>
     </row>
   </sheetData>
@@ -13650,7 +14265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14104,6 +14719,29 @@
         <v>-0.17</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>24154.9</v>
+      </c>
+      <c r="C20" t="n">
+        <v>24366</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>445.95</v>
+      </c>
+      <c r="D3" t="n">
         <v>452.9</v>
       </c>
-      <c r="D3" t="n">
-        <v>465.35</v>
-      </c>
       <c r="E3" t="n">
-        <v>-2.68</v>
+        <v>-1.53</v>
       </c>
       <c r="F3" t="n">
-        <v>2.65</v>
+        <v>-1.77</v>
       </c>
       <c r="G3" t="n">
-        <v>17.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>396701</v>
+        <v>200373</v>
       </c>
       <c r="I3" t="n">
-        <v>713278</v>
+        <v>396713</v>
       </c>
       <c r="J3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.27</v>
+        <v>0.02</v>
       </c>
       <c r="L3" t="n">
-        <v>64.5</v>
+        <v>61.3</v>
       </c>
       <c r="M3" t="n">
-        <v>337.53</v>
+        <v>337.73</v>
       </c>
       <c r="N3" t="n">
-        <v>383.28</v>
+        <v>385.86</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-5.51</v>
+        <v>-6.96</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>88.26000000000001</v>
+        <v>85.37</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D4" t="n">
         <v>45.09</v>
       </c>
-      <c r="D4" t="n">
-        <v>45.22</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.29</v>
+        <v>-0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.01</v>
+        <v>-0.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0.32</v>
+        <v>1.89</v>
       </c>
       <c r="H4" t="n">
-        <v>5224300</v>
+        <v>4426235</v>
       </c>
       <c r="I4" t="n">
-        <v>5696877</v>
+        <v>5224750</v>
       </c>
       <c r="J4" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>45</v>
+        <v>44.4</v>
       </c>
       <c r="M4" t="n">
-        <v>40.96</v>
+        <v>40.99</v>
       </c>
       <c r="N4" t="n">
-        <v>45.79</v>
+        <v>45.82</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.1</v>
+        <v>-6.29</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>59.27</v>
+        <v>58.95</v>
       </c>
     </row>
     <row r="5">
@@ -666,49 +666,49 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>267.05</v>
+      </c>
+      <c r="D5" t="n">
         <v>270</v>
       </c>
-      <c r="D5" t="n">
-        <v>273.05</v>
-      </c>
       <c r="E5" t="n">
-        <v>-1.12</v>
+        <v>-1.09</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.23</v>
+        <v>-3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.81</v>
+        <v>-5.54</v>
       </c>
       <c r="H5" t="n">
-        <v>14222864</v>
+        <v>13812489</v>
       </c>
       <c r="I5" t="n">
-        <v>12795275</v>
+        <v>14561572</v>
       </c>
       <c r="J5" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>31.5</v>
+        <v>28.7</v>
       </c>
       <c r="M5" t="n">
-        <v>315.84</v>
+        <v>315.18</v>
       </c>
       <c r="N5" t="n">
-        <v>284.43</v>
+        <v>284.17</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-32.83</v>
+        <v>-33.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>270</v>
+        <v>267.05</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>886.85</v>
+      </c>
+      <c r="D6" t="n">
         <v>898.35</v>
       </c>
-      <c r="D6" t="n">
-        <v>889.8</v>
-      </c>
       <c r="E6" t="n">
-        <v>0.96</v>
+        <v>-1.28</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.33</v>
+        <v>-2.22</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.36</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>280967</v>
+        <v>317991</v>
       </c>
       <c r="I6" t="n">
-        <v>844481</v>
+        <v>281134</v>
       </c>
       <c r="J6" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7</v>
+        <v>40.2</v>
       </c>
       <c r="M6" t="n">
-        <v>944.37</v>
+        <v>944.6900000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>916.22</v>
+        <v>916.08</v>
       </c>
       <c r="O6" t="n">
         <v>1206</v>
       </c>
       <c r="P6" t="n">
-        <v>-25.51</v>
+        <v>-26.46</v>
       </c>
       <c r="Q6" t="n">
         <v>790.1799999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>13.69</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D7" t="n">
         <v>72.33</v>
       </c>
-      <c r="D7" t="n">
-        <v>72.20999999999999</v>
-      </c>
       <c r="E7" t="n">
-        <v>0.17</v>
+        <v>-0.73</v>
       </c>
       <c r="F7" t="n">
-        <v>3.12</v>
+        <v>-0.8</v>
       </c>
       <c r="G7" t="n">
-        <v>11.48</v>
+        <v>9.4</v>
       </c>
       <c r="H7" t="n">
-        <v>11366563</v>
+        <v>12221760</v>
       </c>
       <c r="I7" t="n">
-        <v>9089704</v>
+        <v>11368755</v>
       </c>
       <c r="J7" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.28</v>
+        <v>0.15</v>
       </c>
       <c r="L7" t="n">
-        <v>62.9</v>
+        <v>60.5</v>
       </c>
       <c r="M7" t="n">
-        <v>58.32</v>
+        <v>58.41</v>
       </c>
       <c r="N7" t="n">
-        <v>63.95</v>
+        <v>64.3</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.19</v>
+        <v>-0.92</v>
       </c>
       <c r="Q7" t="n">
         <v>42.43</v>
       </c>
       <c r="R7" t="n">
-        <v>70.47</v>
+        <v>69.22</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>852.35</v>
+      </c>
+      <c r="D8" t="n">
         <v>854</v>
       </c>
-      <c r="D8" t="n">
-        <v>842.85</v>
-      </c>
       <c r="E8" t="n">
-        <v>1.32</v>
+        <v>-0.19</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.29</v>
+        <v>-1.84</v>
       </c>
       <c r="G8" t="n">
-        <v>1.24</v>
+        <v>-0.51</v>
       </c>
       <c r="H8" t="n">
-        <v>218146</v>
+        <v>149580</v>
       </c>
       <c r="I8" t="n">
-        <v>191341</v>
+        <v>218447</v>
       </c>
       <c r="J8" t="n">
-        <v>0.73</v>
+        <v>0.49</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.01</v>
+        <v>0.24</v>
       </c>
       <c r="L8" t="n">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="M8" t="n">
-        <v>748.67</v>
+        <v>749.25</v>
       </c>
       <c r="N8" t="n">
-        <v>843.84</v>
+        <v>844.49</v>
       </c>
       <c r="O8" t="n">
         <v>898.22</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.92</v>
+        <v>-5.11</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>55.14</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
         <v>7.97</v>
       </c>
-      <c r="D10" t="n">
-        <v>7.9</v>
-      </c>
       <c r="E10" t="n">
-        <v>0.89</v>
+        <v>0.38</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.98</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>14.35</v>
+        <v>11.11</v>
       </c>
       <c r="H10" t="n">
+        <v>2898</v>
+      </c>
+      <c r="I10" t="n">
         <v>2283</v>
       </c>
-      <c r="I10" t="n">
-        <v>1589</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="K10" t="n">
-        <v>0.17</v>
+        <v>0.64</v>
       </c>
       <c r="L10" t="n">
-        <v>59.3</v>
+        <v>60.2</v>
       </c>
       <c r="M10" t="n">
-        <v>9.17</v>
+        <v>9.08</v>
       </c>
       <c r="N10" t="n">
-        <v>6.77</v>
+        <v>6.79</v>
       </c>
       <c r="O10" t="n">
-        <v>14.13</v>
+        <v>13.95</v>
       </c>
       <c r="P10" t="n">
-        <v>-43.6</v>
+        <v>-42.65</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>50.66</v>
+        <v>51.23</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D11" t="n">
         <v>1014.7</v>
       </c>
-      <c r="D11" t="n">
-        <v>1015.5</v>
-      </c>
       <c r="E11" t="n">
-        <v>-0.08</v>
+        <v>-1.25</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.36</v>
+        <v>-2.35</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.58</v>
+        <v>-7.77</v>
       </c>
       <c r="H11" t="n">
+        <v>420896</v>
+      </c>
+      <c r="I11" t="n">
         <v>538817</v>
       </c>
-      <c r="I11" t="n">
-        <v>430713</v>
-      </c>
       <c r="J11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="K11" t="n">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="L11" t="n">
-        <v>43.4</v>
+        <v>40.4</v>
       </c>
       <c r="M11" t="n">
-        <v>936.54</v>
+        <v>936.0599999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>1049.73</v>
+        <v>1048.04</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-9.17</v>
+        <v>-10.31</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>48.65</v>
+        <v>46.79</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="D12" t="n">
         <v>23.3</v>
       </c>
-      <c r="D12" t="n">
-        <v>23</v>
-      </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>4.03</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>10.23</v>
       </c>
       <c r="G12" t="n">
-        <v>4.16</v>
+        <v>9.34</v>
       </c>
       <c r="H12" t="n">
-        <v>13988980</v>
+        <v>67100399</v>
       </c>
       <c r="I12" t="n">
-        <v>12864772</v>
+        <v>14002263</v>
       </c>
       <c r="J12" t="n">
-        <v>3.19</v>
+        <v>13.55</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="L12" t="n">
-        <v>61.9</v>
+        <v>69.5</v>
       </c>
       <c r="M12" t="n">
-        <v>25.02</v>
+        <v>24.99</v>
       </c>
       <c r="N12" t="n">
-        <v>22.5</v>
+        <v>22.55</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-28.37</v>
+        <v>-25.48</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>8.42</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.45</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.37</v>
-      </c>
       <c r="E13" t="n">
-        <v>1.49</v>
+        <v>0.92</v>
       </c>
       <c r="F13" t="n">
-        <v>1.11</v>
+        <v>3.38</v>
       </c>
       <c r="G13" t="n">
-        <v>1.49</v>
+        <v>4.17</v>
       </c>
       <c r="H13" t="n">
-        <v>595969</v>
+        <v>1726633</v>
       </c>
       <c r="I13" t="n">
-        <v>196403</v>
+        <v>596863</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>8.15</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="L13" t="n">
-        <v>53.9</v>
+        <v>56.1</v>
       </c>
       <c r="M13" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="N13" t="n">
-        <v>5.44</v>
+        <v>5.43</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-43.93</v>
+        <v>-43.42</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>30.38</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24078.3</v>
+      </c>
+      <c r="D17" t="n">
         <v>24154.9</v>
       </c>
-      <c r="D17" t="n">
-        <v>24366</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.87</v>
+        <v>-0.32</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.74</v>
+        <v>-1.46</v>
       </c>
       <c r="G17" t="n">
-        <v>0.43</v>
+        <v>0.02</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.07</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57239.75</v>
+      </c>
+      <c r="D18" t="n">
         <v>57262.4</v>
       </c>
-      <c r="D18" t="n">
-        <v>57491.1</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.4</v>
+        <v>-0.04</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.74</v>
+        <v>-1.12</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.35</v>
+        <v>-1.03</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.44</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>90.88</v>
+        <v>91.69</v>
       </c>
       <c r="D19" t="n">
-        <v>90.87</v>
+        <v>91.02</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01</v>
+        <v>0.74</v>
       </c>
       <c r="F19" t="n">
-        <v>2.22</v>
+        <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86</v>
+        <v>0.75</v>
       </c>
       <c r="H19" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4445.3</v>
+        <v>4423.4</v>
       </c>
       <c r="D20" t="n">
-        <v>4417.8</v>
+        <v>4366</v>
       </c>
       <c r="E20" t="n">
-        <v>0.62</v>
+        <v>1.31</v>
       </c>
       <c r="F20" t="n">
-        <v>1.42</v>
+        <v>0.33</v>
       </c>
       <c r="G20" t="n">
-        <v>10.85</v>
+        <v>8.65</v>
       </c>
       <c r="H20" t="n">
-        <v>1.91</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="21">
@@ -1321,8 +1321,23 @@
           <t>^DJI</t>
         </is>
       </c>
+      <c r="C21" t="n">
+        <v>53343.4</v>
+      </c>
       <c r="D21" t="n">
-        <v>53732.41</v>
+        <v>53459.78</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="22">
@@ -1337,22 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.39</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.31</v>
-      </c>
       <c r="E22" t="n">
-        <v>0.71</v>
+        <v>-0.61</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.02</v>
+        <v>-3.17</v>
       </c>
       <c r="G22" t="n">
-        <v>-17.16</v>
+        <v>-10.16</v>
       </c>
       <c r="H22" t="n">
-        <v>0.14</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1366,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1841,6 +1856,29 @@
       </c>
       <c r="G20" t="n">
         <v>-0.44</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57239.75</v>
+      </c>
+      <c r="C21" t="n">
+        <v>57262.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>
@@ -1854,7 +1892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2329,6 +2367,29 @@
       </c>
       <c r="G20" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="C21" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -2342,7 +2403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2817,6 +2878,29 @@
       </c>
       <c r="G20" t="n">
         <v>1.91</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4423.4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4366</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -2830,7 +2914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,6 +3351,29 @@
       </c>
       <c r="C19" t="n">
         <v>53732.41</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>53343.4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>53459.78</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3707,6 +3814,29 @@
       </c>
       <c r="G20" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="C21" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-10.16</v>
+      </c>
+      <c r="G21" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3720,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4735,6 +4865,59 @@
       </c>
       <c r="Q19" t="n">
         <v>50.66</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2898</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2283</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K20" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="N20" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-42.65</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>51.23</v>
       </c>
     </row>
   </sheetData>
@@ -4748,7 +4931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5763,6 +5946,59 @@
       </c>
       <c r="Q19" t="n">
         <v>8.42</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B20" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="C20" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="G20" t="n">
+        <v>67100399</v>
+      </c>
+      <c r="H20" t="n">
+        <v>14002263</v>
+      </c>
+      <c r="I20" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="K20" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="M20" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="N20" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-25.48</v>
+      </c>
+      <c r="P20" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>12.8</v>
       </c>
     </row>
   </sheetData>
@@ -5776,7 +6012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6685,6 +6921,59 @@
       </c>
       <c r="Q17" t="n">
         <v>59.27</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B18" t="n">
+        <v>45</v>
+      </c>
+      <c r="C18" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4426235</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5224750</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="M18" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="N18" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="P18" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>58.95</v>
       </c>
     </row>
   </sheetData>
@@ -6698,7 +6987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7766,6 +8055,59 @@
       </c>
       <c r="Q20" t="n">
         <v>88.26000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>445.95</v>
+      </c>
+      <c r="C21" t="n">
+        <v>452.9</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>200373</v>
+      </c>
+      <c r="H21" t="n">
+        <v>396713</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K21" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>337.73</v>
+      </c>
+      <c r="M21" t="n">
+        <v>385.86</v>
+      </c>
+      <c r="N21" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="P21" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>85.37</v>
       </c>
     </row>
   </sheetData>
@@ -7779,7 +8121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8846,6 +9188,59 @@
         <v>270</v>
       </c>
       <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>267.05</v>
+      </c>
+      <c r="C21" t="n">
+        <v>270</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-5.54</v>
+      </c>
+      <c r="G21" t="n">
+        <v>13812489</v>
+      </c>
+      <c r="H21" t="n">
+        <v>14561572</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>315.18</v>
+      </c>
+      <c r="M21" t="n">
+        <v>284.17</v>
+      </c>
+      <c r="N21" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-33.57</v>
+      </c>
+      <c r="P21" t="n">
+        <v>267.05</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8860,7 +9255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9928,6 +10323,59 @@
       </c>
       <c r="Q20" t="n">
         <v>13.69</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>886.85</v>
+      </c>
+      <c r="C21" t="n">
+        <v>898.35</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>317991</v>
+      </c>
+      <c r="H21" t="n">
+        <v>281134</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K21" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>944.6900000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>916.08</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1206</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-26.46</v>
+      </c>
+      <c r="P21" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>12.23</v>
       </c>
     </row>
   </sheetData>
@@ -9941,7 +10389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11009,6 +11457,59 @@
       </c>
       <c r="Q20" t="n">
         <v>48.65</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1014.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-7.77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>420896</v>
+      </c>
+      <c r="H21" t="n">
+        <v>538817</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K21" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>936.0599999999999</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1048.04</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-10.31</v>
+      </c>
+      <c r="P21" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>46.79</v>
       </c>
     </row>
   </sheetData>
@@ -11022,7 +11523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12090,6 +12591,59 @@
       </c>
       <c r="Q20" t="n">
         <v>70.47</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12221760</v>
+      </c>
+      <c r="H21" t="n">
+        <v>11368755</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K21" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="M21" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="P21" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>69.22</v>
       </c>
     </row>
   </sheetData>
@@ -12103,7 +12657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13171,6 +13725,59 @@
       </c>
       <c r="Q20" t="n">
         <v>30.38</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1726633</v>
+      </c>
+      <c r="H21" t="n">
+        <v>596863</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="K21" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="N21" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-43.42</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>31.58</v>
       </c>
     </row>
   </sheetData>
@@ -13184,7 +13791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14252,6 +14859,59 @@
       </c>
       <c r="Q20" t="n">
         <v>55.14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>852.35</v>
+      </c>
+      <c r="C21" t="n">
+        <v>854</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="G21" t="n">
+        <v>149580</v>
+      </c>
+      <c r="H21" t="n">
+        <v>218447</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K21" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>749.25</v>
+      </c>
+      <c r="M21" t="n">
+        <v>844.49</v>
+      </c>
+      <c r="N21" t="n">
+        <v>898.22</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="P21" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>54.84</v>
       </c>
     </row>
   </sheetData>
@@ -14265,7 +14925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14742,6 +15402,29 @@
         <v>-1.07</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>24078.3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>24154.9</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>453.6</v>
+      </c>
+      <c r="D3" t="n">
         <v>445.95</v>
       </c>
-      <c r="D3" t="n">
-        <v>452.9</v>
-      </c>
       <c r="E3" t="n">
-        <v>-1.53</v>
+        <v>1.72</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.77</v>
+        <v>-0.38</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.37</v>
       </c>
       <c r="H3" t="n">
-        <v>200373</v>
+        <v>343268</v>
       </c>
       <c r="I3" t="n">
-        <v>396713</v>
+        <v>200418</v>
       </c>
       <c r="J3" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
         <v>0.02</v>
       </c>
       <c r="L3" t="n">
-        <v>61.3</v>
+        <v>63.5</v>
       </c>
       <c r="M3" t="n">
-        <v>337.73</v>
+        <v>337.99</v>
       </c>
       <c r="N3" t="n">
-        <v>385.86</v>
+        <v>388.78</v>
       </c>
       <c r="O3" t="n">
         <v>479.33</v>
       </c>
       <c r="P3" t="n">
-        <v>-6.96</v>
+        <v>-5.37</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>85.37</v>
+        <v>88.55</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="D4" t="n">
         <v>45</v>
       </c>
-      <c r="D4" t="n">
-        <v>45.09</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.2</v>
+        <v>0.36</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="G4" t="n">
-        <v>1.89</v>
+        <v>-4.99</v>
       </c>
       <c r="H4" t="n">
-        <v>4426235</v>
+        <v>9571567</v>
       </c>
       <c r="I4" t="n">
-        <v>5224750</v>
+        <v>4428294</v>
       </c>
       <c r="J4" t="n">
-        <v>0.42</v>
+        <v>1.21</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="L4" t="n">
-        <v>44.4</v>
+        <v>45.4</v>
       </c>
       <c r="M4" t="n">
-        <v>40.99</v>
+        <v>41.13</v>
       </c>
       <c r="N4" t="n">
-        <v>45.82</v>
+        <v>45.9</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.29</v>
+        <v>-5.96</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>58.95</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>271.65</v>
+      </c>
+      <c r="D5" t="n">
         <v>267.05</v>
       </c>
-      <c r="D5" t="n">
-        <v>270</v>
-      </c>
       <c r="E5" t="n">
-        <v>-1.09</v>
+        <v>1.72</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.3</v>
+        <v>-2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>-5.54</v>
+        <v>-3.26</v>
       </c>
       <c r="H5" t="n">
-        <v>13812489</v>
+        <v>28226089</v>
       </c>
       <c r="I5" t="n">
-        <v>14561572</v>
+        <v>13821291</v>
       </c>
       <c r="J5" t="n">
-        <v>0.88</v>
+        <v>1.78</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="L5" t="n">
-        <v>28.7</v>
+        <v>37.8</v>
       </c>
       <c r="M5" t="n">
-        <v>315.18</v>
+        <v>313.96</v>
       </c>
       <c r="N5" t="n">
-        <v>284.17</v>
+        <v>283.9</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-33.57</v>
+        <v>-32.42</v>
       </c>
       <c r="Q5" t="n">
         <v>267.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>886.85</v>
+        <v>877.5</v>
       </c>
       <c r="D6" t="n">
-        <v>898.35</v>
+        <v>885.35</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.28</v>
+        <v>-0.89</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.22</v>
+        <v>-7.64</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.210000000000001</v>
+        <v>-5.92</v>
       </c>
       <c r="H6" t="n">
-        <v>317991</v>
+        <v>275977</v>
       </c>
       <c r="I6" t="n">
-        <v>281134</v>
+        <v>318070</v>
       </c>
       <c r="J6" t="n">
-        <v>0.95</v>
+        <v>0.62</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04</v>
+        <v>1.67</v>
       </c>
       <c r="L6" t="n">
-        <v>40.2</v>
+        <v>38.1</v>
       </c>
       <c r="M6" t="n">
-        <v>944.6900000000001</v>
+        <v>944.92</v>
       </c>
       <c r="N6" t="n">
-        <v>916.08</v>
+        <v>919.27</v>
       </c>
       <c r="O6" t="n">
-        <v>1206</v>
+        <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-26.46</v>
+        <v>-27.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>790.1799999999999</v>
+        <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>12.23</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>71.93000000000001</v>
+      </c>
+      <c r="D7" t="n">
         <v>71.8</v>
       </c>
-      <c r="D7" t="n">
-        <v>72.33</v>
-      </c>
       <c r="E7" t="n">
-        <v>-0.73</v>
+        <v>0.18</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>9.4</v>
+        <v>10.58</v>
       </c>
       <c r="H7" t="n">
-        <v>12221760</v>
+        <v>23704043</v>
       </c>
       <c r="I7" t="n">
-        <v>11368755</v>
+        <v>12226495</v>
       </c>
       <c r="J7" t="n">
-        <v>0.48</v>
+        <v>0.92</v>
       </c>
       <c r="K7" t="n">
-        <v>0.15</v>
+        <v>0.92</v>
       </c>
       <c r="L7" t="n">
-        <v>60.5</v>
+        <v>60.9</v>
       </c>
       <c r="M7" t="n">
-        <v>58.41</v>
+        <v>58.58</v>
       </c>
       <c r="N7" t="n">
-        <v>64.3</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.92</v>
+        <v>-0.75</v>
       </c>
       <c r="Q7" t="n">
         <v>42.43</v>
       </c>
       <c r="R7" t="n">
-        <v>69.22</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>847.85</v>
+      </c>
+      <c r="D8" t="n">
         <v>852.35</v>
       </c>
-      <c r="D8" t="n">
-        <v>854</v>
-      </c>
       <c r="E8" t="n">
-        <v>-0.19</v>
+        <v>-0.53</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.84</v>
+        <v>0.38</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.51</v>
+        <v>-0.35</v>
       </c>
       <c r="H8" t="n">
-        <v>149580</v>
+        <v>193370</v>
       </c>
       <c r="I8" t="n">
-        <v>218447</v>
+        <v>149592</v>
       </c>
       <c r="J8" t="n">
-        <v>0.49</v>
+        <v>0.64</v>
       </c>
       <c r="K8" t="n">
-        <v>0.24</v>
+        <v>-0.67</v>
       </c>
       <c r="L8" t="n">
-        <v>51.2</v>
+        <v>49.6</v>
       </c>
       <c r="M8" t="n">
-        <v>749.25</v>
+        <v>749.42</v>
       </c>
       <c r="N8" t="n">
-        <v>844.49</v>
+        <v>844.9400000000001</v>
       </c>
       <c r="O8" t="n">
         <v>898.22</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.11</v>
+        <v>-5.61</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>54.84</v>
+        <v>54.02</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="D10" t="n">
         <v>8</v>
       </c>
-      <c r="D10" t="n">
-        <v>7.97</v>
-      </c>
       <c r="E10" t="n">
-        <v>0.38</v>
+        <v>-4.25</v>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>-6.59</v>
       </c>
       <c r="G10" t="n">
-        <v>11.11</v>
+        <v>6.39</v>
       </c>
       <c r="H10" t="n">
+        <v>2253</v>
+      </c>
+      <c r="I10" t="n">
         <v>2898</v>
       </c>
-      <c r="I10" t="n">
-        <v>2283</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="K10" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>60.2</v>
+        <v>53.9</v>
       </c>
       <c r="M10" t="n">
-        <v>9.08</v>
+        <v>9.09</v>
       </c>
       <c r="N10" t="n">
-        <v>6.79</v>
+        <v>6.82</v>
       </c>
       <c r="O10" t="n">
         <v>13.95</v>
       </c>
       <c r="P10" t="n">
-        <v>-42.65</v>
+        <v>-45.09</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>51.23</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D11" t="n">
         <v>1002</v>
       </c>
-      <c r="D11" t="n">
-        <v>1014.7</v>
-      </c>
       <c r="E11" t="n">
-        <v>-1.25</v>
+        <v>3.79</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.35</v>
+        <v>0.41</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.77</v>
+        <v>-0.8</v>
       </c>
       <c r="H11" t="n">
-        <v>420896</v>
+        <v>1306787</v>
       </c>
       <c r="I11" t="n">
-        <v>538817</v>
+        <v>421715</v>
       </c>
       <c r="J11" t="n">
-        <v>0.48</v>
+        <v>1.55</v>
       </c>
       <c r="K11" t="n">
-        <v>0.41</v>
+        <v>0.95</v>
       </c>
       <c r="L11" t="n">
-        <v>40.4</v>
+        <v>51.2</v>
       </c>
       <c r="M11" t="n">
-        <v>936.0599999999999</v>
+        <v>935.79</v>
       </c>
       <c r="N11" t="n">
-        <v>1048.04</v>
+        <v>1047.52</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-10.31</v>
+        <v>-6.91</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>46.79</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="D12" t="n">
         <v>24.24</v>
       </c>
-      <c r="D12" t="n">
-        <v>23.3</v>
-      </c>
       <c r="E12" t="n">
-        <v>4.03</v>
+        <v>7.8</v>
       </c>
       <c r="F12" t="n">
-        <v>10.23</v>
+        <v>18.13</v>
       </c>
       <c r="G12" t="n">
-        <v>9.34</v>
+        <v>18.66</v>
       </c>
       <c r="H12" t="n">
-        <v>67100399</v>
+        <v>95122839</v>
       </c>
       <c r="I12" t="n">
-        <v>14002263</v>
+        <v>67106466</v>
       </c>
       <c r="J12" t="n">
-        <v>13.55</v>
+        <v>11.74</v>
       </c>
       <c r="K12" t="n">
-        <v>1.47</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>69.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>24.99</v>
+        <v>24.94</v>
       </c>
       <c r="N12" t="n">
-        <v>22.55</v>
+        <v>22.64</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-25.48</v>
+        <v>-19.67</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>12.8</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="13">
@@ -1093,37 +1093,37 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.5</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.45</v>
-      </c>
       <c r="E13" t="n">
-        <v>0.92</v>
+        <v>4.73</v>
       </c>
       <c r="F13" t="n">
-        <v>3.38</v>
+        <v>5.69</v>
       </c>
       <c r="G13" t="n">
-        <v>4.17</v>
+        <v>9.51</v>
       </c>
       <c r="H13" t="n">
-        <v>1726633</v>
+        <v>2966016</v>
       </c>
       <c r="I13" t="n">
-        <v>596863</v>
+        <v>1729809</v>
       </c>
       <c r="J13" t="n">
-        <v>8.15</v>
+        <v>10.12</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.09</v>
+        <v>2.42</v>
       </c>
       <c r="L13" t="n">
-        <v>56.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="N13" t="n">
         <v>5.43</v>
@@ -1132,13 +1132,13 @@
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-43.42</v>
+        <v>-40.74</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>31.58</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24231.85</v>
+      </c>
+      <c r="D17" t="n">
         <v>24078.3</v>
       </c>
-      <c r="D17" t="n">
-        <v>24154.9</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.32</v>
+        <v>0.64</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.46</v>
+        <v>-0.67</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02</v>
+        <v>0.98</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.02</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57495.9</v>
+      </c>
+      <c r="D18" t="n">
         <v>57239.75</v>
       </c>
-      <c r="D18" t="n">
-        <v>57262.4</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.04</v>
+        <v>0.45</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.12</v>
+        <v>-0.24</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.03</v>
+        <v>0.65</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.01</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>91.69</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>91.02</v>
+        <v>91.62</v>
       </c>
       <c r="E19" t="n">
-        <v>0.74</v>
+        <v>2.95</v>
       </c>
       <c r="F19" t="n">
-        <v>3.05</v>
+        <v>8.33</v>
       </c>
       <c r="G19" t="n">
-        <v>0.75</v>
+        <v>0.27</v>
       </c>
       <c r="H19" t="n">
-        <v>0.16</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4423.4</v>
+        <v>4536.8</v>
       </c>
       <c r="D20" t="n">
-        <v>4366</v>
+        <v>4489.4</v>
       </c>
       <c r="E20" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="F20" t="n">
-        <v>0.33</v>
+        <v>3.97</v>
       </c>
       <c r="G20" t="n">
-        <v>8.65</v>
+        <v>9.4</v>
       </c>
       <c r="H20" t="n">
-        <v>0.89</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>53463.05</v>
+      </c>
+      <c r="D21" t="n">
         <v>53343.4</v>
       </c>
-      <c r="D21" t="n">
-        <v>53459.78</v>
-      </c>
       <c r="E21" t="n">
-        <v>-0.22</v>
+        <v>0.22</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.83</v>
+        <v>-0.57</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.49</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.32</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.39</v>
-      </c>
       <c r="E22" t="n">
-        <v>-0.61</v>
+        <v>-4.95</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.17</v>
+        <v>-5.78</v>
       </c>
       <c r="G22" t="n">
-        <v>-10.16</v>
+        <v>-14.6</v>
       </c>
       <c r="H22" t="n">
-        <v/>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1879,6 +1879,29 @@
       </c>
       <c r="G21" t="n">
         <v>-0.01</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57495.9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>57239.75</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -1892,7 +1915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2390,6 +2413,29 @@
       </c>
       <c r="G21" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="C22" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -2403,7 +2449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2901,6 +2947,29 @@
       </c>
       <c r="G21" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4536.8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4489.4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.97</v>
       </c>
     </row>
   </sheetData>
@@ -2914,7 +2983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3374,6 +3443,29 @@
       </c>
       <c r="G20" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>53463.05</v>
+      </c>
+      <c r="C21" t="n">
+        <v>53343.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -3387,7 +3479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3835,8 +3927,28 @@
       <c r="F21" t="n">
         <v>-10.16</v>
       </c>
-      <c r="G21" t="n">
-        <v/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="C22" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4918,6 +5030,59 @@
       </c>
       <c r="Q20" t="n">
         <v>51.23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B21" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-6.59</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2253</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2898</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="M21" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-45.09</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>44.8</v>
       </c>
     </row>
   </sheetData>
@@ -4931,7 +5096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5999,6 +6164,59 @@
       </c>
       <c r="Q20" t="n">
         <v>12.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B21" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="C21" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="F21" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="G21" t="n">
+        <v>95122839</v>
+      </c>
+      <c r="H21" t="n">
+        <v>67106466</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="L21" t="n">
+        <v>24.94</v>
+      </c>
+      <c r="M21" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="N21" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-19.67</v>
+      </c>
+      <c r="P21" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>21.59</v>
       </c>
     </row>
   </sheetData>
@@ -6012,7 +6230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6974,6 +7192,59 @@
       </c>
       <c r="Q18" t="n">
         <v>58.95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B19" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>45</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9571567</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4428294</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="M19" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="N19" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="P19" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>59.52</v>
       </c>
     </row>
   </sheetData>
@@ -6987,7 +7258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8108,6 +8379,59 @@
       </c>
       <c r="Q21" t="n">
         <v>85.37</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>453.6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>445.95</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="G22" t="n">
+        <v>343268</v>
+      </c>
+      <c r="H22" t="n">
+        <v>200418</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K22" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>337.99</v>
+      </c>
+      <c r="M22" t="n">
+        <v>388.78</v>
+      </c>
+      <c r="N22" t="n">
+        <v>479.33</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-5.37</v>
+      </c>
+      <c r="P22" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>88.55</v>
       </c>
     </row>
   </sheetData>
@@ -8121,7 +8445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9242,6 +9566,59 @@
       </c>
       <c r="Q21" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>271.65</v>
+      </c>
+      <c r="C22" t="n">
+        <v>267.05</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="G22" t="n">
+        <v>28226089</v>
+      </c>
+      <c r="H22" t="n">
+        <v>13821291</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K22" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>313.96</v>
+      </c>
+      <c r="M22" t="n">
+        <v>283.9</v>
+      </c>
+      <c r="N22" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-32.42</v>
+      </c>
+      <c r="P22" t="n">
+        <v>267.05</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>
@@ -9255,7 +9632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10376,6 +10753,59 @@
       </c>
       <c r="Q21" t="n">
         <v>12.23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>877.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>885.35</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-7.64</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="G22" t="n">
+        <v>275977</v>
+      </c>
+      <c r="H22" t="n">
+        <v>318070</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K22" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>944.92</v>
+      </c>
+      <c r="M22" t="n">
+        <v>919.27</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-27.12</v>
+      </c>
+      <c r="P22" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>11.24</v>
       </c>
     </row>
   </sheetData>
@@ -10389,7 +10819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11510,6 +11940,59 @@
       </c>
       <c r="Q21" t="n">
         <v>46.79</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1040</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1306787</v>
+      </c>
+      <c r="H22" t="n">
+        <v>421715</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K22" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>935.79</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1047.52</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="P22" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>52.36</v>
       </c>
     </row>
   </sheetData>
@@ -11523,7 +12006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12644,6 +13127,59 @@
       </c>
       <c r="Q21" t="n">
         <v>69.22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>71.93000000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F22" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23704043</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12226495</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K22" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>58.58</v>
+      </c>
+      <c r="M22" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="N22" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="P22" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>69.53</v>
       </c>
     </row>
   </sheetData>
@@ -12657,7 +13193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13778,6 +14314,59 @@
       </c>
       <c r="Q21" t="n">
         <v>31.58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2966016</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1729809</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K22" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="N22" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-40.74</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>37.8</v>
       </c>
     </row>
   </sheetData>
@@ -13791,7 +14380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14912,6 +15501,59 @@
       </c>
       <c r="Q21" t="n">
         <v>54.84</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>847.85</v>
+      </c>
+      <c r="C22" t="n">
+        <v>852.35</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="G22" t="n">
+        <v>193370</v>
+      </c>
+      <c r="H22" t="n">
+        <v>149592</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="K22" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>749.42</v>
+      </c>
+      <c r="M22" t="n">
+        <v>844.9400000000001</v>
+      </c>
+      <c r="N22" t="n">
+        <v>898.22</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-5.61</v>
+      </c>
+      <c r="P22" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>54.02</v>
       </c>
     </row>
   </sheetData>
@@ -14925,7 +15567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15425,6 +16067,29 @@
         <v>-0.02</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>24231.85</v>
+      </c>
+      <c r="C22" t="n">
+        <v>24078.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>458.8</v>
+      </c>
+      <c r="D3" t="n">
         <v>453.6</v>
       </c>
-      <c r="D3" t="n">
-        <v>445.95</v>
-      </c>
       <c r="E3" t="n">
-        <v>1.72</v>
+        <v>1.15</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.38</v>
+        <v>1.91</v>
       </c>
       <c r="G3" t="n">
-        <v>4.37</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>343268</v>
+        <v>233840</v>
       </c>
       <c r="I3" t="n">
-        <v>200418</v>
+        <v>343273</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02</v>
+        <v>0.44</v>
       </c>
       <c r="L3" t="n">
-        <v>63.5</v>
+        <v>65.2</v>
       </c>
       <c r="M3" t="n">
-        <v>337.99</v>
+        <v>338.27</v>
       </c>
       <c r="N3" t="n">
-        <v>388.78</v>
+        <v>393.46</v>
       </c>
       <c r="O3" t="n">
-        <v>479.33</v>
+        <v>465.35</v>
       </c>
       <c r="P3" t="n">
-        <v>-5.37</v>
+        <v>-1.41</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>88.55</v>
+        <v>90.70999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="D4" t="n">
         <v>45.16</v>
       </c>
-      <c r="D4" t="n">
-        <v>45</v>
-      </c>
       <c r="E4" t="n">
-        <v>0.36</v>
+        <v>-0.42</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1</v>
+        <v>-1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.99</v>
+        <v>-4.4</v>
       </c>
       <c r="H4" t="n">
-        <v>9571567</v>
+        <v>4130548</v>
       </c>
       <c r="I4" t="n">
-        <v>4428294</v>
+        <v>9571667</v>
       </c>
       <c r="J4" t="n">
-        <v>1.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="L4" t="n">
-        <v>45.4</v>
+        <v>43.9</v>
       </c>
       <c r="M4" t="n">
-        <v>41.13</v>
+        <v>41.17</v>
       </c>
       <c r="N4" t="n">
-        <v>45.9</v>
+        <v>45.87</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.96</v>
+        <v>-6.35</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>59.52</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>269.4</v>
+      </c>
+      <c r="D5" t="n">
         <v>271.65</v>
       </c>
-      <c r="D5" t="n">
-        <v>267.05</v>
-      </c>
       <c r="E5" t="n">
-        <v>1.72</v>
+        <v>-0.83</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.46</v>
+        <v>-3.16</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.26</v>
+        <v>-4.23</v>
       </c>
       <c r="H5" t="n">
-        <v>28226089</v>
+        <v>8308411</v>
       </c>
       <c r="I5" t="n">
-        <v>13821291</v>
+        <v>28272797</v>
       </c>
       <c r="J5" t="n">
-        <v>1.78</v>
+        <v>0.51</v>
       </c>
       <c r="K5" t="n">
-        <v>0.83</v>
+        <v>-0.04</v>
       </c>
       <c r="L5" t="n">
-        <v>37.8</v>
+        <v>35.4</v>
       </c>
       <c r="M5" t="n">
-        <v>313.96</v>
+        <v>313.36</v>
       </c>
       <c r="N5" t="n">
-        <v>283.9</v>
+        <v>283.59</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-32.42</v>
+        <v>-32.98</v>
       </c>
       <c r="Q5" t="n">
         <v>267.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>882.4</v>
+      </c>
+      <c r="D6" t="n">
         <v>877.5</v>
       </c>
-      <c r="D6" t="n">
-        <v>885.35</v>
-      </c>
       <c r="E6" t="n">
-        <v>-0.89</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-7.64</v>
+        <v>-2.13</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.92</v>
+        <v>-3.77</v>
       </c>
       <c r="H6" t="n">
-        <v>275977</v>
+        <v>363664</v>
       </c>
       <c r="I6" t="n">
-        <v>318070</v>
+        <v>275997</v>
       </c>
       <c r="J6" t="n">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="K6" t="n">
-        <v>1.67</v>
+        <v>0.57</v>
       </c>
       <c r="L6" t="n">
-        <v>38.1</v>
+        <v>39.9</v>
       </c>
       <c r="M6" t="n">
-        <v>944.92</v>
+        <v>945.25</v>
       </c>
       <c r="N6" t="n">
-        <v>919.27</v>
+        <v>919.67</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-27.12</v>
+        <v>-26.71</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>11.24</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>72.06999999999999</v>
+      </c>
+      <c r="D7" t="n">
         <v>71.93000000000001</v>
       </c>
-      <c r="D7" t="n">
-        <v>71.8</v>
-      </c>
       <c r="E7" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>-0.55</v>
       </c>
       <c r="G7" t="n">
-        <v>10.58</v>
+        <v>4.78</v>
       </c>
       <c r="H7" t="n">
-        <v>23704043</v>
+        <v>7760184</v>
       </c>
       <c r="I7" t="n">
-        <v>12226495</v>
+        <v>23704583</v>
       </c>
       <c r="J7" t="n">
-        <v>0.92</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0.92</v>
+        <v>-0.09</v>
       </c>
       <c r="L7" t="n">
-        <v>60.9</v>
+        <v>61.3</v>
       </c>
       <c r="M7" t="n">
-        <v>58.58</v>
+        <v>58.68</v>
       </c>
       <c r="N7" t="n">
-        <v>64.93000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.75</v>
+        <v>-0.55</v>
       </c>
       <c r="Q7" t="n">
         <v>42.43</v>
       </c>
       <c r="R7" t="n">
-        <v>69.53</v>
+        <v>69.86</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>855.15</v>
+      </c>
+      <c r="D8" t="n">
         <v>847.85</v>
       </c>
-      <c r="D8" t="n">
-        <v>852.35</v>
-      </c>
       <c r="E8" t="n">
-        <v>-0.53</v>
+        <v>0.86</v>
       </c>
       <c r="F8" t="n">
-        <v>0.38</v>
+        <v>1.24</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.35</v>
+        <v>1.67</v>
       </c>
       <c r="H8" t="n">
-        <v>193370</v>
+        <v>171782</v>
       </c>
       <c r="I8" t="n">
-        <v>149592</v>
+        <v>193401</v>
       </c>
       <c r="J8" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.67</v>
+        <v>0.04</v>
       </c>
       <c r="L8" t="n">
-        <v>49.6</v>
+        <v>52.2</v>
       </c>
       <c r="M8" t="n">
-        <v>749.42</v>
+        <v>749.59</v>
       </c>
       <c r="N8" t="n">
-        <v>844.9400000000001</v>
+        <v>845.25</v>
       </c>
       <c r="O8" t="n">
         <v>898.22</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.61</v>
+        <v>-4.8</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>54.02</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="9">
@@ -913,37 +913,37 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D10" t="n">
         <v>7.66</v>
       </c>
-      <c r="D10" t="n">
-        <v>8</v>
-      </c>
       <c r="E10" t="n">
-        <v>-4.25</v>
+        <v>-0.78</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.59</v>
+        <v>-7.32</v>
       </c>
       <c r="G10" t="n">
-        <v>6.39</v>
+        <v>8.57</v>
       </c>
       <c r="H10" t="n">
+        <v>3919</v>
+      </c>
+      <c r="I10" t="n">
         <v>2253</v>
       </c>
-      <c r="I10" t="n">
-        <v>2898</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="L10" t="n">
-        <v>53.9</v>
+        <v>53.2</v>
       </c>
       <c r="M10" t="n">
-        <v>9.09</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>6.82</v>
@@ -952,13 +952,13 @@
         <v>13.95</v>
       </c>
       <c r="P10" t="n">
-        <v>-45.09</v>
+        <v>-45.52</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>44.8</v>
+        <v>43.67</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D11" t="n">
         <v>1040</v>
       </c>
-      <c r="D11" t="n">
-        <v>1002</v>
-      </c>
       <c r="E11" t="n">
-        <v>3.79</v>
+        <v>1.25</v>
       </c>
       <c r="F11" t="n">
-        <v>0.41</v>
+        <v>3.51</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8</v>
+        <v>2.76</v>
       </c>
       <c r="H11" t="n">
-        <v>1306787</v>
+        <v>2710042</v>
       </c>
       <c r="I11" t="n">
-        <v>421715</v>
+        <v>1306864</v>
       </c>
       <c r="J11" t="n">
-        <v>1.55</v>
+        <v>3.08</v>
       </c>
       <c r="K11" t="n">
-        <v>0.95</v>
+        <v>1.47</v>
       </c>
       <c r="L11" t="n">
-        <v>51.2</v>
+        <v>54.5</v>
       </c>
       <c r="M11" t="n">
-        <v>935.79</v>
+        <v>935.64</v>
       </c>
       <c r="N11" t="n">
-        <v>1047.52</v>
+        <v>1047.17</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.91</v>
+        <v>-5.75</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>52.36</v>
+        <v>54.26</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="D12" t="n">
         <v>26.13</v>
       </c>
-      <c r="D12" t="n">
-        <v>24.24</v>
-      </c>
       <c r="E12" t="n">
-        <v>7.8</v>
+        <v>-3.79</v>
       </c>
       <c r="F12" t="n">
-        <v>18.13</v>
+        <v>14.53</v>
       </c>
       <c r="G12" t="n">
-        <v>18.66</v>
+        <v>15.96</v>
       </c>
       <c r="H12" t="n">
-        <v>95122839</v>
+        <v>54892054</v>
       </c>
       <c r="I12" t="n">
-        <v>67106466</v>
+        <v>95136169</v>
       </c>
       <c r="J12" t="n">
-        <v>11.74</v>
+        <v>4.31</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>79.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="M12" t="n">
-        <v>24.94</v>
+        <v>24.92</v>
       </c>
       <c r="N12" t="n">
-        <v>22.64</v>
+        <v>22.7</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-19.67</v>
+        <v>-22.72</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>21.59</v>
+        <v>16.98</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.76</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.5</v>
-      </c>
       <c r="E13" t="n">
-        <v>4.73</v>
+        <v>-1.22</v>
       </c>
       <c r="F13" t="n">
-        <v>5.69</v>
+        <v>7.56</v>
       </c>
       <c r="G13" t="n">
-        <v>9.51</v>
+        <v>8.17</v>
       </c>
       <c r="H13" t="n">
-        <v>2966016</v>
+        <v>715248</v>
       </c>
       <c r="I13" t="n">
-        <v>1729809</v>
+        <v>2968868</v>
       </c>
       <c r="J13" t="n">
-        <v>10.12</v>
+        <v>1.59</v>
       </c>
       <c r="K13" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>65.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="M13" t="n">
-        <v>5.99</v>
+        <v>5.96</v>
       </c>
       <c r="N13" t="n">
-        <v>5.43</v>
+        <v>5.42</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-40.74</v>
+        <v>-41.46</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>37.8</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24252</v>
+      </c>
+      <c r="D17" t="n">
         <v>24231.85</v>
       </c>
-      <c r="D17" t="n">
-        <v>24078.3</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.64</v>
+        <v>0.08</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.67</v>
+        <v>-0.47</v>
       </c>
       <c r="G17" t="n">
-        <v>0.98</v>
+        <v>1.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.53</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57761.95</v>
+      </c>
+      <c r="D18" t="n">
         <v>57495.9</v>
       </c>
-      <c r="D18" t="n">
-        <v>57239.75</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.24</v>
+        <v>0.47</v>
       </c>
       <c r="G18" t="n">
-        <v>0.65</v>
+        <v>2.07</v>
       </c>
       <c r="H18" t="n">
-        <v>1.25</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>94.31999999999999</v>
+        <v>93.09</v>
       </c>
       <c r="D19" t="n">
-        <v>91.62</v>
+        <v>93.78</v>
       </c>
       <c r="E19" t="n">
-        <v>2.95</v>
+        <v>-0.74</v>
       </c>
       <c r="F19" t="n">
-        <v>8.33</v>
+        <v>5.16</v>
       </c>
       <c r="G19" t="n">
-        <v>0.27</v>
+        <v>-7.55</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.06</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4536.8</v>
+        <v>4660.3</v>
       </c>
       <c r="D20" t="n">
-        <v>4489.4</v>
+        <v>4516.3</v>
       </c>
       <c r="E20" t="n">
-        <v>1.06</v>
+        <v>3.19</v>
       </c>
       <c r="F20" t="n">
-        <v>3.97</v>
+        <v>6.39</v>
       </c>
       <c r="G20" t="n">
-        <v>9.4</v>
+        <v>15.17</v>
       </c>
       <c r="H20" t="n">
-        <v>2.97</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>52759.21</v>
+      </c>
+      <c r="D21" t="n">
         <v>53463.05</v>
       </c>
-      <c r="D21" t="n">
-        <v>53343.4</v>
-      </c>
       <c r="E21" t="n">
-        <v>0.22</v>
+        <v>-1.32</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.57</v>
+        <v>-2.01</v>
       </c>
       <c r="G21" t="n">
-        <v>2.37</v>
+        <v>1.04</v>
       </c>
       <c r="H21" t="n">
-        <v>0.55</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="D22" t="n">
         <v>10.76</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.32</v>
-      </c>
       <c r="E22" t="n">
-        <v>-4.95</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.78</v>
+        <v>-1.06</v>
       </c>
       <c r="G22" t="n">
-        <v>-14.6</v>
+        <v>-16.99</v>
       </c>
       <c r="H22" t="n">
-        <v>0.03</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1902,6 +1902,29 @@
       </c>
       <c r="G22" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57761.95</v>
+      </c>
+      <c r="C23" t="n">
+        <v>57495.9</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -1915,7 +1938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2436,6 +2459,29 @@
       </c>
       <c r="G22" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93.09</v>
+      </c>
+      <c r="C23" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -2449,7 +2495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2970,6 +3016,29 @@
       </c>
       <c r="G22" t="n">
         <v>2.97</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4660.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4516.3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="F23" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.03</v>
       </c>
     </row>
   </sheetData>
@@ -2983,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3466,6 +3535,29 @@
       </c>
       <c r="G21" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>52759.21</v>
+      </c>
+      <c r="C22" t="n">
+        <v>53463.05</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -3479,7 +3571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3949,6 +4041,29 @@
       </c>
       <c r="G22" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-16.99</v>
+      </c>
+      <c r="G23" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3962,7 +4077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5083,6 +5198,59 @@
       </c>
       <c r="Q21" t="n">
         <v>44.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-7.32</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3919</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2253</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K22" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="M22" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="N22" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-45.52</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>43.67</v>
       </c>
     </row>
   </sheetData>
@@ -5096,7 +5264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6217,6 +6385,59 @@
       </c>
       <c r="Q21" t="n">
         <v>21.59</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B22" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="C22" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="E22" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="F22" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="G22" t="n">
+        <v>54892054</v>
+      </c>
+      <c r="H22" t="n">
+        <v>95136169</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="M22" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="N22" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-22.72</v>
+      </c>
+      <c r="P22" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>16.98</v>
       </c>
     </row>
   </sheetData>
@@ -6230,7 +6451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7245,6 +7466,59 @@
       </c>
       <c r="Q19" t="n">
         <v>59.52</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B20" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="C20" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4130548</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9571667</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="M20" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="N20" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-6.35</v>
+      </c>
+      <c r="P20" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>58.85</v>
       </c>
     </row>
   </sheetData>
@@ -7258,7 +7532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8432,6 +8706,59 @@
       </c>
       <c r="Q22" t="n">
         <v>88.55</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>458.8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>453.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F23" t="n">
+        <v>13</v>
+      </c>
+      <c r="G23" t="n">
+        <v>233840</v>
+      </c>
+      <c r="H23" t="n">
+        <v>343273</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K23" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>338.27</v>
+      </c>
+      <c r="M23" t="n">
+        <v>393.46</v>
+      </c>
+      <c r="N23" t="n">
+        <v>465.35</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="P23" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>90.70999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8445,7 +8772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9619,6 +9946,59 @@
       </c>
       <c r="Q22" t="n">
         <v>1.72</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>269.4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>271.65</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-3.16</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8308411</v>
+      </c>
+      <c r="H23" t="n">
+        <v>28272797</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="K23" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>313.36</v>
+      </c>
+      <c r="M23" t="n">
+        <v>283.59</v>
+      </c>
+      <c r="N23" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-32.98</v>
+      </c>
+      <c r="P23" t="n">
+        <v>267.05</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -9632,7 +10012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10806,6 +11186,59 @@
       </c>
       <c r="Q22" t="n">
         <v>11.24</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>882.4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>877.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="G23" t="n">
+        <v>363664</v>
+      </c>
+      <c r="H23" t="n">
+        <v>275997</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K23" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>945.25</v>
+      </c>
+      <c r="M23" t="n">
+        <v>919.67</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-26.71</v>
+      </c>
+      <c r="P23" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>11.86</v>
       </c>
     </row>
   </sheetData>
@@ -10819,7 +11252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11993,6 +12426,59 @@
       </c>
       <c r="Q22" t="n">
         <v>52.36</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1053</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2710042</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1306864</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="K23" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>935.64</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1047.17</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="P23" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>54.26</v>
       </c>
     </row>
   </sheetData>
@@ -12006,7 +12492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13180,6 +13666,59 @@
       </c>
       <c r="Q22" t="n">
         <v>69.53</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>72.06999999999999</v>
+      </c>
+      <c r="C23" t="n">
+        <v>71.93000000000001</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7760184</v>
+      </c>
+      <c r="H23" t="n">
+        <v>23704583</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="K23" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="M23" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="N23" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="P23" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>69.86</v>
       </c>
     </row>
   </sheetData>
@@ -13193,7 +13732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14367,6 +14906,59 @@
       </c>
       <c r="Q22" t="n">
         <v>37.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="G23" t="n">
+        <v>715248</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2968868</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-41.46</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>36.12</v>
       </c>
     </row>
   </sheetData>
@@ -14380,7 +14972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15554,6 +16146,59 @@
       </c>
       <c r="Q22" t="n">
         <v>54.02</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>855.15</v>
+      </c>
+      <c r="C23" t="n">
+        <v>847.85</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G23" t="n">
+        <v>171782</v>
+      </c>
+      <c r="H23" t="n">
+        <v>193401</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K23" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>749.59</v>
+      </c>
+      <c r="M23" t="n">
+        <v>845.25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>898.22</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>55.35</v>
       </c>
     </row>
   </sheetData>
@@ -15567,7 +16212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16090,6 +16735,29 @@
         <v>1.53</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>24252</v>
+      </c>
+      <c r="C23" t="n">
+        <v>24231.85</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>433.7</v>
+      </c>
+      <c r="D3" t="n">
         <v>458.8</v>
       </c>
-      <c r="D3" t="n">
-        <v>453.6</v>
-      </c>
       <c r="E3" t="n">
-        <v>1.15</v>
+        <v>-5.47</v>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>-6.8</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>7.78</v>
       </c>
       <c r="H3" t="n">
-        <v>233840</v>
+        <v>958978</v>
       </c>
       <c r="I3" t="n">
-        <v>343273</v>
+        <v>233935</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.44</v>
+        <v>2.22</v>
       </c>
       <c r="L3" t="n">
-        <v>65.2</v>
+        <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>338.27</v>
+        <v>338.56</v>
       </c>
       <c r="N3" t="n">
-        <v>393.46</v>
+        <v>395.73</v>
       </c>
       <c r="O3" t="n">
         <v>465.35</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.41</v>
+        <v>-6.8</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>90.70999999999999</v>
+        <v>80.28</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="D4" t="n">
         <v>44.97</v>
       </c>
-      <c r="D4" t="n">
-        <v>45.16</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.42</v>
+        <v>0.42</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.68</v>
+        <v>-0.13</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.4</v>
+        <v>-1.97</v>
       </c>
       <c r="H4" t="n">
-        <v>4130548</v>
+        <v>8487392</v>
       </c>
       <c r="I4" t="n">
-        <v>9571667</v>
+        <v>4130558</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4</v>
+        <v>0.83</v>
       </c>
       <c r="L4" t="n">
-        <v>43.9</v>
+        <v>45.8</v>
       </c>
       <c r="M4" t="n">
-        <v>41.17</v>
+        <v>41.21</v>
       </c>
       <c r="N4" t="n">
-        <v>45.87</v>
+        <v>45.85</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.35</v>
+        <v>-5.96</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>58.85</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="D5" t="n">
         <v>269.4</v>
       </c>
-      <c r="D5" t="n">
-        <v>271.65</v>
-      </c>
       <c r="E5" t="n">
-        <v>-0.83</v>
+        <v>0.11</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.16</v>
+        <v>-1.23</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.23</v>
+        <v>-4.85</v>
       </c>
       <c r="H5" t="n">
-        <v>8308411</v>
+        <v>8511454</v>
       </c>
       <c r="I5" t="n">
-        <v>28272797</v>
+        <v>8312928</v>
       </c>
       <c r="J5" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.04</v>
+        <v>0.9</v>
       </c>
       <c r="L5" t="n">
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="M5" t="n">
-        <v>313.36</v>
+        <v>312.77</v>
       </c>
       <c r="N5" t="n">
-        <v>283.59</v>
+        <v>283.22</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-32.98</v>
+        <v>-32.91</v>
       </c>
       <c r="Q5" t="n">
         <v>267.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.88</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>884.05</v>
+      </c>
+      <c r="D6" t="n">
         <v>882.4</v>
       </c>
-      <c r="D6" t="n">
-        <v>877.5</v>
-      </c>
       <c r="E6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.13</v>
+        <v>-0.48</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.77</v>
+        <v>-3.9</v>
       </c>
       <c r="H6" t="n">
-        <v>363664</v>
+        <v>317408</v>
       </c>
       <c r="I6" t="n">
-        <v>275997</v>
+        <v>363713</v>
       </c>
       <c r="J6" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="K6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>39.9</v>
+        <v>40.5</v>
       </c>
       <c r="M6" t="n">
-        <v>945.25</v>
+        <v>945.6900000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>919.67</v>
+        <v>920.42</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-26.71</v>
+        <v>-26.57</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>11.86</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>70.29000000000001</v>
+      </c>
+      <c r="D7" t="n">
         <v>72.06999999999999</v>
       </c>
-      <c r="D7" t="n">
-        <v>71.93000000000001</v>
-      </c>
       <c r="E7" t="n">
-        <v>0.19</v>
+        <v>-2.47</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.55</v>
+        <v>-2.66</v>
       </c>
       <c r="G7" t="n">
-        <v>4.78</v>
+        <v>-0.61</v>
       </c>
       <c r="H7" t="n">
-        <v>7760184</v>
+        <v>16995343</v>
       </c>
       <c r="I7" t="n">
-        <v>23704583</v>
+        <v>7761634</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>61.3</v>
+        <v>53.1</v>
       </c>
       <c r="M7" t="n">
-        <v>58.68</v>
+        <v>58.77</v>
       </c>
       <c r="N7" t="n">
-        <v>65.28</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.55</v>
+        <v>-3.01</v>
       </c>
       <c r="Q7" t="n">
         <v>42.43</v>
       </c>
       <c r="R7" t="n">
-        <v>69.86</v>
+        <v>65.66</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>907.55</v>
+      </c>
+      <c r="D8" t="n">
         <v>855.15</v>
       </c>
-      <c r="D8" t="n">
-        <v>847.85</v>
-      </c>
       <c r="E8" t="n">
-        <v>0.86</v>
+        <v>6.13</v>
       </c>
       <c r="F8" t="n">
-        <v>1.24</v>
+        <v>7.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.67</v>
+        <v>8.26</v>
       </c>
       <c r="H8" t="n">
-        <v>171782</v>
+        <v>1156116</v>
       </c>
       <c r="I8" t="n">
-        <v>193401</v>
+        <v>171823</v>
       </c>
       <c r="J8" t="n">
-        <v>0.57</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04</v>
+        <v>0.53</v>
       </c>
       <c r="L8" t="n">
-        <v>52.2</v>
+        <v>66.2</v>
       </c>
       <c r="M8" t="n">
-        <v>749.59</v>
+        <v>750.16</v>
       </c>
       <c r="N8" t="n">
-        <v>845.25</v>
+        <v>846.83</v>
       </c>
       <c r="O8" t="n">
-        <v>898.22</v>
+        <v>907.55</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.8</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>55.35</v>
+        <v>64.87</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="D10" t="n">
         <v>7.6</v>
       </c>
-      <c r="D10" t="n">
-        <v>7.66</v>
-      </c>
       <c r="E10" t="n">
-        <v>-0.78</v>
+        <v>0.79</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.32</v>
+        <v>-3.04</v>
       </c>
       <c r="G10" t="n">
-        <v>8.57</v>
+        <v>14.84</v>
       </c>
       <c r="H10" t="n">
+        <v>2657</v>
+      </c>
+      <c r="I10" t="n">
         <v>3919</v>
       </c>
-      <c r="I10" t="n">
-        <v>2253</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.46</v>
+        <v>0.31</v>
       </c>
       <c r="K10" t="n">
-        <v>1.17</v>
+        <v>0.18</v>
       </c>
       <c r="L10" t="n">
-        <v>53.2</v>
+        <v>54.1</v>
       </c>
       <c r="M10" t="n">
-        <v>9.029999999999999</v>
+        <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>6.82</v>
+        <v>6.84</v>
       </c>
       <c r="O10" t="n">
         <v>13.95</v>
       </c>
       <c r="P10" t="n">
-        <v>-45.52</v>
+        <v>-45.09</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>43.67</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1030</v>
+      </c>
+      <c r="D11" t="n">
         <v>1053</v>
       </c>
-      <c r="D11" t="n">
-        <v>1040</v>
-      </c>
       <c r="E11" t="n">
-        <v>1.25</v>
+        <v>-2.18</v>
       </c>
       <c r="F11" t="n">
-        <v>3.51</v>
+        <v>1.43</v>
       </c>
       <c r="G11" t="n">
-        <v>2.76</v>
+        <v>1.05</v>
       </c>
       <c r="H11" t="n">
-        <v>2710042</v>
+        <v>633391</v>
       </c>
       <c r="I11" t="n">
-        <v>1306864</v>
+        <v>2710310</v>
       </c>
       <c r="J11" t="n">
-        <v>3.08</v>
+        <v>0.65</v>
       </c>
       <c r="K11" t="n">
-        <v>1.47</v>
+        <v>-0.01</v>
       </c>
       <c r="L11" t="n">
-        <v>54.5</v>
+        <v>48.6</v>
       </c>
       <c r="M11" t="n">
-        <v>935.64</v>
+        <v>935.77</v>
       </c>
       <c r="N11" t="n">
-        <v>1047.17</v>
+        <v>1046.86</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.75</v>
+        <v>-7.81</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>54.26</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="D12" t="n">
         <v>25.14</v>
       </c>
-      <c r="D12" t="n">
-        <v>26.13</v>
-      </c>
       <c r="E12" t="n">
-        <v>-3.79</v>
+        <v>1.31</v>
       </c>
       <c r="F12" t="n">
-        <v>14.53</v>
+        <v>10.74</v>
       </c>
       <c r="G12" t="n">
-        <v>15.96</v>
+        <v>14.57</v>
       </c>
       <c r="H12" t="n">
-        <v>54892054</v>
+        <v>120511223</v>
       </c>
       <c r="I12" t="n">
-        <v>95136169</v>
+        <v>54941556</v>
       </c>
       <c r="J12" t="n">
-        <v>4.31</v>
+        <v>7.87</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="L12" t="n">
-        <v>67.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>24.92</v>
+        <v>24.9</v>
       </c>
       <c r="N12" t="n">
-        <v>22.7</v>
+        <v>22.72</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-22.72</v>
+        <v>-21.7</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>16.98</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.69</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.76</v>
-      </c>
       <c r="E13" t="n">
-        <v>-1.22</v>
+        <v>19.33</v>
       </c>
       <c r="F13" t="n">
-        <v>7.56</v>
+        <v>26.44</v>
       </c>
       <c r="G13" t="n">
-        <v>8.17</v>
+        <v>30.83</v>
       </c>
       <c r="H13" t="n">
-        <v>715248</v>
+        <v>9314778</v>
       </c>
       <c r="I13" t="n">
-        <v>2968868</v>
+        <v>715848</v>
       </c>
       <c r="J13" t="n">
-        <v>1.59</v>
+        <v>19.47</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="L13" t="n">
-        <v>61.8</v>
+        <v>80.5</v>
       </c>
       <c r="M13" t="n">
-        <v>5.96</v>
+        <v>5.95</v>
       </c>
       <c r="N13" t="n">
-        <v>5.42</v>
+        <v>5.44</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-41.46</v>
+        <v>-30.14</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>36.12</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24219.05</v>
+      </c>
+      <c r="D17" t="n">
         <v>24252</v>
       </c>
-      <c r="D17" t="n">
-        <v>24231.85</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.47</v>
+        <v>-0.28</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="H17" t="n">
-        <v>0.53</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57525.95</v>
+      </c>
+      <c r="D18" t="n">
         <v>57761.95</v>
       </c>
-      <c r="D18" t="n">
-        <v>57495.9</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.46</v>
+        <v>-0.41</v>
       </c>
       <c r="F18" t="n">
-        <v>0.47</v>
+        <v>0.05</v>
       </c>
       <c r="G18" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="H18" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>93.09</v>
+        <v>92.95</v>
       </c>
       <c r="D19" t="n">
-        <v>93.78</v>
+        <v>94.39</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.74</v>
+        <v>-1.53</v>
       </c>
       <c r="F19" t="n">
-        <v>5.16</v>
+        <v>2.29</v>
       </c>
       <c r="G19" t="n">
-        <v>-7.55</v>
+        <v>-3.96</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.25</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4660.3</v>
+        <v>4723.3</v>
       </c>
       <c r="D20" t="n">
-        <v>4516.3</v>
+        <v>4624.1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.19</v>
+        <v>2.15</v>
       </c>
       <c r="F20" t="n">
-        <v>6.39</v>
+        <v>6.92</v>
       </c>
       <c r="G20" t="n">
-        <v>15.17</v>
+        <v>16.12</v>
       </c>
       <c r="H20" t="n">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>53277.01</v>
+      </c>
+      <c r="D21" t="n">
         <v>52759.21</v>
       </c>
-      <c r="D21" t="n">
-        <v>53463.05</v>
-      </c>
       <c r="E21" t="n">
-        <v>-1.32</v>
+        <v>0.98</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.01</v>
+        <v>-0.85</v>
       </c>
       <c r="G21" t="n">
-        <v>1.04</v>
+        <v>3.03</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.38</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11.19</v>
+        <v>11.52</v>
       </c>
       <c r="D22" t="n">
-        <v>10.76</v>
+        <v>11.2</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.06</v>
+        <v>1.68</v>
       </c>
       <c r="G22" t="n">
-        <v>-16.99</v>
+        <v>-17.89</v>
       </c>
       <c r="H22" t="n">
         <v/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1925,6 +1925,29 @@
       </c>
       <c r="G23" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57525.95</v>
+      </c>
+      <c r="C24" t="n">
+        <v>57761.95</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -1938,7 +1961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2482,6 +2505,29 @@
       </c>
       <c r="G23" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="C24" t="n">
+        <v>94.39</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>
@@ -2495,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3039,6 +3085,29 @@
       </c>
       <c r="G23" t="n">
         <v>2.03</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4723.3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4624.1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="F24" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>
@@ -3052,7 +3121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3558,6 +3627,29 @@
       </c>
       <c r="G22" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>53277.01</v>
+      </c>
+      <c r="C23" t="n">
+        <v>52759.21</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -3571,7 +3663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4062,7 +4154,27 @@
       <c r="F23" t="n">
         <v>-16.99</v>
       </c>
-      <c r="G23" t="n">
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="C24" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-17.89</v>
+      </c>
+      <c r="G24" t="n">
         <v/>
       </c>
     </row>
@@ -4077,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5251,6 +5363,59 @@
       </c>
       <c r="Q22" t="n">
         <v>43.67</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B23" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="C23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="F23" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2657</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3919</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K23" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>9</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="N23" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-45.09</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>44.8</v>
       </c>
     </row>
   </sheetData>
@@ -5264,7 +5429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6438,6 +6603,59 @@
       </c>
       <c r="Q22" t="n">
         <v>16.98</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B23" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="C23" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="F23" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="G23" t="n">
+        <v>120511223</v>
+      </c>
+      <c r="H23" t="n">
+        <v>54941556</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K23" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="L23" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M23" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="N23" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-21.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>18.52</v>
       </c>
     </row>
   </sheetData>
@@ -6451,7 +6669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7519,6 +7737,59 @@
       </c>
       <c r="Q20" t="n">
         <v>58.85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B21" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8487392</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4130558</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K21" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="M21" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="N21" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="P21" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>59.52</v>
       </c>
     </row>
   </sheetData>
@@ -7532,7 +7803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8759,6 +9030,59 @@
       </c>
       <c r="Q23" t="n">
         <v>90.70999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>433.7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>458.8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="G24" t="n">
+        <v>958978</v>
+      </c>
+      <c r="H24" t="n">
+        <v>233935</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K24" t="n">
+        <v>54</v>
+      </c>
+      <c r="L24" t="n">
+        <v>338.56</v>
+      </c>
+      <c r="M24" t="n">
+        <v>395.73</v>
+      </c>
+      <c r="N24" t="n">
+        <v>465.35</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="P24" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>80.28</v>
       </c>
     </row>
   </sheetData>
@@ -8772,7 +9096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9999,6 +10323,59 @@
       </c>
       <c r="Q23" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>269.4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8511454</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8312928</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>36</v>
+      </c>
+      <c r="L24" t="n">
+        <v>312.77</v>
+      </c>
+      <c r="M24" t="n">
+        <v>283.22</v>
+      </c>
+      <c r="N24" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-32.91</v>
+      </c>
+      <c r="P24" t="n">
+        <v>267.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -10012,7 +10389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11239,6 +11616,59 @@
       </c>
       <c r="Q23" t="n">
         <v>11.86</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>884.05</v>
+      </c>
+      <c r="C24" t="n">
+        <v>882.4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>317408</v>
+      </c>
+      <c r="H24" t="n">
+        <v>363713</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>945.6900000000001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>920.42</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-26.57</v>
+      </c>
+      <c r="P24" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>12.07</v>
       </c>
     </row>
   </sheetData>
@@ -11252,7 +11682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12479,6 +12909,59 @@
       </c>
       <c r="Q23" t="n">
         <v>54.26</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1030</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G24" t="n">
+        <v>633391</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2710310</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="K24" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>935.77</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1046.86</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-7.81</v>
+      </c>
+      <c r="P24" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>50.89</v>
       </c>
     </row>
   </sheetData>
@@ -12492,7 +12975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13719,6 +14202,59 @@
       </c>
       <c r="Q23" t="n">
         <v>69.86</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>70.29000000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>72.06999999999999</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="G24" t="n">
+        <v>16995343</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7761634</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="M24" t="n">
+        <v>65.54000000000001</v>
+      </c>
+      <c r="N24" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="P24" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>65.66</v>
       </c>
     </row>
   </sheetData>
@@ -13732,7 +14268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14959,6 +15495,59 @@
       </c>
       <c r="Q23" t="n">
         <v>36.12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="D24" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="E24" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="F24" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9314778</v>
+      </c>
+      <c r="H24" t="n">
+        <v>715848</v>
+      </c>
+      <c r="I24" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K24" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="N24" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-30.14</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>62.44</v>
       </c>
     </row>
   </sheetData>
@@ -14972,7 +15561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16199,6 +16788,59 @@
       </c>
       <c r="Q23" t="n">
         <v>55.35</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>907.55</v>
+      </c>
+      <c r="C24" t="n">
+        <v>855.15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1156116</v>
+      </c>
+      <c r="H24" t="n">
+        <v>171823</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K24" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>750.16</v>
+      </c>
+      <c r="M24" t="n">
+        <v>846.83</v>
+      </c>
+      <c r="N24" t="n">
+        <v>907.55</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>64.87</v>
       </c>
     </row>
   </sheetData>
@@ -16212,7 +16854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16758,6 +17400,29 @@
         <v>0.53</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>24219.05</v>
+      </c>
+      <c r="C24" t="n">
+        <v>24252</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>428.25</v>
+      </c>
+      <c r="D3" t="n">
         <v>433.7</v>
       </c>
-      <c r="D3" t="n">
-        <v>458.8</v>
-      </c>
       <c r="E3" t="n">
-        <v>-5.47</v>
+        <v>-1.26</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.8</v>
+        <v>-5.44</v>
       </c>
       <c r="G3" t="n">
-        <v>7.78</v>
+        <v>3.22</v>
       </c>
       <c r="H3" t="n">
-        <v>958978</v>
+        <v>284453</v>
       </c>
       <c r="I3" t="n">
-        <v>233935</v>
+        <v>959780</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8</v>
+        <v>0.52</v>
       </c>
       <c r="K3" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>54</v>
+        <v>51.9</v>
       </c>
       <c r="M3" t="n">
-        <v>338.56</v>
+        <v>338.88</v>
       </c>
       <c r="N3" t="n">
-        <v>395.73</v>
+        <v>397.77</v>
       </c>
       <c r="O3" t="n">
         <v>465.35</v>
       </c>
       <c r="P3" t="n">
-        <v>-6.8</v>
+        <v>-7.97</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>80.28</v>
+        <v>78.01000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>45.35</v>
+      </c>
+      <c r="D4" t="n">
         <v>45.16</v>
-      </c>
-      <c r="D4" t="n">
-        <v>44.97</v>
       </c>
       <c r="E4" t="n">
         <v>0.42</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.13</v>
+        <v>0.58</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.97</v>
+        <v>-4.39</v>
       </c>
       <c r="H4" t="n">
-        <v>8487392</v>
+        <v>6449392</v>
       </c>
       <c r="I4" t="n">
-        <v>4130558</v>
+        <v>8487952</v>
       </c>
       <c r="J4" t="n">
-        <v>1.21</v>
+        <v>0.97</v>
       </c>
       <c r="K4" t="n">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="L4" t="n">
-        <v>45.8</v>
+        <v>47.7</v>
       </c>
       <c r="M4" t="n">
-        <v>41.21</v>
+        <v>41.25</v>
       </c>
       <c r="N4" t="n">
-        <v>45.85</v>
+        <v>45.82</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.96</v>
+        <v>-5.56</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>59.52</v>
+        <v>60.19</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>271.4</v>
+      </c>
+      <c r="D5" t="n">
         <v>269.7</v>
       </c>
-      <c r="D5" t="n">
-        <v>269.4</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.11</v>
+        <v>0.63</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.23</v>
+        <v>0.52</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.85</v>
+        <v>-5.06</v>
       </c>
       <c r="H5" t="n">
-        <v>8511454</v>
+        <v>8402741</v>
       </c>
       <c r="I5" t="n">
-        <v>8312928</v>
+        <v>8518400</v>
       </c>
       <c r="J5" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>39.3</v>
       </c>
       <c r="M5" t="n">
-        <v>312.77</v>
+        <v>312.2</v>
       </c>
       <c r="N5" t="n">
-        <v>283.22</v>
+        <v>282.82</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-32.91</v>
+        <v>-32.49</v>
       </c>
       <c r="Q5" t="n">
         <v>267.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.99</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>866.25</v>
+      </c>
+      <c r="D6" t="n">
         <v>884.05</v>
       </c>
-      <c r="D6" t="n">
-        <v>882.4</v>
-      </c>
       <c r="E6" t="n">
-        <v>0.19</v>
+        <v>-2.01</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.48</v>
+        <v>-3.41</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.9</v>
+        <v>-6.41</v>
       </c>
       <c r="H6" t="n">
-        <v>317408</v>
+        <v>443232</v>
       </c>
       <c r="I6" t="n">
-        <v>363713</v>
+        <v>317429</v>
       </c>
       <c r="J6" t="n">
-        <v>0.71</v>
+        <v>0.98</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>-0.02</v>
       </c>
       <c r="L6" t="n">
-        <v>40.5</v>
+        <v>36.1</v>
       </c>
       <c r="M6" t="n">
-        <v>945.6900000000001</v>
+        <v>946.03</v>
       </c>
       <c r="N6" t="n">
-        <v>920.42</v>
+        <v>920.75</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-26.57</v>
+        <v>-28.05</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>12.07</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>69.45999999999999</v>
+      </c>
+      <c r="D7" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="D7" t="n">
-        <v>72.06999999999999</v>
-      </c>
       <c r="E7" t="n">
-        <v>-2.47</v>
+        <v>-1.18</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.66</v>
+        <v>-3.97</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.61</v>
+        <v>-2.95</v>
       </c>
       <c r="H7" t="n">
-        <v>16995343</v>
+        <v>10199383</v>
       </c>
       <c r="I7" t="n">
-        <v>7761634</v>
+        <v>16995792</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="L7" t="n">
-        <v>53.1</v>
+        <v>49.8</v>
       </c>
       <c r="M7" t="n">
-        <v>58.77</v>
+        <v>58.86</v>
       </c>
       <c r="N7" t="n">
-        <v>65.54000000000001</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.01</v>
+        <v>-4.15</v>
       </c>
       <c r="Q7" t="n">
         <v>42.43</v>
       </c>
       <c r="R7" t="n">
-        <v>65.66</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="8">
@@ -846,43 +846,43 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>923.05</v>
+      </c>
+      <c r="D8" t="n">
         <v>907.55</v>
       </c>
-      <c r="D8" t="n">
-        <v>855.15</v>
-      </c>
       <c r="E8" t="n">
-        <v>6.13</v>
+        <v>1.71</v>
       </c>
       <c r="F8" t="n">
-        <v>7.68</v>
+        <v>8.09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.26</v>
+        <v>9.44</v>
       </c>
       <c r="H8" t="n">
-        <v>1156116</v>
+        <v>900077</v>
       </c>
       <c r="I8" t="n">
-        <v>171823</v>
+        <v>1156221</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>2.57</v>
       </c>
       <c r="K8" t="n">
-        <v>0.53</v>
+        <v>2.28</v>
       </c>
       <c r="L8" t="n">
-        <v>66.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>750.16</v>
+        <v>750.86</v>
       </c>
       <c r="N8" t="n">
-        <v>846.83</v>
+        <v>848.74</v>
       </c>
       <c r="O8" t="n">
-        <v>907.55</v>
+        <v>923.05</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>64.87</v>
+        <v>67.68000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -928,16 +928,16 @@
         <v>14.84</v>
       </c>
       <c r="H10" t="n">
-        <v>2657</v>
+        <v>5959</v>
       </c>
       <c r="I10" t="n">
         <v>3919</v>
       </c>
       <c r="J10" t="n">
-        <v>0.31</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="L10" t="n">
         <v>54.1</v>
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D11" t="n">
         <v>1030</v>
       </c>
-      <c r="D11" t="n">
-        <v>1053</v>
-      </c>
       <c r="E11" t="n">
-        <v>-2.18</v>
+        <v>0.58</v>
       </c>
       <c r="F11" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>1.05</v>
+        <v>-0.38</v>
       </c>
       <c r="H11" t="n">
-        <v>633391</v>
+        <v>489862</v>
       </c>
       <c r="I11" t="n">
-        <v>2710310</v>
+        <v>634282</v>
       </c>
       <c r="J11" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.01</v>
+        <v>-0.31</v>
       </c>
       <c r="L11" t="n">
-        <v>48.6</v>
+        <v>50.1</v>
       </c>
       <c r="M11" t="n">
-        <v>935.77</v>
+        <v>935.8099999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>1046.86</v>
+        <v>1046.48</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.81</v>
+        <v>-7.27</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>50.89</v>
+        <v>51.77</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="D12" t="n">
         <v>25.47</v>
       </c>
-      <c r="D12" t="n">
-        <v>25.14</v>
-      </c>
       <c r="E12" t="n">
-        <v>1.31</v>
+        <v>-3.14</v>
       </c>
       <c r="F12" t="n">
-        <v>10.74</v>
+        <v>5.88</v>
       </c>
       <c r="G12" t="n">
-        <v>14.57</v>
+        <v>12.85</v>
       </c>
       <c r="H12" t="n">
-        <v>120511223</v>
+        <v>42634430</v>
       </c>
       <c r="I12" t="n">
-        <v>54941556</v>
+        <v>120525051</v>
       </c>
       <c r="J12" t="n">
-        <v>7.87</v>
+        <v>2.01</v>
       </c>
       <c r="K12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>69.09999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="M12" t="n">
-        <v>24.9</v>
+        <v>24.88</v>
       </c>
       <c r="N12" t="n">
-        <v>22.72</v>
+        <v>22.74</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-21.7</v>
+        <v>-24.16</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>18.52</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="D13" t="n">
         <v>6.79</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.69</v>
-      </c>
       <c r="E13" t="n">
-        <v>19.33</v>
+        <v>-7.36</v>
       </c>
       <c r="F13" t="n">
-        <v>26.44</v>
+        <v>15.41</v>
       </c>
       <c r="G13" t="n">
-        <v>30.83</v>
+        <v>19.81</v>
       </c>
       <c r="H13" t="n">
-        <v>9314778</v>
+        <v>2328484</v>
       </c>
       <c r="I13" t="n">
-        <v>715848</v>
+        <v>9320681</v>
       </c>
       <c r="J13" t="n">
-        <v>19.47</v>
+        <v>2.48</v>
       </c>
       <c r="K13" t="n">
-        <v>0.58</v>
+        <v>1.09</v>
       </c>
       <c r="L13" t="n">
-        <v>80.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>5.95</v>
       </c>
       <c r="N13" t="n">
-        <v>5.44</v>
+        <v>5.45</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-30.14</v>
+        <v>-35.29</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>62.44</v>
+        <v>50.48</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24334.55</v>
+      </c>
+      <c r="D17" t="n">
         <v>24219.05</v>
       </c>
-      <c r="D17" t="n">
-        <v>24252</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.14</v>
+        <v>0.48</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.28</v>
+        <v>0.74</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="H17" t="n">
-        <v>0.39</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57514.2</v>
+      </c>
+      <c r="D18" t="n">
         <v>57525.95</v>
       </c>
-      <c r="D18" t="n">
-        <v>57761.95</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.41</v>
+        <v>-0.02</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05</v>
+        <v>0.44</v>
       </c>
       <c r="G18" t="n">
-        <v>1.47</v>
+        <v>0.75</v>
       </c>
       <c r="H18" t="n">
-        <v>0.35</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>92.95</v>
+        <v>87.97</v>
       </c>
       <c r="D19" t="n">
-        <v>94.39</v>
+        <v>92.17</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.53</v>
+        <v>-4.56</v>
       </c>
       <c r="F19" t="n">
-        <v>2.29</v>
+        <v>-3.35</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.96</v>
+        <v>-0.44</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.39</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4723.3</v>
+        <v>4700</v>
       </c>
       <c r="D20" t="n">
-        <v>4624.1</v>
+        <v>4640.8</v>
       </c>
       <c r="E20" t="n">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="F20" t="n">
-        <v>6.92</v>
+        <v>7.65</v>
       </c>
       <c r="G20" t="n">
-        <v>16.12</v>
+        <v>15.35</v>
       </c>
       <c r="H20" t="n">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>53417.16</v>
+      </c>
+      <c r="D21" t="n">
         <v>53277.01</v>
       </c>
-      <c r="D21" t="n">
-        <v>52759.21</v>
-      </c>
       <c r="E21" t="n">
-        <v>0.98</v>
+        <v>0.26</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.85</v>
+        <v>-0.08</v>
       </c>
       <c r="G21" t="n">
-        <v>3.03</v>
+        <v>2.83</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11.52</v>
+        <v>11.07</v>
       </c>
       <c r="D22" t="n">
-        <v>11.2</v>
+        <v>11.53</v>
       </c>
       <c r="E22" t="n">
-        <v>2.86</v>
+        <v>-3.99</v>
       </c>
       <c r="F22" t="n">
-        <v>1.68</v>
+        <v>-2.81</v>
       </c>
       <c r="G22" t="n">
-        <v>-17.89</v>
+        <v>-12.56</v>
       </c>
       <c r="H22" t="n">
         <v/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1948,6 +1948,29 @@
       </c>
       <c r="G24" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57514.2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>57525.95</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -1961,7 +1984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2528,6 +2551,29 @@
       </c>
       <c r="G24" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87.97</v>
+      </c>
+      <c r="C25" t="n">
+        <v>92.17</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -2541,7 +2587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3108,6 +3154,29 @@
       </c>
       <c r="G24" t="n">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4640.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="F25" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.21</v>
       </c>
     </row>
   </sheetData>
@@ -3121,7 +3190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3650,6 +3719,29 @@
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>53417.16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>53277.01</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -3663,7 +3755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4174,7 +4266,27 @@
       <c r="F24" t="n">
         <v>-17.89</v>
       </c>
-      <c r="G24" t="n">
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="C25" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-12.56</v>
+      </c>
+      <c r="G25" t="n">
         <v/>
       </c>
     </row>
@@ -4189,7 +4301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5415,6 +5527,59 @@
         <v>5.29</v>
       </c>
       <c r="Q23" t="n">
+        <v>44.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B24" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="C24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="F24" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5959</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3919</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K24" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>9</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="N24" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-45.09</v>
+      </c>
+      <c r="P24" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q24" t="n">
         <v>44.8</v>
       </c>
     </row>
@@ -5429,7 +5594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6656,6 +6821,59 @@
       </c>
       <c r="Q23" t="n">
         <v>18.52</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B24" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="C24" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="G24" t="n">
+        <v>42634430</v>
+      </c>
+      <c r="H24" t="n">
+        <v>120525051</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="M24" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="N24" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-24.16</v>
+      </c>
+      <c r="P24" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>14.8</v>
       </c>
     </row>
   </sheetData>
@@ -6669,7 +6887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7790,6 +8008,59 @@
       </c>
       <c r="Q21" t="n">
         <v>59.52</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B22" t="n">
+        <v>45.35</v>
+      </c>
+      <c r="C22" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6449392</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8487952</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K22" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="L22" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="N22" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="P22" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>60.19</v>
       </c>
     </row>
   </sheetData>
@@ -7803,7 +8074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9083,6 +9354,59 @@
       </c>
       <c r="Q24" t="n">
         <v>80.28</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>428.25</v>
+      </c>
+      <c r="C25" t="n">
+        <v>433.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G25" t="n">
+        <v>284453</v>
+      </c>
+      <c r="H25" t="n">
+        <v>959780</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>338.88</v>
+      </c>
+      <c r="M25" t="n">
+        <v>397.77</v>
+      </c>
+      <c r="N25" t="n">
+        <v>465.35</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-7.97</v>
+      </c>
+      <c r="P25" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>78.01000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -9096,7 +9420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10376,6 +10700,59 @@
       </c>
       <c r="Q24" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>271.4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8402741</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8518400</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>312.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>282.82</v>
+      </c>
+      <c r="N25" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-32.49</v>
+      </c>
+      <c r="P25" t="n">
+        <v>267.05</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>
@@ -10389,7 +10766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11669,6 +12046,59 @@
       </c>
       <c r="Q24" t="n">
         <v>12.07</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>866.25</v>
+      </c>
+      <c r="C25" t="n">
+        <v>884.05</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-6.41</v>
+      </c>
+      <c r="G25" t="n">
+        <v>443232</v>
+      </c>
+      <c r="H25" t="n">
+        <v>317429</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="K25" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>946.03</v>
+      </c>
+      <c r="M25" t="n">
+        <v>920.75</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-28.05</v>
+      </c>
+      <c r="P25" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>9.81</v>
       </c>
     </row>
   </sheetData>
@@ -11682,7 +12112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12962,6 +13392,59 @@
       </c>
       <c r="Q24" t="n">
         <v>50.89</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1036</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1030</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="G25" t="n">
+        <v>489862</v>
+      </c>
+      <c r="H25" t="n">
+        <v>634282</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="K25" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>935.8099999999999</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1046.48</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-7.27</v>
+      </c>
+      <c r="P25" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>51.77</v>
       </c>
     </row>
   </sheetData>
@@ -12975,7 +13458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14255,6 +14738,59 @@
       </c>
       <c r="Q24" t="n">
         <v>65.66</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>69.45999999999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>70.29000000000001</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.97</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10199383</v>
+      </c>
+      <c r="H25" t="n">
+        <v>16995792</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="K25" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="M25" t="n">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="N25" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="P25" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>63.7</v>
       </c>
     </row>
   </sheetData>
@@ -14268,7 +14804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15548,6 +16084,59 @@
       </c>
       <c r="Q24" t="n">
         <v>62.44</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="C25" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-7.36</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="F25" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2328484</v>
+      </c>
+      <c r="H25" t="n">
+        <v>9320681</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K25" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M25" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="N25" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-35.29</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>50.48</v>
       </c>
     </row>
   </sheetData>
@@ -15561,7 +16150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16841,6 +17430,59 @@
       </c>
       <c r="Q24" t="n">
         <v>64.87</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>923.05</v>
+      </c>
+      <c r="C25" t="n">
+        <v>907.55</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="G25" t="n">
+        <v>900077</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1156221</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K25" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="L25" t="n">
+        <v>750.86</v>
+      </c>
+      <c r="M25" t="n">
+        <v>848.74</v>
+      </c>
+      <c r="N25" t="n">
+        <v>923.05</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>67.68000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -16854,7 +17496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17423,6 +18065,29 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>24334.55</v>
+      </c>
+      <c r="C25" t="n">
+        <v>24219.05</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>458.9</v>
+      </c>
+      <c r="D3" t="n">
         <v>428.25</v>
       </c>
-      <c r="D3" t="n">
-        <v>433.7</v>
-      </c>
       <c r="E3" t="n">
-        <v>-1.26</v>
+        <v>7.16</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.44</v>
+        <v>2.9</v>
       </c>
       <c r="G3" t="n">
-        <v>3.22</v>
+        <v>16.28</v>
       </c>
       <c r="H3" t="n">
-        <v>284453</v>
+        <v>671440</v>
       </c>
       <c r="I3" t="n">
-        <v>959780</v>
+        <v>284853</v>
       </c>
       <c r="J3" t="n">
-        <v>0.52</v>
+        <v>1.26</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="L3" t="n">
-        <v>51.9</v>
+        <v>61</v>
       </c>
       <c r="M3" t="n">
-        <v>338.88</v>
+        <v>339.27</v>
       </c>
       <c r="N3" t="n">
-        <v>397.77</v>
+        <v>400.46</v>
       </c>
       <c r="O3" t="n">
         <v>465.35</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.97</v>
+        <v>-1.39</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>78.01000000000001</v>
+        <v>90.76000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="D4" t="n">
         <v>45.35</v>
       </c>
-      <c r="D4" t="n">
-        <v>45.16</v>
-      </c>
       <c r="E4" t="n">
-        <v>0.42</v>
+        <v>2.14</v>
       </c>
       <c r="F4" t="n">
-        <v>0.58</v>
+        <v>2.93</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.39</v>
+        <v>-0.75</v>
       </c>
       <c r="H4" t="n">
+        <v>8352019</v>
+      </c>
+      <c r="I4" t="n">
         <v>6449392</v>
       </c>
-      <c r="I4" t="n">
-        <v>8487952</v>
-      </c>
       <c r="J4" t="n">
-        <v>0.97</v>
+        <v>1.26</v>
       </c>
       <c r="K4" t="n">
-        <v>1.23</v>
+        <v>3.09</v>
       </c>
       <c r="L4" t="n">
-        <v>47.7</v>
+        <v>56.1</v>
       </c>
       <c r="M4" t="n">
-        <v>41.25</v>
+        <v>41.29</v>
       </c>
       <c r="N4" t="n">
-        <v>45.82</v>
+        <v>45.78</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.56</v>
+        <v>-3.54</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>60.19</v>
+        <v>63.62</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>270.25</v>
+      </c>
+      <c r="D5" t="n">
         <v>271.4</v>
       </c>
-      <c r="D5" t="n">
-        <v>269.7</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.63</v>
+        <v>-0.42</v>
       </c>
       <c r="F5" t="n">
-        <v>0.52</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
         <v>-5.06</v>
       </c>
       <c r="H5" t="n">
-        <v>8402741</v>
+        <v>11687310</v>
       </c>
       <c r="I5" t="n">
-        <v>8518400</v>
+        <v>8414719</v>
       </c>
       <c r="J5" t="n">
-        <v>0.57</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="L5" t="n">
-        <v>39.3</v>
+        <v>37.9</v>
       </c>
       <c r="M5" t="n">
-        <v>312.2</v>
+        <v>311.61</v>
       </c>
       <c r="N5" t="n">
-        <v>282.82</v>
+        <v>282.41</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-32.49</v>
+        <v>-32.77</v>
       </c>
       <c r="Q5" t="n">
         <v>267.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>863.4</v>
+      </c>
+      <c r="D6" t="n">
         <v>866.25</v>
       </c>
-      <c r="D6" t="n">
-        <v>884.05</v>
-      </c>
       <c r="E6" t="n">
-        <v>-2.01</v>
+        <v>-0.33</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.41</v>
+        <v>-2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.41</v>
+        <v>-6.51</v>
       </c>
       <c r="H6" t="n">
-        <v>443232</v>
+        <v>371094</v>
       </c>
       <c r="I6" t="n">
-        <v>317429</v>
+        <v>443465</v>
       </c>
       <c r="J6" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02</v>
+        <v>3.42</v>
       </c>
       <c r="L6" t="n">
-        <v>36.1</v>
+        <v>35.5</v>
       </c>
       <c r="M6" t="n">
-        <v>946.03</v>
+        <v>946.37</v>
       </c>
       <c r="N6" t="n">
-        <v>920.75</v>
+        <v>920.7</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-28.05</v>
+        <v>-28.29</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>9.81</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="D7" t="n">
         <v>69.45999999999999</v>
       </c>
-      <c r="D7" t="n">
-        <v>70.29000000000001</v>
-      </c>
       <c r="E7" t="n">
-        <v>-1.18</v>
+        <v>-0.68</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.97</v>
+        <v>-3.91</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.95</v>
+        <v>-1.61</v>
       </c>
       <c r="H7" t="n">
-        <v>10199383</v>
+        <v>15417735</v>
       </c>
       <c r="I7" t="n">
-        <v>16995792</v>
+        <v>10201371</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.35</v>
+        <v>-0.55</v>
       </c>
       <c r="L7" t="n">
-        <v>49.8</v>
+        <v>48</v>
       </c>
       <c r="M7" t="n">
-        <v>58.86</v>
+        <v>58.94</v>
       </c>
       <c r="N7" t="n">
-        <v>65.79000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.15</v>
+        <v>-4.8</v>
       </c>
       <c r="Q7" t="n">
         <v>42.43</v>
       </c>
       <c r="R7" t="n">
-        <v>63.7</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="8">
@@ -846,43 +846,43 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>965.3</v>
+      </c>
+      <c r="D8" t="n">
         <v>923.05</v>
       </c>
-      <c r="D8" t="n">
-        <v>907.55</v>
-      </c>
       <c r="E8" t="n">
-        <v>1.71</v>
+        <v>4.58</v>
       </c>
       <c r="F8" t="n">
-        <v>8.09</v>
+        <v>13.25</v>
       </c>
       <c r="G8" t="n">
-        <v>9.44</v>
+        <v>15.82</v>
       </c>
       <c r="H8" t="n">
-        <v>900077</v>
+        <v>682896</v>
       </c>
       <c r="I8" t="n">
-        <v>1156221</v>
+        <v>900090</v>
       </c>
       <c r="J8" t="n">
-        <v>2.57</v>
+        <v>1.76</v>
       </c>
       <c r="K8" t="n">
-        <v>2.28</v>
+        <v>0.44</v>
       </c>
       <c r="L8" t="n">
-        <v>69.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="M8" t="n">
-        <v>750.86</v>
+        <v>751.71</v>
       </c>
       <c r="N8" t="n">
-        <v>848.74</v>
+        <v>851.62</v>
       </c>
       <c r="O8" t="n">
-        <v>923.05</v>
+        <v>965.3</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>67.68000000000001</v>
+        <v>75.36</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="D10" t="n">
         <v>7.66</v>
       </c>
-      <c r="D10" t="n">
-        <v>7.6</v>
-      </c>
       <c r="E10" t="n">
-        <v>0.79</v>
+        <v>-0.26</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.04</v>
+        <v>-4.5</v>
       </c>
       <c r="G10" t="n">
-        <v>14.84</v>
+        <v>19.37</v>
       </c>
       <c r="H10" t="n">
+        <v>442</v>
+      </c>
+      <c r="I10" t="n">
         <v>5959</v>
       </c>
-      <c r="I10" t="n">
-        <v>3919</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>54.1</v>
+        <v>53.7</v>
       </c>
       <c r="M10" t="n">
-        <v>9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>6.84</v>
+        <v>6.88</v>
       </c>
       <c r="O10" t="n">
         <v>13.95</v>
       </c>
       <c r="P10" t="n">
-        <v>-45.09</v>
+        <v>-45.23</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>44.8</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D11" t="n">
         <v>1036</v>
       </c>
-      <c r="D11" t="n">
-        <v>1030</v>
-      </c>
       <c r="E11" t="n">
-        <v>0.58</v>
+        <v>-2.99</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.38</v>
+        <v>-1.17</v>
       </c>
       <c r="H11" t="n">
-        <v>489862</v>
+        <v>2550757</v>
       </c>
       <c r="I11" t="n">
-        <v>634282</v>
+        <v>490536</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>2.61</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.31</v>
+        <v>0.08</v>
       </c>
       <c r="L11" t="n">
-        <v>50.1</v>
+        <v>43</v>
       </c>
       <c r="M11" t="n">
-        <v>935.8099999999999</v>
+        <v>935.72</v>
       </c>
       <c r="N11" t="n">
-        <v>1046.48</v>
+        <v>1045.46</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.27</v>
+        <v>-10.04</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>51.77</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="D12" t="n">
         <v>24.67</v>
       </c>
-      <c r="D12" t="n">
-        <v>25.47</v>
-      </c>
       <c r="E12" t="n">
-        <v>-3.14</v>
+        <v>-2.96</v>
       </c>
       <c r="F12" t="n">
-        <v>5.88</v>
+        <v>-1.24</v>
       </c>
       <c r="G12" t="n">
-        <v>12.85</v>
+        <v>10.63</v>
       </c>
       <c r="H12" t="n">
-        <v>42634430</v>
+        <v>28386077</v>
       </c>
       <c r="I12" t="n">
-        <v>120525051</v>
+        <v>42636836</v>
       </c>
       <c r="J12" t="n">
-        <v>2.01</v>
+        <v>1.22</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="L12" t="n">
-        <v>61.1</v>
+        <v>54.9</v>
       </c>
       <c r="M12" t="n">
-        <v>24.88</v>
+        <v>24.86</v>
       </c>
       <c r="N12" t="n">
-        <v>22.74</v>
+        <v>22.76</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-24.16</v>
+        <v>-26.41</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>14.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="D13" t="n">
         <v>6.29</v>
       </c>
-      <c r="D13" t="n">
-        <v>6.79</v>
-      </c>
       <c r="E13" t="n">
-        <v>-7.36</v>
+        <v>-2.23</v>
       </c>
       <c r="F13" t="n">
-        <v>15.41</v>
+        <v>11.82</v>
       </c>
       <c r="G13" t="n">
-        <v>19.81</v>
+        <v>18.04</v>
       </c>
       <c r="H13" t="n">
-        <v>2328484</v>
+        <v>696815</v>
       </c>
       <c r="I13" t="n">
-        <v>9320681</v>
+        <v>2330979</v>
       </c>
       <c r="J13" t="n">
-        <v>2.48</v>
+        <v>0.66</v>
       </c>
       <c r="K13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>64.90000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="M13" t="n">
-        <v>5.95</v>
+        <v>5.94</v>
       </c>
       <c r="N13" t="n">
-        <v>5.45</v>
+        <v>5.46</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-35.29</v>
+        <v>-36.73</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>50.48</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24207.75</v>
+      </c>
+      <c r="D17" t="n">
         <v>24334.55</v>
       </c>
-      <c r="D17" t="n">
-        <v>24219.05</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.48</v>
+        <v>-0.52</v>
       </c>
       <c r="F17" t="n">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
       <c r="G17" t="n">
-        <v>1.41</v>
+        <v>0.93</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57783.75</v>
+      </c>
+      <c r="D18" t="n">
         <v>57514.2</v>
       </c>
-      <c r="D18" t="n">
-        <v>57525.95</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.02</v>
+        <v>0.47</v>
       </c>
       <c r="F18" t="n">
-        <v>0.44</v>
+        <v>0.95</v>
       </c>
       <c r="G18" t="n">
-        <v>0.75</v>
+        <v>1.81</v>
       </c>
       <c r="H18" t="n">
-        <v>-1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>87.97</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>92.17</v>
+        <v>88.58</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.56</v>
+        <v>-3.56</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.35</v>
+        <v>-6.76</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.44</v>
+        <v>1.59</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4700</v>
+        <v>4673.3</v>
       </c>
       <c r="D20" t="n">
-        <v>4640.8</v>
+        <v>4638.1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.28</v>
+        <v>0.76</v>
       </c>
       <c r="F20" t="n">
-        <v>7.65</v>
+        <v>4.1</v>
       </c>
       <c r="G20" t="n">
-        <v>15.35</v>
+        <v>15.78</v>
       </c>
       <c r="H20" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>53577.4</v>
+      </c>
+      <c r="D21" t="n">
         <v>53417.16</v>
       </c>
-      <c r="D21" t="n">
-        <v>53277.01</v>
-      </c>
       <c r="E21" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.08</v>
+        <v>0.44</v>
       </c>
       <c r="G21" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.08</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11.07</v>
+        <v>10.56</v>
       </c>
       <c r="D22" t="n">
-        <v>11.53</v>
+        <v>11.08</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.99</v>
+        <v>-4.69</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.81</v>
+        <v>-6.71</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.56</v>
+        <v>-15.92</v>
       </c>
       <c r="H22" t="n">
         <v/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1971,6 +1971,29 @@
       </c>
       <c r="G25" t="n">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57783.75</v>
+      </c>
+      <c r="C26" t="n">
+        <v>57514.2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -1984,7 +2007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2574,6 +2597,29 @@
       </c>
       <c r="G25" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>88.58</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-6.76</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.72</v>
       </c>
     </row>
   </sheetData>
@@ -2587,7 +2633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3223,29 @@
       </c>
       <c r="G25" t="n">
         <v>2.21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4673.3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4638.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>
@@ -3190,7 +3259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3742,6 +3811,29 @@
       </c>
       <c r="G24" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>53577.4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>53417.16</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -3755,7 +3847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4286,7 +4378,27 @@
       <c r="F25" t="n">
         <v>-12.56</v>
       </c>
-      <c r="G25" t="n">
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="C26" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-6.71</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-15.92</v>
+      </c>
+      <c r="G26" t="n">
         <v/>
       </c>
     </row>
@@ -4301,7 +4413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5581,6 +5693,59 @@
       </c>
       <c r="Q24" t="n">
         <v>44.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B25" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="C25" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="G25" t="n">
+        <v>442</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5959</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="L25" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="M25" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="N25" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-45.23</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>44.42</v>
       </c>
     </row>
   </sheetData>
@@ -5594,7 +5759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6874,6 +7039,59 @@
       </c>
       <c r="Q24" t="n">
         <v>14.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="C25" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="G25" t="n">
+        <v>28386077</v>
+      </c>
+      <c r="H25" t="n">
+        <v>42636836</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="K25" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="M25" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="N25" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-26.41</v>
+      </c>
+      <c r="P25" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>11.4</v>
       </c>
     </row>
   </sheetData>
@@ -6887,7 +7105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8061,6 +8279,59 @@
       </c>
       <c r="Q22" t="n">
         <v>60.19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B23" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="C23" t="n">
+        <v>45.35</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8352019</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6449392</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="K23" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="M23" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="N23" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="P23" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>63.62</v>
       </c>
     </row>
   </sheetData>
@@ -8074,7 +8345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9407,6 +9678,59 @@
       </c>
       <c r="Q25" t="n">
         <v>78.01000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>458.9</v>
+      </c>
+      <c r="C26" t="n">
+        <v>428.25</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="G26" t="n">
+        <v>671440</v>
+      </c>
+      <c r="H26" t="n">
+        <v>284853</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="K26" t="n">
+        <v>61</v>
+      </c>
+      <c r="L26" t="n">
+        <v>339.27</v>
+      </c>
+      <c r="M26" t="n">
+        <v>400.46</v>
+      </c>
+      <c r="N26" t="n">
+        <v>465.35</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="P26" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>90.76000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -9420,7 +9744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10753,6 +11077,59 @@
       </c>
       <c r="Q25" t="n">
         <v>1.63</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>270.25</v>
+      </c>
+      <c r="C26" t="n">
+        <v>271.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="G26" t="n">
+        <v>11687310</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8414719</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K26" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="L26" t="n">
+        <v>311.61</v>
+      </c>
+      <c r="M26" t="n">
+        <v>282.41</v>
+      </c>
+      <c r="N26" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-32.77</v>
+      </c>
+      <c r="P26" t="n">
+        <v>267.05</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -10766,7 +11143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12099,6 +12476,59 @@
       </c>
       <c r="Q25" t="n">
         <v>9.81</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>863.4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>866.25</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="G26" t="n">
+        <v>371094</v>
+      </c>
+      <c r="H26" t="n">
+        <v>443465</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="K26" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>946.37</v>
+      </c>
+      <c r="M26" t="n">
+        <v>920.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-28.29</v>
+      </c>
+      <c r="P26" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>9.449999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12112,7 +12542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13445,6 +13875,59 @@
       </c>
       <c r="Q25" t="n">
         <v>51.77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1005</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2550757</v>
+      </c>
+      <c r="H26" t="n">
+        <v>490536</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K26" t="n">
+        <v>43</v>
+      </c>
+      <c r="L26" t="n">
+        <v>935.72</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1045.46</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-10.04</v>
+      </c>
+      <c r="P26" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>47.23</v>
       </c>
     </row>
   </sheetData>
@@ -13458,7 +13941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14791,6 +15274,59 @@
       </c>
       <c r="Q25" t="n">
         <v>63.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>69.45999999999999</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15417735</v>
+      </c>
+      <c r="H26" t="n">
+        <v>10201371</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="K26" t="n">
+        <v>48</v>
+      </c>
+      <c r="L26" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="M26" t="n">
+        <v>66.03</v>
+      </c>
+      <c r="N26" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>62.6</v>
       </c>
     </row>
   </sheetData>
@@ -14804,7 +15340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16137,6 +16673,59 @@
       </c>
       <c r="Q25" t="n">
         <v>50.48</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="C26" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="E26" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="F26" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="G26" t="n">
+        <v>696815</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2330979</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="M26" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="N26" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-36.73</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>47.13</v>
       </c>
     </row>
   </sheetData>
@@ -16150,7 +16739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17483,6 +18072,59 @@
       </c>
       <c r="Q25" t="n">
         <v>67.68000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>965.3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>923.05</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="E26" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F26" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="G26" t="n">
+        <v>682896</v>
+      </c>
+      <c r="H26" t="n">
+        <v>900090</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K26" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>751.71</v>
+      </c>
+      <c r="M26" t="n">
+        <v>851.62</v>
+      </c>
+      <c r="N26" t="n">
+        <v>965.3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>75.36</v>
       </c>
     </row>
   </sheetData>
@@ -17496,7 +18138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18088,6 +18730,29 @@
         <v>-0.5600000000000001</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24207.75</v>
+      </c>
+      <c r="C26" t="n">
+        <v>24334.55</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -545,54 +545,27 @@
           <t>DYCL.NS</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>458.9</v>
       </c>
-      <c r="D3" t="n">
-        <v>428.25</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G3" t="n">
-        <v>16.28</v>
-      </c>
       <c r="H3" t="n">
-        <v>671440</v>
+        <v>236905</v>
       </c>
       <c r="I3" t="n">
-        <v>284853</v>
+        <v>671640</v>
       </c>
       <c r="J3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.37</v>
+        <v>0.43</v>
       </c>
       <c r="L3" t="n">
         <v>61</v>
       </c>
-      <c r="M3" t="n">
-        <v>339.27</v>
-      </c>
-      <c r="N3" t="n">
-        <v>400.46</v>
-      </c>
       <c r="O3" t="n">
         <v>465.35</v>
       </c>
-      <c r="P3" t="n">
-        <v>-1.39</v>
-      </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
-      <c r="R3" t="n">
-        <v>90.76000000000001</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -605,54 +578,27 @@
           <t>SOUTHBANK.NS</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>46.32</v>
       </c>
-      <c r="D4" t="n">
-        <v>45.35</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.75</v>
-      </c>
       <c r="H4" t="n">
-        <v>8352019</v>
+        <v>8299227</v>
       </c>
       <c r="I4" t="n">
-        <v>6449392</v>
+        <v>8354307</v>
       </c>
       <c r="J4" t="n">
         <v>1.26</v>
       </c>
-      <c r="K4" t="n">
-        <v>3.09</v>
-      </c>
       <c r="L4" t="n">
         <v>56.1</v>
       </c>
-      <c r="M4" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="N4" t="n">
-        <v>45.78</v>
-      </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
-      <c r="P4" t="n">
-        <v>-3.54</v>
-      </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
-      <c r="R4" t="n">
-        <v>63.62</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -665,54 +611,27 @@
           <t>ITC.NS</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>270.25</v>
       </c>
-      <c r="D5" t="n">
-        <v>271.4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-5.06</v>
-      </c>
       <c r="H5" t="n">
-        <v>11687310</v>
+        <v>8833123</v>
       </c>
       <c r="I5" t="n">
-        <v>8414719</v>
+        <v>11693367</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.45</v>
+        <v>0.62</v>
       </c>
       <c r="L5" t="n">
         <v>37.9</v>
       </c>
-      <c r="M5" t="n">
-        <v>311.61</v>
-      </c>
-      <c r="N5" t="n">
-        <v>282.41</v>
-      </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
-      <c r="P5" t="n">
-        <v>-32.77</v>
-      </c>
       <c r="Q5" t="n">
         <v>267.05</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -725,54 +644,27 @@
           <t>NATCOPHARM.NS</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>863.4</v>
       </c>
-      <c r="D6" t="n">
-        <v>866.25</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-2.48</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-6.51</v>
-      </c>
       <c r="H6" t="n">
-        <v>371094</v>
+        <v>279133</v>
       </c>
       <c r="I6" t="n">
-        <v>443465</v>
+        <v>371204</v>
       </c>
       <c r="J6" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.42</v>
+        <v>0.58</v>
       </c>
       <c r="L6" t="n">
         <v>35.5</v>
       </c>
-      <c r="M6" t="n">
-        <v>946.37</v>
-      </c>
-      <c r="N6" t="n">
-        <v>920.7</v>
-      </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
-      <c r="P6" t="n">
-        <v>-28.29</v>
-      </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
-      <c r="R6" t="n">
-        <v>9.449999999999999</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -785,54 +677,27 @@
           <t>UJJIVANSFB.NS</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>68.98999999999999</v>
       </c>
-      <c r="D7" t="n">
-        <v>69.45999999999999</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-3.91</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-1.61</v>
-      </c>
       <c r="H7" t="n">
-        <v>15417735</v>
+        <v>14647440</v>
       </c>
       <c r="I7" t="n">
-        <v>10201371</v>
+        <v>15421346</v>
       </c>
       <c r="J7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.55</v>
+        <v>1.1</v>
       </c>
       <c r="L7" t="n">
         <v>48</v>
       </c>
-      <c r="M7" t="n">
-        <v>58.94</v>
-      </c>
-      <c r="N7" t="n">
-        <v>66.03</v>
-      </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
-      <c r="P7" t="n">
-        <v>-4.8</v>
-      </c>
       <c r="Q7" t="n">
         <v>42.43</v>
       </c>
-      <c r="R7" t="n">
-        <v>62.6</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -845,54 +710,27 @@
           <t>YATHARTH.NS</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>965.3</v>
       </c>
-      <c r="D8" t="n">
-        <v>923.05</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="F8" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="G8" t="n">
-        <v>15.82</v>
-      </c>
       <c r="H8" t="n">
-        <v>682896</v>
+        <v>683918</v>
       </c>
       <c r="I8" t="n">
-        <v>900090</v>
+        <v>683118</v>
       </c>
       <c r="J8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.44</v>
+        <v>1.64</v>
       </c>
       <c r="L8" t="n">
         <v>75.2</v>
       </c>
-      <c r="M8" t="n">
-        <v>751.71</v>
-      </c>
-      <c r="N8" t="n">
-        <v>851.62</v>
-      </c>
       <c r="O8" t="n">
         <v>965.3</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
-      <c r="R8" t="n">
-        <v>75.36</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -912,54 +750,27 @@
           <t>BFLAFL.BO</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>7.64</v>
       </c>
-      <c r="D10" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>19.37</v>
-      </c>
       <c r="H10" t="n">
+        <v>1869</v>
+      </c>
+      <c r="I10" t="n">
         <v>442</v>
       </c>
-      <c r="I10" t="n">
-        <v>5959</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="L10" t="n">
         <v>53.7</v>
       </c>
-      <c r="M10" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6.88</v>
-      </c>
       <c r="O10" t="n">
         <v>13.95</v>
       </c>
-      <c r="P10" t="n">
-        <v>-45.23</v>
-      </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
-      <c r="R10" t="n">
-        <v>44.42</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -972,54 +783,27 @@
           <t>PREMIERENE.NS</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>1005</v>
       </c>
-      <c r="D11" t="n">
-        <v>1036</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-2.99</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-1.17</v>
-      </c>
       <c r="H11" t="n">
-        <v>2550757</v>
+        <v>1497436</v>
       </c>
       <c r="I11" t="n">
-        <v>490536</v>
+        <v>2553287</v>
       </c>
       <c r="J11" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.08</v>
+        <v>1.4</v>
       </c>
       <c r="L11" t="n">
         <v>43</v>
       </c>
-      <c r="M11" t="n">
-        <v>935.72</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1045.46</v>
-      </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
-      <c r="P11" t="n">
-        <v>-10.04</v>
-      </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
-      <c r="R11" t="n">
-        <v>47.23</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1032,54 +816,27 @@
           <t>RENUKA.NS</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>23.94</v>
       </c>
-      <c r="D12" t="n">
-        <v>24.67</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="G12" t="n">
-        <v>10.63</v>
-      </c>
       <c r="H12" t="n">
-        <v>28386077</v>
+        <v>17577946</v>
       </c>
       <c r="I12" t="n">
-        <v>42636836</v>
+        <v>28386211</v>
       </c>
       <c r="J12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.37</v>
+        <v>0.72</v>
       </c>
       <c r="L12" t="n">
         <v>54.9</v>
       </c>
-      <c r="M12" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="N12" t="n">
-        <v>22.76</v>
-      </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
-      <c r="P12" t="n">
-        <v>-26.41</v>
-      </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
-      <c r="R12" t="n">
-        <v>11.4</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1092,54 +849,27 @@
           <t>VISHWARAJ.NS</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>6.15</v>
       </c>
-      <c r="D13" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="F13" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="G13" t="n">
-        <v>18.04</v>
-      </c>
       <c r="H13" t="n">
-        <v>696815</v>
+        <v>782799</v>
       </c>
       <c r="I13" t="n">
-        <v>2330979</v>
+        <v>697624</v>
       </c>
       <c r="J13" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="L13" t="n">
         <v>61.4</v>
       </c>
-      <c r="M13" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5.46</v>
-      </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="P13" t="n">
-        <v>-36.73</v>
-      </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
-      <c r="R13" t="n">
-        <v>47.13</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1262,22 +992,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>85.43000000000001</v>
+        <v>88.53</v>
       </c>
       <c r="D19" t="n">
-        <v>88.58</v>
+        <v>87.84</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.56</v>
+        <v>0.79</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.76</v>
+        <v>-5.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.59</v>
+        <v>-2.44</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.72</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1022,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4673.3</v>
+        <v>4657.3</v>
       </c>
       <c r="D20" t="n">
-        <v>4638.1</v>
+        <v>4598.2</v>
       </c>
       <c r="E20" t="n">
-        <v>0.76</v>
+        <v>1.29</v>
       </c>
       <c r="F20" t="n">
-        <v>4.1</v>
+        <v>3.12</v>
       </c>
       <c r="G20" t="n">
-        <v>15.78</v>
+        <v>15.43</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1052,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53577.4</v>
+        <v>53569.44</v>
       </c>
       <c r="D21" t="n">
-        <v>53417.16</v>
+        <v>53463.88</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F21" t="n">
-        <v>0.44</v>
+        <v>1.54</v>
       </c>
       <c r="G21" t="n">
-        <v>2.62</v>
+        <v>3.83</v>
       </c>
       <c r="H21" t="n">
-        <v>0.99</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1082,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10.56</v>
+        <v>10.57</v>
       </c>
       <c r="D22" t="n">
         <v>11.08</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.69</v>
+        <v>-4.6</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.71</v>
+        <v>-6.63</v>
       </c>
       <c r="G22" t="n">
-        <v>-15.92</v>
-      </c>
-      <c r="H22" t="n">
-        <v/>
+        <v>-15.84</v>
       </c>
     </row>
   </sheetData>
@@ -2007,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2620,6 +2347,29 @@
       </c>
       <c r="G26" t="n">
         <v>-1.72</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B27" t="n">
+        <v>88.53</v>
+      </c>
+      <c r="C27" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -2633,7 +2383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3246,6 +2996,29 @@
       </c>
       <c r="G26" t="n">
         <v>2.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4657.3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4598.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.88</v>
       </c>
     </row>
   </sheetData>
@@ -3259,7 +3032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3834,6 +3607,52 @@
       </c>
       <c r="G25" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>53463.88</v>
+      </c>
+      <c r="C26" t="n">
+        <v>53577.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B27" t="n">
+        <v>53569.44</v>
+      </c>
+      <c r="C27" t="n">
+        <v>53463.88</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -4398,9 +4217,6 @@
       <c r="F26" t="n">
         <v>-15.92</v>
       </c>
-      <c r="G26" t="n">
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4413,7 +4229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5746,6 +5562,32 @@
       </c>
       <c r="Q25" t="n">
         <v>44.42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C26" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1869</v>
+      </c>
+      <c r="H26" t="n">
+        <v>442</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K26" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="P26" t="n">
+        <v>5.29</v>
       </c>
     </row>
   </sheetData>
@@ -5759,7 +5601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7092,6 +6934,32 @@
       </c>
       <c r="Q25" t="n">
         <v>11.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C26" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="G26" t="n">
+        <v>17577946</v>
+      </c>
+      <c r="H26" t="n">
+        <v>28386211</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K26" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="N26" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="P26" t="n">
+        <v>21.49</v>
       </c>
     </row>
   </sheetData>
@@ -7105,7 +6973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8332,6 +8200,32 @@
       </c>
       <c r="Q23" t="n">
         <v>63.62</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C24" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8299227</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8354307</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K24" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="P24" t="n">
+        <v>28.31</v>
       </c>
     </row>
   </sheetData>
@@ -8345,7 +8239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9731,6 +9625,32 @@
       </c>
       <c r="Q26" t="n">
         <v>90.76000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C27" t="n">
+        <v>458.9</v>
+      </c>
+      <c r="G27" t="n">
+        <v>236905</v>
+      </c>
+      <c r="H27" t="n">
+        <v>671640</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K27" t="n">
+        <v>61</v>
+      </c>
+      <c r="N27" t="n">
+        <v>465.35</v>
+      </c>
+      <c r="P27" t="n">
+        <v>240.57</v>
       </c>
     </row>
   </sheetData>
@@ -9744,7 +9664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11130,6 +11050,32 @@
       </c>
       <c r="Q26" t="n">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C27" t="n">
+        <v>270.25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8833123</v>
+      </c>
+      <c r="H27" t="n">
+        <v>11693367</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K27" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="N27" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="P27" t="n">
+        <v>267.05</v>
       </c>
     </row>
   </sheetData>
@@ -11143,7 +11089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12529,6 +12475,32 @@
       </c>
       <c r="Q26" t="n">
         <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C27" t="n">
+        <v>863.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>279133</v>
+      </c>
+      <c r="H27" t="n">
+        <v>371204</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K27" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="P27" t="n">
+        <v>788.84</v>
       </c>
     </row>
   </sheetData>
@@ -12542,7 +12514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13928,6 +13900,32 @@
       </c>
       <c r="Q26" t="n">
         <v>47.23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1005</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1497436</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2553287</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>43</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>682.6</v>
       </c>
     </row>
   </sheetData>
@@ -13941,7 +13939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15327,6 +15325,32 @@
       </c>
       <c r="Q26" t="n">
         <v>62.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C27" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>14647440</v>
+      </c>
+      <c r="H27" t="n">
+        <v>15421346</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>48</v>
+      </c>
+      <c r="N27" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="P27" t="n">
+        <v>42.43</v>
       </c>
     </row>
   </sheetData>
@@ -15340,7 +15364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16726,6 +16750,32 @@
       </c>
       <c r="Q26" t="n">
         <v>47.13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C27" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G27" t="n">
+        <v>782799</v>
+      </c>
+      <c r="H27" t="n">
+        <v>697624</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K27" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="P27" t="n">
+        <v>4.18</v>
       </c>
     </row>
   </sheetData>
@@ -16739,7 +16789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18125,6 +18175,32 @@
       </c>
       <c r="Q26" t="n">
         <v>75.36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C27" t="n">
+        <v>965.3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>683918</v>
+      </c>
+      <c r="H27" t="n">
+        <v>683118</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K27" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>965.3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>550.47</v>
       </c>
     </row>
   </sheetData>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,19 +546,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>458.9</v>
+        <v>448.25</v>
       </c>
       <c r="H3" t="n">
+        <v>2565661</v>
+      </c>
+      <c r="I3" t="n">
         <v>236905</v>
       </c>
-      <c r="I3" t="n">
-        <v>671640</v>
-      </c>
       <c r="J3" t="n">
-        <v>0.43</v>
+        <v>4.66</v>
       </c>
       <c r="L3" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="O3" t="n">
         <v>465.35</v>
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>46.32</v>
+        <v>45.73</v>
       </c>
       <c r="H4" t="n">
-        <v>8299227</v>
+        <v>3552939</v>
       </c>
       <c r="I4" t="n">
-        <v>8354307</v>
+        <v>8299347</v>
       </c>
       <c r="J4" t="n">
-        <v>1.26</v>
+        <v>0.53</v>
       </c>
       <c r="L4" t="n">
-        <v>56.1</v>
+        <v>50.8</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
@@ -612,19 +612,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>270.25</v>
+        <v>269</v>
       </c>
       <c r="H5" t="n">
-        <v>8833123</v>
+        <v>15187256</v>
       </c>
       <c r="I5" t="n">
-        <v>11693367</v>
+        <v>8834890</v>
       </c>
       <c r="J5" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="L5" t="n">
-        <v>37.9</v>
+        <v>36.3</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
@@ -645,19 +645,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>863.4</v>
+        <v>857.6</v>
       </c>
       <c r="H6" t="n">
-        <v>279133</v>
+        <v>401815</v>
       </c>
       <c r="I6" t="n">
-        <v>371204</v>
+        <v>279220</v>
       </c>
       <c r="J6" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="L6" t="n">
-        <v>35.5</v>
+        <v>34.1</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68.98999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>14647440</v>
+        <v>6873097</v>
       </c>
       <c r="I7" t="n">
-        <v>15421346</v>
+        <v>14648450</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>0.51</v>
       </c>
       <c r="L7" t="n">
-        <v>48</v>
+        <v>46.3</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
@@ -711,22 +711,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>965.3</v>
+        <v>973.05</v>
       </c>
       <c r="H8" t="n">
-        <v>683918</v>
+        <v>1376296</v>
       </c>
       <c r="I8" t="n">
-        <v>683118</v>
+        <v>684457</v>
       </c>
       <c r="J8" t="n">
-        <v>1.64</v>
+        <v>3.08</v>
       </c>
       <c r="L8" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="O8" t="n">
-        <v>965.3</v>
+        <v>973.05</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
@@ -751,19 +751,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.64</v>
+        <v>7.6</v>
       </c>
       <c r="H10" t="n">
+        <v>981</v>
+      </c>
+      <c r="I10" t="n">
         <v>1869</v>
       </c>
-      <c r="I10" t="n">
-        <v>442</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="L10" t="n">
-        <v>53.7</v>
+        <v>52.8</v>
       </c>
       <c r="O10" t="n">
         <v>13.95</v>
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1497436</v>
+        <v>2307383</v>
       </c>
       <c r="I11" t="n">
-        <v>2553287</v>
+        <v>1498122</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>41.9</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23.94</v>
+        <v>23.43</v>
       </c>
       <c r="H12" t="n">
-        <v>17577946</v>
+        <v>30587627</v>
       </c>
       <c r="I12" t="n">
-        <v>28386211</v>
+        <v>17586067</v>
       </c>
       <c r="J12" t="n">
-        <v>0.72</v>
+        <v>1.21</v>
       </c>
       <c r="L12" t="n">
-        <v>54.9</v>
+        <v>51</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6.15</v>
+        <v>5.92</v>
       </c>
       <c r="H13" t="n">
-        <v>782799</v>
+        <v>562540</v>
       </c>
       <c r="I13" t="n">
-        <v>697624</v>
+        <v>783099</v>
       </c>
       <c r="J13" t="n">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="L13" t="n">
-        <v>61.4</v>
+        <v>55.9</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24090.85</v>
+      </c>
+      <c r="D17" t="n">
         <v>24207.75</v>
       </c>
-      <c r="D17" t="n">
-        <v>24334.55</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.52</v>
+        <v>-0.48</v>
       </c>
       <c r="F17" t="n">
-        <v>0.54</v>
+        <v>-0.58</v>
       </c>
       <c r="G17" t="n">
-        <v>0.93</v>
+        <v>-0.66</v>
       </c>
       <c r="H17" t="n">
-        <v>0.09</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="18">
@@ -962,22 +962,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57509.95</v>
+      </c>
+      <c r="D18" t="n">
         <v>57783.75</v>
       </c>
-      <c r="D18" t="n">
-        <v>57514.2</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.47</v>
+        <v>-0.47</v>
       </c>
       <c r="F18" t="n">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="G18" t="n">
-        <v>1.81</v>
+        <v>0.53</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="19">
@@ -992,22 +992,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>88.53</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>87.84</v>
+        <v>89.7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.79</v>
+        <v>-1.57</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.6</v>
+        <v>-6.46</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.44</v>
+        <v>-0.83</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.75</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="20">
@@ -1022,22 +1022,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4657.3</v>
+        <v>4504.1</v>
       </c>
       <c r="D20" t="n">
-        <v>4598.2</v>
+        <v>4609.7</v>
       </c>
       <c r="E20" t="n">
-        <v>1.29</v>
+        <v>-2.29</v>
       </c>
       <c r="F20" t="n">
-        <v>3.12</v>
+        <v>-2.6</v>
       </c>
       <c r="G20" t="n">
-        <v>15.43</v>
+        <v>9.85</v>
       </c>
       <c r="H20" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="21">
@@ -1052,22 +1052,22 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>53559.99</v>
+      </c>
+      <c r="D21" t="n">
         <v>53569.44</v>
       </c>
-      <c r="D21" t="n">
-        <v>53463.88</v>
-      </c>
       <c r="E21" t="n">
-        <v>0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="F21" t="n">
-        <v>1.54</v>
+        <v>0.53</v>
       </c>
       <c r="G21" t="n">
-        <v>3.83</v>
+        <v>2.59</v>
       </c>
       <c r="H21" t="n">
-        <v>0.87</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="22">
@@ -1082,19 +1082,19 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="D22" t="n">
         <v>10.57</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.08</v>
-      </c>
       <c r="E22" t="n">
-        <v>-4.6</v>
+        <v>4.73</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.63</v>
+        <v>2.88</v>
       </c>
       <c r="G22" t="n">
-        <v>-15.84</v>
+        <v>-7.83</v>
       </c>
     </row>
   </sheetData>
@@ -1108,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1721,6 +1721,29 @@
       </c>
       <c r="G26" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57509.95</v>
+      </c>
+      <c r="C27" t="n">
+        <v>57783.75</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2370,6 +2393,29 @@
       </c>
       <c r="G27" t="n">
         <v>-0.75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B28" t="n">
+        <v>88.29000000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.68</v>
       </c>
     </row>
   </sheetData>
@@ -2383,7 +2429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3019,6 +3065,29 @@
       </c>
       <c r="G27" t="n">
         <v>1.88</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4504.1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4609.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -3032,7 +3101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3653,6 +3722,29 @@
       </c>
       <c r="G27" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B28" t="n">
+        <v>53559.99</v>
+      </c>
+      <c r="C28" t="n">
+        <v>53569.44</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -3666,7 +3758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4216,6 +4308,26 @@
       </c>
       <c r="F26" t="n">
         <v>-15.92</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B27" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="C27" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-7.83</v>
       </c>
     </row>
   </sheetData>
@@ -4229,7 +4341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5587,6 +5699,32 @@
         <v>13.95</v>
       </c>
       <c r="P26" t="n">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G27" t="n">
+        <v>981</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1869</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K27" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="N27" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="P27" t="n">
         <v>5.29</v>
       </c>
     </row>
@@ -5601,7 +5739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6959,6 +7097,32 @@
         <v>32.53</v>
       </c>
       <c r="P26" t="n">
+        <v>21.49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C27" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="G27" t="n">
+        <v>30587627</v>
+      </c>
+      <c r="H27" t="n">
+        <v>17586067</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="K27" t="n">
+        <v>51</v>
+      </c>
+      <c r="N27" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="P27" t="n">
         <v>21.49</v>
       </c>
     </row>
@@ -6973,7 +7137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8225,6 +8389,32 @@
         <v>48.02</v>
       </c>
       <c r="P24" t="n">
+        <v>28.31</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C25" t="n">
+        <v>45.73</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3552939</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8299347</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K25" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="P25" t="n">
         <v>28.31</v>
       </c>
     </row>
@@ -8239,7 +8429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9650,6 +9840,32 @@
         <v>465.35</v>
       </c>
       <c r="P27" t="n">
+        <v>240.57</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C28" t="n">
+        <v>448.25</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2565661</v>
+      </c>
+      <c r="H28" t="n">
+        <v>236905</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="K28" t="n">
+        <v>57</v>
+      </c>
+      <c r="N28" t="n">
+        <v>465.35</v>
+      </c>
+      <c r="P28" t="n">
         <v>240.57</v>
       </c>
     </row>
@@ -9664,7 +9880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11075,6 +11291,32 @@
         <v>401.99</v>
       </c>
       <c r="P27" t="n">
+        <v>267.05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C28" t="n">
+        <v>269</v>
+      </c>
+      <c r="G28" t="n">
+        <v>15187256</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8834890</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K28" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="P28" t="n">
         <v>267.05</v>
       </c>
     </row>
@@ -11089,7 +11331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12500,6 +12742,32 @@
         <v>1203.96</v>
       </c>
       <c r="P27" t="n">
+        <v>788.84</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C28" t="n">
+        <v>857.6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>401815</v>
+      </c>
+      <c r="H28" t="n">
+        <v>279220</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K28" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="P28" t="n">
         <v>788.84</v>
       </c>
     </row>
@@ -12514,7 +12782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13925,6 +14193,32 @@
         <v>1117.2</v>
       </c>
       <c r="P27" t="n">
+        <v>682.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2307383</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1498122</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K28" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="P28" t="n">
         <v>682.6</v>
       </c>
     </row>
@@ -13939,7 +14233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15350,6 +15644,32 @@
         <v>72.47</v>
       </c>
       <c r="P27" t="n">
+        <v>42.43</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C28" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6873097</v>
+      </c>
+      <c r="H28" t="n">
+        <v>14648450</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K28" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="P28" t="n">
         <v>42.43</v>
       </c>
     </row>
@@ -15364,7 +15684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16775,6 +17095,32 @@
         <v>9.720000000000001</v>
       </c>
       <c r="P27" t="n">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="G28" t="n">
+        <v>562540</v>
+      </c>
+      <c r="H28" t="n">
+        <v>783099</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="N28" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="P28" t="n">
         <v>4.18</v>
       </c>
     </row>
@@ -16789,7 +17135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18200,6 +18546,32 @@
         <v>965.3</v>
       </c>
       <c r="P27" t="n">
+        <v>550.47</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C28" t="n">
+        <v>973.05</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1376296</v>
+      </c>
+      <c r="H28" t="n">
+        <v>684457</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K28" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>973.05</v>
+      </c>
+      <c r="P28" t="n">
         <v>550.47</v>
       </c>
     </row>
@@ -18214,7 +18586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18829,6 +19201,29 @@
         <v>0.09</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B27" t="n">
+        <v>24090.85</v>
+      </c>
+      <c r="C27" t="n">
+        <v>24207.75</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -545,27 +545,54 @@
           <t>DYCL.NS</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>493.2</v>
+      </c>
       <c r="D3" t="n">
-        <v>448.25</v>
+        <v>487.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2565661</v>
+        <v>1249156</v>
       </c>
       <c r="I3" t="n">
-        <v>236905</v>
+        <v>2566700</v>
       </c>
       <c r="J3" t="n">
-        <v>4.66</v>
+        <v>1.9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.78</v>
       </c>
       <c r="L3" t="n">
-        <v>57</v>
+        <v>67</v>
+      </c>
+      <c r="M3" t="n">
+        <v>340.77</v>
+      </c>
+      <c r="N3" t="n">
+        <v>407.09</v>
       </c>
       <c r="O3" t="n">
-        <v>465.35</v>
+        <v>493.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
+      <c r="R3" t="n">
+        <v>105.01</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -578,27 +605,54 @@
           <t>SOUTHBANK.NS</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>45.66</v>
+      </c>
       <c r="D4" t="n">
         <v>45.73</v>
       </c>
+      <c r="E4" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.67</v>
+      </c>
       <c r="H4" t="n">
-        <v>3552939</v>
+        <v>12044120</v>
       </c>
       <c r="I4" t="n">
         <v>8299347</v>
       </c>
       <c r="J4" t="n">
-        <v>0.53</v>
+        <v>1.79</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.24</v>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="N4" t="n">
+        <v>45.69</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
+      <c r="P4" t="n">
+        <v>-4.91</v>
+      </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
+      <c r="R4" t="n">
+        <v>61.29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -611,26 +665,53 @@
           <t>ITC.NS</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>255.5</v>
+      </c>
       <c r="D5" t="n">
-        <v>269</v>
+        <v>266</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-9.07</v>
       </c>
       <c r="H5" t="n">
-        <v>15187256</v>
+        <v>24555781</v>
       </c>
       <c r="I5" t="n">
-        <v>8834890</v>
+        <v>15200847</v>
       </c>
       <c r="J5" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>36.3</v>
+        <v>24.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>309.75</v>
+      </c>
+      <c r="N5" t="n">
+        <v>280.72</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
+      <c r="P5" t="n">
+        <v>-36.44</v>
+      </c>
       <c r="Q5" t="n">
-        <v>267.05</v>
+        <v>255.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -644,27 +725,54 @@
           <t>NATCOPHARM.NS</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>841.5</v>
+      </c>
       <c r="D6" t="n">
-        <v>857.6</v>
+        <v>853.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-4.81</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-8.08</v>
       </c>
       <c r="H6" t="n">
-        <v>401815</v>
+        <v>412766</v>
       </c>
       <c r="I6" t="n">
-        <v>279220</v>
+        <v>402204</v>
       </c>
       <c r="J6" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.15</v>
       </c>
       <c r="L6" t="n">
-        <v>34.1</v>
+        <v>30.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>946.99</v>
+      </c>
+      <c r="N6" t="n">
+        <v>918.71</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
+      <c r="P6" t="n">
+        <v>-30.11</v>
+      </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
+      <c r="R6" t="n">
+        <v>6.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -677,26 +785,53 @@
           <t>UJJIVANSFB.NS</t>
         </is>
       </c>
+      <c r="C7" t="n">
+        <v>69.11</v>
+      </c>
       <c r="D7" t="n">
-        <v>68.56999999999999</v>
+        <v>67.84999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-3.68</v>
       </c>
       <c r="H7" t="n">
-        <v>6873097</v>
+        <v>8505250</v>
       </c>
       <c r="I7" t="n">
-        <v>14648450</v>
+        <v>6875259</v>
       </c>
       <c r="J7" t="n">
-        <v>0.51</v>
+        <v>0.66</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1.71</v>
       </c>
       <c r="L7" t="n">
-        <v>46.3</v>
+        <v>49.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>66.69</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
+      <c r="P7" t="n">
+        <v>-4.64</v>
+      </c>
       <c r="Q7" t="n">
-        <v>42.43</v>
+        <v>42.57</v>
+      </c>
+      <c r="R7" t="n">
+        <v>62.34</v>
       </c>
     </row>
     <row r="8">
@@ -710,27 +845,54 @@
           <t>YATHARTH.NS</t>
         </is>
       </c>
+      <c r="C8" t="n">
+        <v>1001.9</v>
+      </c>
       <c r="D8" t="n">
-        <v>973.05</v>
+        <v>967.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>22.49</v>
       </c>
       <c r="H8" t="n">
-        <v>1376296</v>
+        <v>653996</v>
       </c>
       <c r="I8" t="n">
-        <v>684457</v>
+        <v>1376658</v>
       </c>
       <c r="J8" t="n">
-        <v>3.08</v>
+        <v>1.29</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.35</v>
       </c>
       <c r="L8" t="n">
-        <v>76.2</v>
+        <v>78.09999999999999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>755.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>859.76</v>
       </c>
       <c r="O8" t="n">
-        <v>973.05</v>
+        <v>1001.9</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
+      <c r="R8" t="n">
+        <v>82.01000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -750,27 +912,54 @@
           <t>BFLAFL.BO</t>
         </is>
       </c>
+      <c r="C10" t="n">
+        <v>7.45</v>
+      </c>
       <c r="D10" t="n">
         <v>7.6</v>
       </c>
+      <c r="E10" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20.55</v>
+      </c>
       <c r="H10" t="n">
-        <v>981</v>
+        <v>1715</v>
       </c>
       <c r="I10" t="n">
         <v>1869</v>
       </c>
       <c r="J10" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>52.8</v>
+        <v>49.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6.91</v>
       </c>
       <c r="O10" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-46.4</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
+      <c r="R10" t="n">
+        <v>40.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -783,27 +972,54 @@
           <t>PREMIERENE.NS</t>
         </is>
       </c>
+      <c r="C11" t="n">
+        <v>1036.3</v>
+      </c>
       <c r="D11" t="n">
-        <v>1000</v>
+        <v>1013.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.38</v>
       </c>
       <c r="H11" t="n">
-        <v>2307383</v>
+        <v>1312591</v>
       </c>
       <c r="I11" t="n">
-        <v>1498122</v>
+        <v>2307505</v>
       </c>
       <c r="J11" t="n">
-        <v>2.23</v>
+        <v>1.23</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>41.9</v>
+        <v>51.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>935.23</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1042.46</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
+      <c r="P11" t="n">
+        <v>-7.24</v>
+      </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
+      <c r="R11" t="n">
+        <v>51.82</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -816,27 +1032,54 @@
           <t>RENUKA.NS</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v>24.9</v>
+      </c>
       <c r="D12" t="n">
         <v>23.43</v>
       </c>
+      <c r="E12" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15.06</v>
+      </c>
       <c r="H12" t="n">
-        <v>30587627</v>
+        <v>49064966</v>
       </c>
       <c r="I12" t="n">
         <v>17586067</v>
       </c>
       <c r="J12" t="n">
-        <v>1.21</v>
+        <v>1.93</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.19</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>59.9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="N12" t="n">
+        <v>22.8</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
+      <c r="P12" t="n">
+        <v>-23.46</v>
+      </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
+      <c r="R12" t="n">
+        <v>15.87</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -849,27 +1092,54 @@
           <t>VISHWARAJ.NS</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>6.08</v>
+      </c>
       <c r="D13" t="n">
         <v>5.92</v>
       </c>
+      <c r="E13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="G13" t="n">
+        <v>17.37</v>
+      </c>
       <c r="H13" t="n">
-        <v>562540</v>
+        <v>1260683</v>
       </c>
       <c r="I13" t="n">
         <v>783099</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>1.13</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.6</v>
       </c>
       <c r="L13" t="n">
-        <v>55.9</v>
+        <v>58.7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.48</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
+      <c r="P13" t="n">
+        <v>-37.45</v>
+      </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
+      <c r="R13" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -932,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24090.85</v>
+        <v>24080.4</v>
       </c>
       <c r="D17" t="n">
-        <v>24207.75</v>
+        <v>24175.65</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.48</v>
+        <v>-0.39</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.66</v>
+        <v>-1.24</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="18">
@@ -962,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57509.95</v>
+        <v>58024.95</v>
       </c>
       <c r="D18" t="n">
-        <v>57783.75</v>
+        <v>57496.3</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.47</v>
+        <v>0.92</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02</v>
+        <v>0.87</v>
       </c>
       <c r="G18" t="n">
-        <v>0.53</v>
+        <v>1.33</v>
       </c>
       <c r="H18" t="n">
-        <v>1.43</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="19">
@@ -992,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>88.29000000000001</v>
+        <v>88.25</v>
       </c>
       <c r="D19" t="n">
-        <v>89.7</v>
+        <v>89.31</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.57</v>
+        <v>-1.19</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.46</v>
+        <v>-4.25</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.83</v>
+        <v>-2.08</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1022,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4504.1</v>
+        <v>4480.5</v>
       </c>
       <c r="D20" t="n">
-        <v>4609.7</v>
+        <v>4478.1</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.29</v>
+        <v>0.05</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6</v>
+        <v>-3.45</v>
       </c>
       <c r="G20" t="n">
-        <v>9.85</v>
+        <v>10.65</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="21">
@@ -1052,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>53212.7</v>
+      </c>
+      <c r="D21" t="n">
         <v>53559.99</v>
       </c>
-      <c r="D21" t="n">
-        <v>53569.44</v>
-      </c>
       <c r="E21" t="n">
-        <v>-0.02</v>
+        <v>-0.65</v>
       </c>
       <c r="F21" t="n">
-        <v>0.53</v>
+        <v>-0.38</v>
       </c>
       <c r="G21" t="n">
-        <v>2.59</v>
+        <v>1.39</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="22">
@@ -1082,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11.07</v>
+        <v>11.19</v>
       </c>
       <c r="D22" t="n">
-        <v>10.57</v>
+        <v>10.68</v>
       </c>
       <c r="E22" t="n">
-        <v>4.73</v>
+        <v>4.78</v>
       </c>
       <c r="F22" t="n">
-        <v>2.88</v>
+        <v>-2.95</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.83</v>
+        <v>-4.85</v>
       </c>
     </row>
   </sheetData>
@@ -1108,7 +1378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1744,6 +2014,52 @@
       </c>
       <c r="G27" t="n">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57496.3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>57509.95</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58024.95</v>
+      </c>
+      <c r="C29" t="n">
+        <v>57496.3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.97</v>
       </c>
     </row>
   </sheetData>
@@ -1757,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2416,6 +2732,29 @@
       </c>
       <c r="G28" t="n">
         <v>-0.68</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="C29" t="n">
+        <v>89.31</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2429,7 +2768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3088,6 +3427,29 @@
       </c>
       <c r="G28" t="n">
         <v>1.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4480.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4478.1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -3101,7 +3463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3745,6 +4107,29 @@
       </c>
       <c r="G28" t="n">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>53212.7</v>
+      </c>
+      <c r="C29" t="n">
+        <v>53559.99</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -3758,7 +4143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4328,6 +4713,46 @@
       </c>
       <c r="F27" t="n">
         <v>-7.83</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B28" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="C28" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-12.17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="C29" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-4.85</v>
       </c>
     </row>
   </sheetData>
@@ -4341,7 +4766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5726,6 +6151,59 @@
       </c>
       <c r="P27" t="n">
         <v>5.29</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B28" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="C28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="F28" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1715</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1869</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="L28" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="N28" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-46.4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>40.83</v>
       </c>
     </row>
   </sheetData>
@@ -5739,7 +6217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7124,6 +7602,59 @@
       </c>
       <c r="P27" t="n">
         <v>21.49</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B28" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="F28" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="G28" t="n">
+        <v>49064966</v>
+      </c>
+      <c r="H28" t="n">
+        <v>17586067</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="K28" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="M28" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="N28" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-23.46</v>
+      </c>
+      <c r="P28" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>15.87</v>
       </c>
     </row>
   </sheetData>
@@ -7137,7 +7668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8416,6 +8947,59 @@
       </c>
       <c r="P25" t="n">
         <v>28.31</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B26" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="C26" t="n">
+        <v>45.73</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="G26" t="n">
+        <v>12044120</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8299347</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="K26" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="M26" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="N26" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-4.91</v>
+      </c>
+      <c r="P26" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>61.29</v>
       </c>
     </row>
   </sheetData>
@@ -8429,7 +9013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9867,6 +10451,59 @@
       </c>
       <c r="P28" t="n">
         <v>240.57</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>493.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>487.6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E29" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="F29" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1249156</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2566700</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K29" t="n">
+        <v>67</v>
+      </c>
+      <c r="L29" t="n">
+        <v>340.77</v>
+      </c>
+      <c r="M29" t="n">
+        <v>407.09</v>
+      </c>
+      <c r="N29" t="n">
+        <v>493.2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>105.01</v>
       </c>
     </row>
   </sheetData>
@@ -9880,7 +10517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11318,6 +11955,59 @@
       </c>
       <c r="P28" t="n">
         <v>267.05</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>266</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-9.07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>24555781</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15200847</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>309.75</v>
+      </c>
+      <c r="M29" t="n">
+        <v>280.72</v>
+      </c>
+      <c r="N29" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-36.44</v>
+      </c>
+      <c r="P29" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11331,7 +12021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12769,6 +13459,59 @@
       </c>
       <c r="P28" t="n">
         <v>788.84</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>841.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>853.8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-4.81</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-8.08</v>
+      </c>
+      <c r="G29" t="n">
+        <v>412766</v>
+      </c>
+      <c r="H29" t="n">
+        <v>402204</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="K29" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>946.99</v>
+      </c>
+      <c r="M29" t="n">
+        <v>918.71</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-30.11</v>
+      </c>
+      <c r="P29" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.68</v>
       </c>
     </row>
   </sheetData>
@@ -12782,7 +13525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14220,6 +14963,59 @@
       </c>
       <c r="P28" t="n">
         <v>682.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1036.3</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1013.9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1312591</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2307505</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>935.23</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1042.46</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="P29" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>51.82</v>
       </c>
     </row>
   </sheetData>
@@ -14233,7 +15029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15671,6 +16467,59 @@
       </c>
       <c r="P28" t="n">
         <v>42.43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="C29" t="n">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-3.68</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8505250</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6875259</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="K29" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="L29" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>66.69</v>
+      </c>
+      <c r="N29" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="P29" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>62.34</v>
       </c>
     </row>
   </sheetData>
@@ -15684,7 +16533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17122,6 +17971,59 @@
       </c>
       <c r="P28" t="n">
         <v>4.18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="F29" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1260683</v>
+      </c>
+      <c r="H29" t="n">
+        <v>783099</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="N29" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-37.45</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>45.45</v>
       </c>
     </row>
   </sheetData>
@@ -17135,7 +18037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18573,6 +19475,59 @@
       </c>
       <c r="P28" t="n">
         <v>550.47</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>967.4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="G29" t="n">
+        <v>653996</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1376658</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K29" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="L29" t="n">
+        <v>755.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>859.76</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>82.01000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -18586,7 +19541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19224,6 +20179,52 @@
         <v>1.04</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B28" t="n">
+        <v>24175.65</v>
+      </c>
+      <c r="C28" t="n">
+        <v>24090.85</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>24080.4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>24175.65</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,43 +546,43 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>542.4</v>
+      </c>
+      <c r="D3" t="n">
         <v>493.2</v>
       </c>
-      <c r="D3" t="n">
-        <v>487.6</v>
-      </c>
       <c r="E3" t="n">
-        <v>1.15</v>
+        <v>9.98</v>
       </c>
       <c r="F3" t="n">
-        <v>13.72</v>
+        <v>26.65</v>
       </c>
       <c r="G3" t="n">
-        <v>24.8</v>
+        <v>34.77</v>
       </c>
       <c r="H3" t="n">
-        <v>1249156</v>
+        <v>10972768</v>
       </c>
       <c r="I3" t="n">
-        <v>2566700</v>
+        <v>1249206</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9</v>
+        <v>15.59</v>
       </c>
       <c r="K3" t="n">
-        <v>1.78</v>
+        <v>-0.06</v>
       </c>
       <c r="L3" t="n">
-        <v>67</v>
+        <v>74.5</v>
       </c>
       <c r="M3" t="n">
-        <v>340.77</v>
+        <v>341.66</v>
       </c>
       <c r="N3" t="n">
-        <v>407.09</v>
+        <v>410.72</v>
       </c>
       <c r="O3" t="n">
-        <v>493.2</v>
+        <v>542.4</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>105.01</v>
+        <v>125.46</v>
       </c>
     </row>
     <row r="4">
@@ -606,37 +606,37 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="D4" t="n">
         <v>45.66</v>
       </c>
-      <c r="D4" t="n">
-        <v>45.73</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.15</v>
+        <v>0.55</v>
       </c>
       <c r="F4" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.67</v>
+        <v>-1.51</v>
       </c>
       <c r="H4" t="n">
-        <v>12044120</v>
+        <v>12764737</v>
       </c>
       <c r="I4" t="n">
-        <v>8299347</v>
+        <v>12044453</v>
       </c>
       <c r="J4" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.24</v>
+        <v>1.88</v>
       </c>
       <c r="L4" t="n">
-        <v>50.1</v>
+        <v>52.5</v>
       </c>
       <c r="M4" t="n">
-        <v>41.36</v>
+        <v>41.44</v>
       </c>
       <c r="N4" t="n">
         <v>45.69</v>
@@ -645,13 +645,13 @@
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.91</v>
+        <v>-4.39</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>61.29</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="D5" t="n">
         <v>255.5</v>
       </c>
-      <c r="D5" t="n">
-        <v>266</v>
-      </c>
       <c r="E5" t="n">
-        <v>-3.95</v>
+        <v>4.34</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.27</v>
+        <v>-1.77</v>
       </c>
       <c r="G5" t="n">
-        <v>-9.07</v>
+        <v>-7.11</v>
       </c>
       <c r="H5" t="n">
-        <v>24555781</v>
+        <v>31232541</v>
       </c>
       <c r="I5" t="n">
-        <v>15200847</v>
+        <v>24575845</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8</v>
+        <v>2.48</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>24.1</v>
+        <v>41.7</v>
       </c>
       <c r="M5" t="n">
-        <v>309.75</v>
+        <v>309.14</v>
       </c>
       <c r="N5" t="n">
-        <v>280.72</v>
+        <v>280.25</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-36.44</v>
+        <v>-33.68</v>
       </c>
       <c r="Q5" t="n">
         <v>255.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>849.2</v>
+      </c>
+      <c r="D6" t="n">
         <v>841.5</v>
       </c>
-      <c r="D6" t="n">
-        <v>853.8</v>
-      </c>
       <c r="E6" t="n">
-        <v>-1.44</v>
+        <v>0.92</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.81</v>
+        <v>-1.97</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.08</v>
+        <v>-8.44</v>
       </c>
       <c r="H6" t="n">
-        <v>412766</v>
+        <v>241422</v>
       </c>
       <c r="I6" t="n">
-        <v>402204</v>
+        <v>412911</v>
       </c>
       <c r="J6" t="n">
-        <v>0.85</v>
+        <v>0.49</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>30.4</v>
+        <v>34.2</v>
       </c>
       <c r="M6" t="n">
-        <v>946.99</v>
+        <v>947.2</v>
       </c>
       <c r="N6" t="n">
-        <v>918.71</v>
+        <v>917.87</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-30.11</v>
+        <v>-29.47</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>6.68</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="D7" t="n">
         <v>69.11</v>
       </c>
-      <c r="D7" t="n">
-        <v>67.84999999999999</v>
-      </c>
       <c r="E7" t="n">
-        <v>1.86</v>
+        <v>-5.43</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.68</v>
+        <v>-5.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.68</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>8505250</v>
+        <v>18027050</v>
       </c>
       <c r="I7" t="n">
-        <v>6875259</v>
+        <v>8505500</v>
       </c>
       <c r="J7" t="n">
-        <v>0.66</v>
+        <v>1.42</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.71</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
-        <v>49.3</v>
+        <v>37.2</v>
       </c>
       <c r="M7" t="n">
-        <v>59.2</v>
+        <v>59.27</v>
       </c>
       <c r="N7" t="n">
-        <v>66.69</v>
+        <v>66.88</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.64</v>
+        <v>-9.81</v>
       </c>
       <c r="Q7" t="n">
         <v>42.57</v>
       </c>
       <c r="R7" t="n">
-        <v>62.34</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>974.8</v>
+      </c>
+      <c r="D8" t="n">
         <v>1001.9</v>
       </c>
-      <c r="D8" t="n">
-        <v>967.4</v>
-      </c>
       <c r="E8" t="n">
-        <v>3.57</v>
+        <v>-2.7</v>
       </c>
       <c r="F8" t="n">
-        <v>10.4</v>
+        <v>5.61</v>
       </c>
       <c r="G8" t="n">
-        <v>22.49</v>
+        <v>16.96</v>
       </c>
       <c r="H8" t="n">
-        <v>653996</v>
+        <v>373045</v>
       </c>
       <c r="I8" t="n">
-        <v>1376658</v>
+        <v>654071</v>
       </c>
       <c r="J8" t="n">
-        <v>1.29</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="L8" t="n">
-        <v>78.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="M8" t="n">
-        <v>755.2</v>
+        <v>756.1</v>
       </c>
       <c r="N8" t="n">
-        <v>859.76</v>
+        <v>862.2</v>
       </c>
       <c r="O8" t="n">
         <v>1001.9</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>82.01000000000001</v>
+        <v>77.09</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="D10" t="n">
         <v>7.45</v>
       </c>
-      <c r="D10" t="n">
-        <v>7.6</v>
-      </c>
       <c r="E10" t="n">
-        <v>-1.97</v>
+        <v>-4.97</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.97</v>
+        <v>-7.57</v>
       </c>
       <c r="G10" t="n">
-        <v>20.55</v>
+        <v>11.5</v>
       </c>
       <c r="H10" t="n">
+        <v>2093</v>
+      </c>
+      <c r="I10" t="n">
         <v>1715</v>
       </c>
-      <c r="I10" t="n">
-        <v>1869</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="L10" t="n">
-        <v>49.7</v>
+        <v>42.2</v>
       </c>
       <c r="M10" t="n">
-        <v>8.890000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="N10" t="n">
-        <v>6.91</v>
+        <v>6.96</v>
       </c>
       <c r="O10" t="n">
         <v>13.9</v>
       </c>
       <c r="P10" t="n">
-        <v>-46.4</v>
+        <v>-49.06</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>40.83</v>
+        <v>33.84</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1012.9</v>
+      </c>
+      <c r="D11" t="n">
         <v>1036.3</v>
       </c>
-      <c r="D11" t="n">
-        <v>1013.9</v>
-      </c>
       <c r="E11" t="n">
-        <v>2.21</v>
+        <v>-2.26</v>
       </c>
       <c r="F11" t="n">
-        <v>0.61</v>
+        <v>-2.23</v>
       </c>
       <c r="G11" t="n">
-        <v>1.38</v>
+        <v>-0.76</v>
       </c>
       <c r="H11" t="n">
-        <v>1312591</v>
+        <v>506606</v>
       </c>
       <c r="I11" t="n">
-        <v>2307505</v>
+        <v>1331386</v>
       </c>
       <c r="J11" t="n">
-        <v>1.23</v>
+        <v>0.46</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-2.98</v>
       </c>
       <c r="L11" t="n">
-        <v>51.5</v>
+        <v>46.1</v>
       </c>
       <c r="M11" t="n">
-        <v>935.23</v>
+        <v>935.3099999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>1042.46</v>
+        <v>1041.8</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.24</v>
+        <v>-9.34</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>51.82</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="D12" t="n">
         <v>24.9</v>
       </c>
-      <c r="D12" t="n">
-        <v>23.43</v>
-      </c>
       <c r="E12" t="n">
-        <v>6.27</v>
+        <v>-2.77</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.95</v>
+        <v>-1.86</v>
       </c>
       <c r="G12" t="n">
-        <v>15.06</v>
+        <v>8.42</v>
       </c>
       <c r="H12" t="n">
-        <v>49064966</v>
+        <v>13254350</v>
       </c>
       <c r="I12" t="n">
-        <v>17586067</v>
+        <v>49071835</v>
       </c>
       <c r="J12" t="n">
-        <v>1.93</v>
+        <v>0.46</v>
       </c>
       <c r="K12" t="n">
-        <v>3.19</v>
+        <v>0.31</v>
       </c>
       <c r="L12" t="n">
-        <v>59.9</v>
+        <v>54.8</v>
       </c>
       <c r="M12" t="n">
-        <v>24.82</v>
+        <v>24.78</v>
       </c>
       <c r="N12" t="n">
-        <v>22.8</v>
+        <v>22.85</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-23.46</v>
+        <v>-25.58</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>15.87</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="D13" t="n">
         <v>6.08</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.92</v>
-      </c>
       <c r="E13" t="n">
-        <v>2.7</v>
+        <v>-2.3</v>
       </c>
       <c r="F13" t="n">
-        <v>6.85</v>
+        <v>-5.56</v>
       </c>
       <c r="G13" t="n">
-        <v>17.37</v>
+        <v>13.36</v>
       </c>
       <c r="H13" t="n">
-        <v>1260683</v>
+        <v>341704</v>
       </c>
       <c r="I13" t="n">
-        <v>783099</v>
+        <v>1261474</v>
       </c>
       <c r="J13" t="n">
-        <v>1.13</v>
+        <v>0.29</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6</v>
+        <v>0.55</v>
       </c>
       <c r="L13" t="n">
-        <v>58.7</v>
+        <v>55.2</v>
       </c>
       <c r="M13" t="n">
-        <v>5.92</v>
+        <v>5.9</v>
       </c>
       <c r="N13" t="n">
-        <v>5.48</v>
+        <v>5.49</v>
       </c>
       <c r="O13" t="n">
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-37.45</v>
+        <v>-38.89</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>45.45</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>24055.8</v>
+      </c>
+      <c r="D17" t="n">
         <v>24080.4</v>
       </c>
-      <c r="D17" t="n">
-        <v>24175.65</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.39</v>
+        <v>-0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.57</v>
+        <v>-0.67</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.24</v>
+        <v>-1.34</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.86</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57409.6</v>
+      </c>
+      <c r="D18" t="n">
         <v>58024.95</v>
       </c>
-      <c r="D18" t="n">
-        <v>57496.3</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.92</v>
+        <v>-1.06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.87</v>
+        <v>-0.2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.33</v>
+        <v>0.25</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.97</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>88.25</v>
+        <v>92.28</v>
       </c>
       <c r="D19" t="n">
-        <v>89.31</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.19</v>
+        <v>1.98</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.25</v>
+        <v>4.18</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.08</v>
+        <v>10.16</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4480.5</v>
+        <v>4407.7</v>
       </c>
       <c r="D20" t="n">
-        <v>4478.1</v>
+        <v>4431.1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05</v>
+        <v>-0.53</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.45</v>
+        <v>-4.97</v>
       </c>
       <c r="G20" t="n">
-        <v>10.65</v>
+        <v>9.27</v>
       </c>
       <c r="H20" t="n">
-        <v>0.19</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53212.7</v>
+        <v>52960.85</v>
       </c>
       <c r="D21" t="n">
-        <v>53559.99</v>
+        <v>53185.9</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.65</v>
+        <v>-0.42</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.38</v>
+        <v>-0.85</v>
       </c>
       <c r="G21" t="n">
-        <v>1.39</v>
+        <v>0.91</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.71</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="22">
@@ -1355,16 +1355,19 @@
         <v>11.19</v>
       </c>
       <c r="D22" t="n">
-        <v>10.68</v>
+        <v>11.19</v>
       </c>
       <c r="E22" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>-2.95</v>
       </c>
       <c r="G22" t="n">
         <v>-4.85</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2060,6 +2063,29 @@
       </c>
       <c r="G29" t="n">
         <v>-0.97</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57409.6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>58024.95</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-3.09</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2755,6 +2781,29 @@
       </c>
       <c r="G29" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92.28</v>
+      </c>
+      <c r="C30" t="n">
+        <v>90.48999999999999</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-3.71</v>
       </c>
     </row>
   </sheetData>
@@ -2768,7 +2817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3450,6 +3499,29 @@
       </c>
       <c r="G29" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4407.7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4431.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>
@@ -3463,7 +3535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4130,6 +4202,29 @@
       </c>
       <c r="G29" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>52960.85</v>
+      </c>
+      <c r="C30" t="n">
+        <v>53185.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -4143,7 +4238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4753,6 +4848,29 @@
       </c>
       <c r="F29" t="n">
         <v>-4.85</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="C30" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4766,7 +4884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6204,6 +6322,59 @@
       </c>
       <c r="Q28" t="n">
         <v>40.83</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B29" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="C29" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-7.57</v>
+      </c>
+      <c r="F29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2093</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1715</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K29" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="M29" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="N29" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-49.06</v>
+      </c>
+      <c r="P29" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>33.84</v>
       </c>
     </row>
   </sheetData>
@@ -6217,7 +6388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7655,6 +7826,59 @@
       </c>
       <c r="Q28" t="n">
         <v>15.87</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B29" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="C29" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="G29" t="n">
+        <v>13254350</v>
+      </c>
+      <c r="H29" t="n">
+        <v>49071835</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K29" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="L29" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="M29" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="N29" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-25.58</v>
+      </c>
+      <c r="P29" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>12.66</v>
       </c>
     </row>
   </sheetData>
@@ -7668,7 +7892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9000,6 +9224,59 @@
       </c>
       <c r="Q26" t="n">
         <v>61.29</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B27" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="C27" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12764737</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12044453</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K27" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="M27" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="N27" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="P27" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>62.17</v>
       </c>
     </row>
   </sheetData>
@@ -9013,7 +9290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10504,6 +10781,59 @@
       </c>
       <c r="Q29" t="n">
         <v>105.01</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>542.4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>493.2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="E30" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="F30" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10972768</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1249206</v>
+      </c>
+      <c r="I30" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="K30" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>341.66</v>
+      </c>
+      <c r="M30" t="n">
+        <v>410.72</v>
+      </c>
+      <c r="N30" t="n">
+        <v>542.4</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>125.46</v>
       </c>
     </row>
   </sheetData>
@@ -10517,7 +10847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12008,6 +12338,59 @@
       </c>
       <c r="Q29" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-7.11</v>
+      </c>
+      <c r="G30" t="n">
+        <v>31232541</v>
+      </c>
+      <c r="H30" t="n">
+        <v>24575845</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J30" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="K30" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="L30" t="n">
+        <v>309.14</v>
+      </c>
+      <c r="M30" t="n">
+        <v>280.25</v>
+      </c>
+      <c r="N30" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-33.68</v>
+      </c>
+      <c r="P30" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.34</v>
       </c>
     </row>
   </sheetData>
@@ -12021,7 +12404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13512,6 +13895,59 @@
       </c>
       <c r="Q29" t="n">
         <v>6.68</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>849.2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>841.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="G30" t="n">
+        <v>241422</v>
+      </c>
+      <c r="H30" t="n">
+        <v>412911</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>947.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>917.87</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-29.47</v>
+      </c>
+      <c r="P30" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>7.65</v>
       </c>
     </row>
   </sheetData>
@@ -13525,7 +13961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15016,6 +15452,59 @@
       </c>
       <c r="Q29" t="n">
         <v>51.82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1012.9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1036.3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="G30" t="n">
+        <v>506606</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1331386</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-2.98</v>
+      </c>
+      <c r="K30" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>935.3099999999999</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1041.8</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-9.34</v>
+      </c>
+      <c r="P30" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>48.39</v>
       </c>
     </row>
   </sheetData>
@@ -15029,7 +15518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16520,6 +17009,59 @@
       </c>
       <c r="Q29" t="n">
         <v>62.34</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="C30" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>18027050</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8505500</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K30" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>59.27</v>
+      </c>
+      <c r="M30" t="n">
+        <v>66.88</v>
+      </c>
+      <c r="N30" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-9.81</v>
+      </c>
+      <c r="P30" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>53.54</v>
       </c>
     </row>
   </sheetData>
@@ -16533,7 +17075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18024,6 +18566,59 @@
       </c>
       <c r="Q29" t="n">
         <v>45.45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="C30" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="F30" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="G30" t="n">
+        <v>341704</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1261474</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K30" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-38.89</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>42.11</v>
       </c>
     </row>
   </sheetData>
@@ -18037,7 +18632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19528,6 +20123,59 @@
       </c>
       <c r="Q29" t="n">
         <v>82.01000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>974.8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="F30" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="G30" t="n">
+        <v>373045</v>
+      </c>
+      <c r="H30" t="n">
+        <v>654071</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K30" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>756.1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>862.2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="P30" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>77.09</v>
       </c>
     </row>
   </sheetData>
@@ -19541,7 +20189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20225,6 +20873,29 @@
         <v>-0.86</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>24055.8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>24080.4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>535.55</v>
+      </c>
+      <c r="D3" t="n">
         <v>542.4</v>
       </c>
-      <c r="D3" t="n">
-        <v>493.2</v>
-      </c>
       <c r="E3" t="n">
-        <v>9.98</v>
+        <v>-1.26</v>
       </c>
       <c r="F3" t="n">
-        <v>26.65</v>
+        <v>16.7</v>
       </c>
       <c r="G3" t="n">
-        <v>34.77</v>
+        <v>34.46</v>
       </c>
       <c r="H3" t="n">
-        <v>10972768</v>
+        <v>1089912</v>
       </c>
       <c r="I3" t="n">
-        <v>1249206</v>
+        <v>10973790</v>
       </c>
       <c r="J3" t="n">
-        <v>15.59</v>
+        <v>0.88</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="L3" t="n">
-        <v>74.5</v>
+        <v>72</v>
       </c>
       <c r="M3" t="n">
-        <v>341.66</v>
+        <v>342.48</v>
       </c>
       <c r="N3" t="n">
-        <v>410.72</v>
+        <v>414.37</v>
       </c>
       <c r="O3" t="n">
         <v>542.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>125.46</v>
+        <v>122.62</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="D4" t="n">
         <v>45.91</v>
       </c>
-      <c r="D4" t="n">
-        <v>45.66</v>
-      </c>
       <c r="E4" t="n">
-        <v>0.55</v>
+        <v>-0.37</v>
       </c>
       <c r="F4" t="n">
-        <v>1.23</v>
+        <v>-1.25</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.51</v>
+        <v>-1.43</v>
       </c>
       <c r="H4" t="n">
-        <v>12764737</v>
+        <v>5752446</v>
       </c>
       <c r="I4" t="n">
-        <v>12044453</v>
+        <v>12765987</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>1.88</v>
+        <v>-1.24</v>
       </c>
       <c r="L4" t="n">
-        <v>52.5</v>
+        <v>50.8</v>
       </c>
       <c r="M4" t="n">
-        <v>41.44</v>
+        <v>41.48</v>
       </c>
       <c r="N4" t="n">
-        <v>45.69</v>
+        <v>45.7</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.39</v>
+        <v>-4.75</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>62.17</v>
+        <v>61.57</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>266.3</v>
+      </c>
+      <c r="D5" t="n">
         <v>266.6</v>
       </c>
-      <c r="D5" t="n">
-        <v>255.5</v>
-      </c>
       <c r="E5" t="n">
-        <v>4.34</v>
+        <v>-0.11</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.77</v>
+        <v>-1.46</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.11</v>
+        <v>-7.85</v>
       </c>
       <c r="H5" t="n">
-        <v>31232541</v>
+        <v>14636618</v>
       </c>
       <c r="I5" t="n">
-        <v>24575845</v>
+        <v>31258553</v>
       </c>
       <c r="J5" t="n">
-        <v>2.48</v>
+        <v>1.08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.880000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="L5" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="M5" t="n">
-        <v>309.14</v>
+        <v>308.53</v>
       </c>
       <c r="N5" t="n">
-        <v>280.25</v>
+        <v>279.77</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-33.68</v>
+        <v>-33.75</v>
       </c>
       <c r="Q5" t="n">
         <v>255.5</v>
       </c>
       <c r="R5" t="n">
-        <v>4.34</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>843.25</v>
+      </c>
+      <c r="D6" t="n">
         <v>849.2</v>
       </c>
-      <c r="D6" t="n">
-        <v>841.5</v>
-      </c>
       <c r="E6" t="n">
-        <v>0.92</v>
+        <v>-0.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.97</v>
+        <v>-2.33</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.44</v>
+        <v>-7.89</v>
       </c>
       <c r="H6" t="n">
-        <v>241422</v>
+        <v>472716</v>
       </c>
       <c r="I6" t="n">
-        <v>412911</v>
+        <v>241430</v>
       </c>
       <c r="J6" t="n">
-        <v>0.49</v>
+        <v>0.97</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="L6" t="n">
-        <v>34.2</v>
+        <v>32.7</v>
       </c>
       <c r="M6" t="n">
-        <v>947.2</v>
+        <v>947.33</v>
       </c>
       <c r="N6" t="n">
-        <v>917.87</v>
+        <v>916.89</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-29.47</v>
+        <v>-29.96</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>7.65</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="D7" t="n">
         <v>65.36</v>
       </c>
-      <c r="D7" t="n">
-        <v>69.11</v>
-      </c>
       <c r="E7" t="n">
-        <v>-5.43</v>
+        <v>-2.63</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.9</v>
+        <v>-7.75</v>
       </c>
       <c r="G7" t="n">
-        <v>-8.119999999999999</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>18027050</v>
+        <v>49428614</v>
       </c>
       <c r="I7" t="n">
-        <v>8505500</v>
+        <v>18034062</v>
       </c>
       <c r="J7" t="n">
-        <v>1.42</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
-        <v>0.82</v>
+        <v>0.03</v>
       </c>
       <c r="L7" t="n">
-        <v>37.2</v>
+        <v>33.2</v>
       </c>
       <c r="M7" t="n">
-        <v>59.27</v>
+        <v>59.32</v>
       </c>
       <c r="N7" t="n">
-        <v>66.88</v>
+        <v>67</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-9.81</v>
+        <v>-12.18</v>
       </c>
       <c r="Q7" t="n">
         <v>42.57</v>
       </c>
       <c r="R7" t="n">
-        <v>53.54</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>966.5</v>
+      </c>
+      <c r="D8" t="n">
         <v>974.8</v>
       </c>
-      <c r="D8" t="n">
-        <v>1001.9</v>
-      </c>
       <c r="E8" t="n">
-        <v>-2.7</v>
+        <v>-0.85</v>
       </c>
       <c r="F8" t="n">
-        <v>5.61</v>
+        <v>0.12</v>
       </c>
       <c r="G8" t="n">
-        <v>16.96</v>
+        <v>14.38</v>
       </c>
       <c r="H8" t="n">
-        <v>373045</v>
+        <v>241951</v>
       </c>
       <c r="I8" t="n">
-        <v>654071</v>
+        <v>373081</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="K8" t="n">
-        <v>0.24</v>
+        <v>-0.86</v>
       </c>
       <c r="L8" t="n">
-        <v>68.8</v>
+        <v>66.2</v>
       </c>
       <c r="M8" t="n">
-        <v>756.1</v>
+        <v>756.97</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2</v>
+        <v>864.4</v>
       </c>
       <c r="O8" t="n">
         <v>1001.9</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7</v>
+        <v>-3.53</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>77.09</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D10" t="n">
         <v>7.08</v>
       </c>
-      <c r="D10" t="n">
-        <v>7.45</v>
-      </c>
       <c r="E10" t="n">
-        <v>-4.97</v>
+        <v>-2.54</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.57</v>
+        <v>-9.69</v>
       </c>
       <c r="G10" t="n">
-        <v>11.5</v>
+        <v>1.02</v>
       </c>
       <c r="H10" t="n">
+        <v>2751</v>
+      </c>
+      <c r="I10" t="n">
         <v>2093</v>
       </c>
-      <c r="I10" t="n">
-        <v>1715</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>0.77</v>
+        <v>-1.76</v>
       </c>
       <c r="L10" t="n">
-        <v>42.2</v>
+        <v>39.2</v>
       </c>
       <c r="M10" t="n">
-        <v>8.83</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>6.96</v>
+        <v>6.99</v>
       </c>
       <c r="O10" t="n">
         <v>13.9</v>
       </c>
       <c r="P10" t="n">
-        <v>-49.06</v>
+        <v>-50.36</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>33.84</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D11" t="n">
         <v>1012.9</v>
       </c>
-      <c r="D11" t="n">
-        <v>1036.3</v>
-      </c>
       <c r="E11" t="n">
-        <v>-2.26</v>
+        <v>-1.27</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.23</v>
+        <v>-0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.76</v>
+        <v>-3.5</v>
       </c>
       <c r="H11" t="n">
-        <v>506606</v>
+        <v>827427</v>
       </c>
       <c r="I11" t="n">
-        <v>1331386</v>
+        <v>506640</v>
       </c>
       <c r="J11" t="n">
-        <v>0.46</v>
+        <v>0.77</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.98</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>46.1</v>
+        <v>43.4</v>
       </c>
       <c r="M11" t="n">
-        <v>935.3099999999999</v>
+        <v>935.26</v>
       </c>
       <c r="N11" t="n">
-        <v>1041.8</v>
+        <v>1040.73</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-9.34</v>
+        <v>-10.49</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>48.39</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="D12" t="n">
         <v>24.21</v>
       </c>
-      <c r="D12" t="n">
-        <v>24.9</v>
-      </c>
       <c r="E12" t="n">
-        <v>-2.77</v>
+        <v>-1.12</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.86</v>
+        <v>-0</v>
       </c>
       <c r="G12" t="n">
-        <v>8.42</v>
+        <v>6.83</v>
       </c>
       <c r="H12" t="n">
-        <v>13254350</v>
+        <v>12026619</v>
       </c>
       <c r="I12" t="n">
-        <v>49071835</v>
+        <v>13258172</v>
       </c>
       <c r="J12" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="K12" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="L12" t="n">
-        <v>54.8</v>
+        <v>52.8</v>
       </c>
       <c r="M12" t="n">
-        <v>24.78</v>
+        <v>24.76</v>
       </c>
       <c r="N12" t="n">
-        <v>22.85</v>
+        <v>22.87</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-25.58</v>
+        <v>-26.41</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>12.66</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="13">
@@ -1093,37 +1093,37 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.94</v>
       </c>
-      <c r="D13" t="n">
-        <v>6.08</v>
-      </c>
       <c r="E13" t="n">
-        <v>-2.3</v>
+        <v>-1.18</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.56</v>
+        <v>-4.55</v>
       </c>
       <c r="G13" t="n">
-        <v>13.36</v>
+        <v>7.31</v>
       </c>
       <c r="H13" t="n">
-        <v>341704</v>
+        <v>447429</v>
       </c>
       <c r="I13" t="n">
-        <v>1261474</v>
+        <v>342404</v>
       </c>
       <c r="J13" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="K13" t="n">
-        <v>0.55</v>
+        <v>-1.33</v>
       </c>
       <c r="L13" t="n">
-        <v>55.2</v>
+        <v>53.5</v>
       </c>
       <c r="M13" t="n">
-        <v>5.9</v>
+        <v>5.89</v>
       </c>
       <c r="N13" t="n">
         <v>5.49</v>
@@ -1132,13 +1132,13 @@
         <v>9.720000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-38.89</v>
+        <v>-39.61</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>42.11</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>23914.45</v>
+      </c>
+      <c r="D17" t="n">
         <v>24055.8</v>
       </c>
-      <c r="D17" t="n">
-        <v>24080.4</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.1</v>
+        <v>-0.59</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.67</v>
+        <v>-1.21</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.34</v>
+        <v>-2.85</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.04</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57172</v>
+      </c>
+      <c r="D18" t="n">
         <v>57409.6</v>
       </c>
-      <c r="D18" t="n">
-        <v>58024.95</v>
-      </c>
       <c r="E18" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="F18" t="n">
         <v>-1.06</v>
       </c>
-      <c r="F18" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="G18" t="n">
-        <v>0.25</v>
+        <v>-1.27</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.09</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>92.28</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>90.48999999999999</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>4.18</v>
+        <v>7.75</v>
       </c>
       <c r="G19" t="n">
-        <v>10.16</v>
+        <v>19.27</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.71</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4407.7</v>
+        <v>4434.3</v>
       </c>
       <c r="D20" t="n">
-        <v>4431.1</v>
+        <v>4348</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.53</v>
+        <v>1.98</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.97</v>
+        <v>-3.56</v>
       </c>
       <c r="G20" t="n">
-        <v>9.27</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52960.85</v>
+        <v>53171.82</v>
       </c>
       <c r="D21" t="n">
-        <v>53185.9</v>
+        <v>52766.88</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.42</v>
+        <v>0.77</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.85</v>
+        <v>-0.55</v>
       </c>
       <c r="G21" t="n">
-        <v>0.91</v>
+        <v>-1.69</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.73</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11.19</v>
+        <v>11.59</v>
       </c>
       <c r="D22" t="n">
-        <v>11.19</v>
+        <v>11.49</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.95</v>
+        <v>9.65</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.85</v>
+        <v>-4.92</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2086,6 +2086,29 @@
       </c>
       <c r="G30" t="n">
         <v>-3.09</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57172</v>
+      </c>
+      <c r="C31" t="n">
+        <v>57409.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-2.52</v>
       </c>
     </row>
   </sheetData>
@@ -2099,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2804,6 +2827,29 @@
       </c>
       <c r="G30" t="n">
         <v>-3.71</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F31" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>
@@ -2817,7 +2863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3522,6 +3568,29 @@
       </c>
       <c r="G30" t="n">
         <v>2.33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4434.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4348</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3535,7 +3604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4225,6 +4294,29 @@
       </c>
       <c r="G30" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>53171.82</v>
+      </c>
+      <c r="C31" t="n">
+        <v>52766.88</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -4238,7 +4330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4871,6 +4963,29 @@
       </c>
       <c r="G30" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="C31" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="G31" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -4884,7 +4999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6375,6 +6490,59 @@
       </c>
       <c r="Q29" t="n">
         <v>33.84</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B30" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-9.69</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2751</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2093</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="K30" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M30" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="N30" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-50.36</v>
+      </c>
+      <c r="P30" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>30.43</v>
       </c>
     </row>
   </sheetData>
@@ -6388,7 +6556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7879,6 +8047,59 @@
       </c>
       <c r="Q29" t="n">
         <v>12.66</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B30" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="C30" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="G30" t="n">
+        <v>12026619</v>
+      </c>
+      <c r="H30" t="n">
+        <v>13258172</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K30" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="M30" t="n">
+        <v>22.87</v>
+      </c>
+      <c r="N30" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-26.41</v>
+      </c>
+      <c r="P30" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>11.4</v>
       </c>
     </row>
   </sheetData>
@@ -7892,7 +8113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9277,6 +9498,59 @@
       </c>
       <c r="Q27" t="n">
         <v>62.17</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B28" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="C28" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5752446</v>
+      </c>
+      <c r="H28" t="n">
+        <v>12765987</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="K28" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="L28" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="M28" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="N28" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="P28" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>61.57</v>
       </c>
     </row>
   </sheetData>
@@ -9290,7 +9564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10834,6 +11108,59 @@
       </c>
       <c r="Q30" t="n">
         <v>125.46</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>535.55</v>
+      </c>
+      <c r="C31" t="n">
+        <v>542.4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1089912</v>
+      </c>
+      <c r="H31" t="n">
+        <v>10973790</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K31" t="n">
+        <v>72</v>
+      </c>
+      <c r="L31" t="n">
+        <v>342.48</v>
+      </c>
+      <c r="M31" t="n">
+        <v>414.37</v>
+      </c>
+      <c r="N31" t="n">
+        <v>542.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="P31" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>122.62</v>
       </c>
     </row>
   </sheetData>
@@ -10847,7 +11174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12391,6 +12718,59 @@
       </c>
       <c r="Q30" t="n">
         <v>4.34</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>266.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-7.85</v>
+      </c>
+      <c r="G31" t="n">
+        <v>14636618</v>
+      </c>
+      <c r="H31" t="n">
+        <v>31258553</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="K31" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>308.53</v>
+      </c>
+      <c r="M31" t="n">
+        <v>279.77</v>
+      </c>
+      <c r="N31" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-33.75</v>
+      </c>
+      <c r="P31" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.23</v>
       </c>
     </row>
   </sheetData>
@@ -12404,7 +12784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13948,6 +14328,59 @@
       </c>
       <c r="Q30" t="n">
         <v>7.65</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>843.25</v>
+      </c>
+      <c r="C31" t="n">
+        <v>849.2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-7.89</v>
+      </c>
+      <c r="G31" t="n">
+        <v>472716</v>
+      </c>
+      <c r="H31" t="n">
+        <v>241430</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="K31" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>947.33</v>
+      </c>
+      <c r="M31" t="n">
+        <v>916.89</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-29.96</v>
+      </c>
+      <c r="P31" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -13961,7 +14394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15505,6 +15938,59 @@
       </c>
       <c r="Q30" t="n">
         <v>48.39</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1012.9</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>827427</v>
+      </c>
+      <c r="H31" t="n">
+        <v>506640</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>935.26</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1040.73</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-10.49</v>
+      </c>
+      <c r="P31" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>46.5</v>
       </c>
     </row>
   </sheetData>
@@ -15518,7 +16004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17062,6 +17548,59 @@
       </c>
       <c r="Q30" t="n">
         <v>53.54</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="C31" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-7.75</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-9.539999999999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>49428614</v>
+      </c>
+      <c r="H31" t="n">
+        <v>18034062</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K31" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="M31" t="n">
+        <v>67</v>
+      </c>
+      <c r="N31" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-12.18</v>
+      </c>
+      <c r="P31" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>49.49</v>
       </c>
     </row>
   </sheetData>
@@ -17075,7 +17614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18619,6 +19158,59 @@
       </c>
       <c r="Q30" t="n">
         <v>42.11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="C31" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="G31" t="n">
+        <v>447429</v>
+      </c>
+      <c r="H31" t="n">
+        <v>342404</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="K31" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="M31" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="N31" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-39.61</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>40.43</v>
       </c>
     </row>
   </sheetData>
@@ -18632,7 +19224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20176,6 +20768,59 @@
       </c>
       <c r="Q30" t="n">
         <v>77.09</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>966.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>974.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="G31" t="n">
+        <v>241951</v>
+      </c>
+      <c r="H31" t="n">
+        <v>373081</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="K31" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>756.97</v>
+      </c>
+      <c r="M31" t="n">
+        <v>864.4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="P31" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>75.58</v>
       </c>
     </row>
   </sheetData>
@@ -20189,7 +20834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20896,6 +21541,29 @@
         <v>-0.04</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>23914.45</v>
+      </c>
+      <c r="C31" t="n">
+        <v>24055.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-3.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="D3" t="n">
         <v>535.55</v>
       </c>
-      <c r="D3" t="n">
-        <v>542.4</v>
-      </c>
       <c r="E3" t="n">
-        <v>-1.26</v>
+        <v>1.63</v>
       </c>
       <c r="F3" t="n">
-        <v>16.7</v>
+        <v>21.43</v>
       </c>
       <c r="G3" t="n">
-        <v>34.46</v>
+        <v>34.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1089912</v>
+        <v>711681</v>
       </c>
       <c r="I3" t="n">
-        <v>10973790</v>
+        <v>1090048</v>
       </c>
       <c r="J3" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>72</v>
+        <v>73.3</v>
       </c>
       <c r="M3" t="n">
-        <v>342.48</v>
+        <v>343.39</v>
       </c>
       <c r="N3" t="n">
-        <v>414.37</v>
+        <v>417.72</v>
       </c>
       <c r="O3" t="n">
-        <v>542.4</v>
+        <v>544.3</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>122.62</v>
+        <v>126.25</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="D4" t="n">
         <v>45.74</v>
       </c>
-      <c r="D4" t="n">
-        <v>45.91</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.37</v>
+        <v>4.29</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.25</v>
+        <v>4.31</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.43</v>
+        <v>2.66</v>
       </c>
       <c r="H4" t="n">
-        <v>5752446</v>
+        <v>29131306</v>
       </c>
       <c r="I4" t="n">
-        <v>12765987</v>
+        <v>5752468</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.06</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.24</v>
+        <v>1.04</v>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>41.48</v>
+        <v>41.52</v>
       </c>
       <c r="N4" t="n">
-        <v>45.7</v>
+        <v>45.75</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.75</v>
+        <v>-0.67</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>61.57</v>
+        <v>68.48999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>263</v>
+      </c>
+      <c r="D5" t="n">
         <v>266.3</v>
       </c>
-      <c r="D5" t="n">
-        <v>266.6</v>
-      </c>
       <c r="E5" t="n">
-        <v>-0.11</v>
+        <v>-1.24</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.46</v>
+        <v>-2.23</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.85</v>
+        <v>-8.35</v>
       </c>
       <c r="H5" t="n">
-        <v>14636618</v>
+        <v>17805990</v>
       </c>
       <c r="I5" t="n">
-        <v>31258553</v>
+        <v>14643482</v>
       </c>
       <c r="J5" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.39</v>
+        <v>0.13</v>
       </c>
       <c r="L5" t="n">
-        <v>41.4</v>
+        <v>38.4</v>
       </c>
       <c r="M5" t="n">
-        <v>308.53</v>
+        <v>307.91</v>
       </c>
       <c r="N5" t="n">
-        <v>279.77</v>
+        <v>279.23</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-33.75</v>
+        <v>-34.58</v>
       </c>
       <c r="Q5" t="n">
         <v>255.5</v>
       </c>
       <c r="R5" t="n">
-        <v>4.23</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>838.3</v>
+      </c>
+      <c r="D6" t="n">
         <v>843.25</v>
       </c>
-      <c r="D6" t="n">
-        <v>849.2</v>
-      </c>
       <c r="E6" t="n">
-        <v>-0.7</v>
+        <v>-0.59</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.33</v>
+        <v>-2.25</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.89</v>
+        <v>-8.48</v>
       </c>
       <c r="H6" t="n">
-        <v>472716</v>
+        <v>217906</v>
       </c>
       <c r="I6" t="n">
-        <v>241430</v>
+        <v>472795</v>
       </c>
       <c r="J6" t="n">
-        <v>0.97</v>
+        <v>0.44</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.36</v>
+        <v>0.02</v>
       </c>
       <c r="L6" t="n">
-        <v>32.7</v>
+        <v>31.5</v>
       </c>
       <c r="M6" t="n">
-        <v>947.33</v>
+        <v>947.47</v>
       </c>
       <c r="N6" t="n">
-        <v>916.89</v>
+        <v>915.62</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-29.96</v>
+        <v>-30.37</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>6.9</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="D7" t="n">
         <v>63.64</v>
       </c>
-      <c r="D7" t="n">
-        <v>65.36</v>
-      </c>
       <c r="E7" t="n">
-        <v>-2.63</v>
+        <v>-1.02</v>
       </c>
       <c r="F7" t="n">
-        <v>-7.75</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.48</v>
       </c>
       <c r="H7" t="n">
-        <v>49428614</v>
+        <v>21855442</v>
       </c>
       <c r="I7" t="n">
-        <v>18034062</v>
+        <v>49431916</v>
       </c>
       <c r="J7" t="n">
-        <v>3.95</v>
+        <v>1.52</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03</v>
+        <v>1.9</v>
       </c>
       <c r="L7" t="n">
-        <v>33.2</v>
+        <v>31.8</v>
       </c>
       <c r="M7" t="n">
-        <v>59.32</v>
+        <v>59.37</v>
       </c>
       <c r="N7" t="n">
-        <v>67</v>
+        <v>67.14</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-12.18</v>
+        <v>-13.08</v>
       </c>
       <c r="Q7" t="n">
         <v>42.57</v>
       </c>
       <c r="R7" t="n">
-        <v>49.49</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>962.3</v>
+      </c>
+      <c r="D8" t="n">
         <v>966.5</v>
       </c>
-      <c r="D8" t="n">
-        <v>974.8</v>
-      </c>
       <c r="E8" t="n">
-        <v>-0.85</v>
+        <v>-0.43</v>
       </c>
       <c r="F8" t="n">
-        <v>0.12</v>
+        <v>-1.1</v>
       </c>
       <c r="G8" t="n">
-        <v>14.38</v>
+        <v>12.18</v>
       </c>
       <c r="H8" t="n">
-        <v>241951</v>
+        <v>139354</v>
       </c>
       <c r="I8" t="n">
-        <v>373081</v>
+        <v>242009</v>
       </c>
       <c r="J8" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.86</v>
+        <v>0.11</v>
       </c>
       <c r="L8" t="n">
-        <v>66.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>756.97</v>
+        <v>757.9</v>
       </c>
       <c r="N8" t="n">
-        <v>864.4</v>
+        <v>866.92</v>
       </c>
       <c r="O8" t="n">
         <v>1001.9</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.53</v>
+        <v>-3.95</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>75.58</v>
+        <v>74.81</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="D10" t="n">
         <v>6.9</v>
       </c>
-      <c r="D10" t="n">
-        <v>7.08</v>
-      </c>
       <c r="E10" t="n">
-        <v>-2.54</v>
+        <v>-4.93</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.69</v>
+        <v>-13.68</v>
       </c>
       <c r="G10" t="n">
-        <v>1.02</v>
+        <v>-12.65</v>
       </c>
       <c r="H10" t="n">
+        <v>3427</v>
+      </c>
+      <c r="I10" t="n">
         <v>2751</v>
       </c>
-      <c r="I10" t="n">
-        <v>2093</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.76</v>
+        <v>1.73</v>
       </c>
       <c r="L10" t="n">
-        <v>39.2</v>
+        <v>34.2</v>
       </c>
       <c r="M10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="N10" t="n">
-        <v>6.99</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
         <v>13.9</v>
       </c>
       <c r="P10" t="n">
-        <v>-50.36</v>
+        <v>-52.81</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>30.43</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D11" t="n">
         <v>1000</v>
       </c>
-      <c r="D11" t="n">
-        <v>1012.9</v>
-      </c>
       <c r="E11" t="n">
-        <v>-1.27</v>
+        <v>0.8</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5</v>
+        <v>-3.45</v>
       </c>
       <c r="H11" t="n">
-        <v>827427</v>
+        <v>543560</v>
       </c>
       <c r="I11" t="n">
-        <v>506640</v>
+        <v>827532</v>
       </c>
       <c r="J11" t="n">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="L11" t="n">
-        <v>43.4</v>
+        <v>45.5</v>
       </c>
       <c r="M11" t="n">
-        <v>935.26</v>
+        <v>935.33</v>
       </c>
       <c r="N11" t="n">
-        <v>1040.73</v>
+        <v>1039.88</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-10.49</v>
+        <v>-9.77</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>46.5</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="D12" t="n">
         <v>23.94</v>
       </c>
-      <c r="D12" t="n">
-        <v>24.21</v>
-      </c>
       <c r="E12" t="n">
-        <v>-1.12</v>
+        <v>1.38</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>3.59</v>
       </c>
       <c r="G12" t="n">
-        <v>6.83</v>
+        <v>8.69</v>
       </c>
       <c r="H12" t="n">
-        <v>12026619</v>
+        <v>17940384</v>
       </c>
       <c r="I12" t="n">
-        <v>13258172</v>
+        <v>12027252</v>
       </c>
       <c r="J12" t="n">
-        <v>0.41</v>
+        <v>0.61</v>
       </c>
       <c r="K12" t="n">
-        <v>0.47</v>
+        <v>1.16</v>
       </c>
       <c r="L12" t="n">
-        <v>52.8</v>
+        <v>54.9</v>
       </c>
       <c r="M12" t="n">
-        <v>24.76</v>
+        <v>24.74</v>
       </c>
       <c r="N12" t="n">
-        <v>22.87</v>
+        <v>22.91</v>
       </c>
       <c r="O12" t="n">
         <v>32.53</v>
       </c>
       <c r="P12" t="n">
-        <v>-26.41</v>
+        <v>-25.39</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>11.4</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.87</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.94</v>
-      </c>
       <c r="E13" t="n">
-        <v>-1.18</v>
+        <v>1.02</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.55</v>
+        <v>0.17</v>
       </c>
       <c r="G13" t="n">
-        <v>7.31</v>
+        <v>8.41</v>
       </c>
       <c r="H13" t="n">
-        <v>447429</v>
+        <v>490020</v>
       </c>
       <c r="I13" t="n">
-        <v>342404</v>
+        <v>447461</v>
       </c>
       <c r="J13" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.33</v>
+        <v>-0.15</v>
       </c>
       <c r="L13" t="n">
-        <v>53.5</v>
+        <v>54.8</v>
       </c>
       <c r="M13" t="n">
         <v>5.89</v>
       </c>
       <c r="N13" t="n">
-        <v>5.49</v>
+        <v>5.51</v>
       </c>
       <c r="O13" t="n">
-        <v>9.720000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="P13" t="n">
-        <v>-39.61</v>
+        <v>-36.98</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>40.43</v>
+        <v>41.87</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>23873.45</v>
+      </c>
+      <c r="D17" t="n">
         <v>23914.45</v>
       </c>
-      <c r="D17" t="n">
-        <v>24055.8</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.59</v>
+        <v>-0.17</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.21</v>
+        <v>-1.38</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.85</v>
+        <v>-3.01</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.73</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57380.6</v>
+      </c>
+      <c r="D18" t="n">
         <v>57172</v>
       </c>
-      <c r="D18" t="n">
-        <v>57409.6</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.41</v>
+        <v>0.36</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.06</v>
+        <v>-0.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.27</v>
+        <v>-0.91</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.52</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>94.65000000000001</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>94.65000000000001</v>
+        <v>95.63</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="F19" t="n">
         <v>7.75</v>
       </c>
       <c r="G19" t="n">
-        <v>19.27</v>
+        <v>21.65</v>
       </c>
       <c r="H19" t="n">
-        <v>1.03</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4434.3</v>
+        <v>4525.4</v>
       </c>
       <c r="D20" t="n">
-        <v>4348</v>
+        <v>4366.3</v>
       </c>
       <c r="E20" t="n">
-        <v>1.98</v>
+        <v>3.64</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.56</v>
+        <v>-1.83</v>
       </c>
       <c r="G20" t="n">
-        <v>8.279999999999999</v>
+        <v>6.59</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53171.82</v>
+        <v>53412.4</v>
       </c>
       <c r="D21" t="n">
-        <v>52766.88</v>
+        <v>53061.95</v>
       </c>
       <c r="E21" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.55</v>
+        <v>-0.1</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.69</v>
+        <v>-1.25</v>
       </c>
       <c r="H21" t="n">
-        <v>0.71</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.59</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.49</v>
-      </c>
       <c r="E22" t="n">
-        <v>0.87</v>
+        <v>-2.16</v>
       </c>
       <c r="F22" t="n">
-        <v>9.65</v>
+        <v>7.28</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.92</v>
+        <v>-6.97</v>
       </c>
       <c r="H22" t="n">
-        <v/>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2109,6 +2109,29 @@
       </c>
       <c r="G31" t="n">
         <v>-2.52</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57380.6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>57172</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.81</v>
       </c>
     </row>
   </sheetData>
@@ -2122,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2850,6 +2873,29 @@
       </c>
       <c r="G31" t="n">
         <v>1.03</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>95.63</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.52</v>
       </c>
     </row>
   </sheetData>
@@ -2863,7 +2909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3591,6 +3637,29 @@
       </c>
       <c r="G31" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4525.4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4366.3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.41</v>
       </c>
     </row>
   </sheetData>
@@ -3604,7 +3673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4317,6 +4386,29 @@
       </c>
       <c r="G31" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>53412.4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>53061.95</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.74</v>
       </c>
     </row>
   </sheetData>
@@ -4330,7 +4422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4984,8 +5076,28 @@
       <c r="F31" t="n">
         <v>-4.92</v>
       </c>
-      <c r="G31" t="n">
-        <v/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="C32" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-6.97</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -4999,7 +5111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,6 +6655,59 @@
       </c>
       <c r="Q30" t="n">
         <v>30.43</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="C31" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-13.68</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-12.65</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3427</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2751</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="K31" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7</v>
+      </c>
+      <c r="N31" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-52.81</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>24.01</v>
       </c>
     </row>
   </sheetData>
@@ -6556,7 +6721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8063,7 +8228,7 @@
         <v>-1.12</v>
       </c>
       <c r="E30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>6.83</v>
@@ -8100,6 +8265,59 @@
       </c>
       <c r="Q30" t="n">
         <v>11.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B31" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="C31" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="G31" t="n">
+        <v>17940384</v>
+      </c>
+      <c r="H31" t="n">
+        <v>12027252</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K31" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="M31" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="N31" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-25.39</v>
+      </c>
+      <c r="P31" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>12.94</v>
       </c>
     </row>
   </sheetData>
@@ -8113,7 +8331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9551,6 +9769,59 @@
       </c>
       <c r="Q28" t="n">
         <v>61.57</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B29" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="C29" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G29" t="n">
+        <v>29131306</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5752468</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K29" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="L29" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="M29" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="N29" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="P29" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>68.48999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11161,6 +11432,59 @@
       </c>
       <c r="Q31" t="n">
         <v>122.62</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>535.55</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E32" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="F32" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>711681</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K32" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>343.39</v>
+      </c>
+      <c r="M32" t="n">
+        <v>417.72</v>
+      </c>
+      <c r="N32" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>126.25</v>
       </c>
     </row>
   </sheetData>
@@ -11174,7 +11498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12771,6 +13095,59 @@
       </c>
       <c r="Q31" t="n">
         <v>4.23</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>263</v>
+      </c>
+      <c r="C32" t="n">
+        <v>266.3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-8.35</v>
+      </c>
+      <c r="G32" t="n">
+        <v>17805990</v>
+      </c>
+      <c r="H32" t="n">
+        <v>14643482</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K32" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>307.91</v>
+      </c>
+      <c r="M32" t="n">
+        <v>279.23</v>
+      </c>
+      <c r="N32" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-34.58</v>
+      </c>
+      <c r="P32" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.94</v>
       </c>
     </row>
   </sheetData>
@@ -12784,7 +13161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14381,6 +14758,59 @@
       </c>
       <c r="Q31" t="n">
         <v>6.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>838.3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>843.25</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-8.48</v>
+      </c>
+      <c r="G32" t="n">
+        <v>217906</v>
+      </c>
+      <c r="H32" t="n">
+        <v>472795</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K32" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>947.47</v>
+      </c>
+      <c r="M32" t="n">
+        <v>915.62</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-30.37</v>
+      </c>
+      <c r="P32" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>6.27</v>
       </c>
     </row>
   </sheetData>
@@ -14394,7 +14824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15991,6 +16421,59 @@
       </c>
       <c r="Q31" t="n">
         <v>46.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1008</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="G32" t="n">
+        <v>543560</v>
+      </c>
+      <c r="H32" t="n">
+        <v>827532</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K32" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>935.33</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1039.88</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-9.77</v>
+      </c>
+      <c r="P32" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>47.67</v>
       </c>
     </row>
   </sheetData>
@@ -16004,7 +16487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17601,6 +18084,59 @@
       </c>
       <c r="Q31" t="n">
         <v>49.49</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="C32" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="G32" t="n">
+        <v>21855442</v>
+      </c>
+      <c r="H32" t="n">
+        <v>49431916</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="M32" t="n">
+        <v>67.14</v>
+      </c>
+      <c r="N32" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-13.08</v>
+      </c>
+      <c r="P32" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>47.97</v>
       </c>
     </row>
   </sheetData>
@@ -17614,7 +18150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19211,6 +19747,59 @@
       </c>
       <c r="Q31" t="n">
         <v>40.43</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="G32" t="n">
+        <v>490020</v>
+      </c>
+      <c r="H32" t="n">
+        <v>447461</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="K32" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="N32" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-36.98</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>41.87</v>
       </c>
     </row>
   </sheetData>
@@ -19224,7 +19813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20821,6 +21410,59 @@
       </c>
       <c r="Q31" t="n">
         <v>75.58</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>962.3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>966.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="G32" t="n">
+        <v>139354</v>
+      </c>
+      <c r="H32" t="n">
+        <v>242009</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K32" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="L32" t="n">
+        <v>757.9</v>
+      </c>
+      <c r="M32" t="n">
+        <v>866.92</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="P32" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>74.81</v>
       </c>
     </row>
   </sheetData>
@@ -20834,7 +21476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21564,6 +22206,29 @@
         <v>-3.73</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>23873.45</v>
+      </c>
+      <c r="C32" t="n">
+        <v>23914.45</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>487.9</v>
+      </c>
+      <c r="D3" t="n">
         <v>544.3</v>
       </c>
-      <c r="D3" t="n">
-        <v>535.55</v>
-      </c>
       <c r="E3" t="n">
-        <v>1.63</v>
+        <v>-10.36</v>
       </c>
       <c r="F3" t="n">
-        <v>21.43</v>
+        <v>0.06</v>
       </c>
       <c r="G3" t="n">
-        <v>34.2</v>
+        <v>20.47</v>
       </c>
       <c r="H3" t="n">
-        <v>711681</v>
+        <v>1788207</v>
       </c>
       <c r="I3" t="n">
-        <v>1090048</v>
+        <v>711940</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.85</v>
       </c>
       <c r="L3" t="n">
-        <v>73.3</v>
+        <v>56.3</v>
       </c>
       <c r="M3" t="n">
-        <v>343.39</v>
+        <v>344.02</v>
       </c>
       <c r="N3" t="n">
-        <v>417.72</v>
+        <v>419.94</v>
       </c>
       <c r="O3" t="n">
         <v>544.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-10.36</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>126.25</v>
+        <v>102.81</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="D4" t="n">
         <v>47.7</v>
       </c>
-      <c r="D4" t="n">
-        <v>45.74</v>
-      </c>
       <c r="E4" t="n">
-        <v>4.29</v>
+        <v>-0.86</v>
       </c>
       <c r="F4" t="n">
-        <v>4.31</v>
+        <v>4.23</v>
       </c>
       <c r="G4" t="n">
-        <v>2.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>29131306</v>
+        <v>8813687</v>
       </c>
       <c r="I4" t="n">
-        <v>5752468</v>
+        <v>29134346</v>
       </c>
       <c r="J4" t="n">
-        <v>4.06</v>
+        <v>1.08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="L4" t="n">
-        <v>64.40000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="M4" t="n">
-        <v>41.52</v>
+        <v>41.55</v>
       </c>
       <c r="N4" t="n">
-        <v>45.75</v>
+        <v>45.8</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.67</v>
+        <v>-1.52</v>
       </c>
       <c r="Q4" t="n">
         <v>28.31</v>
       </c>
       <c r="R4" t="n">
-        <v>68.48999999999999</v>
+        <v>67.04000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>264.1</v>
+      </c>
+      <c r="D5" t="n">
         <v>263</v>
       </c>
-      <c r="D5" t="n">
-        <v>266.3</v>
-      </c>
       <c r="E5" t="n">
-        <v>-1.24</v>
+        <v>0.42</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.23</v>
+        <v>-0.71</v>
       </c>
       <c r="G5" t="n">
-        <v>-8.35</v>
+        <v>-7.63</v>
       </c>
       <c r="H5" t="n">
-        <v>17805990</v>
+        <v>9513896</v>
       </c>
       <c r="I5" t="n">
-        <v>14643482</v>
+        <v>17813663</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3</v>
+        <v>0.68</v>
       </c>
       <c r="K5" t="n">
-        <v>0.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>38.4</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>307.91</v>
+        <v>307.31</v>
       </c>
       <c r="N5" t="n">
-        <v>279.23</v>
+        <v>278.71</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-34.58</v>
+        <v>-34.3</v>
       </c>
       <c r="Q5" t="n">
         <v>255.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2.94</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>828.65</v>
+      </c>
+      <c r="D6" t="n">
         <v>838.3</v>
       </c>
-      <c r="D6" t="n">
-        <v>843.25</v>
-      </c>
       <c r="E6" t="n">
-        <v>-0.59</v>
+        <v>-1.15</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.25</v>
+        <v>-2.95</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.48</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>217906</v>
+        <v>444927</v>
       </c>
       <c r="I6" t="n">
-        <v>472795</v>
+        <v>217962</v>
       </c>
       <c r="J6" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02</v>
+        <v>0.22</v>
       </c>
       <c r="L6" t="n">
-        <v>31.5</v>
+        <v>29.3</v>
       </c>
       <c r="M6" t="n">
-        <v>947.47</v>
+        <v>947.48</v>
       </c>
       <c r="N6" t="n">
-        <v>915.62</v>
+        <v>914.15</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-30.37</v>
+        <v>-31.17</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>6.27</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="D7" t="n">
         <v>62.99</v>
       </c>
-      <c r="D7" t="n">
-        <v>63.64</v>
-      </c>
       <c r="E7" t="n">
-        <v>-1.02</v>
+        <v>2.29</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.140000000000001</v>
+        <v>-5.04</v>
       </c>
       <c r="G7" t="n">
-        <v>-9.48</v>
+        <v>-10.58</v>
       </c>
       <c r="H7" t="n">
-        <v>21855442</v>
+        <v>12163205</v>
       </c>
       <c r="I7" t="n">
-        <v>49431916</v>
+        <v>21859923</v>
       </c>
       <c r="J7" t="n">
-        <v>1.52</v>
+        <v>0.83</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>31.8</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>59.37</v>
+        <v>59.42</v>
       </c>
       <c r="N7" t="n">
-        <v>67.14</v>
+        <v>67.31</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-13.08</v>
+        <v>-11.09</v>
       </c>
       <c r="Q7" t="n">
         <v>42.57</v>
       </c>
       <c r="R7" t="n">
-        <v>47.97</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>991.1</v>
+      </c>
+      <c r="D8" t="n">
         <v>962.3</v>
       </c>
-      <c r="D8" t="n">
-        <v>966.5</v>
-      </c>
       <c r="E8" t="n">
-        <v>-0.43</v>
+        <v>2.99</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1</v>
+        <v>2.45</v>
       </c>
       <c r="G8" t="n">
-        <v>12.18</v>
+        <v>13.8</v>
       </c>
       <c r="H8" t="n">
-        <v>139354</v>
+        <v>314142</v>
       </c>
       <c r="I8" t="n">
-        <v>242009</v>
+        <v>139358</v>
       </c>
       <c r="J8" t="n">
-        <v>0.26</v>
+        <v>0.59</v>
       </c>
       <c r="K8" t="n">
-        <v>0.11</v>
+        <v>2.09</v>
       </c>
       <c r="L8" t="n">
-        <v>64.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>757.9</v>
+        <v>759.02</v>
       </c>
       <c r="N8" t="n">
-        <v>866.92</v>
+        <v>870.01</v>
       </c>
       <c r="O8" t="n">
         <v>1001.9</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.95</v>
+        <v>-1.08</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>74.81</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="D10" t="n">
         <v>6.56</v>
       </c>
-      <c r="D10" t="n">
-        <v>6.9</v>
-      </c>
       <c r="E10" t="n">
-        <v>-4.93</v>
+        <v>4.88</v>
       </c>
       <c r="F10" t="n">
-        <v>-13.68</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-12.65</v>
+        <v>-12.91</v>
       </c>
       <c r="H10" t="n">
+        <v>2123</v>
+      </c>
+      <c r="I10" t="n">
         <v>3427</v>
       </c>
-      <c r="I10" t="n">
-        <v>2751</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.59</v>
+        <v>0.38</v>
       </c>
       <c r="K10" t="n">
-        <v>1.73</v>
+        <v>0.24</v>
       </c>
       <c r="L10" t="n">
-        <v>34.2</v>
+        <v>41.7</v>
       </c>
       <c r="M10" t="n">
-        <v>8.77</v>
+        <v>8.75</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>7.01</v>
       </c>
       <c r="O10" t="n">
-        <v>13.9</v>
+        <v>13.78</v>
       </c>
       <c r="P10" t="n">
-        <v>-52.81</v>
+        <v>-50.07</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>24.01</v>
+        <v>30.06</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D11" t="n">
         <v>1008</v>
       </c>
-      <c r="D11" t="n">
-        <v>1000</v>
-      </c>
       <c r="E11" t="n">
-        <v>0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8</v>
+        <v>-1.17</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.45</v>
+        <v>-3.81</v>
       </c>
       <c r="H11" t="n">
-        <v>543560</v>
+        <v>1046119</v>
       </c>
       <c r="I11" t="n">
-        <v>827532</v>
+        <v>543617</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.96</v>
       </c>
       <c r="K11" t="n">
-        <v>0.88</v>
+        <v>-1</v>
       </c>
       <c r="L11" t="n">
-        <v>45.5</v>
+        <v>44.2</v>
       </c>
       <c r="M11" t="n">
-        <v>935.33</v>
+        <v>935.37</v>
       </c>
       <c r="N11" t="n">
-        <v>1039.88</v>
+        <v>1038.91</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-9.77</v>
+        <v>-10.31</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>47.67</v>
+        <v>46.79</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="D12" t="n">
         <v>24.27</v>
       </c>
-      <c r="D12" t="n">
-        <v>23.94</v>
-      </c>
       <c r="E12" t="n">
-        <v>1.38</v>
+        <v>-0.95</v>
       </c>
       <c r="F12" t="n">
-        <v>3.59</v>
+        <v>-0.41</v>
       </c>
       <c r="G12" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="H12" t="n">
-        <v>17940384</v>
+        <v>13574795</v>
       </c>
       <c r="I12" t="n">
-        <v>12027252</v>
+        <v>17941170</v>
       </c>
       <c r="J12" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="K12" t="n">
-        <v>1.16</v>
+        <v>0.19</v>
       </c>
       <c r="L12" t="n">
-        <v>54.9</v>
+        <v>53.1</v>
       </c>
       <c r="M12" t="n">
-        <v>24.74</v>
+        <v>24.72</v>
       </c>
       <c r="N12" t="n">
-        <v>22.91</v>
+        <v>22.94</v>
       </c>
       <c r="O12" t="n">
-        <v>32.53</v>
+        <v>32.31</v>
       </c>
       <c r="P12" t="n">
-        <v>-25.39</v>
+        <v>-25.6</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>12.94</v>
+        <v>11.87</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.93</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.87</v>
-      </c>
       <c r="E13" t="n">
-        <v>1.02</v>
+        <v>-0.51</v>
       </c>
       <c r="F13" t="n">
-        <v>0.17</v>
+        <v>-2.32</v>
       </c>
       <c r="G13" t="n">
-        <v>8.41</v>
+        <v>11.32</v>
       </c>
       <c r="H13" t="n">
-        <v>490020</v>
+        <v>289338</v>
       </c>
       <c r="I13" t="n">
-        <v>447461</v>
+        <v>495020</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41</v>
+        <v>0.24</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.15</v>
+        <v>1.06</v>
       </c>
       <c r="L13" t="n">
-        <v>54.8</v>
+        <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="N13" t="n">
-        <v>5.51</v>
+        <v>5.52</v>
       </c>
       <c r="O13" t="n">
         <v>9.41</v>
       </c>
       <c r="P13" t="n">
-        <v>-36.98</v>
+        <v>-37.3</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>41.87</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>23897.7</v>
+      </c>
+      <c r="D17" t="n">
         <v>23873.45</v>
       </c>
-      <c r="D17" t="n">
-        <v>23914.45</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.17</v>
+        <v>0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.38</v>
+        <v>-1.15</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.01</v>
+        <v>-3</v>
       </c>
       <c r="H17" t="n">
-        <v>1.22</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57369.65</v>
+      </c>
+      <c r="D18" t="n">
         <v>57380.6</v>
       </c>
-      <c r="D18" t="n">
-        <v>57172</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.36</v>
+        <v>-0.02</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7</v>
+        <v>-0.22</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.91</v>
+        <v>-1.2</v>
       </c>
       <c r="H18" t="n">
-        <v>1.81</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>96.65000000000001</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>95.63</v>
+        <v>95.52</v>
       </c>
       <c r="E19" t="n">
-        <v>1.07</v>
+        <v>-1.52</v>
       </c>
       <c r="F19" t="n">
-        <v>7.75</v>
+        <v>5.33</v>
       </c>
       <c r="G19" t="n">
-        <v>21.65</v>
+        <v>14.04</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.52</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4525.4</v>
+        <v>4478.4</v>
       </c>
       <c r="D20" t="n">
-        <v>4366.3</v>
+        <v>4491.7</v>
       </c>
       <c r="E20" t="n">
-        <v>3.64</v>
+        <v>-0.3</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.83</v>
+        <v>0.01</v>
       </c>
       <c r="G20" t="n">
-        <v>6.59</v>
+        <v>5.57</v>
       </c>
       <c r="H20" t="n">
-        <v>2.41</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53412.4</v>
+        <v>53409.5</v>
       </c>
       <c r="D21" t="n">
-        <v>53061.95</v>
+        <v>53686.11</v>
       </c>
       <c r="E21" t="n">
-        <v>0.66</v>
+        <v>-0.52</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1</v>
+        <v>-0.28</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.25</v>
+        <v>-0.88</v>
       </c>
       <c r="H21" t="n">
-        <v>2.74</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.34</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.59</v>
-      </c>
       <c r="E22" t="n">
-        <v>-2.16</v>
+        <v>-5.82</v>
       </c>
       <c r="F22" t="n">
-        <v>7.28</v>
+        <v>-0</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.97</v>
+        <v>-12.17</v>
       </c>
       <c r="H22" t="n">
-        <v>0.03</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2132,6 +2132,29 @@
       </c>
       <c r="G32" t="n">
         <v>1.81</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57369.65</v>
+      </c>
+      <c r="C33" t="n">
+        <v>57380.6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -2145,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2896,6 +2919,29 @@
       </c>
       <c r="G32" t="n">
         <v>-0.52</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>94.06999999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>95.52</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -2909,7 +2955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3660,6 +3706,29 @@
       </c>
       <c r="G32" t="n">
         <v>2.41</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4478.4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4491.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -3673,7 +3742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4409,6 +4478,29 @@
       </c>
       <c r="G32" t="n">
         <v>2.74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>53409.5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>53686.11</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-1.04</v>
       </c>
     </row>
   </sheetData>
@@ -4422,7 +4514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5098,6 +5190,29 @@
       </c>
       <c r="G32" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="C33" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-12.17</v>
+      </c>
+      <c r="G33" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -5111,7 +5226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6708,6 +6823,59 @@
       </c>
       <c r="Q31" t="n">
         <v>24.01</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B32" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="C32" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-9.470000000000001</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-12.91</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2123</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3427</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K32" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M32" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-50.07</v>
+      </c>
+      <c r="P32" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>30.06</v>
       </c>
     </row>
   </sheetData>
@@ -6721,7 +6889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8318,6 +8486,59 @@
       </c>
       <c r="Q31" t="n">
         <v>12.94</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B32" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="C32" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="G32" t="n">
+        <v>13574795</v>
+      </c>
+      <c r="H32" t="n">
+        <v>17941170</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K32" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="M32" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="N32" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-25.6</v>
+      </c>
+      <c r="P32" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>11.87</v>
       </c>
     </row>
   </sheetData>
@@ -8331,7 +8552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9822,6 +10043,59 @@
       </c>
       <c r="Q29" t="n">
         <v>68.48999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B30" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="C30" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8813687</v>
+      </c>
+      <c r="H30" t="n">
+        <v>29134346</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K30" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="L30" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="M30" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="N30" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="P30" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>67.04000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -9835,7 +10109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11485,6 +11759,59 @@
       </c>
       <c r="Q32" t="n">
         <v>126.25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>487.9</v>
+      </c>
+      <c r="C33" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-10.36</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F33" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1788207</v>
+      </c>
+      <c r="H33" t="n">
+        <v>711940</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="K33" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>344.02</v>
+      </c>
+      <c r="M33" t="n">
+        <v>419.94</v>
+      </c>
+      <c r="N33" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-10.36</v>
+      </c>
+      <c r="P33" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>102.81</v>
       </c>
     </row>
   </sheetData>
@@ -11498,7 +11825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13148,6 +13475,59 @@
       </c>
       <c r="Q32" t="n">
         <v>2.94</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>264.1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>263</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-7.63</v>
+      </c>
+      <c r="G33" t="n">
+        <v>9513896</v>
+      </c>
+      <c r="H33" t="n">
+        <v>17813663</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K33" t="n">
+        <v>40</v>
+      </c>
+      <c r="L33" t="n">
+        <v>307.31</v>
+      </c>
+      <c r="M33" t="n">
+        <v>278.71</v>
+      </c>
+      <c r="N33" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-34.3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.37</v>
       </c>
     </row>
   </sheetData>
@@ -13161,7 +13541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14811,6 +15191,59 @@
       </c>
       <c r="Q32" t="n">
         <v>6.27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>828.65</v>
+      </c>
+      <c r="C33" t="n">
+        <v>838.3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="G33" t="n">
+        <v>444927</v>
+      </c>
+      <c r="H33" t="n">
+        <v>217962</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K33" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>947.48</v>
+      </c>
+      <c r="M33" t="n">
+        <v>914.15</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-31.17</v>
+      </c>
+      <c r="P33" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.05</v>
       </c>
     </row>
   </sheetData>
@@ -14824,7 +15257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16474,6 +16907,59 @@
       </c>
       <c r="Q32" t="n">
         <v>47.67</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1046119</v>
+      </c>
+      <c r="H33" t="n">
+        <v>543617</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>935.37</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1038.91</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-10.31</v>
+      </c>
+      <c r="P33" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>46.79</v>
       </c>
     </row>
   </sheetData>
@@ -16487,7 +16973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18137,6 +18623,59 @@
       </c>
       <c r="Q32" t="n">
         <v>47.97</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-10.58</v>
+      </c>
+      <c r="G33" t="n">
+        <v>12163205</v>
+      </c>
+      <c r="H33" t="n">
+        <v>21859923</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>38</v>
+      </c>
+      <c r="L33" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="M33" t="n">
+        <v>67.31</v>
+      </c>
+      <c r="N33" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-11.09</v>
+      </c>
+      <c r="P33" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>51.35</v>
       </c>
     </row>
   </sheetData>
@@ -18150,7 +18689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19800,6 +20339,59 @@
       </c>
       <c r="Q32" t="n">
         <v>41.87</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C33" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="G33" t="n">
+        <v>289338</v>
+      </c>
+      <c r="H33" t="n">
+        <v>495020</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K33" t="n">
+        <v>54</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="M33" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="N33" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-37.3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>41.15</v>
       </c>
     </row>
   </sheetData>
@@ -19813,7 +20405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21463,6 +22055,59 @@
       </c>
       <c r="Q32" t="n">
         <v>74.81</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>991.1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>962.3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F33" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G33" t="n">
+        <v>314142</v>
+      </c>
+      <c r="H33" t="n">
+        <v>139358</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K33" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="L33" t="n">
+        <v>759.02</v>
+      </c>
+      <c r="M33" t="n">
+        <v>870.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="P33" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>80.05</v>
       </c>
     </row>
   </sheetData>
@@ -21476,7 +22121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22229,6 +22874,29 @@
         <v>1.22</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>23897.7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>23873.45</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>461.05</v>
+      </c>
+      <c r="D3" t="n">
         <v>487.9</v>
       </c>
-      <c r="D3" t="n">
-        <v>544.3</v>
-      </c>
       <c r="E3" t="n">
-        <v>-10.36</v>
+        <v>-5.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06</v>
+        <v>-6.52</v>
       </c>
       <c r="G3" t="n">
-        <v>20.47</v>
+        <v>14.72</v>
       </c>
       <c r="H3" t="n">
-        <v>1788207</v>
+        <v>1245587</v>
       </c>
       <c r="I3" t="n">
-        <v>711940</v>
+        <v>1789647</v>
       </c>
       <c r="J3" t="n">
-        <v>1.38</v>
+        <v>0.91</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>56.3</v>
+        <v>50.4</v>
       </c>
       <c r="M3" t="n">
-        <v>344.02</v>
+        <v>344.5</v>
       </c>
       <c r="N3" t="n">
-        <v>419.94</v>
+        <v>421.78</v>
       </c>
       <c r="O3" t="n">
         <v>544.3</v>
       </c>
       <c r="P3" t="n">
-        <v>-10.36</v>
+        <v>-15.29</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>102.81</v>
+        <v>91.65000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="D4" t="n">
         <v>47.29</v>
       </c>
-      <c r="D4" t="n">
-        <v>47.7</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.86</v>
+        <v>-1.59</v>
       </c>
       <c r="F4" t="n">
-        <v>4.23</v>
+        <v>1.93</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.37</v>
       </c>
       <c r="H4" t="n">
-        <v>8813687</v>
+        <v>4946728</v>
       </c>
       <c r="I4" t="n">
-        <v>29134346</v>
+        <v>8819050</v>
       </c>
       <c r="J4" t="n">
-        <v>1.08</v>
+        <v>0.59</v>
       </c>
       <c r="K4" t="n">
-        <v>1.78</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>60.7</v>
+        <v>54.4</v>
       </c>
       <c r="M4" t="n">
-        <v>41.55</v>
+        <v>41.6</v>
       </c>
       <c r="N4" t="n">
-        <v>45.8</v>
+        <v>45.82</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.52</v>
+        <v>-3.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>28.31</v>
+        <v>28.34</v>
       </c>
       <c r="R4" t="n">
-        <v>67.04000000000001</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="D5" t="n">
         <v>264.1</v>
       </c>
-      <c r="D5" t="n">
-        <v>263</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.42</v>
+        <v>-0.23</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.71</v>
+        <v>3.13</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.63</v>
+        <v>-7.9</v>
       </c>
       <c r="H5" t="n">
-        <v>9513896</v>
+        <v>6684240</v>
       </c>
       <c r="I5" t="n">
-        <v>17813663</v>
+        <v>9519153</v>
       </c>
       <c r="J5" t="n">
-        <v>0.68</v>
+        <v>0.47</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>39.4</v>
       </c>
       <c r="M5" t="n">
-        <v>307.31</v>
+        <v>306.69</v>
       </c>
       <c r="N5" t="n">
-        <v>278.71</v>
+        <v>278.17</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-34.3</v>
+        <v>-34.45</v>
       </c>
       <c r="Q5" t="n">
         <v>255.5</v>
       </c>
       <c r="R5" t="n">
-        <v>3.37</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>838.3</v>
+      </c>
+      <c r="D6" t="n">
         <v>828.65</v>
       </c>
-      <c r="D6" t="n">
-        <v>838.3</v>
-      </c>
       <c r="E6" t="n">
-        <v>-1.15</v>
+        <v>1.16</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.95</v>
+        <v>-0.38</v>
       </c>
       <c r="G6" t="n">
-        <v>-9.039999999999999</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>444927</v>
+        <v>301132</v>
       </c>
       <c r="I6" t="n">
-        <v>217962</v>
+        <v>445370</v>
       </c>
       <c r="J6" t="n">
-        <v>0.89</v>
+        <v>0.59</v>
       </c>
       <c r="K6" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="L6" t="n">
-        <v>29.3</v>
+        <v>34.3</v>
       </c>
       <c r="M6" t="n">
-        <v>947.48</v>
+        <v>947.34</v>
       </c>
       <c r="N6" t="n">
-        <v>914.15</v>
+        <v>912.55</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-31.17</v>
+        <v>-30.37</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>5.05</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="D7" t="n">
         <v>64.43000000000001</v>
       </c>
-      <c r="D7" t="n">
-        <v>62.99</v>
-      </c>
       <c r="E7" t="n">
-        <v>2.29</v>
+        <v>1.02</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.04</v>
+        <v>-5.82</v>
       </c>
       <c r="G7" t="n">
-        <v>-10.58</v>
+        <v>-7.16</v>
       </c>
       <c r="H7" t="n">
-        <v>12163205</v>
+        <v>9338903</v>
       </c>
       <c r="I7" t="n">
-        <v>21859923</v>
+        <v>12168369</v>
       </c>
       <c r="J7" t="n">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>40.7</v>
       </c>
       <c r="M7" t="n">
-        <v>59.42</v>
+        <v>59.48</v>
       </c>
       <c r="N7" t="n">
-        <v>67.31</v>
+        <v>67.47</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-11.09</v>
+        <v>-10.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>42.57</v>
+        <v>44.17</v>
       </c>
       <c r="R7" t="n">
-        <v>51.35</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>994.8</v>
+      </c>
+      <c r="D8" t="n">
         <v>991.1</v>
       </c>
-      <c r="D8" t="n">
-        <v>962.3</v>
-      </c>
       <c r="E8" t="n">
-        <v>2.99</v>
+        <v>0.37</v>
       </c>
       <c r="F8" t="n">
-        <v>2.45</v>
+        <v>-0.71</v>
       </c>
       <c r="G8" t="n">
-        <v>13.8</v>
+        <v>14.35</v>
       </c>
       <c r="H8" t="n">
-        <v>314142</v>
+        <v>356880</v>
       </c>
       <c r="I8" t="n">
-        <v>139358</v>
+        <v>314144</v>
       </c>
       <c r="J8" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="K8" t="n">
-        <v>2.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>69.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="M8" t="n">
-        <v>759.02</v>
+        <v>760.14</v>
       </c>
       <c r="N8" t="n">
-        <v>870.01</v>
+        <v>872.9400000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1001.9</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.08</v>
+        <v>-0.71</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>80.05</v>
+        <v>80.72</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D10" t="n">
         <v>6.88</v>
       </c>
-      <c r="D10" t="n">
-        <v>6.56</v>
-      </c>
       <c r="E10" t="n">
-        <v>4.88</v>
+        <v>0.29</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.470000000000001</v>
+        <v>-7.38</v>
       </c>
       <c r="G10" t="n">
-        <v>-12.91</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="H10" t="n">
+        <v>2811</v>
+      </c>
+      <c r="I10" t="n">
         <v>2123</v>
       </c>
-      <c r="I10" t="n">
-        <v>3427</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.24</v>
+        <v>0.68</v>
       </c>
       <c r="L10" t="n">
-        <v>41.7</v>
+        <v>42.2</v>
       </c>
       <c r="M10" t="n">
-        <v>8.75</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>7.01</v>
+        <v>7.03</v>
       </c>
       <c r="O10" t="n">
         <v>13.78</v>
       </c>
       <c r="P10" t="n">
-        <v>-50.07</v>
+        <v>-49.93</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>30.06</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>990</v>
+      </c>
+      <c r="D11" t="n">
         <v>1002</v>
       </c>
-      <c r="D11" t="n">
-        <v>1008</v>
-      </c>
       <c r="E11" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.17</v>
+        <v>-4.47</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.81</v>
+        <v>-5.46</v>
       </c>
       <c r="H11" t="n">
-        <v>1046119</v>
+        <v>543348</v>
       </c>
       <c r="I11" t="n">
-        <v>543617</v>
+        <v>1046394</v>
       </c>
       <c r="J11" t="n">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="K11" t="n">
-        <v>-1</v>
+        <v>-0.42</v>
       </c>
       <c r="L11" t="n">
-        <v>44.2</v>
+        <v>41.5</v>
       </c>
       <c r="M11" t="n">
-        <v>935.37</v>
+        <v>935.33</v>
       </c>
       <c r="N11" t="n">
-        <v>1038.91</v>
+        <v>1038.12</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-10.31</v>
+        <v>-11.39</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>46.79</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="D12" t="n">
         <v>24.04</v>
       </c>
-      <c r="D12" t="n">
-        <v>24.27</v>
-      </c>
       <c r="E12" t="n">
-        <v>-0.95</v>
+        <v>4.62</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.41</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>8.68</v>
+        <v>13.44</v>
       </c>
       <c r="H12" t="n">
-        <v>13574795</v>
+        <v>34684845</v>
       </c>
       <c r="I12" t="n">
-        <v>17941170</v>
+        <v>13578560</v>
       </c>
       <c r="J12" t="n">
-        <v>0.45</v>
+        <v>1.14</v>
       </c>
       <c r="K12" t="n">
-        <v>0.19</v>
+        <v>0.39</v>
       </c>
       <c r="L12" t="n">
-        <v>53.1</v>
+        <v>60</v>
       </c>
       <c r="M12" t="n">
-        <v>24.72</v>
+        <v>24.7</v>
       </c>
       <c r="N12" t="n">
-        <v>22.94</v>
+        <v>23</v>
       </c>
       <c r="O12" t="n">
         <v>32.31</v>
       </c>
       <c r="P12" t="n">
-        <v>-25.6</v>
+        <v>-22.16</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>11.87</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.9</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.93</v>
-      </c>
       <c r="E13" t="n">
-        <v>-0.51</v>
+        <v>1.02</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.32</v>
+        <v>-1.97</v>
       </c>
       <c r="G13" t="n">
-        <v>11.32</v>
+        <v>12.03</v>
       </c>
       <c r="H13" t="n">
-        <v>289338</v>
+        <v>861570</v>
       </c>
       <c r="I13" t="n">
-        <v>495020</v>
+        <v>290468</v>
       </c>
       <c r="J13" t="n">
-        <v>0.24</v>
+        <v>0.71</v>
       </c>
       <c r="K13" t="n">
-        <v>1.06</v>
+        <v>0.15</v>
       </c>
       <c r="L13" t="n">
-        <v>54</v>
+        <v>55.4</v>
       </c>
       <c r="M13" t="n">
-        <v>5.88</v>
+        <v>5.87</v>
       </c>
       <c r="N13" t="n">
-        <v>5.52</v>
+        <v>5.53</v>
       </c>
       <c r="O13" t="n">
         <v>9.41</v>
       </c>
       <c r="P13" t="n">
-        <v>-37.3</v>
+        <v>-36.66</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>41.15</v>
+        <v>42.58</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>23779.15</v>
+      </c>
+      <c r="D17" t="n">
         <v>23897.7</v>
       </c>
-      <c r="D17" t="n">
-        <v>23873.45</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.15</v>
+        <v>-1.25</v>
       </c>
       <c r="G17" t="n">
-        <v>-3</v>
+        <v>-3.22</v>
       </c>
       <c r="H17" t="n">
-        <v>0.53</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>57088.3</v>
+      </c>
+      <c r="D18" t="n">
         <v>57369.65</v>
       </c>
-      <c r="D18" t="n">
-        <v>57380.6</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.02</v>
+        <v>-0.49</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.22</v>
+        <v>-1.61</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2</v>
+        <v>-1.14</v>
       </c>
       <c r="H18" t="n">
-        <v>0.57</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>94.06999999999999</v>
+        <v>96.28</v>
       </c>
       <c r="D19" t="n">
-        <v>95.52</v>
+        <v>96.28</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.52</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>5.33</v>
+        <v>6.4</v>
       </c>
       <c r="G19" t="n">
-        <v>14.04</v>
+        <v>15.24</v>
       </c>
       <c r="H19" t="n">
-        <v>0.62</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4478.4</v>
+        <v>4476.6</v>
       </c>
       <c r="D20" t="n">
-        <v>4491.7</v>
+        <v>4429.8</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3</v>
+        <v>1.06</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01</v>
+        <v>1.03</v>
       </c>
       <c r="G20" t="n">
-        <v>5.57</v>
+        <v>3.13</v>
       </c>
       <c r="H20" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="21">
@@ -1322,19 +1322,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53409.5</v>
+        <v>53414.25</v>
       </c>
       <c r="D21" t="n">
         <v>53686.11</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.52</v>
+        <v>-0.51</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.88</v>
+        <v>-0.87</v>
       </c>
       <c r="H21" t="n">
         <v>-1.04</v>
@@ -1352,22 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="D22" t="n">
         <v>10.68</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.34</v>
-      </c>
       <c r="E22" t="n">
-        <v>-5.82</v>
+        <v>4.49</v>
       </c>
       <c r="F22" t="n">
-        <v>-0</v>
+        <v>-0.27</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.17</v>
-      </c>
-      <c r="H22" t="n">
-        <v/>
+        <v>-8.220000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2155,6 +2152,29 @@
       </c>
       <c r="G33" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57088.3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>57369.65</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>
@@ -2168,7 +2188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2942,6 +2962,29 @@
       </c>
       <c r="G33" t="n">
         <v>0.62</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="C34" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -2955,7 +2998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3729,6 +3772,29 @@
       </c>
       <c r="G33" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4476.6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4429.8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -4514,7 +4580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5206,13 +5272,30 @@
         <v>-5.82</v>
       </c>
       <c r="E33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>-12.17</v>
       </c>
-      <c r="G33" t="n">
-        <v/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-8.220000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5226,7 +5309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6876,6 +6959,59 @@
       </c>
       <c r="Q32" t="n">
         <v>30.06</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B33" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C33" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-7.38</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2811</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2123</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K33" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="M33" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="N33" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-49.93</v>
+      </c>
+      <c r="P33" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>30.43</v>
       </c>
     </row>
   </sheetData>
@@ -6889,7 +7025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8539,6 +8675,59 @@
       </c>
       <c r="Q32" t="n">
         <v>11.87</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B33" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="C33" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34684845</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13578560</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K33" t="n">
+        <v>60</v>
+      </c>
+      <c r="L33" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="M33" t="n">
+        <v>23</v>
+      </c>
+      <c r="N33" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-22.16</v>
+      </c>
+      <c r="P33" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>17.03</v>
       </c>
     </row>
   </sheetData>
@@ -8552,7 +8741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10096,6 +10285,59 @@
       </c>
       <c r="Q30" t="n">
         <v>67.04000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B31" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="C31" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4946728</v>
+      </c>
+      <c r="H31" t="n">
+        <v>8819050</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K31" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="N31" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="P31" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>64.22</v>
       </c>
     </row>
   </sheetData>
@@ -10109,7 +10351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11812,6 +12054,59 @@
       </c>
       <c r="Q33" t="n">
         <v>102.81</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>461.05</v>
+      </c>
+      <c r="C34" t="n">
+        <v>487.9</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="F34" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1245587</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1789647</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>421.78</v>
+      </c>
+      <c r="N34" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-15.29</v>
+      </c>
+      <c r="P34" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>91.65000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11825,7 +12120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13528,6 +13823,59 @@
       </c>
       <c r="Q33" t="n">
         <v>3.37</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>264.1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6684240</v>
+      </c>
+      <c r="H34" t="n">
+        <v>9519153</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>306.69</v>
+      </c>
+      <c r="M34" t="n">
+        <v>278.17</v>
+      </c>
+      <c r="N34" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-34.45</v>
+      </c>
+      <c r="P34" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.13</v>
       </c>
     </row>
   </sheetData>
@@ -13541,7 +13889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15244,6 +15592,59 @@
       </c>
       <c r="Q33" t="n">
         <v>5.05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>838.3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>828.65</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>301132</v>
+      </c>
+      <c r="H34" t="n">
+        <v>445370</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K34" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>947.34</v>
+      </c>
+      <c r="M34" t="n">
+        <v>912.55</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-30.37</v>
+      </c>
+      <c r="P34" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6.27</v>
       </c>
     </row>
   </sheetData>
@@ -15257,7 +15658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16960,6 +17361,59 @@
       </c>
       <c r="Q33" t="n">
         <v>46.79</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>990</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="G34" t="n">
+        <v>543348</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1046394</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="K34" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>935.33</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1038.12</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-11.39</v>
+      </c>
+      <c r="P34" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>45.03</v>
       </c>
     </row>
   </sheetData>
@@ -16973,7 +17427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18676,6 +19130,59 @@
       </c>
       <c r="Q33" t="n">
         <v>51.35</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="C34" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-7.16</v>
+      </c>
+      <c r="G34" t="n">
+        <v>9338903</v>
+      </c>
+      <c r="H34" t="n">
+        <v>12168369</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K34" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="L34" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="M34" t="n">
+        <v>67.47</v>
+      </c>
+      <c r="N34" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-10.18</v>
+      </c>
+      <c r="P34" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>47.36</v>
       </c>
     </row>
   </sheetData>
@@ -18689,7 +19196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20392,6 +20899,59 @@
       </c>
       <c r="Q33" t="n">
         <v>41.15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="F34" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="G34" t="n">
+        <v>861570</v>
+      </c>
+      <c r="H34" t="n">
+        <v>290468</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K34" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="M34" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="N34" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-36.66</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>42.58</v>
       </c>
     </row>
   </sheetData>
@@ -20405,7 +20965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22108,6 +22668,59 @@
       </c>
       <c r="Q33" t="n">
         <v>80.05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>994.8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>991.1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="F34" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="G34" t="n">
+        <v>356880</v>
+      </c>
+      <c r="H34" t="n">
+        <v>314144</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K34" t="n">
+        <v>70</v>
+      </c>
+      <c r="L34" t="n">
+        <v>760.14</v>
+      </c>
+      <c r="M34" t="n">
+        <v>872.9400000000001</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="P34" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>80.72</v>
       </c>
     </row>
   </sheetData>
@@ -22121,7 +22734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22897,6 +23510,29 @@
         <v>0.53</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>23779.15</v>
+      </c>
+      <c r="C34" t="n">
+        <v>23897.7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>461.05</v>
+        <v>460.6</v>
       </c>
       <c r="D3" t="n">
         <v>487.9</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.5</v>
+        <v>-5.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.52</v>
+        <v>-6.61</v>
       </c>
       <c r="G3" t="n">
-        <v>14.72</v>
+        <v>14.61</v>
       </c>
       <c r="H3" t="n">
-        <v>1245587</v>
+        <v>1015754</v>
       </c>
       <c r="I3" t="n">
         <v>1789647</v>
       </c>
       <c r="J3" t="n">
-        <v>0.91</v>
+        <v>0.74</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="M3" t="n">
-        <v>344.5</v>
+        <v>344.49</v>
       </c>
       <c r="N3" t="n">
-        <v>421.78</v>
+        <v>421.77</v>
       </c>
       <c r="O3" t="n">
         <v>544.3</v>
       </c>
       <c r="P3" t="n">
-        <v>-15.29</v>
+        <v>-15.38</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>91.65000000000001</v>
+        <v>91.45999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="D4" t="n">
         <v>46.54</v>
       </c>
-      <c r="D4" t="n">
-        <v>47.29</v>
-      </c>
       <c r="E4" t="n">
-        <v>-1.59</v>
+        <v>0.6</v>
       </c>
       <c r="F4" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.37</v>
+        <v>2.78</v>
       </c>
       <c r="H4" t="n">
-        <v>4946728</v>
+        <v>4494405</v>
       </c>
       <c r="I4" t="n">
-        <v>8819050</v>
+        <v>4949017</v>
       </c>
       <c r="J4" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="L4" t="n">
-        <v>54.4</v>
+        <v>56.2</v>
       </c>
       <c r="M4" t="n">
-        <v>41.6</v>
+        <v>41.64</v>
       </c>
       <c r="N4" t="n">
-        <v>45.82</v>
+        <v>45.85</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.08</v>
+        <v>-2.5</v>
       </c>
       <c r="Q4" t="n">
         <v>28.34</v>
       </c>
       <c r="R4" t="n">
-        <v>64.22</v>
+        <v>65.20999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -669,25 +669,25 @@
         <v>263.5</v>
       </c>
       <c r="D5" t="n">
-        <v>264.1</v>
+        <v>263.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3.13</v>
+        <v>-1.16</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.9</v>
+        <v>-6.78</v>
       </c>
       <c r="H5" t="n">
-        <v>6684240</v>
+        <v>7404037</v>
       </c>
       <c r="I5" t="n">
-        <v>9519153</v>
+        <v>6688002</v>
       </c>
       <c r="J5" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>39.4</v>
       </c>
       <c r="M5" t="n">
-        <v>306.69</v>
+        <v>306.06</v>
       </c>
       <c r="N5" t="n">
-        <v>278.17</v>
+        <v>277.7</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>838.3</v>
+        <v>825.75</v>
       </c>
       <c r="D6" t="n">
         <v>828.65</v>
       </c>
       <c r="E6" t="n">
-        <v>1.16</v>
+        <v>-0.35</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.38</v>
+        <v>-1.87</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.390000000000001</v>
+        <v>-9.76</v>
       </c>
       <c r="H6" t="n">
-        <v>301132</v>
+        <v>301905</v>
       </c>
       <c r="I6" t="n">
         <v>445370</v>
@@ -750,28 +750,28 @@
         <v>0.59</v>
       </c>
       <c r="K6" t="n">
-        <v>0.11</v>
+        <v>3.01</v>
       </c>
       <c r="L6" t="n">
-        <v>34.3</v>
+        <v>28.6</v>
       </c>
       <c r="M6" t="n">
-        <v>947.34</v>
+        <v>947.28</v>
       </c>
       <c r="N6" t="n">
-        <v>912.55</v>
+        <v>912.3</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-30.37</v>
+        <v>-31.41</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>6.27</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="7">
@@ -786,34 +786,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>65.09</v>
+        <v>64.86</v>
       </c>
       <c r="D7" t="n">
         <v>64.43000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.02</v>
+        <v>0.67</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.82</v>
+        <v>-6.15</v>
       </c>
       <c r="G7" t="n">
-        <v>-7.16</v>
+        <v>-7.49</v>
       </c>
       <c r="H7" t="n">
-        <v>9338903</v>
+        <v>8047852</v>
       </c>
       <c r="I7" t="n">
         <v>12168369</v>
       </c>
       <c r="J7" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="K7" t="n">
-        <v>0.25</v>
+        <v>1.58</v>
       </c>
       <c r="L7" t="n">
-        <v>40.7</v>
+        <v>39.8</v>
       </c>
       <c r="M7" t="n">
         <v>59.48</v>
@@ -825,13 +825,13 @@
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-10.18</v>
+        <v>-10.5</v>
       </c>
       <c r="Q7" t="n">
         <v>44.17</v>
       </c>
       <c r="R7" t="n">
-        <v>47.36</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>994.8</v>
+        <v>969.9</v>
       </c>
       <c r="D8" t="n">
         <v>991.1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.37</v>
+        <v>-2.14</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.71</v>
+        <v>-3.19</v>
       </c>
       <c r="G8" t="n">
-        <v>14.35</v>
+        <v>11.48</v>
       </c>
       <c r="H8" t="n">
-        <v>356880</v>
+        <v>264257</v>
       </c>
       <c r="I8" t="n">
         <v>314144</v>
       </c>
       <c r="J8" t="n">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="L8" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="M8" t="n">
-        <v>760.14</v>
+        <v>760.01</v>
       </c>
       <c r="N8" t="n">
-        <v>872.9400000000001</v>
+        <v>872.4400000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1001.9</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.71</v>
+        <v>-3.19</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>80.72</v>
+        <v>76.19</v>
       </c>
     </row>
     <row r="9">
@@ -913,34 +913,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="D10" t="n">
         <v>6.88</v>
       </c>
       <c r="E10" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.38</v>
+        <v>-7.25</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.609999999999999</v>
+        <v>-8.48</v>
       </c>
       <c r="H10" t="n">
-        <v>2811</v>
+        <v>3677</v>
       </c>
       <c r="I10" t="n">
         <v>2123</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="K10" t="n">
-        <v>0.68</v>
+        <v>2.02</v>
       </c>
       <c r="L10" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="M10" t="n">
         <v>8.720000000000001</v>
@@ -952,13 +952,13 @@
         <v>13.78</v>
       </c>
       <c r="P10" t="n">
-        <v>-49.93</v>
+        <v>-49.85</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>30.43</v>
+        <v>30.62</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>988.8</v>
+      </c>
+      <c r="D11" t="n">
         <v>990</v>
       </c>
-      <c r="D11" t="n">
-        <v>1002</v>
-      </c>
       <c r="E11" t="n">
-        <v>-1.2</v>
+        <v>-0.12</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.47</v>
+        <v>-2.38</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.46</v>
+        <v>-5.3</v>
       </c>
       <c r="H11" t="n">
-        <v>543348</v>
+        <v>355349</v>
       </c>
       <c r="I11" t="n">
-        <v>1046394</v>
+        <v>543434</v>
       </c>
       <c r="J11" t="n">
-        <v>0.54</v>
+        <v>0.36</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="M11" t="n">
-        <v>935.33</v>
+        <v>935.34</v>
       </c>
       <c r="N11" t="n">
-        <v>1038.12</v>
+        <v>1036.88</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-11.39</v>
+        <v>-11.49</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>45.03</v>
+        <v>44.86</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="D12" t="n">
         <v>25.15</v>
       </c>
-      <c r="D12" t="n">
-        <v>24.04</v>
-      </c>
       <c r="E12" t="n">
-        <v>4.62</v>
+        <v>0.16</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>4.05</v>
       </c>
       <c r="G12" t="n">
-        <v>13.44</v>
+        <v>12.25</v>
       </c>
       <c r="H12" t="n">
-        <v>34684845</v>
+        <v>20636745</v>
       </c>
       <c r="I12" t="n">
-        <v>13578560</v>
+        <v>34693464</v>
       </c>
       <c r="J12" t="n">
-        <v>1.14</v>
+        <v>0.65</v>
       </c>
       <c r="K12" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="M12" t="n">
-        <v>24.7</v>
+        <v>24.69</v>
       </c>
       <c r="N12" t="n">
-        <v>23</v>
+        <v>23.06</v>
       </c>
       <c r="O12" t="n">
         <v>32.31</v>
       </c>
       <c r="P12" t="n">
-        <v>-22.16</v>
+        <v>-22.04</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>17.03</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="D13" t="n">
         <v>5.9</v>
       </c>
       <c r="E13" t="n">
-        <v>1.02</v>
+        <v>-0.68</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.97</v>
+        <v>-3.62</v>
       </c>
       <c r="G13" t="n">
-        <v>12.03</v>
+        <v>10.15</v>
       </c>
       <c r="H13" t="n">
-        <v>861570</v>
+        <v>498550</v>
       </c>
       <c r="I13" t="n">
         <v>290468</v>
       </c>
       <c r="J13" t="n">
-        <v>0.71</v>
+        <v>0.41</v>
       </c>
       <c r="K13" t="n">
-        <v>0.15</v>
+        <v>1.18</v>
       </c>
       <c r="L13" t="n">
-        <v>55.4</v>
+        <v>52.9</v>
       </c>
       <c r="M13" t="n">
         <v>5.87</v>
       </c>
       <c r="N13" t="n">
-        <v>5.53</v>
+        <v>5.52</v>
       </c>
       <c r="O13" t="n">
         <v>9.41</v>
       </c>
       <c r="P13" t="n">
-        <v>-36.66</v>
+        <v>-37.73</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>42.58</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>23635.1</v>
+      </c>
+      <c r="D17" t="n">
         <v>23779.15</v>
       </c>
-      <c r="D17" t="n">
-        <v>23897.7</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.5</v>
+        <v>-0.61</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.25</v>
+        <v>-1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.22</v>
+        <v>-3.86</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.21</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>56777.55</v>
+      </c>
+      <c r="D18" t="n">
         <v>57088.3</v>
       </c>
-      <c r="D18" t="n">
-        <v>57369.65</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.49</v>
+        <v>-0.54</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.61</v>
+        <v>-1.1</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.14</v>
+        <v>-1.58</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.13</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="19">
@@ -1262,19 +1262,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>96.28</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="D19" t="n">
         <v>96.28</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="F19" t="n">
-        <v>6.4</v>
+        <v>8.56</v>
       </c>
       <c r="G19" t="n">
-        <v>15.24</v>
+        <v>17.58</v>
       </c>
       <c r="H19" t="n">
         <v>1.14</v>
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4476.6</v>
+        <v>4441.3</v>
       </c>
       <c r="D20" t="n">
         <v>4429.8</v>
       </c>
       <c r="E20" t="n">
-        <v>1.06</v>
+        <v>0.26</v>
       </c>
       <c r="F20" t="n">
-        <v>1.03</v>
+        <v>0.23</v>
       </c>
       <c r="G20" t="n">
-        <v>3.13</v>
+        <v>2.32</v>
       </c>
       <c r="H20" t="n">
         <v>1.14</v>
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>52787.17</v>
+      </c>
+      <c r="D21" t="n">
         <v>53414.25</v>
       </c>
-      <c r="D21" t="n">
-        <v>53686.11</v>
-      </c>
       <c r="E21" t="n">
-        <v>-0.51</v>
+        <v>-1.17</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.27</v>
+        <v>-0.75</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.87</v>
+        <v>-2.31</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.04</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="22">
@@ -1355,16 +1355,16 @@
         <v>11.16</v>
       </c>
       <c r="D22" t="n">
-        <v>10.68</v>
+        <v>11.16</v>
       </c>
       <c r="E22" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.27</v>
+        <v>-2.87</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.220000000000001</v>
+        <v>-8.9</v>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2175,6 +2175,29 @@
       </c>
       <c r="G34" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56777.55</v>
+      </c>
+      <c r="C35" t="n">
+        <v>57088.3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2188,7 +2211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2984,6 +3007,29 @@
         <v>15.24</v>
       </c>
       <c r="G34" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="C35" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="F35" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="G35" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -2998,7 +3044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3794,6 +3840,29 @@
         <v>3.13</v>
       </c>
       <c r="G34" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4441.3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4429.8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G35" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -3808,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4567,6 +4636,29 @@
       </c>
       <c r="G33" t="n">
         <v>-1.04</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B34" t="n">
+        <v>52787.17</v>
+      </c>
+      <c r="C34" t="n">
+        <v>53414.25</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-3.05</v>
       </c>
     </row>
   </sheetData>
@@ -4580,7 +4672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5296,6 +5388,26 @@
       </c>
       <c r="F34" t="n">
         <v>-8.220000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-8.9</v>
       </c>
     </row>
   </sheetData>
@@ -5309,7 +5421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7012,6 +7124,59 @@
       </c>
       <c r="Q33" t="n">
         <v>30.43</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B34" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="C34" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-8.48</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3677</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2123</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="K34" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="M34" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="N34" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-49.85</v>
+      </c>
+      <c r="P34" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>30.62</v>
       </c>
     </row>
   </sheetData>
@@ -7025,7 +7190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8728,6 +8893,59 @@
       </c>
       <c r="Q33" t="n">
         <v>17.03</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B34" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="C34" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F34" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20636745</v>
+      </c>
+      <c r="H34" t="n">
+        <v>34693464</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="M34" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="N34" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-22.04</v>
+      </c>
+      <c r="P34" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>17.22</v>
       </c>
     </row>
   </sheetData>
@@ -8741,7 +8959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10338,6 +10556,59 @@
       </c>
       <c r="Q31" t="n">
         <v>64.22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B32" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="C32" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4494405</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4949017</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K32" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="M32" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="N32" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>65.20999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10351,7 +10622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12107,6 +12378,59 @@
       </c>
       <c r="Q34" t="n">
         <v>91.65000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>460.6</v>
+      </c>
+      <c r="C35" t="n">
+        <v>487.9</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="F35" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1015754</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1789647</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="K35" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="L35" t="n">
+        <v>344.49</v>
+      </c>
+      <c r="M35" t="n">
+        <v>421.77</v>
+      </c>
+      <c r="N35" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-15.38</v>
+      </c>
+      <c r="P35" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>91.45999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12120,7 +12444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13875,6 +14199,59 @@
         <v>255.5</v>
       </c>
       <c r="Q34" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-6.78</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7404037</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6688002</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>306.06</v>
+      </c>
+      <c r="M35" t="n">
+        <v>277.7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-34.45</v>
+      </c>
+      <c r="P35" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3.13</v>
       </c>
     </row>
@@ -13889,7 +14266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15645,6 +16022,59 @@
       </c>
       <c r="Q34" t="n">
         <v>6.27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>825.75</v>
+      </c>
+      <c r="C35" t="n">
+        <v>828.65</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-9.76</v>
+      </c>
+      <c r="G35" t="n">
+        <v>301905</v>
+      </c>
+      <c r="H35" t="n">
+        <v>445370</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="K35" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="L35" t="n">
+        <v>947.28</v>
+      </c>
+      <c r="M35" t="n">
+        <v>912.3</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-31.41</v>
+      </c>
+      <c r="P35" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.68</v>
       </c>
     </row>
   </sheetData>
@@ -15658,7 +16088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17414,6 +17844,59 @@
       </c>
       <c r="Q34" t="n">
         <v>45.03</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>988.8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>990</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>355349</v>
+      </c>
+      <c r="H35" t="n">
+        <v>543434</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="L35" t="n">
+        <v>935.34</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1036.88</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-11.49</v>
+      </c>
+      <c r="P35" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>44.86</v>
       </c>
     </row>
   </sheetData>
@@ -17427,7 +17910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19183,6 +19666,59 @@
       </c>
       <c r="Q34" t="n">
         <v>47.36</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>64.86</v>
+      </c>
+      <c r="C35" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-6.15</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8047852</v>
+      </c>
+      <c r="H35" t="n">
+        <v>12168369</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K35" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="M35" t="n">
+        <v>67.47</v>
+      </c>
+      <c r="N35" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>46.84</v>
       </c>
     </row>
   </sheetData>
@@ -19196,7 +19732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20952,6 +21488,59 @@
       </c>
       <c r="Q34" t="n">
         <v>42.58</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-3.62</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="G35" t="n">
+        <v>498550</v>
+      </c>
+      <c r="H35" t="n">
+        <v>290468</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="K35" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="M35" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="N35" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-37.73</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>40.19</v>
       </c>
     </row>
   </sheetData>
@@ -20965,7 +21554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22721,6 +23310,59 @@
       </c>
       <c r="Q34" t="n">
         <v>80.72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>969.9</v>
+      </c>
+      <c r="C35" t="n">
+        <v>991.1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="F35" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="G35" t="n">
+        <v>264257</v>
+      </c>
+      <c r="H35" t="n">
+        <v>314144</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K35" t="n">
+        <v>63</v>
+      </c>
+      <c r="L35" t="n">
+        <v>760.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>872.4400000000001</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="P35" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>76.19</v>
       </c>
     </row>
   </sheetData>
@@ -22734,7 +23376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23533,6 +24175,29 @@
         <v>-0.21</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>23635.1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>23779.15</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>456.5</v>
+      </c>
+      <c r="D3" t="n">
         <v>460.6</v>
       </c>
-      <c r="D3" t="n">
-        <v>487.9</v>
-      </c>
       <c r="E3" t="n">
-        <v>-5.6</v>
+        <v>-0.89</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.61</v>
+        <v>-15.84</v>
       </c>
       <c r="G3" t="n">
-        <v>14.61</v>
+        <v>7.96</v>
       </c>
       <c r="H3" t="n">
-        <v>1015754</v>
+        <v>426014</v>
       </c>
       <c r="I3" t="n">
-        <v>1789647</v>
+        <v>1016331</v>
       </c>
       <c r="J3" t="n">
-        <v>0.74</v>
+        <v>0.31</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.710000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="L3" t="n">
-        <v>50.3</v>
+        <v>49.4</v>
       </c>
       <c r="M3" t="n">
-        <v>344.49</v>
+        <v>344.98</v>
       </c>
       <c r="N3" t="n">
-        <v>421.77</v>
+        <v>423.56</v>
       </c>
       <c r="O3" t="n">
         <v>544.3</v>
       </c>
       <c r="P3" t="n">
-        <v>-15.38</v>
+        <v>-16.13</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>91.45999999999999</v>
+        <v>89.76000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="D4" t="n">
         <v>46.82</v>
       </c>
-      <c r="D4" t="n">
-        <v>46.54</v>
-      </c>
       <c r="E4" t="n">
-        <v>0.6</v>
+        <v>-0.88</v>
       </c>
       <c r="F4" t="n">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78</v>
+        <v>2.31</v>
       </c>
       <c r="H4" t="n">
-        <v>4494405</v>
+        <v>8184904</v>
       </c>
       <c r="I4" t="n">
-        <v>4949017</v>
+        <v>4494492</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>0.43</v>
+        <v>-2.25</v>
       </c>
       <c r="L4" t="n">
-        <v>56.2</v>
+        <v>52.9</v>
       </c>
       <c r="M4" t="n">
-        <v>41.64</v>
+        <v>41.69</v>
       </c>
       <c r="N4" t="n">
-        <v>45.85</v>
+        <v>45.88</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.5</v>
+        <v>-3.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>28.34</v>
+        <v>28.35</v>
       </c>
       <c r="R4" t="n">
-        <v>65.20999999999999</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>263.5</v>
+        <v>260.8</v>
       </c>
       <c r="D5" t="n">
         <v>263.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.16</v>
+        <v>-2.07</v>
       </c>
       <c r="G5" t="n">
-        <v>-6.78</v>
+        <v>-6.52</v>
       </c>
       <c r="H5" t="n">
-        <v>7404037</v>
+        <v>10059662</v>
       </c>
       <c r="I5" t="n">
-        <v>6688002</v>
+        <v>7406617</v>
       </c>
       <c r="J5" t="n">
-        <v>0.53</v>
+        <v>0.74</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="L5" t="n">
-        <v>39.4</v>
+        <v>36.5</v>
       </c>
       <c r="M5" t="n">
-        <v>306.06</v>
+        <v>305.44</v>
       </c>
       <c r="N5" t="n">
-        <v>277.7</v>
+        <v>277.11</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-34.45</v>
+        <v>-35.12</v>
       </c>
       <c r="Q5" t="n">
         <v>255.5</v>
       </c>
       <c r="R5" t="n">
-        <v>3.13</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>826.3</v>
+      </c>
+      <c r="D6" t="n">
         <v>825.75</v>
       </c>
-      <c r="D6" t="n">
-        <v>828.65</v>
-      </c>
       <c r="E6" t="n">
-        <v>-0.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.87</v>
+        <v>-2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>-9.76</v>
+        <v>-9.09</v>
       </c>
       <c r="H6" t="n">
-        <v>301905</v>
+        <v>537043</v>
       </c>
       <c r="I6" t="n">
-        <v>445370</v>
+        <v>302502</v>
       </c>
       <c r="J6" t="n">
-        <v>0.59</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
-        <v>3.01</v>
+        <v>0.58</v>
       </c>
       <c r="L6" t="n">
-        <v>28.6</v>
+        <v>28.9</v>
       </c>
       <c r="M6" t="n">
-        <v>947.28</v>
+        <v>947.1</v>
       </c>
       <c r="N6" t="n">
-        <v>912.3</v>
+        <v>910.23</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-31.41</v>
+        <v>-31.37</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>4.68</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="D7" t="n">
         <v>64.86</v>
       </c>
-      <c r="D7" t="n">
-        <v>64.43000000000001</v>
-      </c>
       <c r="E7" t="n">
-        <v>0.67</v>
+        <v>-1.14</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.15</v>
+        <v>-1.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-7.49</v>
+        <v>-8.08</v>
       </c>
       <c r="H7" t="n">
-        <v>8047852</v>
+        <v>14563255</v>
       </c>
       <c r="I7" t="n">
-        <v>12168369</v>
+        <v>8048113</v>
       </c>
       <c r="J7" t="n">
-        <v>0.54</v>
+        <v>0.97</v>
       </c>
       <c r="K7" t="n">
-        <v>1.58</v>
+        <v>-1.85</v>
       </c>
       <c r="L7" t="n">
-        <v>39.8</v>
+        <v>37.8</v>
       </c>
       <c r="M7" t="n">
-        <v>59.48</v>
+        <v>59.53</v>
       </c>
       <c r="N7" t="n">
-        <v>67.47</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-10.5</v>
+        <v>-11.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>44.17</v>
+        <v>44.18</v>
       </c>
       <c r="R7" t="n">
-        <v>46.84</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>989.7</v>
+      </c>
+      <c r="D8" t="n">
         <v>969.9</v>
       </c>
-      <c r="D8" t="n">
-        <v>991.1</v>
-      </c>
       <c r="E8" t="n">
-        <v>-2.14</v>
+        <v>2.04</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.19</v>
+        <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>11.48</v>
+        <v>10.18</v>
       </c>
       <c r="H8" t="n">
-        <v>264257</v>
+        <v>233379</v>
       </c>
       <c r="I8" t="n">
-        <v>314144</v>
+        <v>264267</v>
       </c>
       <c r="J8" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="K8" t="n">
-        <v>0.77</v>
+        <v>0.23</v>
       </c>
       <c r="L8" t="n">
-        <v>63</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>760.01</v>
+        <v>761.17</v>
       </c>
       <c r="N8" t="n">
-        <v>872.4400000000001</v>
+        <v>875.0700000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1001.9</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.19</v>
+        <v>-1.22</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>76.19</v>
+        <v>79.79000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="D10" t="n">
         <v>6.91</v>
       </c>
-      <c r="D10" t="n">
-        <v>6.88</v>
-      </c>
       <c r="E10" t="n">
-        <v>0.44</v>
+        <v>-2.89</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.25</v>
+        <v>-5.23</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.48</v>
+        <v>-15.28</v>
       </c>
       <c r="H10" t="n">
+        <v>6879</v>
+      </c>
+      <c r="I10" t="n">
         <v>3677</v>
       </c>
-      <c r="I10" t="n">
-        <v>2123</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.66</v>
+        <v>1.29</v>
       </c>
       <c r="K10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>42.4</v>
+        <v>39.2</v>
       </c>
       <c r="M10" t="n">
-        <v>8.720000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>7.03</v>
+        <v>7.04</v>
       </c>
       <c r="O10" t="n">
         <v>13.78</v>
       </c>
       <c r="P10" t="n">
-        <v>-49.85</v>
+        <v>-51.31</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>30.62</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>975.9</v>
+      </c>
+      <c r="D11" t="n">
         <v>988.8</v>
       </c>
-      <c r="D11" t="n">
-        <v>990</v>
-      </c>
       <c r="E11" t="n">
-        <v>-0.12</v>
+        <v>-1.3</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.38</v>
+        <v>-2.41</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.3</v>
+        <v>-7.06</v>
       </c>
       <c r="H11" t="n">
-        <v>355349</v>
+        <v>583259</v>
       </c>
       <c r="I11" t="n">
-        <v>543434</v>
+        <v>355380</v>
       </c>
       <c r="J11" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="L11" t="n">
-        <v>41.3</v>
+        <v>38.4</v>
       </c>
       <c r="M11" t="n">
-        <v>935.34</v>
+        <v>935.27</v>
       </c>
       <c r="N11" t="n">
-        <v>1036.88</v>
+        <v>1035.37</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-11.49</v>
+        <v>-12.65</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>44.86</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="D12" t="n">
         <v>25.19</v>
       </c>
-      <c r="D12" t="n">
-        <v>25.15</v>
-      </c>
       <c r="E12" t="n">
-        <v>0.16</v>
+        <v>-3.33</v>
       </c>
       <c r="F12" t="n">
-        <v>4.05</v>
+        <v>1.71</v>
       </c>
       <c r="G12" t="n">
-        <v>12.25</v>
+        <v>9.73</v>
       </c>
       <c r="H12" t="n">
-        <v>20636745</v>
+        <v>15111655</v>
       </c>
       <c r="I12" t="n">
-        <v>34693464</v>
+        <v>20638935</v>
       </c>
       <c r="J12" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="L12" t="n">
-        <v>60.2</v>
+        <v>53.4</v>
       </c>
       <c r="M12" t="n">
-        <v>24.69</v>
+        <v>24.67</v>
       </c>
       <c r="N12" t="n">
-        <v>23.06</v>
+        <v>23.09</v>
       </c>
       <c r="O12" t="n">
         <v>32.31</v>
       </c>
       <c r="P12" t="n">
-        <v>-22.04</v>
+        <v>-24.64</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>17.22</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.86</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.9</v>
-      </c>
       <c r="E13" t="n">
-        <v>-0.68</v>
+        <v>-3.41</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.62</v>
+        <v>-4.71</v>
       </c>
       <c r="G13" t="n">
-        <v>10.15</v>
+        <v>4.81</v>
       </c>
       <c r="H13" t="n">
+        <v>406089</v>
+      </c>
+      <c r="I13" t="n">
         <v>498550</v>
       </c>
-      <c r="I13" t="n">
-        <v>290468</v>
-      </c>
       <c r="J13" t="n">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
       <c r="K13" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="L13" t="n">
-        <v>52.9</v>
+        <v>47.6</v>
       </c>
       <c r="M13" t="n">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
       <c r="N13" t="n">
-        <v>5.52</v>
+        <v>5.53</v>
       </c>
       <c r="O13" t="n">
         <v>9.41</v>
       </c>
       <c r="P13" t="n">
-        <v>-37.73</v>
+        <v>-39.85</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>40.19</v>
+        <v>35.41</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>23431.5</v>
+      </c>
+      <c r="D17" t="n">
         <v>23635.1</v>
       </c>
-      <c r="D17" t="n">
-        <v>23779.15</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.61</v>
+        <v>-0.86</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.75</v>
+        <v>-2.02</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.86</v>
+        <v>-4.25</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.53</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>56295.55</v>
+      </c>
+      <c r="D18" t="n">
         <v>56777.55</v>
       </c>
-      <c r="D18" t="n">
-        <v>57088.3</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.54</v>
+        <v>-0.85</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1</v>
+        <v>-1.53</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.58</v>
+        <v>-2</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>98.23999999999999</v>
+        <v>101.11</v>
       </c>
       <c r="D19" t="n">
-        <v>96.28</v>
+        <v>97.92</v>
       </c>
       <c r="E19" t="n">
-        <v>2.04</v>
+        <v>3.26</v>
       </c>
       <c r="F19" t="n">
-        <v>8.56</v>
+        <v>6.83</v>
       </c>
       <c r="G19" t="n">
-        <v>17.58</v>
+        <v>15.26</v>
       </c>
       <c r="H19" t="n">
-        <v>1.14</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4441.3</v>
+        <v>4466.2</v>
       </c>
       <c r="D20" t="n">
-        <v>4429.8</v>
+        <v>4393.9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.26</v>
+        <v>1.65</v>
       </c>
       <c r="F20" t="n">
-        <v>0.23</v>
+        <v>2.72</v>
       </c>
       <c r="G20" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="H20" t="n">
-        <v>1.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52787.17</v>
+        <v>52475.56</v>
       </c>
       <c r="D21" t="n">
-        <v>53414.25</v>
+        <v>52786.07</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.17</v>
+        <v>-0.59</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.75</v>
+        <v>-0.55</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.31</v>
+        <v>-2.78</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.05</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11.16</v>
+        <v>11.92</v>
       </c>
       <c r="D22" t="n">
-        <v>11.16</v>
+        <v>11.23</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.87</v>
+        <v>2.85</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.9</v>
+        <v>0.51</v>
+      </c>
+      <c r="H22" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2198,6 +2201,29 @@
       </c>
       <c r="G35" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56295.55</v>
+      </c>
+      <c r="C36" t="n">
+        <v>56777.55</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-1.44</v>
       </c>
     </row>
   </sheetData>
@@ -2211,7 +2237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3031,6 +3057,29 @@
       </c>
       <c r="G35" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="C36" t="n">
+        <v>97.92</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="F36" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>
@@ -3044,7 +3093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3864,6 +3913,29 @@
       </c>
       <c r="G35" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4466.2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4393.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -3877,7 +3949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4659,6 +4731,29 @@
       </c>
       <c r="G34" t="n">
         <v>-3.05</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B35" t="n">
+        <v>52475.56</v>
+      </c>
+      <c r="C35" t="n">
+        <v>52786.07</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -4672,7 +4767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5408,6 +5503,29 @@
       </c>
       <c r="F35" t="n">
         <v>-8.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="C36" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G36" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -5421,7 +5539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7177,6 +7295,59 @@
       </c>
       <c r="Q34" t="n">
         <v>30.62</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B35" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="C35" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-5.23</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-15.28</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6879</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3677</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M35" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="N35" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-51.31</v>
+      </c>
+      <c r="P35" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>26.84</v>
       </c>
     </row>
   </sheetData>
@@ -7190,7 +7361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8946,6 +9117,59 @@
       </c>
       <c r="Q34" t="n">
         <v>17.22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B35" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="C35" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F35" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="G35" t="n">
+        <v>15111655</v>
+      </c>
+      <c r="H35" t="n">
+        <v>20638935</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="M35" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="N35" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-24.64</v>
+      </c>
+      <c r="P35" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>13.31</v>
       </c>
     </row>
   </sheetData>
@@ -8959,7 +9183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10609,6 +10833,59 @@
       </c>
       <c r="Q32" t="n">
         <v>65.20999999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B33" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="C33" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8184904</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4494492</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="K33" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="L33" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="M33" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="N33" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="P33" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>63.7</v>
       </c>
     </row>
   </sheetData>
@@ -10622,7 +10899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12431,6 +12708,59 @@
       </c>
       <c r="Q35" t="n">
         <v>91.45999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>456.5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>460.6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-15.84</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="G36" t="n">
+        <v>426014</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1016331</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K36" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>344.98</v>
+      </c>
+      <c r="M36" t="n">
+        <v>423.56</v>
+      </c>
+      <c r="N36" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-16.13</v>
+      </c>
+      <c r="P36" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>89.76000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -12444,7 +12774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14253,6 +14583,59 @@
       </c>
       <c r="Q35" t="n">
         <v>3.13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>260.8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10059662</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7406617</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K36" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>305.44</v>
+      </c>
+      <c r="M36" t="n">
+        <v>277.11</v>
+      </c>
+      <c r="N36" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-35.12</v>
+      </c>
+      <c r="P36" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.07</v>
       </c>
     </row>
   </sheetData>
@@ -14266,7 +14649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16075,6 +16458,59 @@
       </c>
       <c r="Q35" t="n">
         <v>4.68</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>826.3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>825.75</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-9.09</v>
+      </c>
+      <c r="G36" t="n">
+        <v>537043</v>
+      </c>
+      <c r="H36" t="n">
+        <v>302502</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K36" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="L36" t="n">
+        <v>947.1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>910.23</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-31.37</v>
+      </c>
+      <c r="P36" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.75</v>
       </c>
     </row>
   </sheetData>
@@ -16088,7 +16524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17897,6 +18333,59 @@
       </c>
       <c r="Q35" t="n">
         <v>44.86</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>975.9</v>
+      </c>
+      <c r="C36" t="n">
+        <v>988.8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-7.06</v>
+      </c>
+      <c r="G36" t="n">
+        <v>583259</v>
+      </c>
+      <c r="H36" t="n">
+        <v>355380</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K36" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>935.27</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1035.37</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-12.65</v>
+      </c>
+      <c r="P36" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>42.97</v>
       </c>
     </row>
   </sheetData>
@@ -17910,7 +18399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19719,6 +20208,59 @@
       </c>
       <c r="Q35" t="n">
         <v>46.84</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="C36" t="n">
+        <v>64.86</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-8.08</v>
+      </c>
+      <c r="G36" t="n">
+        <v>14563255</v>
+      </c>
+      <c r="H36" t="n">
+        <v>8048113</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="K36" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="L36" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="M36" t="n">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="N36" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-11.52</v>
+      </c>
+      <c r="P36" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>45.13</v>
       </c>
     </row>
   </sheetData>
@@ -19732,7 +20274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21541,6 +22083,59 @@
       </c>
       <c r="Q35" t="n">
         <v>40.19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="C36" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="G36" t="n">
+        <v>406089</v>
+      </c>
+      <c r="H36" t="n">
+        <v>498550</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K36" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="N36" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-39.85</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>35.41</v>
       </c>
     </row>
   </sheetData>
@@ -21554,7 +22149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23363,6 +23958,59 @@
       </c>
       <c r="Q35" t="n">
         <v>76.19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>989.7</v>
+      </c>
+      <c r="C36" t="n">
+        <v>969.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="G36" t="n">
+        <v>233379</v>
+      </c>
+      <c r="H36" t="n">
+        <v>264267</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K36" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="L36" t="n">
+        <v>761.17</v>
+      </c>
+      <c r="M36" t="n">
+        <v>875.0700000000001</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="P36" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>79.79000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23376,7 +24024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24198,6 +24846,29 @@
         <v>-0.53</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>23431.5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>23635.1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-1.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>454.65</v>
+      </c>
+      <c r="D3" t="n">
         <v>456.5</v>
       </c>
-      <c r="D3" t="n">
-        <v>460.6</v>
-      </c>
       <c r="E3" t="n">
-        <v>-0.89</v>
+        <v>-0.41</v>
       </c>
       <c r="F3" t="n">
-        <v>-15.84</v>
+        <v>-15.11</v>
       </c>
       <c r="G3" t="n">
-        <v>7.96</v>
+        <v>3.05</v>
       </c>
       <c r="H3" t="n">
-        <v>426014</v>
+        <v>856335</v>
       </c>
       <c r="I3" t="n">
-        <v>1016331</v>
+        <v>426020</v>
       </c>
       <c r="J3" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="L3" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="M3" t="n">
-        <v>344.98</v>
+        <v>345.53</v>
       </c>
       <c r="N3" t="n">
-        <v>423.56</v>
+        <v>425.37</v>
       </c>
       <c r="O3" t="n">
         <v>544.3</v>
       </c>
       <c r="P3" t="n">
-        <v>-16.13</v>
+        <v>-16.47</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>89.76000000000001</v>
+        <v>88.98999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="D4" t="n">
         <v>46.41</v>
       </c>
-      <c r="D4" t="n">
-        <v>46.82</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.88</v>
+        <v>-0.71</v>
       </c>
       <c r="F4" t="n">
-        <v>1.46</v>
+        <v>-3.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.31</v>
+        <v>0.68</v>
       </c>
       <c r="H4" t="n">
-        <v>8184904</v>
+        <v>5590539</v>
       </c>
       <c r="I4" t="n">
-        <v>4494492</v>
+        <v>8187411</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.25</v>
+        <v>0.42</v>
       </c>
       <c r="L4" t="n">
-        <v>52.9</v>
+        <v>50.3</v>
       </c>
       <c r="M4" t="n">
-        <v>41.69</v>
+        <v>41.73</v>
       </c>
       <c r="N4" t="n">
-        <v>45.88</v>
+        <v>45.9</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.35</v>
+        <v>-4.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>28.35</v>
+        <v>28.36</v>
       </c>
       <c r="R4" t="n">
-        <v>63.7</v>
+        <v>62.48</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>259.3</v>
+      </c>
+      <c r="D5" t="n">
         <v>260.8</v>
       </c>
-      <c r="D5" t="n">
-        <v>263.5</v>
-      </c>
       <c r="E5" t="n">
-        <v>-1.02</v>
+        <v>-0.58</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.07</v>
+        <v>-1.41</v>
       </c>
       <c r="G5" t="n">
-        <v>-6.52</v>
+        <v>-6.1</v>
       </c>
       <c r="H5" t="n">
-        <v>10059662</v>
+        <v>17444123</v>
       </c>
       <c r="I5" t="n">
-        <v>7406617</v>
+        <v>10065188</v>
       </c>
       <c r="J5" t="n">
-        <v>0.74</v>
+        <v>1.29</v>
       </c>
       <c r="K5" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="L5" t="n">
-        <v>36.5</v>
+        <v>35</v>
       </c>
       <c r="M5" t="n">
-        <v>305.44</v>
+        <v>304.83</v>
       </c>
       <c r="N5" t="n">
-        <v>277.11</v>
+        <v>276.5</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-35.12</v>
+        <v>-35.5</v>
       </c>
       <c r="Q5" t="n">
         <v>255.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2.07</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>818.65</v>
+      </c>
+      <c r="D6" t="n">
         <v>826.3</v>
       </c>
-      <c r="D6" t="n">
-        <v>825.75</v>
-      </c>
       <c r="E6" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.93</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.7</v>
+        <v>-2.92</v>
       </c>
       <c r="G6" t="n">
-        <v>-9.09</v>
+        <v>-9.59</v>
       </c>
       <c r="H6" t="n">
-        <v>537043</v>
+        <v>236459</v>
       </c>
       <c r="I6" t="n">
-        <v>302502</v>
+        <v>537495</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>0.45</v>
       </c>
       <c r="K6" t="n">
-        <v>0.58</v>
+        <v>-0.2</v>
       </c>
       <c r="L6" t="n">
-        <v>28.9</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>947.1</v>
+        <v>947</v>
       </c>
       <c r="N6" t="n">
-        <v>910.23</v>
+        <v>908.11</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-31.37</v>
+        <v>-32</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>4.75</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>66.52</v>
+      </c>
+      <c r="D7" t="n">
         <v>64.12</v>
       </c>
-      <c r="D7" t="n">
-        <v>64.86</v>
-      </c>
       <c r="E7" t="n">
-        <v>-1.14</v>
+        <v>3.74</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9</v>
+        <v>4.53</v>
       </c>
       <c r="G7" t="n">
-        <v>-8.08</v>
+        <v>-5.16</v>
       </c>
       <c r="H7" t="n">
-        <v>14563255</v>
+        <v>14339495</v>
       </c>
       <c r="I7" t="n">
-        <v>8048113</v>
+        <v>14563305</v>
       </c>
       <c r="J7" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.85</v>
+        <v>2.2</v>
       </c>
       <c r="L7" t="n">
-        <v>37.8</v>
+        <v>47.1</v>
       </c>
       <c r="M7" t="n">
-        <v>59.53</v>
+        <v>59.59</v>
       </c>
       <c r="N7" t="n">
-        <v>67.56999999999999</v>
+        <v>67.67</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-11.52</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="Q7" t="n">
         <v>44.18</v>
       </c>
       <c r="R7" t="n">
-        <v>45.13</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>977.2</v>
+      </c>
+      <c r="D8" t="n">
         <v>989.7</v>
       </c>
-      <c r="D8" t="n">
-        <v>969.9</v>
-      </c>
       <c r="E8" t="n">
-        <v>2.04</v>
+        <v>-1.26</v>
       </c>
       <c r="F8" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="G8" t="n">
-        <v>10.18</v>
+        <v>12.95</v>
       </c>
       <c r="H8" t="n">
-        <v>233379</v>
+        <v>249885</v>
       </c>
       <c r="I8" t="n">
-        <v>264267</v>
+        <v>233441</v>
       </c>
       <c r="J8" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="K8" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>66.09999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="M8" t="n">
-        <v>761.17</v>
+        <v>762.14</v>
       </c>
       <c r="N8" t="n">
-        <v>875.0700000000001</v>
+        <v>877.49</v>
       </c>
       <c r="O8" t="n">
         <v>1001.9</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.22</v>
+        <v>-2.47</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>79.79000000000001</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="9">
@@ -913,52 +913,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="D10" t="n">
         <v>6.71</v>
       </c>
-      <c r="D10" t="n">
-        <v>6.91</v>
-      </c>
       <c r="E10" t="n">
-        <v>-2.89</v>
+        <v>0.15</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.23</v>
+        <v>-2.61</v>
       </c>
       <c r="G10" t="n">
-        <v>-15.28</v>
+        <v>-19.04</v>
       </c>
       <c r="H10" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I10" t="n">
         <v>6879</v>
       </c>
-      <c r="I10" t="n">
-        <v>3677</v>
-      </c>
       <c r="J10" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="L10" t="n">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
       <c r="M10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="N10" t="n">
-        <v>7.04</v>
+        <v>7.06</v>
       </c>
       <c r="O10" t="n">
         <v>13.78</v>
       </c>
       <c r="P10" t="n">
-        <v>-51.31</v>
+        <v>-51.23</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>26.84</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>967.9</v>
+      </c>
+      <c r="D11" t="n">
         <v>975.9</v>
       </c>
-      <c r="D11" t="n">
-        <v>988.8</v>
-      </c>
       <c r="E11" t="n">
-        <v>-1.3</v>
+        <v>-0.82</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.41</v>
+        <v>-3.98</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.06</v>
+        <v>-5.67</v>
       </c>
       <c r="H11" t="n">
-        <v>583259</v>
+        <v>992962</v>
       </c>
       <c r="I11" t="n">
-        <v>355380</v>
+        <v>583491</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
       <c r="L11" t="n">
-        <v>38.4</v>
+        <v>36.7</v>
       </c>
       <c r="M11" t="n">
-        <v>935.27</v>
+        <v>935.28</v>
       </c>
       <c r="N11" t="n">
-        <v>1035.37</v>
+        <v>1033.72</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-12.65</v>
+        <v>-13.36</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>42.97</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="D12" t="n">
         <v>24.35</v>
       </c>
-      <c r="D12" t="n">
-        <v>25.19</v>
-      </c>
       <c r="E12" t="n">
-        <v>-3.33</v>
+        <v>1.93</v>
       </c>
       <c r="F12" t="n">
-        <v>1.71</v>
+        <v>2.27</v>
       </c>
       <c r="G12" t="n">
-        <v>9.73</v>
+        <v>12.87</v>
       </c>
       <c r="H12" t="n">
-        <v>15111655</v>
+        <v>18009206</v>
       </c>
       <c r="I12" t="n">
-        <v>20638935</v>
+        <v>15123230</v>
       </c>
       <c r="J12" t="n">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>53.4</v>
+        <v>56.4</v>
       </c>
       <c r="M12" t="n">
-        <v>24.67</v>
+        <v>24.66</v>
       </c>
       <c r="N12" t="n">
-        <v>23.09</v>
+        <v>23.12</v>
       </c>
       <c r="O12" t="n">
         <v>32.31</v>
       </c>
       <c r="P12" t="n">
-        <v>-24.64</v>
+        <v>-23.18</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>13.31</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="13">
@@ -1093,34 +1093,34 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.66</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.86</v>
-      </c>
       <c r="E13" t="n">
-        <v>-3.41</v>
+        <v>-0.71</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.71</v>
+        <v>-4.26</v>
       </c>
       <c r="G13" t="n">
-        <v>4.81</v>
+        <v>4.27</v>
       </c>
       <c r="H13" t="n">
-        <v>406089</v>
+        <v>337896</v>
       </c>
       <c r="I13" t="n">
-        <v>498550</v>
+        <v>406094</v>
       </c>
       <c r="J13" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="K13" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="L13" t="n">
-        <v>47.6</v>
+        <v>46.5</v>
       </c>
       <c r="M13" t="n">
         <v>5.86</v>
@@ -1129,16 +1129,16 @@
         <v>5.53</v>
       </c>
       <c r="O13" t="n">
-        <v>9.41</v>
+        <v>9.33</v>
       </c>
       <c r="P13" t="n">
-        <v>-39.85</v>
+        <v>-39.76</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>35.41</v>
+        <v>34.45</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>23477.8</v>
+      </c>
+      <c r="D17" t="n">
         <v>23431.5</v>
       </c>
-      <c r="D17" t="n">
-        <v>23635.1</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.86</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.02</v>
+        <v>-1.66</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.25</v>
+        <v>-3.92</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.66</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>56471.95</v>
+      </c>
+      <c r="D18" t="n">
         <v>56295.55</v>
       </c>
-      <c r="D18" t="n">
-        <v>56777.55</v>
-      </c>
       <c r="E18" t="n">
-        <v>-0.85</v>
+        <v>0.31</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.53</v>
+        <v>-1.58</v>
       </c>
       <c r="G18" t="n">
-        <v>-2</v>
+        <v>-2.44</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.44</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>101.11</v>
+        <v>104.78</v>
       </c>
       <c r="D19" t="n">
-        <v>97.92</v>
+        <v>101.21</v>
       </c>
       <c r="E19" t="n">
-        <v>3.26</v>
+        <v>3.53</v>
       </c>
       <c r="F19" t="n">
-        <v>6.83</v>
+        <v>9.57</v>
       </c>
       <c r="G19" t="n">
-        <v>15.26</v>
+        <v>17.85</v>
       </c>
       <c r="H19" t="n">
-        <v>2.78</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4466.2</v>
+        <v>4405</v>
       </c>
       <c r="D20" t="n">
-        <v>4393.9</v>
+        <v>4416</v>
       </c>
       <c r="E20" t="n">
-        <v>1.65</v>
+        <v>-0.25</v>
       </c>
       <c r="F20" t="n">
-        <v>2.72</v>
+        <v>0.89</v>
       </c>
       <c r="G20" t="n">
-        <v>2.39</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
-        <v>0.16</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52475.56</v>
+        <v>52163.78</v>
       </c>
       <c r="D21" t="n">
-        <v>52786.07</v>
+        <v>52380.66</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.59</v>
+        <v>-0.41</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.55</v>
+        <v>-1.69</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.78</v>
+        <v>-3.03</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.65</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.92</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.23</v>
-      </c>
       <c r="E22" t="n">
-        <v>6.14</v>
+        <v>-1.01</v>
       </c>
       <c r="F22" t="n">
-        <v>2.85</v>
+        <v>4.06</v>
       </c>
       <c r="G22" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H22" t="n">
-        <v/>
+        <v>0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2224,6 +2221,29 @@
       </c>
       <c r="G36" t="n">
         <v>-1.44</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56471.95</v>
+      </c>
+      <c r="C37" t="n">
+        <v>56295.55</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.16</v>
       </c>
     </row>
   </sheetData>
@@ -2237,7 +2257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3080,6 +3100,29 @@
       </c>
       <c r="G36" t="n">
         <v>2.78</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>104.78</v>
+      </c>
+      <c r="C37" t="n">
+        <v>101.21</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="F37" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -3093,7 +3136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3936,6 +3979,29 @@
       </c>
       <c r="G36" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4405</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4416</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>
@@ -3949,7 +4015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4754,6 +4820,29 @@
       </c>
       <c r="G35" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B36" t="n">
+        <v>52163.78</v>
+      </c>
+      <c r="C36" t="n">
+        <v>52380.66</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -4767,7 +4856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5524,8 +5613,25 @@
       <c r="F36" t="n">
         <v>0.51</v>
       </c>
-      <c r="G36" t="n">
-        <v/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5539,7 +5645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7348,6 +7454,59 @@
       </c>
       <c r="Q35" t="n">
         <v>26.84</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B36" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="C36" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-19.04</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5700</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6879</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K36" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="N36" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-51.23</v>
+      </c>
+      <c r="P36" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>27.03</v>
       </c>
     </row>
   </sheetData>
@@ -7361,7 +7520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9170,6 +9329,59 @@
       </c>
       <c r="Q35" t="n">
         <v>13.31</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B36" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="C36" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F36" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="G36" t="n">
+        <v>18009206</v>
+      </c>
+      <c r="H36" t="n">
+        <v>15123230</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="M36" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="N36" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-23.18</v>
+      </c>
+      <c r="P36" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>15.5</v>
       </c>
     </row>
   </sheetData>
@@ -9183,7 +9395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10886,6 +11098,59 @@
       </c>
       <c r="Q33" t="n">
         <v>63.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B34" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="C34" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5590539</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8187411</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K34" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="M34" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="N34" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="P34" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>62.48</v>
       </c>
     </row>
   </sheetData>
@@ -10899,7 +11164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12761,6 +13026,59 @@
       </c>
       <c r="Q36" t="n">
         <v>89.76000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>454.65</v>
+      </c>
+      <c r="C37" t="n">
+        <v>456.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-15.11</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G37" t="n">
+        <v>856335</v>
+      </c>
+      <c r="H37" t="n">
+        <v>426020</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>49</v>
+      </c>
+      <c r="L37" t="n">
+        <v>345.53</v>
+      </c>
+      <c r="M37" t="n">
+        <v>425.37</v>
+      </c>
+      <c r="N37" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-16.47</v>
+      </c>
+      <c r="P37" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>88.98999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -12774,7 +13092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14636,6 +14954,59 @@
       </c>
       <c r="Q36" t="n">
         <v>2.07</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>259.3</v>
+      </c>
+      <c r="C37" t="n">
+        <v>260.8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>17444123</v>
+      </c>
+      <c r="H37" t="n">
+        <v>10065188</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K37" t="n">
+        <v>35</v>
+      </c>
+      <c r="L37" t="n">
+        <v>304.83</v>
+      </c>
+      <c r="M37" t="n">
+        <v>276.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>
@@ -14649,7 +15020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16511,6 +16882,59 @@
       </c>
       <c r="Q36" t="n">
         <v>4.75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>818.65</v>
+      </c>
+      <c r="C37" t="n">
+        <v>826.3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-9.59</v>
+      </c>
+      <c r="G37" t="n">
+        <v>236459</v>
+      </c>
+      <c r="H37" t="n">
+        <v>537495</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>27</v>
+      </c>
+      <c r="L37" t="n">
+        <v>947</v>
+      </c>
+      <c r="M37" t="n">
+        <v>908.11</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-32</v>
+      </c>
+      <c r="P37" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.78</v>
       </c>
     </row>
   </sheetData>
@@ -16524,7 +16948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18386,6 +18810,59 @@
       </c>
       <c r="Q36" t="n">
         <v>42.97</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>967.9</v>
+      </c>
+      <c r="C37" t="n">
+        <v>975.9</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="G37" t="n">
+        <v>992962</v>
+      </c>
+      <c r="H37" t="n">
+        <v>583491</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K37" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="L37" t="n">
+        <v>935.28</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1033.72</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-13.36</v>
+      </c>
+      <c r="P37" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>41.8</v>
       </c>
     </row>
   </sheetData>
@@ -18399,7 +18876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20261,6 +20738,59 @@
       </c>
       <c r="Q36" t="n">
         <v>45.13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>66.52</v>
+      </c>
+      <c r="C37" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="G37" t="n">
+        <v>14339495</v>
+      </c>
+      <c r="H37" t="n">
+        <v>14563305</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="M37" t="n">
+        <v>67.67</v>
+      </c>
+      <c r="N37" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="P37" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>50.57</v>
       </c>
     </row>
   </sheetData>
@@ -20274,7 +20804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22136,6 +22666,59 @@
       </c>
       <c r="Q36" t="n">
         <v>35.41</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="G37" t="n">
+        <v>337896</v>
+      </c>
+      <c r="H37" t="n">
+        <v>406094</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K37" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="N37" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-39.76</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>34.45</v>
       </c>
     </row>
   </sheetData>
@@ -22149,7 +22732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24011,6 +24594,59 @@
       </c>
       <c r="Q36" t="n">
         <v>79.79000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>977.2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>989.7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F37" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="G37" t="n">
+        <v>249885</v>
+      </c>
+      <c r="H37" t="n">
+        <v>233441</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>762.14</v>
+      </c>
+      <c r="M37" t="n">
+        <v>877.49</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="P37" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>77.52</v>
       </c>
     </row>
   </sheetData>
@@ -24024,7 +24660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24869,6 +25505,29 @@
         <v>-1.66</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>23477.8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>23431.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>455.45</v>
+      </c>
+      <c r="D3" t="n">
         <v>454.65</v>
       </c>
-      <c r="D3" t="n">
-        <v>456.5</v>
-      </c>
       <c r="E3" t="n">
-        <v>-0.41</v>
+        <v>0.18</v>
       </c>
       <c r="F3" t="n">
-        <v>-15.11</v>
+        <v>-16.32</v>
       </c>
       <c r="G3" t="n">
-        <v>3.05</v>
+        <v>0.32</v>
       </c>
       <c r="H3" t="n">
-        <v>856335</v>
+        <v>397741</v>
       </c>
       <c r="I3" t="n">
-        <v>426020</v>
+        <v>856388</v>
       </c>
       <c r="J3" t="n">
-        <v>0.64</v>
+        <v>0.31</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2</v>
+        <v>-0.42</v>
       </c>
       <c r="L3" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="M3" t="n">
-        <v>345.53</v>
+        <v>346.05</v>
       </c>
       <c r="N3" t="n">
-        <v>425.37</v>
+        <v>427.19</v>
       </c>
       <c r="O3" t="n">
         <v>544.3</v>
       </c>
       <c r="P3" t="n">
-        <v>-16.47</v>
+        <v>-16.32</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>88.98999999999999</v>
+        <v>89.31999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="D4" t="n">
         <v>46.08</v>
       </c>
-      <c r="D4" t="n">
-        <v>46.41</v>
-      </c>
       <c r="E4" t="n">
-        <v>-0.71</v>
+        <v>0.22</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.4</v>
+        <v>-2.35</v>
       </c>
       <c r="G4" t="n">
-        <v>0.68</v>
+        <v>1.14</v>
       </c>
       <c r="H4" t="n">
-        <v>5590539</v>
+        <v>5755589</v>
       </c>
       <c r="I4" t="n">
-        <v>8187411</v>
+        <v>5591541</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="K4" t="n">
-        <v>0.42</v>
+        <v>-3</v>
       </c>
       <c r="L4" t="n">
-        <v>50.3</v>
+        <v>51.1</v>
       </c>
       <c r="M4" t="n">
-        <v>41.73</v>
+        <v>41.76</v>
       </c>
       <c r="N4" t="n">
-        <v>45.9</v>
+        <v>45.91</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.04</v>
+        <v>-3.83</v>
       </c>
       <c r="Q4" t="n">
         <v>28.36</v>
       </c>
       <c r="R4" t="n">
-        <v>62.48</v>
+        <v>62.83</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>259.85</v>
+      </c>
+      <c r="D5" t="n">
         <v>259.3</v>
       </c>
-      <c r="D5" t="n">
-        <v>260.8</v>
-      </c>
       <c r="E5" t="n">
-        <v>-0.58</v>
+        <v>0.21</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.41</v>
+        <v>-1.61</v>
       </c>
       <c r="G5" t="n">
-        <v>-6.1</v>
+        <v>-6.7</v>
       </c>
       <c r="H5" t="n">
-        <v>17444123</v>
+        <v>11105461</v>
       </c>
       <c r="I5" t="n">
-        <v>10065188</v>
+        <v>17541602</v>
       </c>
       <c r="J5" t="n">
-        <v>1.29</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.14</v>
+        <v>-0.93</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>36.1</v>
       </c>
       <c r="M5" t="n">
-        <v>304.83</v>
+        <v>304.21</v>
       </c>
       <c r="N5" t="n">
-        <v>276.5</v>
+        <v>275.9</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-35.5</v>
+        <v>-35.36</v>
       </c>
       <c r="Q5" t="n">
         <v>255.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>815.35</v>
+      </c>
+      <c r="D6" t="n">
         <v>818.65</v>
       </c>
-      <c r="D6" t="n">
-        <v>826.3</v>
-      </c>
       <c r="E6" t="n">
-        <v>-0.93</v>
+        <v>-0.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.92</v>
+        <v>-2.74</v>
       </c>
       <c r="G6" t="n">
-        <v>-9.59</v>
+        <v>-10.77</v>
       </c>
       <c r="H6" t="n">
-        <v>236459</v>
+        <v>567640</v>
       </c>
       <c r="I6" t="n">
-        <v>537495</v>
+        <v>236487</v>
       </c>
       <c r="J6" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>26.3</v>
       </c>
       <c r="M6" t="n">
-        <v>947</v>
+        <v>946.9299999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>908.11</v>
+        <v>905.76</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-32</v>
+        <v>-32.28</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>3.78</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>65.54000000000001</v>
+      </c>
+      <c r="D7" t="n">
         <v>66.52</v>
       </c>
-      <c r="D7" t="n">
-        <v>64.12</v>
-      </c>
       <c r="E7" t="n">
-        <v>3.74</v>
+        <v>-1.47</v>
       </c>
       <c r="F7" t="n">
-        <v>4.53</v>
+        <v>4.05</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.16</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>14339495</v>
+        <v>9596321</v>
       </c>
       <c r="I7" t="n">
-        <v>14563305</v>
+        <v>14339627</v>
       </c>
       <c r="J7" t="n">
-        <v>0.95</v>
+        <v>0.64</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2</v>
+        <v>-1.67</v>
       </c>
       <c r="L7" t="n">
-        <v>47.1</v>
+        <v>44.2</v>
       </c>
       <c r="M7" t="n">
-        <v>59.59</v>
+        <v>59.65</v>
       </c>
       <c r="N7" t="n">
-        <v>67.67</v>
+        <v>67.75</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.210000000000001</v>
+        <v>-9.56</v>
       </c>
       <c r="Q7" t="n">
         <v>44.18</v>
       </c>
       <c r="R7" t="n">
-        <v>50.57</v>
+        <v>48.35</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>966.3</v>
+      </c>
+      <c r="D8" t="n">
         <v>977.2</v>
       </c>
-      <c r="D8" t="n">
-        <v>989.7</v>
-      </c>
       <c r="E8" t="n">
-        <v>-1.26</v>
+        <v>-1.12</v>
       </c>
       <c r="F8" t="n">
-        <v>1.11</v>
+        <v>0.42</v>
       </c>
       <c r="G8" t="n">
-        <v>12.95</v>
+        <v>11.28</v>
       </c>
       <c r="H8" t="n">
-        <v>249885</v>
+        <v>128405</v>
       </c>
       <c r="I8" t="n">
-        <v>233441</v>
+        <v>249886</v>
       </c>
       <c r="J8" t="n">
-        <v>0.55</v>
+        <v>0.29</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-1.58</v>
       </c>
       <c r="L8" t="n">
-        <v>62.5</v>
+        <v>59.4</v>
       </c>
       <c r="M8" t="n">
-        <v>762.14</v>
+        <v>763.11</v>
       </c>
       <c r="N8" t="n">
-        <v>877.49</v>
+        <v>879.5700000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1001.9</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.47</v>
+        <v>-3.55</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>77.52</v>
+        <v>75.54000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -913,37 +913,37 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="D10" t="n">
         <v>6.72</v>
       </c>
-      <c r="D10" t="n">
-        <v>6.71</v>
-      </c>
       <c r="E10" t="n">
-        <v>0.15</v>
+        <v>-3.12</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.61</v>
+        <v>-0.76</v>
       </c>
       <c r="G10" t="n">
-        <v>-19.04</v>
+        <v>-17.8</v>
       </c>
       <c r="H10" t="n">
+        <v>10517</v>
+      </c>
+      <c r="I10" t="n">
         <v>5700</v>
       </c>
-      <c r="I10" t="n">
-        <v>6879</v>
-      </c>
       <c r="J10" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="K10" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>39.4</v>
+        <v>36.1</v>
       </c>
       <c r="M10" t="n">
-        <v>8.67</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>7.06</v>
@@ -952,13 +952,13 @@
         <v>13.78</v>
       </c>
       <c r="P10" t="n">
-        <v>-51.23</v>
+        <v>-52.76</v>
       </c>
       <c r="Q10" t="n">
         <v>5.29</v>
       </c>
       <c r="R10" t="n">
-        <v>27.03</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="11">
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>974.2</v>
+      </c>
+      <c r="D11" t="n">
         <v>967.9</v>
       </c>
-      <c r="D11" t="n">
-        <v>975.9</v>
-      </c>
       <c r="E11" t="n">
-        <v>-0.82</v>
+        <v>0.65</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.98</v>
+        <v>-2.77</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.67</v>
+        <v>-5.95</v>
       </c>
       <c r="H11" t="n">
-        <v>992962</v>
+        <v>1527780</v>
       </c>
       <c r="I11" t="n">
-        <v>583491</v>
+        <v>992989</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="K11" t="n">
-        <v>0.21</v>
+        <v>0.85</v>
       </c>
       <c r="L11" t="n">
-        <v>36.7</v>
+        <v>39</v>
       </c>
       <c r="M11" t="n">
-        <v>935.28</v>
+        <v>935.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1033.72</v>
+        <v>1032.27</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-13.36</v>
+        <v>-12.8</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>41.8</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="D12" t="n">
         <v>24.82</v>
       </c>
-      <c r="D12" t="n">
-        <v>24.35</v>
-      </c>
       <c r="E12" t="n">
-        <v>1.93</v>
+        <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>2.27</v>
+        <v>3.45</v>
       </c>
       <c r="G12" t="n">
-        <v>12.87</v>
+        <v>12.43</v>
       </c>
       <c r="H12" t="n">
-        <v>18009206</v>
+        <v>19191666</v>
       </c>
       <c r="I12" t="n">
-        <v>15123230</v>
+        <v>18011981</v>
       </c>
       <c r="J12" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>-1.93</v>
       </c>
       <c r="L12" t="n">
-        <v>56.4</v>
+        <v>56.7</v>
       </c>
       <c r="M12" t="n">
-        <v>24.66</v>
+        <v>24.65</v>
       </c>
       <c r="N12" t="n">
-        <v>23.12</v>
+        <v>23.16</v>
       </c>
       <c r="O12" t="n">
         <v>32.31</v>
       </c>
       <c r="P12" t="n">
-        <v>-23.18</v>
+        <v>-23.03</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>15.5</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="13">
@@ -1093,52 +1093,52 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.62</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.66</v>
-      </c>
       <c r="E13" t="n">
-        <v>-0.71</v>
+        <v>-4.27</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.26</v>
+        <v>-9.27</v>
       </c>
       <c r="G13" t="n">
-        <v>4.27</v>
+        <v>1.13</v>
       </c>
       <c r="H13" t="n">
-        <v>337896</v>
+        <v>934016</v>
       </c>
       <c r="I13" t="n">
-        <v>406094</v>
+        <v>346180</v>
       </c>
       <c r="J13" t="n">
-        <v>0.27</v>
+        <v>0.75</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4</v>
+        <v>-1.59</v>
       </c>
       <c r="L13" t="n">
-        <v>46.5</v>
+        <v>40.9</v>
       </c>
       <c r="M13" t="n">
-        <v>5.86</v>
+        <v>5.85</v>
       </c>
       <c r="N13" t="n">
         <v>5.53</v>
       </c>
       <c r="O13" t="n">
-        <v>9.33</v>
+        <v>9.31</v>
       </c>
       <c r="P13" t="n">
-        <v>-39.76</v>
+        <v>-42.21</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>34.45</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>23398.1</v>
+      </c>
+      <c r="D17" t="n">
         <v>23477.8</v>
       </c>
-      <c r="D17" t="n">
-        <v>23431.5</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.2</v>
+        <v>-0.34</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.66</v>
+        <v>-2.09</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.92</v>
+        <v>-4.09</v>
       </c>
       <c r="H17" t="n">
-        <v>0.21</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>56606.55</v>
+      </c>
+      <c r="D18" t="n">
         <v>56471.95</v>
       </c>
-      <c r="D18" t="n">
-        <v>56295.55</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.58</v>
+        <v>-1.33</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.44</v>
+        <v>-1.78</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.16</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>104.78</v>
+        <v>104.96</v>
       </c>
       <c r="D19" t="n">
-        <v>101.21</v>
+        <v>107.63</v>
       </c>
       <c r="E19" t="n">
-        <v>3.53</v>
+        <v>-2.48</v>
       </c>
       <c r="F19" t="n">
-        <v>9.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>17.85</v>
+        <v>17.96</v>
       </c>
       <c r="H19" t="n">
-        <v>0.84</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4405</v>
+        <v>4426.3</v>
       </c>
       <c r="D20" t="n">
-        <v>4416</v>
+        <v>4364.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.25</v>
+        <v>1.42</v>
       </c>
       <c r="F20" t="n">
-        <v>0.89</v>
+        <v>-1.46</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52163.78</v>
+        <v>52521.97</v>
       </c>
       <c r="D21" t="n">
-        <v>52380.66</v>
+        <v>52064.1</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.41</v>
+        <v>0.88</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.69</v>
+        <v>-2.17</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.03</v>
+        <v>-2.32</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.73</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="D22" t="n">
         <v>11.8</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.92</v>
-      </c>
       <c r="E22" t="n">
-        <v>-1.01</v>
+        <v>4.07</v>
       </c>
       <c r="F22" t="n">
-        <v>4.06</v>
+        <v>14.98</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9399999999999999</v>
+        <v>7.53</v>
+      </c>
+      <c r="H22" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2244,6 +2247,29 @@
       </c>
       <c r="G37" t="n">
         <v>-0.16</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>56606.55</v>
+      </c>
+      <c r="C38" t="n">
+        <v>56471.95</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-2.51</v>
       </c>
     </row>
   </sheetData>
@@ -2257,7 +2283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3123,6 +3149,29 @@
       </c>
       <c r="G37" t="n">
         <v>0.84</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>104.96</v>
+      </c>
+      <c r="C38" t="n">
+        <v>107.63</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="E38" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="F38" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.01</v>
       </c>
     </row>
   </sheetData>
@@ -3136,7 +3185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4002,6 +4051,29 @@
       </c>
       <c r="G37" t="n">
         <v>1.04</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4426.3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4364.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.17</v>
       </c>
     </row>
   </sheetData>
@@ -4015,7 +4087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4843,6 +4915,29 @@
       </c>
       <c r="G36" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B37" t="n">
+        <v>52521.97</v>
+      </c>
+      <c r="C37" t="n">
+        <v>52064.1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>
@@ -4856,7 +4951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5632,6 +5727,29 @@
       </c>
       <c r="F37" t="n">
         <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="C38" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="E38" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="G38" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -5645,7 +5763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7507,6 +7625,59 @@
       </c>
       <c r="Q36" t="n">
         <v>27.03</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B37" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10517</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="M37" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="N37" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-52.76</v>
+      </c>
+      <c r="P37" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>23.06</v>
       </c>
     </row>
   </sheetData>
@@ -7520,7 +7691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9382,6 +9553,59 @@
       </c>
       <c r="Q36" t="n">
         <v>15.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B37" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="C37" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="F37" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="G37" t="n">
+        <v>19191666</v>
+      </c>
+      <c r="H37" t="n">
+        <v>18011981</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="K37" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="L37" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="M37" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="N37" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-23.03</v>
+      </c>
+      <c r="P37" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>15.73</v>
       </c>
     </row>
   </sheetData>
@@ -9395,7 +9619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11151,6 +11375,59 @@
       </c>
       <c r="Q34" t="n">
         <v>62.48</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B35" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="C35" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5755589</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5591541</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="M35" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="N35" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-3.83</v>
+      </c>
+      <c r="P35" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>62.83</v>
       </c>
     </row>
   </sheetData>
@@ -11164,7 +11441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13079,6 +13356,59 @@
       </c>
       <c r="Q37" t="n">
         <v>88.98999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>455.45</v>
+      </c>
+      <c r="C38" t="n">
+        <v>454.65</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-16.32</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G38" t="n">
+        <v>397741</v>
+      </c>
+      <c r="H38" t="n">
+        <v>856388</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="K38" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>346.05</v>
+      </c>
+      <c r="M38" t="n">
+        <v>427.19</v>
+      </c>
+      <c r="N38" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-16.32</v>
+      </c>
+      <c r="P38" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>89.31999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -13092,7 +13422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15007,6 +15337,59 @@
       </c>
       <c r="Q37" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>259.85</v>
+      </c>
+      <c r="C38" t="n">
+        <v>259.3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="G38" t="n">
+        <v>11105461</v>
+      </c>
+      <c r="H38" t="n">
+        <v>17541602</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="K38" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>304.21</v>
+      </c>
+      <c r="M38" t="n">
+        <v>275.9</v>
+      </c>
+      <c r="N38" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-35.36</v>
+      </c>
+      <c r="P38" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -15020,7 +15403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16935,6 +17318,59 @@
       </c>
       <c r="Q37" t="n">
         <v>3.78</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>815.35</v>
+      </c>
+      <c r="C38" t="n">
+        <v>818.65</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-10.77</v>
+      </c>
+      <c r="G38" t="n">
+        <v>567640</v>
+      </c>
+      <c r="H38" t="n">
+        <v>236487</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="K38" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>946.9299999999999</v>
+      </c>
+      <c r="M38" t="n">
+        <v>905.76</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-32.28</v>
+      </c>
+      <c r="P38" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.36</v>
       </c>
     </row>
   </sheetData>
@@ -16948,7 +17384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18863,6 +19299,59 @@
       </c>
       <c r="Q37" t="n">
         <v>41.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>974.2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>967.9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-5.95</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1527780</v>
+      </c>
+      <c r="H38" t="n">
+        <v>992989</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K38" t="n">
+        <v>39</v>
+      </c>
+      <c r="L38" t="n">
+        <v>935.25</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1032.27</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>42.72</v>
       </c>
     </row>
   </sheetData>
@@ -18876,7 +19365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20791,6 +21280,59 @@
       </c>
       <c r="Q37" t="n">
         <v>50.57</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>65.54000000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>66.52</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="G38" t="n">
+        <v>9596321</v>
+      </c>
+      <c r="H38" t="n">
+        <v>14339627</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="K38" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="M38" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="N38" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-9.56</v>
+      </c>
+      <c r="P38" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>48.35</v>
       </c>
     </row>
   </sheetData>
@@ -20804,7 +21346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22719,6 +23261,59 @@
       </c>
       <c r="Q37" t="n">
         <v>34.45</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="C38" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-9.27</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G38" t="n">
+        <v>934016</v>
+      </c>
+      <c r="H38" t="n">
+        <v>346180</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="K38" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="N38" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-42.21</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>28.71</v>
       </c>
     </row>
   </sheetData>
@@ -22732,7 +23327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24647,6 +25242,59 @@
       </c>
       <c r="Q37" t="n">
         <v>77.52</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>966.3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>977.2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F38" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="G38" t="n">
+        <v>128405</v>
+      </c>
+      <c r="H38" t="n">
+        <v>249886</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="K38" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>763.11</v>
+      </c>
+      <c r="M38" t="n">
+        <v>879.5700000000001</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="P38" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>75.54000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -24660,7 +25308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25528,6 +26176,29 @@
         <v>0.21</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>23398.1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>23477.8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-2.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
